--- a/data/movie.xlsx
+++ b/data/movie.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="664">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1536" uniqueCount="917">
   <si>
     <t>movieId</t>
   </si>
@@ -128,7 +128,7 @@
     <t>fhjp91776196</t>
   </si>
   <si>
-    <t>鋼之鍊金術師劇場版</t>
+    <t>鋼之鍊金術師：嘆息之丘的聖星</t>
   </si>
   <si>
     <t>https://www.atmovies.com.tw/photo101/fhjp91776196/pl_fhjp91776196.jpg</t>
@@ -137,6 +137,9 @@
     <t>2011-10-28 00:00:00</t>
   </si>
   <si>
+    <t>2026-10-19 11:26:54</t>
+  </si>
+  <si>
     <t>8</t>
   </si>
   <si>
@@ -458,12 +461,15 @@
     <t>fhth43380212</t>
   </si>
   <si>
-    <t>猛鬼大學4</t>
+    <t>猛鬼大學：4不瞑目</t>
   </si>
   <si>
     <t>https://www.atmovies.com.tw/photo101/fhth43380212/pl_fhth43380212.jpg</t>
   </si>
   <si>
+    <t>2026-10-19 11:27:59</t>
+  </si>
+  <si>
     <t>32</t>
   </si>
   <si>
@@ -746,12 +752,15 @@
     <t>frcn38633224</t>
   </si>
   <si>
-    <t>粽邪4</t>
+    <t>粽邪4：坤蒂拉娜</t>
   </si>
   <si>
     <t>https://www.atmovies.com.tw/photo101/frcn38633224/pl_frcn38633224.jpg</t>
   </si>
   <si>
+    <t>2026-10-19 11:27:55</t>
+  </si>
+  <si>
     <t>53</t>
   </si>
   <si>
@@ -1061,7 +1070,7 @@
     <t>ffjp90246378</t>
   </si>
   <si>
-    <t>鋼之鍊金術師</t>
+    <t>鋼之鍊金術師：香巴拉的征服者</t>
   </si>
   <si>
     <t>https://www.atmovies.com.tw/photo101/ffjp90246378/pl_ffjp90246378.jpg</t>
@@ -1070,6 +1079,9 @@
     <t>2005-12-23 00:00:00</t>
   </si>
   <si>
+    <t>2026-10-19 11:26:50</t>
+  </si>
+  <si>
     <t>74</t>
   </si>
   <si>
@@ -1955,7 +1967,10 @@
     <t>https://www.atmovies.com.tw/photo101/fhen38077943/pl_fhen38077943.jpg</t>
   </si>
   <si>
-    <t>2026-11-25 00:00:00</t>
+    <t>2026-11-26 00:00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 11:26:26</t>
   </si>
   <si>
     <t>138</t>
@@ -2004,6 +2019,750 @@
   </si>
   <si>
     <t>2026-12-04 00:00:00</t>
+  </si>
+  <si>
+    <t>141</t>
+  </si>
+  <si>
+    <t>fwen42582802</t>
+  </si>
+  <si>
+    <t>進擊的鼓手</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/fwen42582802/pl_fwen42582802.jpg</t>
+  </si>
+  <si>
+    <t>2015-01-30 00:00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 11:22:36</t>
+  </si>
+  <si>
+    <t>142</t>
+  </si>
+  <si>
+    <t>futh28766949</t>
+  </si>
+  <si>
+    <t>跳越時空的愛戀</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/futh28766949/pl_futh28766949.jpg</t>
+  </si>
+  <si>
+    <t>2024-08-28 00:00:00</t>
+  </si>
+  <si>
+    <t>143</t>
+  </si>
+  <si>
+    <t>fbjp39335288</t>
+  </si>
+  <si>
+    <t>劇場版</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/fbjp39335288/pl_fbjp39335288.jpg</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>144</t>
+  </si>
+  <si>
+    <t>fmone0412214</t>
+  </si>
+  <si>
+    <t>男歡女愛</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/fmone0412214/pl_fmone0412214.jpg</t>
+  </si>
+  <si>
+    <t>2025-01-17 00:00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 11:22:57</t>
+  </si>
+  <si>
+    <t>145</t>
+  </si>
+  <si>
+    <t>fszh45452981</t>
+  </si>
+  <si>
+    <t>國有器官</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/fszh45452981/pl_fszh45452981.jpg</t>
+  </si>
+  <si>
+    <t>2024-10-01 00:00:00</t>
+  </si>
+  <si>
+    <t>146</t>
+  </si>
+  <si>
+    <t>ficn82691592</t>
+  </si>
+  <si>
+    <t>我未許願先吹蠟燭</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/ficn82691592/pl_ficn82691592.jpg</t>
+  </si>
+  <si>
+    <t>2026-10-19 11:22:59</t>
+  </si>
+  <si>
+    <t>147</t>
+  </si>
+  <si>
+    <t>feen31170389</t>
+  </si>
+  <si>
+    <t>屍變焚場</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/feen31170389/pl_feen31170389.jpg</t>
+  </si>
+  <si>
+    <t>2026-10-19 11:23:01</t>
+  </si>
+  <si>
+    <t>148</t>
+  </si>
+  <si>
+    <t>fmen34542628</t>
+  </si>
+  <si>
+    <t>蒙克聲音拼貼</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/fmen34542628/pl_fmen34542628.jpg</t>
+  </si>
+  <si>
+    <t>2026-10-19 11:23:03</t>
+  </si>
+  <si>
+    <t>149</t>
+  </si>
+  <si>
+    <t>fako33364791</t>
+  </si>
+  <si>
+    <t>活命水特弓隊</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/fako33364791/pl_fako33364791.jpg</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>fajp75923132</t>
+  </si>
+  <si>
+    <t>加速世界 劇場版</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/fajp75923132/pl_fajp75923132.jpg</t>
+  </si>
+  <si>
+    <t>151</t>
+  </si>
+  <si>
+    <t>fcpl33305572</t>
+  </si>
+  <si>
+    <t>蕭邦！蕭邦！</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/fcpl33305572/pl_fcpl33305572.jpg</t>
+  </si>
+  <si>
+    <t>2026-10-19 11:38:38</t>
+  </si>
+  <si>
+    <t>152</t>
+  </si>
+  <si>
+    <t>ftjp95459925</t>
+  </si>
+  <si>
+    <t>2026秋山眞緒 Final 現場直播</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/ftjp95459925/pl_ftjp95459925.jpg</t>
+  </si>
+  <si>
+    <t>2026-10-26 00:00:00</t>
+  </si>
+  <si>
+    <t>153</t>
+  </si>
+  <si>
+    <t>fcth44632295</t>
+  </si>
+  <si>
+    <t>薩滿的最後告解</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/fcth44632295/pl_fcth44632295.jpg</t>
+  </si>
+  <si>
+    <t>154</t>
+  </si>
+  <si>
+    <t>ften35298123</t>
+  </si>
+  <si>
+    <t>屍控片場性愛死</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/ften35298123/pl_ften35298123.jpg</t>
+  </si>
+  <si>
+    <t>155</t>
+  </si>
+  <si>
+    <t>fajp39382917</t>
+  </si>
+  <si>
+    <t>全家就弒你家</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/fajp39382917/pl_fajp39382917.jpg</t>
+  </si>
+  <si>
+    <t>156</t>
+  </si>
+  <si>
+    <t>fmtw53870342</t>
+  </si>
+  <si>
+    <t>我要當總統</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/fmtw53870342/pl_fmtw53870342.jpg</t>
+  </si>
+  <si>
+    <t>157</t>
+  </si>
+  <si>
+    <t>fdcn25375197</t>
+  </si>
+  <si>
+    <t>黑潮</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/fdcn25375197/pl_fdcn25375197.jpg</t>
+  </si>
+  <si>
+    <t>158</t>
+  </si>
+  <si>
+    <t>fsjp43722621</t>
+  </si>
+  <si>
+    <t>跟我一起玩吧？</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/fsjp43722621/pl_fsjp43722621.jpg</t>
+  </si>
+  <si>
+    <t>2026-10-19 11:38:36</t>
+  </si>
+  <si>
+    <t>159</t>
+  </si>
+  <si>
+    <t>fwcn39673991</t>
+  </si>
+  <si>
+    <t>日光</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/fwcn39673991/pl_fwcn39673991.jpg</t>
+  </si>
+  <si>
+    <t>160</t>
+  </si>
+  <si>
+    <t>fben29355194</t>
+  </si>
+  <si>
+    <t>紐約古書店尋寶記</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/fben29355194/pl_fben29355194.jpg</t>
+  </si>
+  <si>
+    <t>2026-12-11 00:00:00</t>
+  </si>
+  <si>
+    <t>161</t>
+  </si>
+  <si>
+    <t>faen21357150</t>
+  </si>
+  <si>
+    <t>復仇者聯盟：末日崛起</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/faen21357150/pl_faen21357150.jpg</t>
+  </si>
+  <si>
+    <t>2026-12-16 00:00:00</t>
+  </si>
+  <si>
+    <t>162</t>
+  </si>
+  <si>
+    <t>fden31378509</t>
+  </si>
+  <si>
+    <t>沙丘：第三部</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/fden31378509/pl_fden31378509.jpg</t>
+  </si>
+  <si>
+    <t>163</t>
+  </si>
+  <si>
+    <t>facn35683770</t>
+  </si>
+  <si>
+    <t>泡泡糖女孩</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/facn35683770/pl_facn35683770.jpg</t>
+  </si>
+  <si>
+    <t>2026-12-18 00:00:00</t>
+  </si>
+  <si>
+    <t>164</t>
+  </si>
+  <si>
+    <t>fwen29611136</t>
+  </si>
+  <si>
+    <t>就是柳柳的他</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/fwen29611136/pl_fwen29611136.jpg</t>
+  </si>
+  <si>
+    <t>165</t>
+  </si>
+  <si>
+    <t>fien34512981</t>
+  </si>
+  <si>
+    <t>冰原歷險記6：沸常危機</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/fien34512981/pl_fien34512981.jpg</t>
+  </si>
+  <si>
+    <t>2027-02-05 00:00:00</t>
+  </si>
+  <si>
+    <t>166</t>
+  </si>
+  <si>
+    <t>fcen36593129</t>
+  </si>
+  <si>
+    <t>復出之王</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/fcen36593129/pl_fcen36593129.jpg</t>
+  </si>
+  <si>
+    <t>167</t>
+  </si>
+  <si>
+    <t>fnen99077514</t>
+  </si>
+  <si>
+    <t>納尼亞：魔法師的外甥</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/fnen99077514/pl_fnen99077514.jpg</t>
+  </si>
+  <si>
+    <t>2027-02-10 00:00:00</t>
+  </si>
+  <si>
+    <t>168</t>
+  </si>
+  <si>
+    <t>fgen26443610</t>
+  </si>
+  <si>
+    <t>貓的急轉彎</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/fgen26443610/pl_fgen26443610.jpg</t>
+  </si>
+  <si>
+    <t>2027-03-05 00:00:00</t>
+  </si>
+  <si>
+    <t>169</t>
+  </si>
+  <si>
+    <t>fnen43609247</t>
+  </si>
+  <si>
+    <t>外星三寶團</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/fnen43609247/pl_fnen43609247.jpg</t>
+  </si>
+  <si>
+    <t>2027-04-04 00:00:00</t>
+  </si>
+  <si>
+    <t>170</t>
+  </si>
+  <si>
+    <t>fsen46113186</t>
+  </si>
+  <si>
+    <t>史瑞克5</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/fsen46113186/pl_fsen46113186.jpg</t>
+  </si>
+  <si>
+    <t>2027-06-30 00:00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 11:38:34</t>
+  </si>
+  <si>
+    <t>171</t>
+  </si>
+  <si>
+    <t>fben35050152</t>
+  </si>
+  <si>
+    <t>妙妙犬布麗電影</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/fben35050152/pl_fben35050152.jpg</t>
+  </si>
+  <si>
+    <t>2027-08-06 00:00:00</t>
+  </si>
+  <si>
+    <t>172</t>
+  </si>
+  <si>
+    <t>fben19850008</t>
+  </si>
+  <si>
+    <t>蝙蝠俠2</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/fben19850008/pl_fben19850008.jpg</t>
+  </si>
+  <si>
+    <t>2028-02-18 00:00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 11:38:32</t>
+  </si>
+  <si>
+    <t>173</t>
+  </si>
+  <si>
+    <t>fhcn43696728</t>
+  </si>
+  <si>
+    <t>幸福快樂的日子</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/fhcn43696728/pl_fhcn43696728.jpg</t>
+  </si>
+  <si>
+    <t>174</t>
+  </si>
+  <si>
+    <t>fscn44979318</t>
+  </si>
+  <si>
+    <t>蕩蕩蕩寇誌</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/fscn44979318/pl_fscn44979318.jpg</t>
+  </si>
+  <si>
+    <t>175</t>
+  </si>
+  <si>
+    <t>faen38686316</t>
+  </si>
+  <si>
+    <t>大天使</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/faen38686316/pl_faen38686316.jpg</t>
+  </si>
+  <si>
+    <t>2026-12-24 00:00:00</t>
+  </si>
+  <si>
+    <t>176</t>
+  </si>
+  <si>
+    <t>faen32557122</t>
+  </si>
+  <si>
+    <t>憤怒鳥玩電影3：全家總動員</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/faen32557122/pl_faen32557122.jpg</t>
+  </si>
+  <si>
+    <t>2027-01-01 00:00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 11:23:04</t>
+  </si>
+  <si>
+    <t>177</t>
+  </si>
+  <si>
+    <t>fren35606013</t>
+  </si>
+  <si>
+    <t>全力救援</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/fren35606013/pl_fren35606013.jpg</t>
+  </si>
+  <si>
+    <t>2027-01-29 00:00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 11:23:05</t>
+  </si>
+  <si>
+    <t>178</t>
+  </si>
+  <si>
+    <t>fren35621542</t>
+  </si>
+  <si>
+    <t>滯留</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/fren35621542/pl_fren35621542.jpg</t>
+  </si>
+  <si>
+    <t>2027-02-12 00:00:00</t>
+  </si>
+  <si>
+    <t>179</t>
+  </si>
+  <si>
+    <t>fwen35514120</t>
+  </si>
+  <si>
+    <t>人狼沃武夫</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/fwen35514120/pl_fwen35514120.jpg</t>
+  </si>
+  <si>
+    <t>2027-02-19 00:00:00</t>
+  </si>
+  <si>
+    <t>180</t>
+  </si>
+  <si>
+    <t>fcen31339071</t>
+  </si>
+  <si>
+    <t>可可瓜瓜大電影</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/fcen31339071/pl_fcen31339071.jpg</t>
+  </si>
+  <si>
+    <t>2027-02-26 00:00:00</t>
+  </si>
+  <si>
+    <t>181</t>
+  </si>
+  <si>
+    <t>fken98992304</t>
+  </si>
+  <si>
+    <t>K-POP:星夢 初登場</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/fken98992304/pl_fken98992304.jpg</t>
+  </si>
+  <si>
+    <t>182</t>
+  </si>
+  <si>
+    <t>feen32492552</t>
+  </si>
+  <si>
+    <t>大法師:殉道</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/feen32492552/pl_feen32492552.jpg</t>
+  </si>
+  <si>
+    <t>2027-03-12 00:00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 11:23:06</t>
+  </si>
+  <si>
+    <t>183</t>
+  </si>
+  <si>
+    <t>fsen56744566</t>
+  </si>
+  <si>
+    <t>音速小子4</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/fsen56744566/pl_fsen56744566.jpg</t>
+  </si>
+  <si>
+    <t>2027-03-19 00:00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 11:23:07</t>
+  </si>
+  <si>
+    <t>2026-10-19 11:38:30</t>
+  </si>
+  <si>
+    <t>184</t>
+  </si>
+  <si>
+    <t>facn38893248</t>
+  </si>
+  <si>
+    <t>狂忘警探</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/facn38893248/pl_facn38893248.jpg</t>
+  </si>
+  <si>
+    <t>2027-03-26 00:00:00</t>
+  </si>
+  <si>
+    <t>185</t>
+  </si>
+  <si>
+    <t>fwma47658526</t>
+  </si>
+  <si>
+    <t>我妳她</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/fwma47658526/pl_fwma47658526.jpg</t>
+  </si>
+  <si>
+    <t>186</t>
+  </si>
+  <si>
+    <t>fyen32104007</t>
+  </si>
+  <si>
+    <t>華盛頓崛起</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/fyen32104007/pl_fyen32104007.jpg</t>
+  </si>
+  <si>
+    <t>187</t>
+  </si>
+  <si>
+    <t>ftcn44934439</t>
+  </si>
+  <si>
+    <t>有用的人</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/ftcn44934439/pl_ftcn44934439.jpg</t>
+  </si>
+  <si>
+    <t>188</t>
+  </si>
+  <si>
+    <t>ftjp15437998</t>
+  </si>
+  <si>
+    <t>人魚戀習曲</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/ftjp15437998/pl_ftjp15437998.jpg</t>
+  </si>
+  <si>
+    <t>2026-10-19 11:23:08</t>
+  </si>
+  <si>
+    <t>189</t>
+  </si>
+  <si>
+    <t>fjen26735127</t>
+  </si>
+  <si>
+    <t>野蠻遊戲：虛實世界</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/fjen26735127/pl_fjen26735127.jpg</t>
+  </si>
+  <si>
+    <t>2026-12-23 00:00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 11:23:09</t>
+  </si>
+  <si>
+    <t>190</t>
+  </si>
+  <si>
+    <t>fcen96779038</t>
+  </si>
+  <si>
+    <t>歐瑞莎傳奇血與骨的孩子</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/fcen96779038/pl_fcen96779038.jpg</t>
+  </si>
+  <si>
+    <t>2027-01-22 00:00:00</t>
+  </si>
+  <si>
+    <t>191</t>
+  </si>
+  <si>
+    <t>ften45500064</t>
+  </si>
+  <si>
+    <t>天羅地網</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/ften45500064/pl_ften45500064.jpg</t>
+  </si>
+  <si>
+    <t>2026-10-19 11:23:10</t>
   </si>
 </sst>
 </file>
@@ -2048,7 +2807,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H141"/>
+  <dimension ref="A1:H192"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -2256,21 +3015,21 @@
         <v>31</v>
       </c>
       <c r="H8" t="s" s="0">
-        <v>31</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E9" t="s" s="0">
         <v>12</v>
@@ -2287,42 +3046,42 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E10" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F10" t="s" s="0">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G10" t="s" s="0">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H10" t="s" s="0">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E11" t="s" s="0">
         <v>12</v>
@@ -2331,24 +3090,24 @@
         <v>13</v>
       </c>
       <c r="G11" t="s" s="0">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H11" t="s" s="0">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E12" t="s" s="0">
         <v>12</v>
@@ -2357,24 +3116,24 @@
         <v>13</v>
       </c>
       <c r="G12" t="s" s="0">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H12" t="s" s="0">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E13" t="s" s="0">
         <v>12</v>
@@ -2383,50 +3142,50 @@
         <v>13</v>
       </c>
       <c r="G13" t="s" s="0">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H13" t="s" s="0">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E14" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F14" t="s" s="0">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G14" t="s" s="0">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H14" t="s" s="0">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E15" t="s" s="0">
         <v>12</v>
@@ -2435,3286 +3194,4612 @@
         <v>13</v>
       </c>
       <c r="G15" t="s" s="0">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H15" t="s" s="0">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E16" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F16" t="s" s="0">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G16" t="s" s="0">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H16" t="s" s="0">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E17" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F17" t="s" s="0">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G17" t="s" s="0">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H17" t="s" s="0">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="D18" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="E18" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F18" t="s" s="0">
         <v>83</v>
       </c>
-      <c r="B18" t="s" s="0">
-        <v>84</v>
-      </c>
-      <c r="C18" t="s" s="0">
-        <v>85</v>
-      </c>
-      <c r="D18" t="s" s="0">
-        <v>86</v>
-      </c>
-      <c r="E18" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F18" t="s" s="0">
-        <v>82</v>
-      </c>
       <c r="G18" t="s" s="0">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H18" t="s" s="0">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="D19" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="E19" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F19" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="G19" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="B19" t="s" s="0">
-        <v>89</v>
-      </c>
-      <c r="C19" t="s" s="0">
-        <v>90</v>
-      </c>
-      <c r="D19" t="s" s="0">
-        <v>91</v>
-      </c>
-      <c r="E19" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F19" t="s" s="0">
-        <v>92</v>
-      </c>
-      <c r="G19" t="s" s="0">
-        <v>87</v>
-      </c>
       <c r="H19" t="s" s="0">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D20" t="s" s="0">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E20" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F20" t="s" s="0">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G20" t="s" s="0">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H20" t="s" s="0">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D21" t="s" s="0">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E21" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F21" t="s" s="0">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G21" t="s" s="0">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H21" t="s" s="0">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D22" t="s" s="0">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E22" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F22" t="s" s="0">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G22" t="s" s="0">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H22" t="s" s="0">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="C23" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="D23" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="E23" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F23" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="G23" t="s" s="0">
         <v>106</v>
       </c>
-      <c r="B23" t="s" s="0">
-        <v>107</v>
-      </c>
-      <c r="C23" t="s" s="0">
-        <v>108</v>
-      </c>
-      <c r="D23" t="s" s="0">
-        <v>109</v>
-      </c>
-      <c r="E23" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F23" t="s" s="0">
-        <v>82</v>
-      </c>
-      <c r="G23" t="s" s="0">
-        <v>105</v>
-      </c>
       <c r="H23" t="s" s="0">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D24" t="s" s="0">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E24" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F24" t="s" s="0">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G24" t="s" s="0">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H24" t="s" s="0">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D25" t="s" s="0">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E25" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F25" t="s" s="0">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G25" t="s" s="0">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H25" t="s" s="0">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D26" t="s" s="0">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E26" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F26" t="s" s="0">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G26" t="s" s="0">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H26" t="s" s="0">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
+        <v>125</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>126</v>
+      </c>
+      <c r="C27" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="D27" t="s" s="0">
+        <v>128</v>
+      </c>
+      <c r="E27" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F27" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="G27" t="s" s="0">
         <v>124</v>
       </c>
-      <c r="B27" t="s" s="0">
-        <v>125</v>
-      </c>
-      <c r="C27" t="s" s="0">
-        <v>126</v>
-      </c>
-      <c r="D27" t="s" s="0">
-        <v>127</v>
-      </c>
-      <c r="E27" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F27" t="s" s="0">
-        <v>128</v>
-      </c>
-      <c r="G27" t="s" s="0">
-        <v>123</v>
-      </c>
       <c r="H27" t="s" s="0">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D28" t="s" s="0">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E28" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F28" t="s" s="0">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G28" t="s" s="0">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H28" t="s" s="0">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C29" t="s" s="0">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D29" t="s" s="0">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E29" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F29" t="s" s="0">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G29" t="s" s="0">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H29" t="s" s="0">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C30" t="s" s="0">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D30" t="s" s="0">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E30" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F30" t="s" s="0">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G30" t="s" s="0">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H30" t="s" s="0">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>144</v>
+      </c>
+      <c r="C31" t="s" s="0">
+        <v>145</v>
+      </c>
+      <c r="D31" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="E31" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F31" t="s" s="0">
+        <v>123</v>
+      </c>
+      <c r="G31" t="s" s="0">
         <v>142</v>
       </c>
-      <c r="B31" t="s" s="0">
-        <v>143</v>
-      </c>
-      <c r="C31" t="s" s="0">
-        <v>144</v>
-      </c>
-      <c r="D31" t="s" s="0">
-        <v>145</v>
-      </c>
-      <c r="E31" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F31" t="s" s="0">
-        <v>122</v>
-      </c>
-      <c r="G31" t="s" s="0">
-        <v>141</v>
-      </c>
       <c r="H31" t="s" s="0">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C32" t="s" s="0">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D32" t="s" s="0">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E32" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F32" t="s" s="0">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G32" t="s" s="0">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H32" t="s" s="0">
-        <v>141</v>
+        <v>151</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C33" t="s" s="0">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D33" t="s" s="0">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E33" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F33" t="s" s="0">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G33" t="s" s="0">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H33" t="s" s="0">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C34" t="s" s="0">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D34" t="s" s="0">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E34" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F34" t="s" s="0">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G34" t="s" s="0">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H34" t="s" s="0">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B35" t="s" s="0">
+        <v>162</v>
+      </c>
+      <c r="C35" t="s" s="0">
+        <v>163</v>
+      </c>
+      <c r="D35" t="s" s="0">
+        <v>164</v>
+      </c>
+      <c r="E35" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F35" t="s" s="0">
+        <v>123</v>
+      </c>
+      <c r="G35" t="s" s="0">
         <v>160</v>
       </c>
-      <c r="C35" t="s" s="0">
-        <v>161</v>
-      </c>
-      <c r="D35" t="s" s="0">
-        <v>162</v>
-      </c>
-      <c r="E35" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F35" t="s" s="0">
-        <v>122</v>
-      </c>
-      <c r="G35" t="s" s="0">
-        <v>158</v>
-      </c>
       <c r="H35" t="s" s="0">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C36" t="s" s="0">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D36" t="s" s="0">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E36" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F36" t="s" s="0">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G36" t="s" s="0">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H36" t="s" s="0">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C37" t="s" s="0">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D37" t="s" s="0">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E37" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F37" t="s" s="0">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G37" t="s" s="0">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H37" t="s" s="0">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B38" t="s" s="0">
+        <v>176</v>
+      </c>
+      <c r="C38" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="D38" t="s" s="0">
+        <v>178</v>
+      </c>
+      <c r="E38" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F38" t="s" s="0">
         <v>174</v>
       </c>
-      <c r="C38" t="s" s="0">
-        <v>175</v>
-      </c>
-      <c r="D38" t="s" s="0">
-        <v>176</v>
-      </c>
-      <c r="E38" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F38" t="s" s="0">
-        <v>172</v>
-      </c>
       <c r="G38" t="s" s="0">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="H38" t="s" s="0">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B39" t="s" s="0">
+        <v>181</v>
+      </c>
+      <c r="C39" t="s" s="0">
+        <v>182</v>
+      </c>
+      <c r="D39" t="s" s="0">
+        <v>183</v>
+      </c>
+      <c r="E39" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F39" t="s" s="0">
+        <v>174</v>
+      </c>
+      <c r="G39" t="s" s="0">
         <v>179</v>
       </c>
-      <c r="C39" t="s" s="0">
-        <v>180</v>
-      </c>
-      <c r="D39" t="s" s="0">
-        <v>181</v>
-      </c>
-      <c r="E39" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F39" t="s" s="0">
-        <v>172</v>
-      </c>
-      <c r="G39" t="s" s="0">
-        <v>177</v>
-      </c>
       <c r="H39" t="s" s="0">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B40" t="s" s="0">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C40" t="s" s="0">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D40" t="s" s="0">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E40" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F40" t="s" s="0">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G40" t="s" s="0">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="H40" t="s" s="0">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B41" t="s" s="0">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C41" t="s" s="0">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D41" t="s" s="0">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E41" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F41" t="s" s="0">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G41" t="s" s="0">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="H41" t="s" s="0">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B42" t="s" s="0">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C42" t="s" s="0">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D42" t="s" s="0">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E42" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F42" t="s" s="0">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G42" t="s" s="0">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H42" t="s" s="0">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B43" t="s" s="0">
+        <v>198</v>
+      </c>
+      <c r="C43" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="D43" t="s" s="0">
+        <v>200</v>
+      </c>
+      <c r="E43" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F43" t="s" s="0">
+        <v>174</v>
+      </c>
+      <c r="G43" t="s" s="0">
         <v>196</v>
       </c>
-      <c r="C43" t="s" s="0">
-        <v>197</v>
-      </c>
-      <c r="D43" t="s" s="0">
-        <v>198</v>
-      </c>
-      <c r="E43" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F43" t="s" s="0">
-        <v>172</v>
-      </c>
-      <c r="G43" t="s" s="0">
-        <v>194</v>
-      </c>
       <c r="H43" t="s" s="0">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B44" t="s" s="0">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C44" t="s" s="0">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D44" t="s" s="0">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E44" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F44" t="s" s="0">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G44" t="s" s="0">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H44" t="s" s="0">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B45" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C45" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="D45" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="E45" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F45" t="s" s="0">
         <v>205</v>
       </c>
-      <c r="C45" t="s" s="0">
-        <v>206</v>
-      </c>
-      <c r="D45" t="s" s="0">
-        <v>207</v>
-      </c>
-      <c r="E45" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F45" t="s" s="0">
-        <v>203</v>
-      </c>
       <c r="G45" t="s" s="0">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H45" t="s" s="0">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B46" t="s" s="0">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C46" t="s" s="0">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D46" t="s" s="0">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E46" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F46" t="s" s="0">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G46" t="s" s="0">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H46" t="s" s="0">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B47" t="s" s="0">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C47" t="s" s="0">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D47" t="s" s="0">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E47" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F47" t="s" s="0">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G47" t="s" s="0">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="H47" t="s" s="0">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B48" t="s" s="0">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C48" t="s" s="0">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D48" t="s" s="0">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E48" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F48" t="s" s="0">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="G48" t="s" s="0">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="H48" t="s" s="0">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B49" t="s" s="0">
+        <v>226</v>
+      </c>
+      <c r="C49" t="s" s="0">
+        <v>227</v>
+      </c>
+      <c r="D49" t="s" s="0">
+        <v>228</v>
+      </c>
+      <c r="E49" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F49" t="s" s="0">
+        <v>229</v>
+      </c>
+      <c r="G49" t="s" s="0">
         <v>224</v>
       </c>
-      <c r="C49" t="s" s="0">
-        <v>225</v>
-      </c>
-      <c r="D49" t="s" s="0">
-        <v>226</v>
-      </c>
-      <c r="E49" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F49" t="s" s="0">
-        <v>227</v>
-      </c>
-      <c r="G49" t="s" s="0">
-        <v>222</v>
-      </c>
       <c r="H49" t="s" s="0">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B50" t="s" s="0">
+        <v>231</v>
+      </c>
+      <c r="C50" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="D50" t="s" s="0">
+        <v>233</v>
+      </c>
+      <c r="E50" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F50" t="s" s="0">
         <v>229</v>
       </c>
-      <c r="C50" t="s" s="0">
-        <v>230</v>
-      </c>
-      <c r="D50" t="s" s="0">
-        <v>231</v>
-      </c>
-      <c r="E50" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F50" t="s" s="0">
-        <v>227</v>
-      </c>
       <c r="G50" t="s" s="0">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="H50" t="s" s="0">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B51" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C51" t="s" s="0">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D51" t="s" s="0">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E51" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F51" t="s" s="0">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G51" t="s" s="0">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H51" t="s" s="0">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B52" t="s" s="0">
+        <v>240</v>
+      </c>
+      <c r="C52" t="s" s="0">
+        <v>241</v>
+      </c>
+      <c r="D52" t="s" s="0">
+        <v>242</v>
+      </c>
+      <c r="E52" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F52" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="G52" t="s" s="0">
         <v>238</v>
       </c>
-      <c r="C52" t="s" s="0">
-        <v>239</v>
-      </c>
-      <c r="D52" t="s" s="0">
-        <v>240</v>
-      </c>
-      <c r="E52" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F52" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="G52" t="s" s="0">
-        <v>236</v>
-      </c>
       <c r="H52" t="s" s="0">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B53" t="s" s="0">
+        <v>245</v>
+      </c>
+      <c r="C53" t="s" s="0">
+        <v>246</v>
+      </c>
+      <c r="D53" t="s" s="0">
+        <v>247</v>
+      </c>
+      <c r="E53" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F53" t="s" s="0">
         <v>243</v>
       </c>
-      <c r="C53" t="s" s="0">
-        <v>244</v>
-      </c>
-      <c r="D53" t="s" s="0">
-        <v>245</v>
-      </c>
-      <c r="E53" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F53" t="s" s="0">
-        <v>241</v>
-      </c>
       <c r="G53" t="s" s="0">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H53" t="s" s="0">
-        <v>236</v>
+        <v>248</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B54" t="s" s="0">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C54" t="s" s="0">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D54" t="s" s="0">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E54" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F54" t="s" s="0">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="G54" t="s" s="0">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H54" t="s" s="0">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B55" t="s" s="0">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C55" t="s" s="0">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D55" t="s" s="0">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="E55" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F55" t="s" s="0">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="G55" t="s" s="0">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="H55" t="s" s="0">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B56" t="s" s="0">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C56" t="s" s="0">
+        <v>262</v>
+      </c>
+      <c r="D56" t="s" s="0">
+        <v>263</v>
+      </c>
+      <c r="E56" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F56" t="s" s="0">
+        <v>264</v>
+      </c>
+      <c r="G56" t="s" s="0">
         <v>259</v>
       </c>
-      <c r="D56" t="s" s="0">
-        <v>260</v>
-      </c>
-      <c r="E56" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F56" t="s" s="0">
-        <v>261</v>
-      </c>
-      <c r="G56" t="s" s="0">
-        <v>256</v>
-      </c>
       <c r="H56" t="s" s="0">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B57" t="s" s="0">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C57" t="s" s="0">
+        <v>267</v>
+      </c>
+      <c r="D57" t="s" s="0">
+        <v>268</v>
+      </c>
+      <c r="E57" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F57" t="s" s="0">
         <v>264</v>
       </c>
-      <c r="D57" t="s" s="0">
-        <v>265</v>
-      </c>
-      <c r="E57" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F57" t="s" s="0">
-        <v>261</v>
-      </c>
       <c r="G57" t="s" s="0">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="H57" t="s" s="0">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B58" t="s" s="0">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C58" t="s" s="0">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="D58" t="s" s="0">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="E58" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F58" t="s" s="0">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="G58" t="s" s="0">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="H58" t="s" s="0">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B59" t="s" s="0">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C59" t="s" s="0">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="D59" t="s" s="0">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="E59" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F59" t="s" s="0">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="G59" t="s" s="0">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="H59" t="s" s="0">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B60" t="s" s="0">
+        <v>280</v>
+      </c>
+      <c r="C60" t="s" s="0">
+        <v>281</v>
+      </c>
+      <c r="D60" t="s" s="0">
+        <v>282</v>
+      </c>
+      <c r="E60" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F60" t="s" s="0">
         <v>277</v>
       </c>
-      <c r="C60" t="s" s="0">
+      <c r="G60" t="s" s="0">
         <v>278</v>
       </c>
-      <c r="D60" t="s" s="0">
-        <v>279</v>
-      </c>
-      <c r="E60" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F60" t="s" s="0">
-        <v>274</v>
-      </c>
-      <c r="G60" t="s" s="0">
-        <v>275</v>
-      </c>
       <c r="H60" t="s" s="0">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B61" t="s" s="0">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C61" t="s" s="0">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D61" t="s" s="0">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="E61" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F61" t="s" s="0">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="G61" t="s" s="0">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="H61" t="s" s="0">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B62" t="s" s="0">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C62" t="s" s="0">
+        <v>290</v>
+      </c>
+      <c r="D62" t="s" s="0">
+        <v>291</v>
+      </c>
+      <c r="E62" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F62" t="s" s="0">
         <v>287</v>
       </c>
-      <c r="D62" t="s" s="0">
-        <v>288</v>
-      </c>
-      <c r="E62" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F62" t="s" s="0">
-        <v>284</v>
-      </c>
       <c r="G62" t="s" s="0">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="H62" t="s" s="0">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B63" t="s" s="0">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C63" t="s" s="0">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="D63" t="s" s="0">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="E63" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F63" t="s" s="0">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="G63" t="s" s="0">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="H63" t="s" s="0">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B64" t="s" s="0">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C64" t="s" s="0">
+        <v>300</v>
+      </c>
+      <c r="D64" t="s" s="0">
+        <v>301</v>
+      </c>
+      <c r="E64" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F64" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="G64" t="s" s="0">
         <v>297</v>
       </c>
-      <c r="D64" t="s" s="0">
-        <v>298</v>
-      </c>
-      <c r="E64" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F64" t="s" s="0">
-        <v>299</v>
-      </c>
-      <c r="G64" t="s" s="0">
-        <v>294</v>
-      </c>
       <c r="H64" t="s" s="0">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B65" t="s" s="0">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C65" t="s" s="0">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="D65" t="s" s="0">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="E65" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F65" t="s" s="0">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="G65" t="s" s="0">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="H65" t="s" s="0">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B66" t="s" s="0">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C66" t="s" s="0">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D66" t="s" s="0">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="E66" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F66" t="s" s="0">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="G66" t="s" s="0">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="H66" t="s" s="0">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B67" t="s" s="0">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="C67" t="s" s="0">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="D67" t="s" s="0">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E67" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F67" t="s" s="0">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="G67" t="s" s="0">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="H67" t="s" s="0">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B68" t="s" s="0">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C68" t="s" s="0">
+        <v>321</v>
+      </c>
+      <c r="D68" t="s" s="0">
+        <v>322</v>
+      </c>
+      <c r="E68" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F68" t="s" s="0">
+        <v>323</v>
+      </c>
+      <c r="G68" t="s" s="0">
         <v>318</v>
       </c>
-      <c r="D68" t="s" s="0">
-        <v>319</v>
-      </c>
-      <c r="E68" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F68" t="s" s="0">
-        <v>320</v>
-      </c>
-      <c r="G68" t="s" s="0">
-        <v>315</v>
-      </c>
       <c r="H68" t="s" s="0">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B69" t="s" s="0">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C69" t="s" s="0">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="D69" t="s" s="0">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="E69" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F69" t="s" s="0">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="G69" t="s" s="0">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="H69" t="s" s="0">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B70" t="s" s="0">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C70" t="s" s="0">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D70" t="s" s="0">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="E70" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F70" t="s" s="0">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="G70" t="s" s="0">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="H70" t="s" s="0">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B71" t="s" s="0">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C71" t="s" s="0">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="D71" t="s" s="0">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="E71" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F71" t="s" s="0">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="G71" t="s" s="0">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="H71" t="s" s="0">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B72" t="s" s="0">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C72" t="s" s="0">
+        <v>342</v>
+      </c>
+      <c r="D72" t="s" s="0">
+        <v>343</v>
+      </c>
+      <c r="E72" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F72" t="s" s="0">
+        <v>344</v>
+      </c>
+      <c r="G72" t="s" s="0">
         <v>339</v>
       </c>
-      <c r="D72" t="s" s="0">
-        <v>340</v>
-      </c>
-      <c r="E72" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F72" t="s" s="0">
-        <v>341</v>
-      </c>
-      <c r="G72" t="s" s="0">
-        <v>336</v>
-      </c>
       <c r="H72" t="s" s="0">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B73" t="s" s="0">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C73" t="s" s="0">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="D73" t="s" s="0">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="E73" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F73" t="s" s="0">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="G73" t="s" s="0">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="H73" t="s" s="0">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B74" t="s" s="0">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C74" t="s" s="0">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="D74" t="s" s="0">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="E74" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F74" t="s" s="0">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="G74" t="s" s="0">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="H74" t="s" s="0">
-        <v>336</v>
+        <v>355</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="B75" t="s" s="0">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C75" t="s" s="0">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D75" t="s" s="0">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="E75" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F75" t="s" s="0">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="G75" t="s" s="0">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="H75" t="s" s="0">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="B76" t="s" s="0">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="C76" t="s" s="0">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="D76" t="s" s="0">
+        <v>365</v>
+      </c>
+      <c r="E76" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F76" t="s" s="0">
+        <v>312</v>
+      </c>
+      <c r="G76" t="s" s="0">
         <v>361</v>
       </c>
-      <c r="E76" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F76" t="s" s="0">
-        <v>309</v>
-      </c>
-      <c r="G76" t="s" s="0">
-        <v>357</v>
-      </c>
       <c r="H76" t="s" s="0">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B77" t="s" s="0">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C77" t="s" s="0">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="D77" t="s" s="0">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="E77" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F77" t="s" s="0">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="G77" t="s" s="0">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="H77" t="s" s="0">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B78" t="s" s="0">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C78" t="s" s="0">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="D78" t="s" s="0">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="E78" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F78" t="s" s="0">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="G78" t="s" s="0">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="H78" t="s" s="0">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B79" t="s" s="0">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="C79" t="s" s="0">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="D79" t="s" s="0">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="E79" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F79" t="s" s="0">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="G79" t="s" s="0">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="H79" t="s" s="0">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="B80" t="s" s="0">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C80" t="s" s="0">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="D80" t="s" s="0">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="E80" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F80" t="s" s="0">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="G80" t="s" s="0">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="H80" t="s" s="0">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B81" t="s" s="0">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="C81" t="s" s="0">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="D81" t="s" s="0">
+        <v>390</v>
+      </c>
+      <c r="E81" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F81" t="s" s="0">
+        <v>391</v>
+      </c>
+      <c r="G81" t="s" s="0">
         <v>386</v>
       </c>
-      <c r="E81" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F81" t="s" s="0">
-        <v>387</v>
-      </c>
-      <c r="G81" t="s" s="0">
-        <v>382</v>
-      </c>
       <c r="H81" t="s" s="0">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B82" t="s" s="0">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="C82" t="s" s="0">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="D82" t="s" s="0">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="E82" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F82" t="s" s="0">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="G82" t="s" s="0">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="H82" t="s" s="0">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="B83" t="s" s="0">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="C83" t="s" s="0">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="D83" t="s" s="0">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="E83" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F83" t="s" s="0">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="G83" t="s" s="0">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="H83" t="s" s="0">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="B84" t="s" s="0">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="C84" t="s" s="0">
+        <v>405</v>
+      </c>
+      <c r="D84" t="s" s="0">
+        <v>406</v>
+      </c>
+      <c r="E84" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F84" t="s" s="0">
         <v>401</v>
       </c>
-      <c r="D84" t="s" s="0">
+      <c r="G84" t="s" s="0">
         <v>402</v>
       </c>
-      <c r="E84" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F84" t="s" s="0">
-        <v>397</v>
-      </c>
-      <c r="G84" t="s" s="0">
-        <v>398</v>
-      </c>
       <c r="H84" t="s" s="0">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="B85" t="s" s="0">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="C85" t="s" s="0">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="D85" t="s" s="0">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="E85" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F85" t="s" s="0">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="G85" t="s" s="0">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="H85" t="s" s="0">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="0">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B86" t="s" s="0">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="C86" t="s" s="0">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="D86" t="s" s="0">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="E86" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F86" t="s" s="0">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="G86" t="s" s="0">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="H86" t="s" s="0">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="0">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="B87" t="s" s="0">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C87" t="s" s="0">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="D87" t="s" s="0">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="E87" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F87" t="s" s="0">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="G87" t="s" s="0">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="H87" t="s" s="0">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="0">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="B88" t="s" s="0">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="C88" t="s" s="0">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="D88" t="s" s="0">
+        <v>426</v>
+      </c>
+      <c r="E88" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F88" t="s" s="0">
+        <v>427</v>
+      </c>
+      <c r="G88" t="s" s="0">
         <v>422</v>
       </c>
-      <c r="E88" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F88" t="s" s="0">
-        <v>423</v>
-      </c>
-      <c r="G88" t="s" s="0">
-        <v>418</v>
-      </c>
       <c r="H88" t="s" s="0">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="0">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="B89" t="s" s="0">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="C89" t="s" s="0">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="D89" t="s" s="0">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="E89" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F89" t="s" s="0">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="G89" t="s" s="0">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="H89" t="s" s="0">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="0">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="B90" t="s" s="0">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C90" t="s" s="0">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="D90" t="s" s="0">
+        <v>436</v>
+      </c>
+      <c r="E90" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F90" t="s" s="0">
         <v>432</v>
       </c>
-      <c r="E90" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F90" t="s" s="0">
-        <v>428</v>
-      </c>
       <c r="G90" t="s" s="0">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="H90" t="s" s="0">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="0">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B91" t="s" s="0">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="C91" t="s" s="0">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="D91" t="s" s="0">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="E91" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F91" t="s" s="0">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="G91" t="s" s="0">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="H91" t="s" s="0">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="0">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="B92" t="s" s="0">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="C92" t="s" s="0">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="D92" t="s" s="0">
+        <v>445</v>
+      </c>
+      <c r="E92" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F92" t="s" s="0">
+        <v>432</v>
+      </c>
+      <c r="G92" t="s" s="0">
         <v>441</v>
       </c>
-      <c r="E92" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F92" t="s" s="0">
-        <v>428</v>
-      </c>
-      <c r="G92" t="s" s="0">
-        <v>437</v>
-      </c>
       <c r="H92" t="s" s="0">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="0">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="B93" t="s" s="0">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="C93" t="s" s="0">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="D93" t="s" s="0">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="E93" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F93" t="s" s="0">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="G93" t="s" s="0">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="H93" t="s" s="0">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="0">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="B94" t="s" s="0">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="C94" t="s" s="0">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="D94" t="s" s="0">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="E94" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F94" t="s" s="0">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="G94" t="s" s="0">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="H94" t="s" s="0">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="0">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="B95" t="s" s="0">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="C95" t="s" s="0">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="D95" t="s" s="0">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="E95" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F95" t="s" s="0">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="G95" t="s" s="0">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="H95" t="s" s="0">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="0">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="B96" t="s" s="0">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="C96" t="s" s="0">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="D96" t="s" s="0">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="E96" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F96" t="s" s="0">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="G96" t="s" s="0">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="H96" t="s" s="0">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="0">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B97" t="s" s="0">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="C97" t="s" s="0">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="D97" t="s" s="0">
+        <v>466</v>
+      </c>
+      <c r="E97" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F97" t="s" s="0">
+        <v>432</v>
+      </c>
+      <c r="G97" t="s" s="0">
         <v>462</v>
       </c>
-      <c r="E97" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F97" t="s" s="0">
-        <v>428</v>
-      </c>
-      <c r="G97" t="s" s="0">
-        <v>458</v>
-      </c>
       <c r="H97" t="s" s="0">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="0">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="B98" t="s" s="0">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="C98" t="s" s="0">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="D98" t="s" s="0">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="E98" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F98" t="s" s="0">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="G98" t="s" s="0">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="H98" t="s" s="0">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="0">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="B99" t="s" s="0">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="C99" t="s" s="0">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="D99" t="s" s="0">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="E99" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F99" t="s" s="0">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="G99" t="s" s="0">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="H99" t="s" s="0">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="0">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="B100" t="s" s="0">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="C100" t="s" s="0">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="D100" t="s" s="0">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="E100" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F100" t="s" s="0">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="G100" t="s" s="0">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="H100" t="s" s="0">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="0">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="B101" t="s" s="0">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="C101" t="s" s="0">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="D101" t="s" s="0">
+        <v>483</v>
+      </c>
+      <c r="E101" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F101" t="s" s="0">
+        <v>432</v>
+      </c>
+      <c r="G101" t="s" s="0">
         <v>479</v>
       </c>
-      <c r="E101" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F101" t="s" s="0">
-        <v>428</v>
-      </c>
-      <c r="G101" t="s" s="0">
-        <v>475</v>
-      </c>
       <c r="H101" t="s" s="0">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="0">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="B102" t="s" s="0">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="C102" t="s" s="0">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="D102" t="s" s="0">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="E102" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F102" t="s" s="0">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="G102" t="s" s="0">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="H102" t="s" s="0">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="0">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="B103" t="s" s="0">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="C103" t="s" s="0">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="D103" t="s" s="0">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="E103" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F103" t="s" s="0">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="G103" t="s" s="0">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="H103" t="s" s="0">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="0">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="B104" t="s" s="0">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="C104" t="s" s="0">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="D104" t="s" s="0">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="E104" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F104" t="s" s="0">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="G104" t="s" s="0">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="H104" t="s" s="0">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="0">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="B105" t="s" s="0">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="C105" t="s" s="0">
+        <v>502</v>
+      </c>
+      <c r="D105" t="s" s="0">
+        <v>503</v>
+      </c>
+      <c r="E105" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F105" t="s" s="0">
         <v>498</v>
       </c>
-      <c r="D105" t="s" s="0">
+      <c r="G105" t="s" s="0">
         <v>499</v>
       </c>
-      <c r="E105" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F105" t="s" s="0">
-        <v>494</v>
-      </c>
-      <c r="G105" t="s" s="0">
-        <v>495</v>
-      </c>
       <c r="H105" t="s" s="0">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="0">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="B106" t="s" s="0">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="C106" t="s" s="0">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="D106" t="s" s="0">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="E106" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F106" t="s" s="0">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="G106" t="s" s="0">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="H106" t="s" s="0">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="0">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="B107" t="s" s="0">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="C107" t="s" s="0">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="D107" t="s" s="0">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="E107" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F107" t="s" s="0">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="G107" t="s" s="0">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="H107" t="s" s="0">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="0">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="B108" t="s" s="0">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="C108" t="s" s="0">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="D108" t="s" s="0">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="E108" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F108" t="s" s="0">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="G108" t="s" s="0">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="H108" t="s" s="0">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="0">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="B109" t="s" s="0">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="C109" t="s" s="0">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="D109" t="s" s="0">
+        <v>520</v>
+      </c>
+      <c r="E109" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F109" t="s" s="0">
+        <v>498</v>
+      </c>
+      <c r="G109" t="s" s="0">
         <v>516</v>
       </c>
-      <c r="E109" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F109" t="s" s="0">
-        <v>494</v>
-      </c>
-      <c r="G109" t="s" s="0">
-        <v>512</v>
-      </c>
       <c r="H109" t="s" s="0">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="0">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="B110" t="s" s="0">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="C110" t="s" s="0">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="D110" t="s" s="0">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="E110" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F110" t="s" s="0">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="G110" t="s" s="0">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="H110" t="s" s="0">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="0">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="B111" t="s" s="0">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="C111" t="s" s="0">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="D111" t="s" s="0">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="E111" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F111" t="s" s="0">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="G111" t="s" s="0">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="H111" t="s" s="0">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="0">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="B112" t="s" s="0">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="C112" t="s" s="0">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="D112" t="s" s="0">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="E112" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F112" t="s" s="0">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="G112" t="s" s="0">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="H112" t="s" s="0">
-        <v>529</v>
+        <v>533</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="0">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="B113" t="s" s="0">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="C113" t="s" s="0">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="D113" t="s" s="0">
+        <v>537</v>
+      </c>
+      <c r="E113" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F113" t="s" s="0">
+        <v>498</v>
+      </c>
+      <c r="G113" t="s" s="0">
         <v>533</v>
       </c>
-      <c r="E113" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F113" t="s" s="0">
-        <v>494</v>
-      </c>
-      <c r="G113" t="s" s="0">
-        <v>529</v>
-      </c>
       <c r="H113" t="s" s="0">
-        <v>529</v>
+        <v>533</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="0">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="B114" t="s" s="0">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="C114" t="s" s="0">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="D114" t="s" s="0">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="E114" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F114" t="s" s="0">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="G114" t="s" s="0">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="H114" t="s" s="0">
-        <v>539</v>
+        <v>543</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="0">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="B115" t="s" s="0">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="C115" t="s" s="0">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="D115" t="s" s="0">
+        <v>547</v>
+      </c>
+      <c r="E115" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F115" t="s" s="0">
+        <v>548</v>
+      </c>
+      <c r="G115" t="s" s="0">
         <v>543</v>
       </c>
-      <c r="E115" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F115" t="s" s="0">
-        <v>544</v>
-      </c>
-      <c r="G115" t="s" s="0">
-        <v>539</v>
-      </c>
       <c r="H115" t="s" s="0">
-        <v>539</v>
+        <v>543</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="0">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="B116" t="s" s="0">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="C116" t="s" s="0">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="D116" t="s" s="0">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="E116" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F116" t="s" s="0">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="G116" t="s" s="0">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="H116" t="s" s="0">
-        <v>550</v>
+        <v>554</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s" s="0">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="B117" t="s" s="0">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="C117" t="s" s="0">
+        <v>557</v>
+      </c>
+      <c r="D117" t="s" s="0">
+        <v>558</v>
+      </c>
+      <c r="E117" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F117" t="s" s="0">
         <v>553</v>
       </c>
-      <c r="D117" t="s" s="0">
+      <c r="G117" t="s" s="0">
         <v>554</v>
       </c>
-      <c r="E117" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F117" t="s" s="0">
-        <v>549</v>
-      </c>
-      <c r="G117" t="s" s="0">
-        <v>550</v>
-      </c>
       <c r="H117" t="s" s="0">
-        <v>550</v>
+        <v>554</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="0">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="B118" t="s" s="0">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="C118" t="s" s="0">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="D118" t="s" s="0">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="E118" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F118" t="s" s="0">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="G118" t="s" s="0">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="H118" t="s" s="0">
-        <v>550</v>
+        <v>554</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="0">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="B119" t="s" s="0">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="C119" t="s" s="0">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="D119" t="s" s="0">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="E119" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F119" t="s" s="0">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="G119" t="s" s="0">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="H119" t="s" s="0">
-        <v>550</v>
+        <v>554</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s" s="0">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="B120" t="s" s="0">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="C120" t="s" s="0">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="D120" t="s" s="0">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="E120" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F120" t="s" s="0">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="G120" t="s" s="0">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="H120" t="s" s="0">
-        <v>567</v>
+        <v>571</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="0">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="B121" t="s" s="0">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="C121" t="s" s="0">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="D121" t="s" s="0">
+        <v>575</v>
+      </c>
+      <c r="E121" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F121" t="s" s="0">
+        <v>553</v>
+      </c>
+      <c r="G121" t="s" s="0">
         <v>571</v>
       </c>
-      <c r="E121" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F121" t="s" s="0">
-        <v>549</v>
-      </c>
-      <c r="G121" t="s" s="0">
-        <v>567</v>
-      </c>
       <c r="H121" t="s" s="0">
-        <v>567</v>
+        <v>571</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="0">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="B122" t="s" s="0">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="C122" t="s" s="0">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="D122" t="s" s="0">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="E122" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F122" t="s" s="0">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="G122" t="s" s="0">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="H122" t="s" s="0">
-        <v>567</v>
+        <v>571</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="0">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="B123" t="s" s="0">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C123" t="s" s="0">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="D123" t="s" s="0">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="E123" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F123" t="s" s="0">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="G123" t="s" s="0">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="H123" t="s" s="0">
-        <v>567</v>
+        <v>571</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="0">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="B124" t="s" s="0">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="C124" t="s" s="0">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="D124" t="s" s="0">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="E124" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F124" t="s" s="0">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="G124" t="s" s="0">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="H124" t="s" s="0">
-        <v>585</v>
+        <v>589</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="0">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="B125" t="s" s="0">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="C125" t="s" s="0">
+        <v>592</v>
+      </c>
+      <c r="D125" t="s" s="0">
+        <v>593</v>
+      </c>
+      <c r="E125" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F125" t="s" s="0">
         <v>588</v>
       </c>
-      <c r="D125" t="s" s="0">
+      <c r="G125" t="s" s="0">
         <v>589</v>
       </c>
-      <c r="E125" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F125" t="s" s="0">
-        <v>584</v>
-      </c>
-      <c r="G125" t="s" s="0">
-        <v>585</v>
-      </c>
       <c r="H125" t="s" s="0">
-        <v>585</v>
+        <v>589</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s" s="0">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="B126" t="s" s="0">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="C126" t="s" s="0">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="D126" t="s" s="0">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="E126" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F126" t="s" s="0">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="G126" t="s" s="0">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="H126" t="s" s="0">
-        <v>585</v>
+        <v>589</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s" s="0">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="B127" t="s" s="0">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="C127" t="s" s="0">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="D127" t="s" s="0">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="E127" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F127" t="s" s="0">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="G127" t="s" s="0">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="H127" t="s" s="0">
-        <v>585</v>
+        <v>589</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s" s="0">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="B128" t="s" s="0">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="C128" t="s" s="0">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="D128" t="s" s="0">
+        <v>606</v>
+      </c>
+      <c r="E128" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F128" t="s" s="0">
         <v>602</v>
       </c>
-      <c r="E128" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F128" t="s" s="0">
-        <v>598</v>
-      </c>
       <c r="G128" t="s" s="0">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="H128" t="s" s="0">
-        <v>603</v>
+        <v>607</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s" s="0">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="B129" t="s" s="0">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="C129" t="s" s="0">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="D129" t="s" s="0">
+        <v>611</v>
+      </c>
+      <c r="E129" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F129" t="s" s="0">
+        <v>602</v>
+      </c>
+      <c r="G129" t="s" s="0">
         <v>607</v>
       </c>
-      <c r="E129" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F129" t="s" s="0">
-        <v>598</v>
-      </c>
-      <c r="G129" t="s" s="0">
-        <v>603</v>
-      </c>
       <c r="H129" t="s" s="0">
-        <v>603</v>
+        <v>607</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s" s="0">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="B130" t="s" s="0">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="C130" t="s" s="0">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="D130" t="s" s="0">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="E130" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F130" t="s" s="0">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="G130" t="s" s="0">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="H130" t="s" s="0">
-        <v>603</v>
+        <v>607</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s" s="0">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="B131" t="s" s="0">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="C131" t="s" s="0">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="D131" t="s" s="0">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="E131" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F131" t="s" s="0">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="G131" t="s" s="0">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="H131" t="s" s="0">
-        <v>603</v>
+        <v>607</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s" s="0">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B132" t="s" s="0">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="C132" t="s" s="0">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D132" t="s" s="0">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="E132" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F132" t="s" s="0">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="G132" t="s" s="0">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="H132" t="s" s="0">
-        <v>620</v>
+        <v>624</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s" s="0">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="B133" t="s" s="0">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="C133" t="s" s="0">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D133" t="s" s="0">
+        <v>628</v>
+      </c>
+      <c r="E133" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F133" t="s" s="0">
+        <v>602</v>
+      </c>
+      <c r="G133" t="s" s="0">
         <v>624</v>
       </c>
-      <c r="E133" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F133" t="s" s="0">
-        <v>598</v>
-      </c>
-      <c r="G133" t="s" s="0">
-        <v>620</v>
-      </c>
       <c r="H133" t="s" s="0">
-        <v>620</v>
+        <v>624</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="0">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="B134" t="s" s="0">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="C134" t="s" s="0">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="D134" t="s" s="0">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="E134" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F134" t="s" s="0">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="G134" t="s" s="0">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="H134" t="s" s="0">
-        <v>620</v>
+        <v>624</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s" s="0">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="B135" t="s" s="0">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="C135" t="s" s="0">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="D135" t="s" s="0">
+        <v>637</v>
+      </c>
+      <c r="E135" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F135" t="s" s="0">
         <v>633</v>
       </c>
-      <c r="E135" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F135" t="s" s="0">
-        <v>629</v>
-      </c>
       <c r="G135" t="s" s="0">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="H135" t="s" s="0">
-        <v>620</v>
+        <v>624</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s" s="0">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="B136" t="s" s="0">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="C136" t="s" s="0">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="D136" t="s" s="0">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="E136" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F136" t="s" s="0">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="G136" t="s" s="0">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="H136" t="s" s="0">
-        <v>638</v>
+        <v>642</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s" s="0">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="B137" t="s" s="0">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="C137" t="s" s="0">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="D137" t="s" s="0">
+        <v>646</v>
+      </c>
+      <c r="E137" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F137" t="s" s="0">
+        <v>633</v>
+      </c>
+      <c r="G137" t="s" s="0">
         <v>642</v>
       </c>
-      <c r="E137" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F137" t="s" s="0">
-        <v>629</v>
-      </c>
-      <c r="G137" t="s" s="0">
-        <v>638</v>
-      </c>
       <c r="H137" t="s" s="0">
-        <v>638</v>
+        <v>642</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s" s="0">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="B138" t="s" s="0">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="C138" t="s" s="0">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="D138" t="s" s="0">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="E138" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F138" t="s" s="0">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="G138" t="s" s="0">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="H138" t="s" s="0">
-        <v>638</v>
+        <v>652</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s" s="0">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="B139" t="s" s="0">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="C139" t="s" s="0">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="D139" t="s" s="0">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="E139" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F139" t="s" s="0">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="G139" t="s" s="0">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="H139" t="s" s="0">
-        <v>638</v>
+        <v>642</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s" s="0">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="B140" t="s" s="0">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="C140" t="s" s="0">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="D140" t="s" s="0">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="E140" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F140" t="s" s="0">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="G140" t="s" s="0">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="H140" t="s" s="0">
-        <v>658</v>
+        <v>663</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s" s="0">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="B141" t="s" s="0">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="C141" t="s" s="0">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="D141" t="s" s="0">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="E141" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F141" t="s" s="0">
+        <v>668</v>
+      </c>
+      <c r="G141" t="s" s="0">
         <v>663</v>
       </c>
-      <c r="G141" t="s" s="0">
-        <v>658</v>
-      </c>
       <c r="H141" t="s" s="0">
-        <v>658</v>
+        <v>663</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s" s="0">
+        <v>669</v>
+      </c>
+      <c r="B142" t="s" s="0">
+        <v>670</v>
+      </c>
+      <c r="C142" t="s" s="0">
+        <v>671</v>
+      </c>
+      <c r="D142" t="s" s="0">
+        <v>672</v>
+      </c>
+      <c r="E142" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F142" t="s" s="0">
+        <v>673</v>
+      </c>
+      <c r="G142" t="s" s="0">
+        <v>674</v>
+      </c>
+      <c r="H142" t="s" s="0">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s" s="0">
+        <v>675</v>
+      </c>
+      <c r="B143" t="s" s="0">
+        <v>676</v>
+      </c>
+      <c r="C143" t="s" s="0">
+        <v>677</v>
+      </c>
+      <c r="D143" t="s" s="0">
+        <v>678</v>
+      </c>
+      <c r="E143" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F143" t="s" s="0">
+        <v>679</v>
+      </c>
+      <c r="G143" t="s" s="0">
+        <v>674</v>
+      </c>
+      <c r="H143" t="s" s="0">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s" s="0">
+        <v>680</v>
+      </c>
+      <c r="B144" t="s" s="0">
+        <v>681</v>
+      </c>
+      <c r="C144" t="s" s="0">
+        <v>682</v>
+      </c>
+      <c r="D144" t="s" s="0">
+        <v>683</v>
+      </c>
+      <c r="E144" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F144" t="s" s="0">
+        <v>684</v>
+      </c>
+      <c r="G144" t="s" s="0">
+        <v>674</v>
+      </c>
+      <c r="H144" t="s" s="0">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s" s="0">
+        <v>685</v>
+      </c>
+      <c r="B145" t="s" s="0">
+        <v>686</v>
+      </c>
+      <c r="C145" t="s" s="0">
+        <v>687</v>
+      </c>
+      <c r="D145" t="s" s="0">
+        <v>688</v>
+      </c>
+      <c r="E145" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F145" t="s" s="0">
+        <v>689</v>
+      </c>
+      <c r="G145" t="s" s="0">
+        <v>690</v>
+      </c>
+      <c r="H145" t="s" s="0">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s" s="0">
+        <v>691</v>
+      </c>
+      <c r="B146" t="s" s="0">
+        <v>692</v>
+      </c>
+      <c r="C146" t="s" s="0">
+        <v>693</v>
+      </c>
+      <c r="D146" t="s" s="0">
+        <v>694</v>
+      </c>
+      <c r="E146" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F146" t="s" s="0">
+        <v>695</v>
+      </c>
+      <c r="G146" t="s" s="0">
+        <v>690</v>
+      </c>
+      <c r="H146" t="s" s="0">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s" s="0">
+        <v>696</v>
+      </c>
+      <c r="B147" t="s" s="0">
+        <v>697</v>
+      </c>
+      <c r="C147" t="s" s="0">
+        <v>698</v>
+      </c>
+      <c r="D147" t="s" s="0">
+        <v>699</v>
+      </c>
+      <c r="E147" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F147" t="s" s="0">
+        <v>264</v>
+      </c>
+      <c r="G147" t="s" s="0">
+        <v>700</v>
+      </c>
+      <c r="H147" t="s" s="0">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s" s="0">
+        <v>701</v>
+      </c>
+      <c r="B148" t="s" s="0">
+        <v>702</v>
+      </c>
+      <c r="C148" t="s" s="0">
+        <v>703</v>
+      </c>
+      <c r="D148" t="s" s="0">
+        <v>704</v>
+      </c>
+      <c r="E148" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F148" t="s" s="0">
+        <v>312</v>
+      </c>
+      <c r="G148" t="s" s="0">
+        <v>705</v>
+      </c>
+      <c r="H148" t="s" s="0">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s" s="0">
+        <v>706</v>
+      </c>
+      <c r="B149" t="s" s="0">
+        <v>707</v>
+      </c>
+      <c r="C149" t="s" s="0">
+        <v>708</v>
+      </c>
+      <c r="D149" t="s" s="0">
+        <v>709</v>
+      </c>
+      <c r="E149" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F149" t="s" s="0">
+        <v>498</v>
+      </c>
+      <c r="G149" t="s" s="0">
+        <v>710</v>
+      </c>
+      <c r="H149" t="s" s="0">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s" s="0">
+        <v>711</v>
+      </c>
+      <c r="B150" t="s" s="0">
+        <v>712</v>
+      </c>
+      <c r="C150" t="s" s="0">
+        <v>713</v>
+      </c>
+      <c r="D150" t="s" s="0">
+        <v>714</v>
+      </c>
+      <c r="E150" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F150" t="s" s="0">
+        <v>498</v>
+      </c>
+      <c r="G150" t="s" s="0">
+        <v>710</v>
+      </c>
+      <c r="H150" t="s" s="0">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s" s="0">
+        <v>715</v>
+      </c>
+      <c r="B151" t="s" s="0">
+        <v>716</v>
+      </c>
+      <c r="C151" t="s" s="0">
+        <v>717</v>
+      </c>
+      <c r="D151" t="s" s="0">
+        <v>718</v>
+      </c>
+      <c r="E151" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F151" t="s" s="0">
+        <v>498</v>
+      </c>
+      <c r="G151" t="s" s="0">
+        <v>710</v>
+      </c>
+      <c r="H151" t="s" s="0">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s" s="0">
+        <v>719</v>
+      </c>
+      <c r="B152" t="s" s="0">
+        <v>720</v>
+      </c>
+      <c r="C152" t="s" s="0">
+        <v>721</v>
+      </c>
+      <c r="D152" t="s" s="0">
+        <v>722</v>
+      </c>
+      <c r="E152" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F152" t="s" s="0">
+        <v>498</v>
+      </c>
+      <c r="G152" t="s" s="0">
+        <v>710</v>
+      </c>
+      <c r="H152" t="s" s="0">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s" s="0">
+        <v>724</v>
+      </c>
+      <c r="B153" t="s" s="0">
+        <v>725</v>
+      </c>
+      <c r="C153" t="s" s="0">
+        <v>726</v>
+      </c>
+      <c r="D153" t="s" s="0">
+        <v>727</v>
+      </c>
+      <c r="E153" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F153" t="s" s="0">
+        <v>728</v>
+      </c>
+      <c r="G153" t="s" s="0">
+        <v>710</v>
+      </c>
+      <c r="H153" t="s" s="0">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s" s="0">
+        <v>729</v>
+      </c>
+      <c r="B154" t="s" s="0">
+        <v>730</v>
+      </c>
+      <c r="C154" t="s" s="0">
+        <v>731</v>
+      </c>
+      <c r="D154" t="s" s="0">
+        <v>732</v>
+      </c>
+      <c r="E154" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F154" t="s" s="0">
+        <v>553</v>
+      </c>
+      <c r="G154" t="s" s="0">
+        <v>710</v>
+      </c>
+      <c r="H154" t="s" s="0">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s" s="0">
+        <v>733</v>
+      </c>
+      <c r="B155" t="s" s="0">
+        <v>734</v>
+      </c>
+      <c r="C155" t="s" s="0">
+        <v>735</v>
+      </c>
+      <c r="D155" t="s" s="0">
+        <v>736</v>
+      </c>
+      <c r="E155" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F155" t="s" s="0">
+        <v>553</v>
+      </c>
+      <c r="G155" t="s" s="0">
+        <v>710</v>
+      </c>
+      <c r="H155" t="s" s="0">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s" s="0">
+        <v>737</v>
+      </c>
+      <c r="B156" t="s" s="0">
+        <v>738</v>
+      </c>
+      <c r="C156" t="s" s="0">
+        <v>739</v>
+      </c>
+      <c r="D156" t="s" s="0">
+        <v>740</v>
+      </c>
+      <c r="E156" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F156" t="s" s="0">
+        <v>588</v>
+      </c>
+      <c r="G156" t="s" s="0">
+        <v>710</v>
+      </c>
+      <c r="H156" t="s" s="0">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s" s="0">
+        <v>741</v>
+      </c>
+      <c r="B157" t="s" s="0">
+        <v>742</v>
+      </c>
+      <c r="C157" t="s" s="0">
+        <v>743</v>
+      </c>
+      <c r="D157" t="s" s="0">
+        <v>744</v>
+      </c>
+      <c r="E157" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F157" t="s" s="0">
+        <v>588</v>
+      </c>
+      <c r="G157" t="s" s="0">
+        <v>710</v>
+      </c>
+      <c r="H157" t="s" s="0">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s" s="0">
+        <v>745</v>
+      </c>
+      <c r="B158" t="s" s="0">
+        <v>746</v>
+      </c>
+      <c r="C158" t="s" s="0">
+        <v>747</v>
+      </c>
+      <c r="D158" t="s" s="0">
+        <v>748</v>
+      </c>
+      <c r="E158" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F158" t="s" s="0">
+        <v>602</v>
+      </c>
+      <c r="G158" t="s" s="0">
+        <v>710</v>
+      </c>
+      <c r="H158" t="s" s="0">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s" s="0">
+        <v>749</v>
+      </c>
+      <c r="B159" t="s" s="0">
+        <v>750</v>
+      </c>
+      <c r="C159" t="s" s="0">
+        <v>751</v>
+      </c>
+      <c r="D159" t="s" s="0">
+        <v>752</v>
+      </c>
+      <c r="E159" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F159" t="s" s="0">
+        <v>602</v>
+      </c>
+      <c r="G159" t="s" s="0">
+        <v>710</v>
+      </c>
+      <c r="H159" t="s" s="0">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s" s="0">
+        <v>754</v>
+      </c>
+      <c r="B160" t="s" s="0">
+        <v>755</v>
+      </c>
+      <c r="C160" t="s" s="0">
+        <v>756</v>
+      </c>
+      <c r="D160" t="s" s="0">
+        <v>757</v>
+      </c>
+      <c r="E160" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F160" t="s" s="0">
+        <v>668</v>
+      </c>
+      <c r="G160" t="s" s="0">
+        <v>710</v>
+      </c>
+      <c r="H160" t="s" s="0">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s" s="0">
+        <v>758</v>
+      </c>
+      <c r="B161" t="s" s="0">
+        <v>759</v>
+      </c>
+      <c r="C161" t="s" s="0">
+        <v>760</v>
+      </c>
+      <c r="D161" t="s" s="0">
+        <v>761</v>
+      </c>
+      <c r="E161" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F161" t="s" s="0">
+        <v>762</v>
+      </c>
+      <c r="G161" t="s" s="0">
+        <v>710</v>
+      </c>
+      <c r="H161" t="s" s="0">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s" s="0">
+        <v>763</v>
+      </c>
+      <c r="B162" t="s" s="0">
+        <v>764</v>
+      </c>
+      <c r="C162" t="s" s="0">
+        <v>765</v>
+      </c>
+      <c r="D162" t="s" s="0">
+        <v>766</v>
+      </c>
+      <c r="E162" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F162" t="s" s="0">
+        <v>767</v>
+      </c>
+      <c r="G162" t="s" s="0">
+        <v>710</v>
+      </c>
+      <c r="H162" t="s" s="0">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s" s="0">
+        <v>768</v>
+      </c>
+      <c r="B163" t="s" s="0">
+        <v>769</v>
+      </c>
+      <c r="C163" t="s" s="0">
+        <v>770</v>
+      </c>
+      <c r="D163" t="s" s="0">
+        <v>771</v>
+      </c>
+      <c r="E163" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F163" t="s" s="0">
+        <v>767</v>
+      </c>
+      <c r="G163" t="s" s="0">
+        <v>710</v>
+      </c>
+      <c r="H163" t="s" s="0">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s" s="0">
+        <v>772</v>
+      </c>
+      <c r="B164" t="s" s="0">
+        <v>773</v>
+      </c>
+      <c r="C164" t="s" s="0">
+        <v>774</v>
+      </c>
+      <c r="D164" t="s" s="0">
+        <v>775</v>
+      </c>
+      <c r="E164" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F164" t="s" s="0">
+        <v>776</v>
+      </c>
+      <c r="G164" t="s" s="0">
+        <v>710</v>
+      </c>
+      <c r="H164" t="s" s="0">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s" s="0">
+        <v>777</v>
+      </c>
+      <c r="B165" t="s" s="0">
+        <v>778</v>
+      </c>
+      <c r="C165" t="s" s="0">
+        <v>779</v>
+      </c>
+      <c r="D165" t="s" s="0">
+        <v>780</v>
+      </c>
+      <c r="E165" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F165" t="s" s="0">
+        <v>776</v>
+      </c>
+      <c r="G165" t="s" s="0">
+        <v>710</v>
+      </c>
+      <c r="H165" t="s" s="0">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s" s="0">
+        <v>781</v>
+      </c>
+      <c r="B166" t="s" s="0">
+        <v>782</v>
+      </c>
+      <c r="C166" t="s" s="0">
+        <v>783</v>
+      </c>
+      <c r="D166" t="s" s="0">
+        <v>784</v>
+      </c>
+      <c r="E166" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F166" t="s" s="0">
+        <v>785</v>
+      </c>
+      <c r="G166" t="s" s="0">
+        <v>710</v>
+      </c>
+      <c r="H166" t="s" s="0">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s" s="0">
+        <v>786</v>
+      </c>
+      <c r="B167" t="s" s="0">
+        <v>787</v>
+      </c>
+      <c r="C167" t="s" s="0">
+        <v>788</v>
+      </c>
+      <c r="D167" t="s" s="0">
+        <v>789</v>
+      </c>
+      <c r="E167" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F167" t="s" s="0">
+        <v>785</v>
+      </c>
+      <c r="G167" t="s" s="0">
+        <v>710</v>
+      </c>
+      <c r="H167" t="s" s="0">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s" s="0">
+        <v>790</v>
+      </c>
+      <c r="B168" t="s" s="0">
+        <v>791</v>
+      </c>
+      <c r="C168" t="s" s="0">
+        <v>792</v>
+      </c>
+      <c r="D168" t="s" s="0">
+        <v>793</v>
+      </c>
+      <c r="E168" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F168" t="s" s="0">
+        <v>794</v>
+      </c>
+      <c r="G168" t="s" s="0">
+        <v>710</v>
+      </c>
+      <c r="H168" t="s" s="0">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s" s="0">
+        <v>795</v>
+      </c>
+      <c r="B169" t="s" s="0">
+        <v>796</v>
+      </c>
+      <c r="C169" t="s" s="0">
+        <v>797</v>
+      </c>
+      <c r="D169" t="s" s="0">
+        <v>798</v>
+      </c>
+      <c r="E169" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F169" t="s" s="0">
+        <v>799</v>
+      </c>
+      <c r="G169" t="s" s="0">
+        <v>710</v>
+      </c>
+      <c r="H169" t="s" s="0">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s" s="0">
+        <v>800</v>
+      </c>
+      <c r="B170" t="s" s="0">
+        <v>801</v>
+      </c>
+      <c r="C170" t="s" s="0">
+        <v>802</v>
+      </c>
+      <c r="D170" t="s" s="0">
+        <v>803</v>
+      </c>
+      <c r="E170" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F170" t="s" s="0">
+        <v>804</v>
+      </c>
+      <c r="G170" t="s" s="0">
+        <v>710</v>
+      </c>
+      <c r="H170" t="s" s="0">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s" s="0">
+        <v>805</v>
+      </c>
+      <c r="B171" t="s" s="0">
+        <v>806</v>
+      </c>
+      <c r="C171" t="s" s="0">
+        <v>807</v>
+      </c>
+      <c r="D171" t="s" s="0">
+        <v>808</v>
+      </c>
+      <c r="E171" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F171" t="s" s="0">
+        <v>809</v>
+      </c>
+      <c r="G171" t="s" s="0">
+        <v>710</v>
+      </c>
+      <c r="H171" t="s" s="0">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s" s="0">
+        <v>811</v>
+      </c>
+      <c r="B172" t="s" s="0">
+        <v>812</v>
+      </c>
+      <c r="C172" t="s" s="0">
+        <v>813</v>
+      </c>
+      <c r="D172" t="s" s="0">
+        <v>814</v>
+      </c>
+      <c r="E172" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F172" t="s" s="0">
+        <v>815</v>
+      </c>
+      <c r="G172" t="s" s="0">
+        <v>710</v>
+      </c>
+      <c r="H172" t="s" s="0">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s" s="0">
+        <v>816</v>
+      </c>
+      <c r="B173" t="s" s="0">
+        <v>817</v>
+      </c>
+      <c r="C173" t="s" s="0">
+        <v>818</v>
+      </c>
+      <c r="D173" t="s" s="0">
+        <v>819</v>
+      </c>
+      <c r="E173" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F173" t="s" s="0">
+        <v>820</v>
+      </c>
+      <c r="G173" t="s" s="0">
+        <v>710</v>
+      </c>
+      <c r="H173" t="s" s="0">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s" s="0">
+        <v>822</v>
+      </c>
+      <c r="B174" t="s" s="0">
+        <v>823</v>
+      </c>
+      <c r="C174" t="s" s="0">
+        <v>824</v>
+      </c>
+      <c r="D174" t="s" s="0">
+        <v>825</v>
+      </c>
+      <c r="E174" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F174" t="s" s="0">
+        <v>684</v>
+      </c>
+      <c r="G174" t="s" s="0">
+        <v>710</v>
+      </c>
+      <c r="H174" t="s" s="0">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s" s="0">
+        <v>826</v>
+      </c>
+      <c r="B175" t="s" s="0">
+        <v>827</v>
+      </c>
+      <c r="C175" t="s" s="0">
+        <v>828</v>
+      </c>
+      <c r="D175" t="s" s="0">
+        <v>829</v>
+      </c>
+      <c r="E175" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F175" t="s" s="0">
+        <v>684</v>
+      </c>
+      <c r="G175" t="s" s="0">
+        <v>710</v>
+      </c>
+      <c r="H175" t="s" s="0">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s" s="0">
+        <v>830</v>
+      </c>
+      <c r="B176" t="s" s="0">
+        <v>831</v>
+      </c>
+      <c r="C176" t="s" s="0">
+        <v>832</v>
+      </c>
+      <c r="D176" t="s" s="0">
+        <v>833</v>
+      </c>
+      <c r="E176" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F176" t="s" s="0">
+        <v>834</v>
+      </c>
+      <c r="G176" t="s" s="0">
+        <v>710</v>
+      </c>
+      <c r="H176" t="s" s="0">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s" s="0">
+        <v>835</v>
+      </c>
+      <c r="B177" t="s" s="0">
+        <v>836</v>
+      </c>
+      <c r="C177" t="s" s="0">
+        <v>837</v>
+      </c>
+      <c r="D177" t="s" s="0">
+        <v>838</v>
+      </c>
+      <c r="E177" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F177" t="s" s="0">
+        <v>839</v>
+      </c>
+      <c r="G177" t="s" s="0">
+        <v>840</v>
+      </c>
+      <c r="H177" t="s" s="0">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s" s="0">
+        <v>841</v>
+      </c>
+      <c r="B178" t="s" s="0">
+        <v>842</v>
+      </c>
+      <c r="C178" t="s" s="0">
+        <v>843</v>
+      </c>
+      <c r="D178" t="s" s="0">
+        <v>844</v>
+      </c>
+      <c r="E178" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F178" t="s" s="0">
+        <v>845</v>
+      </c>
+      <c r="G178" t="s" s="0">
+        <v>846</v>
+      </c>
+      <c r="H178" t="s" s="0">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s" s="0">
+        <v>847</v>
+      </c>
+      <c r="B179" t="s" s="0">
+        <v>848</v>
+      </c>
+      <c r="C179" t="s" s="0">
+        <v>849</v>
+      </c>
+      <c r="D179" t="s" s="0">
+        <v>850</v>
+      </c>
+      <c r="E179" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F179" t="s" s="0">
+        <v>851</v>
+      </c>
+      <c r="G179" t="s" s="0">
+        <v>846</v>
+      </c>
+      <c r="H179" t="s" s="0">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s" s="0">
+        <v>852</v>
+      </c>
+      <c r="B180" t="s" s="0">
+        <v>853</v>
+      </c>
+      <c r="C180" t="s" s="0">
+        <v>854</v>
+      </c>
+      <c r="D180" t="s" s="0">
+        <v>855</v>
+      </c>
+      <c r="E180" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F180" t="s" s="0">
+        <v>856</v>
+      </c>
+      <c r="G180" t="s" s="0">
+        <v>846</v>
+      </c>
+      <c r="H180" t="s" s="0">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s" s="0">
+        <v>857</v>
+      </c>
+      <c r="B181" t="s" s="0">
+        <v>858</v>
+      </c>
+      <c r="C181" t="s" s="0">
+        <v>859</v>
+      </c>
+      <c r="D181" t="s" s="0">
+        <v>860</v>
+      </c>
+      <c r="E181" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F181" t="s" s="0">
+        <v>861</v>
+      </c>
+      <c r="G181" t="s" s="0">
+        <v>846</v>
+      </c>
+      <c r="H181" t="s" s="0">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s" s="0">
+        <v>862</v>
+      </c>
+      <c r="B182" t="s" s="0">
+        <v>863</v>
+      </c>
+      <c r="C182" t="s" s="0">
+        <v>864</v>
+      </c>
+      <c r="D182" t="s" s="0">
+        <v>865</v>
+      </c>
+      <c r="E182" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F182" t="s" s="0">
+        <v>861</v>
+      </c>
+      <c r="G182" t="s" s="0">
+        <v>846</v>
+      </c>
+      <c r="H182" t="s" s="0">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s" s="0">
+        <v>866</v>
+      </c>
+      <c r="B183" t="s" s="0">
+        <v>867</v>
+      </c>
+      <c r="C183" t="s" s="0">
+        <v>868</v>
+      </c>
+      <c r="D183" t="s" s="0">
+        <v>869</v>
+      </c>
+      <c r="E183" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F183" t="s" s="0">
+        <v>870</v>
+      </c>
+      <c r="G183" t="s" s="0">
+        <v>871</v>
+      </c>
+      <c r="H183" t="s" s="0">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s" s="0">
+        <v>872</v>
+      </c>
+      <c r="B184" t="s" s="0">
+        <v>873</v>
+      </c>
+      <c r="C184" t="s" s="0">
+        <v>874</v>
+      </c>
+      <c r="D184" t="s" s="0">
+        <v>875</v>
+      </c>
+      <c r="E184" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F184" t="s" s="0">
+        <v>876</v>
+      </c>
+      <c r="G184" t="s" s="0">
+        <v>877</v>
+      </c>
+      <c r="H184" t="s" s="0">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s" s="0">
+        <v>879</v>
+      </c>
+      <c r="B185" t="s" s="0">
+        <v>880</v>
+      </c>
+      <c r="C185" t="s" s="0">
+        <v>881</v>
+      </c>
+      <c r="D185" t="s" s="0">
+        <v>882</v>
+      </c>
+      <c r="E185" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F185" t="s" s="0">
+        <v>883</v>
+      </c>
+      <c r="G185" t="s" s="0">
+        <v>877</v>
+      </c>
+      <c r="H185" t="s" s="0">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s" s="0">
+        <v>884</v>
+      </c>
+      <c r="B186" t="s" s="0">
+        <v>885</v>
+      </c>
+      <c r="C186" t="s" s="0">
+        <v>886</v>
+      </c>
+      <c r="D186" t="s" s="0">
+        <v>887</v>
+      </c>
+      <c r="E186" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F186" t="s" s="0">
+        <v>684</v>
+      </c>
+      <c r="G186" t="s" s="0">
+        <v>877</v>
+      </c>
+      <c r="H186" t="s" s="0">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s" s="0">
+        <v>888</v>
+      </c>
+      <c r="B187" t="s" s="0">
+        <v>889</v>
+      </c>
+      <c r="C187" t="s" s="0">
+        <v>890</v>
+      </c>
+      <c r="D187" t="s" s="0">
+        <v>891</v>
+      </c>
+      <c r="E187" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F187" t="s" s="0">
+        <v>684</v>
+      </c>
+      <c r="G187" t="s" s="0">
+        <v>877</v>
+      </c>
+      <c r="H187" t="s" s="0">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s" s="0">
+        <v>892</v>
+      </c>
+      <c r="B188" t="s" s="0">
+        <v>893</v>
+      </c>
+      <c r="C188" t="s" s="0">
+        <v>894</v>
+      </c>
+      <c r="D188" t="s" s="0">
+        <v>895</v>
+      </c>
+      <c r="E188" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F188" t="s" s="0">
+        <v>684</v>
+      </c>
+      <c r="G188" t="s" s="0">
+        <v>877</v>
+      </c>
+      <c r="H188" t="s" s="0">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s" s="0">
+        <v>896</v>
+      </c>
+      <c r="B189" t="s" s="0">
+        <v>897</v>
+      </c>
+      <c r="C189" t="s" s="0">
+        <v>898</v>
+      </c>
+      <c r="D189" t="s" s="0">
+        <v>899</v>
+      </c>
+      <c r="E189" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F189" t="s" s="0">
+        <v>684</v>
+      </c>
+      <c r="G189" t="s" s="0">
+        <v>900</v>
+      </c>
+      <c r="H189" t="s" s="0">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s" s="0">
+        <v>901</v>
+      </c>
+      <c r="B190" t="s" s="0">
+        <v>902</v>
+      </c>
+      <c r="C190" t="s" s="0">
+        <v>903</v>
+      </c>
+      <c r="D190" t="s" s="0">
+        <v>904</v>
+      </c>
+      <c r="E190" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F190" t="s" s="0">
+        <v>905</v>
+      </c>
+      <c r="G190" t="s" s="0">
+        <v>906</v>
+      </c>
+      <c r="H190" t="s" s="0">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s" s="0">
+        <v>907</v>
+      </c>
+      <c r="B191" t="s" s="0">
+        <v>908</v>
+      </c>
+      <c r="C191" t="s" s="0">
+        <v>909</v>
+      </c>
+      <c r="D191" t="s" s="0">
+        <v>910</v>
+      </c>
+      <c r="E191" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F191" t="s" s="0">
+        <v>911</v>
+      </c>
+      <c r="G191" t="s" s="0">
+        <v>906</v>
+      </c>
+      <c r="H191" t="s" s="0">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s" s="0">
+        <v>912</v>
+      </c>
+      <c r="B192" t="s" s="0">
+        <v>913</v>
+      </c>
+      <c r="C192" t="s" s="0">
+        <v>914</v>
+      </c>
+      <c r="D192" t="s" s="0">
+        <v>915</v>
+      </c>
+      <c r="E192" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F192" t="s" s="0">
+        <v>799</v>
+      </c>
+      <c r="G192" t="s" s="0">
+        <v>916</v>
+      </c>
+      <c r="H192" t="s" s="0">
+        <v>916</v>
       </c>
     </row>
   </sheetData>

--- a/data/movie.xlsx
+++ b/data/movie.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1536" uniqueCount="917">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1544" uniqueCount="925">
   <si>
     <t>movieId</t>
   </si>
@@ -158,7 +158,7 @@
     <t>fsko95970896</t>
   </si>
   <si>
-    <t>SB19 Wakas at Simula SB19 Wakas at Simula: The Trilogy Concert Finale In Cinemas</t>
+    <t>SB19 Wakas at Simula: The Trilogy Concert Finale In Cinemas</t>
   </si>
   <si>
     <t>https://www.atmovies.com.tw/photo101/fsko95970896/pl_fsko95970896.jpg</t>
@@ -170,6 +170,9 @@
     <t>2026-10-09 09:45:22</t>
   </si>
   <si>
+    <t>2026-10-19 14:37:30</t>
+  </si>
+  <si>
     <t>10</t>
   </si>
   <si>
@@ -449,12 +452,15 @@
     <t>fpjp99797607</t>
   </si>
   <si>
-    <t>Perfume“Cold Sleep”</t>
+    <t>Perfume“Cold Sleep”-25 years Document</t>
   </si>
   <si>
     <t>https://www.atmovies.com.tw/photo101/fpjp99797607/pl_fpjp99797607.jpg</t>
   </si>
   <si>
+    <t>2026-10-19 14:37:27</t>
+  </si>
+  <si>
     <t>31</t>
   </si>
   <si>
@@ -2763,6 +2769,24 @@
   </si>
   <si>
     <t>2026-10-19 11:23:10</t>
+  </si>
+  <si>
+    <t>192</t>
+  </si>
+  <si>
+    <t>ftko95405162</t>
+  </si>
+  <si>
+    <t>TWS VR CONCERT RUSH ROAD</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/ftko95405162/pl_ftko95405162.jpg</t>
+  </si>
+  <si>
+    <t>2026-03-13 00:00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 14:35:52</t>
   </si>
 </sst>
 </file>
@@ -2807,7 +2831,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H192"/>
+  <dimension ref="A1:H193"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -3067,21 +3091,21 @@
         <v>51</v>
       </c>
       <c r="H10" t="s" s="0">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E11" t="s" s="0">
         <v>12</v>
@@ -3098,16 +3122,16 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E12" t="s" s="0">
         <v>12</v>
@@ -3124,16 +3148,16 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E13" t="s" s="0">
         <v>12</v>
@@ -3150,42 +3174,42 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E14" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F14" t="s" s="0">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G14" t="s" s="0">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H14" t="s" s="0">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E15" t="s" s="0">
         <v>12</v>
@@ -3194,4612 +3218,4638 @@
         <v>13</v>
       </c>
       <c r="G15" t="s" s="0">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H15" t="s" s="0">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E16" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F16" t="s" s="0">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G16" t="s" s="0">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H16" t="s" s="0">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E17" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F17" t="s" s="0">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G17" t="s" s="0">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H17" t="s" s="0">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="D18" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="E18" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F18" t="s" s="0">
         <v>84</v>
       </c>
-      <c r="B18" t="s" s="0">
-        <v>85</v>
-      </c>
-      <c r="C18" t="s" s="0">
-        <v>86</v>
-      </c>
-      <c r="D18" t="s" s="0">
-        <v>87</v>
-      </c>
-      <c r="E18" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F18" t="s" s="0">
-        <v>83</v>
-      </c>
       <c r="G18" t="s" s="0">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H18" t="s" s="0">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="D19" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="E19" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F19" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="G19" t="s" s="0">
         <v>89</v>
       </c>
-      <c r="B19" t="s" s="0">
-        <v>90</v>
-      </c>
-      <c r="C19" t="s" s="0">
-        <v>91</v>
-      </c>
-      <c r="D19" t="s" s="0">
-        <v>92</v>
-      </c>
-      <c r="E19" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F19" t="s" s="0">
-        <v>93</v>
-      </c>
-      <c r="G19" t="s" s="0">
-        <v>88</v>
-      </c>
       <c r="H19" t="s" s="0">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D20" t="s" s="0">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E20" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F20" t="s" s="0">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G20" t="s" s="0">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H20" t="s" s="0">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D21" t="s" s="0">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E21" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F21" t="s" s="0">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G21" t="s" s="0">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H21" t="s" s="0">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D22" t="s" s="0">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E22" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F22" t="s" s="0">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G22" t="s" s="0">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H22" t="s" s="0">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="C23" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="D23" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="E23" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F23" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="G23" t="s" s="0">
         <v>107</v>
       </c>
-      <c r="B23" t="s" s="0">
-        <v>108</v>
-      </c>
-      <c r="C23" t="s" s="0">
-        <v>109</v>
-      </c>
-      <c r="D23" t="s" s="0">
-        <v>110</v>
-      </c>
-      <c r="E23" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F23" t="s" s="0">
-        <v>83</v>
-      </c>
-      <c r="G23" t="s" s="0">
-        <v>106</v>
-      </c>
       <c r="H23" t="s" s="0">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D24" t="s" s="0">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E24" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F24" t="s" s="0">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G24" t="s" s="0">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H24" t="s" s="0">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D25" t="s" s="0">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E25" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F25" t="s" s="0">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G25" t="s" s="0">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H25" t="s" s="0">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D26" t="s" s="0">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E26" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F26" t="s" s="0">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G26" t="s" s="0">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H26" t="s" s="0">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
+        <v>126</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="C27" t="s" s="0">
+        <v>128</v>
+      </c>
+      <c r="D27" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="E27" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F27" t="s" s="0">
+        <v>130</v>
+      </c>
+      <c r="G27" t="s" s="0">
         <v>125</v>
       </c>
-      <c r="B27" t="s" s="0">
-        <v>126</v>
-      </c>
-      <c r="C27" t="s" s="0">
-        <v>127</v>
-      </c>
-      <c r="D27" t="s" s="0">
-        <v>128</v>
-      </c>
-      <c r="E27" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F27" t="s" s="0">
-        <v>129</v>
-      </c>
-      <c r="G27" t="s" s="0">
-        <v>124</v>
-      </c>
       <c r="H27" t="s" s="0">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D28" t="s" s="0">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E28" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F28" t="s" s="0">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G28" t="s" s="0">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H28" t="s" s="0">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C29" t="s" s="0">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D29" t="s" s="0">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E29" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F29" t="s" s="0">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G29" t="s" s="0">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H29" t="s" s="0">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C30" t="s" s="0">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D30" t="s" s="0">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E30" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F30" t="s" s="0">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G30" t="s" s="0">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H30" t="s" s="0">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
+        <v>144</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>145</v>
+      </c>
+      <c r="C31" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="D31" t="s" s="0">
+        <v>147</v>
+      </c>
+      <c r="E31" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F31" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="G31" t="s" s="0">
         <v>143</v>
       </c>
-      <c r="B31" t="s" s="0">
-        <v>144</v>
-      </c>
-      <c r="C31" t="s" s="0">
-        <v>145</v>
-      </c>
-      <c r="D31" t="s" s="0">
-        <v>146</v>
-      </c>
-      <c r="E31" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F31" t="s" s="0">
-        <v>123</v>
-      </c>
-      <c r="G31" t="s" s="0">
-        <v>142</v>
-      </c>
       <c r="H31" t="s" s="0">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C32" t="s" s="0">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D32" t="s" s="0">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E32" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F32" t="s" s="0">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G32" t="s" s="0">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H32" t="s" s="0">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C33" t="s" s="0">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D33" t="s" s="0">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E33" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F33" t="s" s="0">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G33" t="s" s="0">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H33" t="s" s="0">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C34" t="s" s="0">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D34" t="s" s="0">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E34" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F34" t="s" s="0">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G34" t="s" s="0">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H34" t="s" s="0">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B35" t="s" s="0">
+        <v>164</v>
+      </c>
+      <c r="C35" t="s" s="0">
+        <v>165</v>
+      </c>
+      <c r="D35" t="s" s="0">
+        <v>166</v>
+      </c>
+      <c r="E35" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F35" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="G35" t="s" s="0">
         <v>162</v>
       </c>
-      <c r="C35" t="s" s="0">
-        <v>163</v>
-      </c>
-      <c r="D35" t="s" s="0">
-        <v>164</v>
-      </c>
-      <c r="E35" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F35" t="s" s="0">
-        <v>123</v>
-      </c>
-      <c r="G35" t="s" s="0">
-        <v>160</v>
-      </c>
       <c r="H35" t="s" s="0">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C36" t="s" s="0">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D36" t="s" s="0">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E36" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F36" t="s" s="0">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G36" t="s" s="0">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H36" t="s" s="0">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C37" t="s" s="0">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D37" t="s" s="0">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E37" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F37" t="s" s="0">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G37" t="s" s="0">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H37" t="s" s="0">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B38" t="s" s="0">
+        <v>178</v>
+      </c>
+      <c r="C38" t="s" s="0">
+        <v>179</v>
+      </c>
+      <c r="D38" t="s" s="0">
+        <v>180</v>
+      </c>
+      <c r="E38" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F38" t="s" s="0">
         <v>176</v>
       </c>
-      <c r="C38" t="s" s="0">
-        <v>177</v>
-      </c>
-      <c r="D38" t="s" s="0">
-        <v>178</v>
-      </c>
-      <c r="E38" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F38" t="s" s="0">
-        <v>174</v>
-      </c>
       <c r="G38" t="s" s="0">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H38" t="s" s="0">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B39" t="s" s="0">
+        <v>183</v>
+      </c>
+      <c r="C39" t="s" s="0">
+        <v>184</v>
+      </c>
+      <c r="D39" t="s" s="0">
+        <v>185</v>
+      </c>
+      <c r="E39" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F39" t="s" s="0">
+        <v>176</v>
+      </c>
+      <c r="G39" t="s" s="0">
         <v>181</v>
       </c>
-      <c r="C39" t="s" s="0">
-        <v>182</v>
-      </c>
-      <c r="D39" t="s" s="0">
-        <v>183</v>
-      </c>
-      <c r="E39" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F39" t="s" s="0">
-        <v>174</v>
-      </c>
-      <c r="G39" t="s" s="0">
-        <v>179</v>
-      </c>
       <c r="H39" t="s" s="0">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B40" t="s" s="0">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C40" t="s" s="0">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D40" t="s" s="0">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E40" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F40" t="s" s="0">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G40" t="s" s="0">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H40" t="s" s="0">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B41" t="s" s="0">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C41" t="s" s="0">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D41" t="s" s="0">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E41" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F41" t="s" s="0">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G41" t="s" s="0">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H41" t="s" s="0">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B42" t="s" s="0">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C42" t="s" s="0">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D42" t="s" s="0">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E42" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F42" t="s" s="0">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G42" t="s" s="0">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="H42" t="s" s="0">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B43" t="s" s="0">
+        <v>200</v>
+      </c>
+      <c r="C43" t="s" s="0">
+        <v>201</v>
+      </c>
+      <c r="D43" t="s" s="0">
+        <v>202</v>
+      </c>
+      <c r="E43" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F43" t="s" s="0">
+        <v>176</v>
+      </c>
+      <c r="G43" t="s" s="0">
         <v>198</v>
       </c>
-      <c r="C43" t="s" s="0">
-        <v>199</v>
-      </c>
-      <c r="D43" t="s" s="0">
-        <v>200</v>
-      </c>
-      <c r="E43" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F43" t="s" s="0">
-        <v>174</v>
-      </c>
-      <c r="G43" t="s" s="0">
-        <v>196</v>
-      </c>
       <c r="H43" t="s" s="0">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B44" t="s" s="0">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C44" t="s" s="0">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D44" t="s" s="0">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E44" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F44" t="s" s="0">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G44" t="s" s="0">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="H44" t="s" s="0">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B45" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="C45" t="s" s="0">
+        <v>210</v>
+      </c>
+      <c r="D45" t="s" s="0">
+        <v>211</v>
+      </c>
+      <c r="E45" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F45" t="s" s="0">
         <v>207</v>
       </c>
-      <c r="C45" t="s" s="0">
-        <v>208</v>
-      </c>
-      <c r="D45" t="s" s="0">
-        <v>209</v>
-      </c>
-      <c r="E45" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F45" t="s" s="0">
-        <v>205</v>
-      </c>
       <c r="G45" t="s" s="0">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="H45" t="s" s="0">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B46" t="s" s="0">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C46" t="s" s="0">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D46" t="s" s="0">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E46" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F46" t="s" s="0">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G46" t="s" s="0">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="H46" t="s" s="0">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B47" t="s" s="0">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C47" t="s" s="0">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D47" t="s" s="0">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E47" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F47" t="s" s="0">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G47" t="s" s="0">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H47" t="s" s="0">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B48" t="s" s="0">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C48" t="s" s="0">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D48" t="s" s="0">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E48" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F48" t="s" s="0">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="G48" t="s" s="0">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H48" t="s" s="0">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B49" t="s" s="0">
+        <v>228</v>
+      </c>
+      <c r="C49" t="s" s="0">
+        <v>229</v>
+      </c>
+      <c r="D49" t="s" s="0">
+        <v>230</v>
+      </c>
+      <c r="E49" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F49" t="s" s="0">
+        <v>231</v>
+      </c>
+      <c r="G49" t="s" s="0">
         <v>226</v>
       </c>
-      <c r="C49" t="s" s="0">
-        <v>227</v>
-      </c>
-      <c r="D49" t="s" s="0">
-        <v>228</v>
-      </c>
-      <c r="E49" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F49" t="s" s="0">
-        <v>229</v>
-      </c>
-      <c r="G49" t="s" s="0">
-        <v>224</v>
-      </c>
       <c r="H49" t="s" s="0">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B50" t="s" s="0">
+        <v>233</v>
+      </c>
+      <c r="C50" t="s" s="0">
+        <v>234</v>
+      </c>
+      <c r="D50" t="s" s="0">
+        <v>235</v>
+      </c>
+      <c r="E50" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F50" t="s" s="0">
         <v>231</v>
       </c>
-      <c r="C50" t="s" s="0">
-        <v>232</v>
-      </c>
-      <c r="D50" t="s" s="0">
-        <v>233</v>
-      </c>
-      <c r="E50" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F50" t="s" s="0">
-        <v>229</v>
-      </c>
       <c r="G50" t="s" s="0">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H50" t="s" s="0">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B51" t="s" s="0">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C51" t="s" s="0">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D51" t="s" s="0">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E51" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F51" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="G51" t="s" s="0">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="H51" t="s" s="0">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B52" t="s" s="0">
+        <v>242</v>
+      </c>
+      <c r="C52" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="D52" t="s" s="0">
+        <v>244</v>
+      </c>
+      <c r="E52" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F52" t="s" s="0">
+        <v>245</v>
+      </c>
+      <c r="G52" t="s" s="0">
         <v>240</v>
       </c>
-      <c r="C52" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="D52" t="s" s="0">
-        <v>242</v>
-      </c>
-      <c r="E52" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F52" t="s" s="0">
-        <v>243</v>
-      </c>
-      <c r="G52" t="s" s="0">
-        <v>238</v>
-      </c>
       <c r="H52" t="s" s="0">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B53" t="s" s="0">
+        <v>247</v>
+      </c>
+      <c r="C53" t="s" s="0">
+        <v>248</v>
+      </c>
+      <c r="D53" t="s" s="0">
+        <v>249</v>
+      </c>
+      <c r="E53" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F53" t="s" s="0">
         <v>245</v>
       </c>
-      <c r="C53" t="s" s="0">
-        <v>246</v>
-      </c>
-      <c r="D53" t="s" s="0">
-        <v>247</v>
-      </c>
-      <c r="E53" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F53" t="s" s="0">
-        <v>243</v>
-      </c>
       <c r="G53" t="s" s="0">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="H53" t="s" s="0">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B54" t="s" s="0">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C54" t="s" s="0">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D54" t="s" s="0">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E54" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F54" t="s" s="0">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="G54" t="s" s="0">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="H54" t="s" s="0">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B55" t="s" s="0">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C55" t="s" s="0">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D55" t="s" s="0">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E55" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F55" t="s" s="0">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="G55" t="s" s="0">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="H55" t="s" s="0">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B56" t="s" s="0">
+        <v>263</v>
+      </c>
+      <c r="C56" t="s" s="0">
+        <v>264</v>
+      </c>
+      <c r="D56" t="s" s="0">
+        <v>265</v>
+      </c>
+      <c r="E56" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F56" t="s" s="0">
+        <v>266</v>
+      </c>
+      <c r="G56" t="s" s="0">
         <v>261</v>
       </c>
-      <c r="C56" t="s" s="0">
-        <v>262</v>
-      </c>
-      <c r="D56" t="s" s="0">
-        <v>263</v>
-      </c>
-      <c r="E56" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F56" t="s" s="0">
-        <v>264</v>
-      </c>
-      <c r="G56" t="s" s="0">
-        <v>259</v>
-      </c>
       <c r="H56" t="s" s="0">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B57" t="s" s="0">
+        <v>268</v>
+      </c>
+      <c r="C57" t="s" s="0">
+        <v>269</v>
+      </c>
+      <c r="D57" t="s" s="0">
+        <v>270</v>
+      </c>
+      <c r="E57" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F57" t="s" s="0">
         <v>266</v>
       </c>
-      <c r="C57" t="s" s="0">
-        <v>267</v>
-      </c>
-      <c r="D57" t="s" s="0">
-        <v>268</v>
-      </c>
-      <c r="E57" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F57" t="s" s="0">
-        <v>264</v>
-      </c>
       <c r="G57" t="s" s="0">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="H57" t="s" s="0">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B58" t="s" s="0">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C58" t="s" s="0">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D58" t="s" s="0">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E58" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F58" t="s" s="0">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G58" t="s" s="0">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="H58" t="s" s="0">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B59" t="s" s="0">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C59" t="s" s="0">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D59" t="s" s="0">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E59" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F59" t="s" s="0">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="G59" t="s" s="0">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H59" t="s" s="0">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
+        <v>281</v>
+      </c>
+      <c r="B60" t="s" s="0">
+        <v>282</v>
+      </c>
+      <c r="C60" t="s" s="0">
+        <v>283</v>
+      </c>
+      <c r="D60" t="s" s="0">
+        <v>284</v>
+      </c>
+      <c r="E60" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F60" t="s" s="0">
         <v>279</v>
       </c>
-      <c r="B60" t="s" s="0">
+      <c r="G60" t="s" s="0">
         <v>280</v>
       </c>
-      <c r="C60" t="s" s="0">
-        <v>281</v>
-      </c>
-      <c r="D60" t="s" s="0">
-        <v>282</v>
-      </c>
-      <c r="E60" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F60" t="s" s="0">
-        <v>277</v>
-      </c>
-      <c r="G60" t="s" s="0">
-        <v>278</v>
-      </c>
       <c r="H60" t="s" s="0">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B61" t="s" s="0">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C61" t="s" s="0">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D61" t="s" s="0">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E61" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F61" t="s" s="0">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="G61" t="s" s="0">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H61" t="s" s="0">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B62" t="s" s="0">
+        <v>291</v>
+      </c>
+      <c r="C62" t="s" s="0">
+        <v>292</v>
+      </c>
+      <c r="D62" t="s" s="0">
+        <v>293</v>
+      </c>
+      <c r="E62" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F62" t="s" s="0">
         <v>289</v>
       </c>
-      <c r="C62" t="s" s="0">
-        <v>290</v>
-      </c>
-      <c r="D62" t="s" s="0">
-        <v>291</v>
-      </c>
-      <c r="E62" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F62" t="s" s="0">
-        <v>287</v>
-      </c>
       <c r="G62" t="s" s="0">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H62" t="s" s="0">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B63" t="s" s="0">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C63" t="s" s="0">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D63" t="s" s="0">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E63" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F63" t="s" s="0">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="G63" t="s" s="0">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="H63" t="s" s="0">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B64" t="s" s="0">
+        <v>301</v>
+      </c>
+      <c r="C64" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="D64" t="s" s="0">
+        <v>303</v>
+      </c>
+      <c r="E64" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F64" t="s" s="0">
+        <v>304</v>
+      </c>
+      <c r="G64" t="s" s="0">
         <v>299</v>
       </c>
-      <c r="C64" t="s" s="0">
-        <v>300</v>
-      </c>
-      <c r="D64" t="s" s="0">
-        <v>301</v>
-      </c>
-      <c r="E64" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F64" t="s" s="0">
-        <v>302</v>
-      </c>
-      <c r="G64" t="s" s="0">
-        <v>297</v>
-      </c>
       <c r="H64" t="s" s="0">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B65" t="s" s="0">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C65" t="s" s="0">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D65" t="s" s="0">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E65" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F65" t="s" s="0">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="G65" t="s" s="0">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="H65" t="s" s="0">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B66" t="s" s="0">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C66" t="s" s="0">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D66" t="s" s="0">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E66" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F66" t="s" s="0">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="G66" t="s" s="0">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="H66" t="s" s="0">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B67" t="s" s="0">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C67" t="s" s="0">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D67" t="s" s="0">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E67" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F67" t="s" s="0">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="G67" t="s" s="0">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H67" t="s" s="0">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B68" t="s" s="0">
+        <v>322</v>
+      </c>
+      <c r="C68" t="s" s="0">
+        <v>323</v>
+      </c>
+      <c r="D68" t="s" s="0">
+        <v>324</v>
+      </c>
+      <c r="E68" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F68" t="s" s="0">
+        <v>325</v>
+      </c>
+      <c r="G68" t="s" s="0">
         <v>320</v>
       </c>
-      <c r="C68" t="s" s="0">
-        <v>321</v>
-      </c>
-      <c r="D68" t="s" s="0">
-        <v>322</v>
-      </c>
-      <c r="E68" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F68" t="s" s="0">
-        <v>323</v>
-      </c>
-      <c r="G68" t="s" s="0">
-        <v>318</v>
-      </c>
       <c r="H68" t="s" s="0">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B69" t="s" s="0">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C69" t="s" s="0">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D69" t="s" s="0">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E69" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F69" t="s" s="0">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="G69" t="s" s="0">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H69" t="s" s="0">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B70" t="s" s="0">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C70" t="s" s="0">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D70" t="s" s="0">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E70" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F70" t="s" s="0">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="G70" t="s" s="0">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H70" t="s" s="0">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B71" t="s" s="0">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C71" t="s" s="0">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D71" t="s" s="0">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E71" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F71" t="s" s="0">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G71" t="s" s="0">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="H71" t="s" s="0">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B72" t="s" s="0">
+        <v>343</v>
+      </c>
+      <c r="C72" t="s" s="0">
+        <v>344</v>
+      </c>
+      <c r="D72" t="s" s="0">
+        <v>345</v>
+      </c>
+      <c r="E72" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F72" t="s" s="0">
+        <v>346</v>
+      </c>
+      <c r="G72" t="s" s="0">
         <v>341</v>
       </c>
-      <c r="C72" t="s" s="0">
-        <v>342</v>
-      </c>
-      <c r="D72" t="s" s="0">
-        <v>343</v>
-      </c>
-      <c r="E72" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F72" t="s" s="0">
-        <v>344</v>
-      </c>
-      <c r="G72" t="s" s="0">
-        <v>339</v>
-      </c>
       <c r="H72" t="s" s="0">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B73" t="s" s="0">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C73" t="s" s="0">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D73" t="s" s="0">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E73" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F73" t="s" s="0">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G73" t="s" s="0">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="H73" t="s" s="0">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B74" t="s" s="0">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C74" t="s" s="0">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D74" t="s" s="0">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E74" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F74" t="s" s="0">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="G74" t="s" s="0">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="H74" t="s" s="0">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B75" t="s" s="0">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C75" t="s" s="0">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D75" t="s" s="0">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E75" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F75" t="s" s="0">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="G75" t="s" s="0">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="H75" t="s" s="0">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B76" t="s" s="0">
+        <v>365</v>
+      </c>
+      <c r="C76" t="s" s="0">
+        <v>366</v>
+      </c>
+      <c r="D76" t="s" s="0">
+        <v>367</v>
+      </c>
+      <c r="E76" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F76" t="s" s="0">
+        <v>314</v>
+      </c>
+      <c r="G76" t="s" s="0">
         <v>363</v>
       </c>
-      <c r="C76" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D76" t="s" s="0">
-        <v>365</v>
-      </c>
-      <c r="E76" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F76" t="s" s="0">
-        <v>312</v>
-      </c>
-      <c r="G76" t="s" s="0">
-        <v>361</v>
-      </c>
       <c r="H76" t="s" s="0">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B77" t="s" s="0">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C77" t="s" s="0">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D77" t="s" s="0">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E77" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F77" t="s" s="0">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="G77" t="s" s="0">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="H77" t="s" s="0">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B78" t="s" s="0">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C78" t="s" s="0">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D78" t="s" s="0">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E78" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F78" t="s" s="0">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G78" t="s" s="0">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="H78" t="s" s="0">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B79" t="s" s="0">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C79" t="s" s="0">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D79" t="s" s="0">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E79" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F79" t="s" s="0">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="G79" t="s" s="0">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="H79" t="s" s="0">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B80" t="s" s="0">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C80" t="s" s="0">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D80" t="s" s="0">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E80" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F80" t="s" s="0">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="G80" t="s" s="0">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="H80" t="s" s="0">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B81" t="s" s="0">
+        <v>390</v>
+      </c>
+      <c r="C81" t="s" s="0">
+        <v>391</v>
+      </c>
+      <c r="D81" t="s" s="0">
+        <v>392</v>
+      </c>
+      <c r="E81" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F81" t="s" s="0">
+        <v>393</v>
+      </c>
+      <c r="G81" t="s" s="0">
         <v>388</v>
       </c>
-      <c r="C81" t="s" s="0">
-        <v>389</v>
-      </c>
-      <c r="D81" t="s" s="0">
-        <v>390</v>
-      </c>
-      <c r="E81" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F81" t="s" s="0">
-        <v>391</v>
-      </c>
-      <c r="G81" t="s" s="0">
-        <v>386</v>
-      </c>
       <c r="H81" t="s" s="0">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B82" t="s" s="0">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C82" t="s" s="0">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D82" t="s" s="0">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E82" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F82" t="s" s="0">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="G82" t="s" s="0">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="H82" t="s" s="0">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B83" t="s" s="0">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C83" t="s" s="0">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D83" t="s" s="0">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E83" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F83" t="s" s="0">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="G83" t="s" s="0">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="H83" t="s" s="0">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
+        <v>405</v>
+      </c>
+      <c r="B84" t="s" s="0">
+        <v>406</v>
+      </c>
+      <c r="C84" t="s" s="0">
+        <v>407</v>
+      </c>
+      <c r="D84" t="s" s="0">
+        <v>408</v>
+      </c>
+      <c r="E84" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F84" t="s" s="0">
         <v>403</v>
       </c>
-      <c r="B84" t="s" s="0">
+      <c r="G84" t="s" s="0">
         <v>404</v>
       </c>
-      <c r="C84" t="s" s="0">
-        <v>405</v>
-      </c>
-      <c r="D84" t="s" s="0">
-        <v>406</v>
-      </c>
-      <c r="E84" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F84" t="s" s="0">
-        <v>401</v>
-      </c>
-      <c r="G84" t="s" s="0">
-        <v>402</v>
-      </c>
       <c r="H84" t="s" s="0">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B85" t="s" s="0">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C85" t="s" s="0">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D85" t="s" s="0">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E85" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F85" t="s" s="0">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="G85" t="s" s="0">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="H85" t="s" s="0">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="0">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B86" t="s" s="0">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C86" t="s" s="0">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D86" t="s" s="0">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E86" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F86" t="s" s="0">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="G86" t="s" s="0">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="H86" t="s" s="0">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="0">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B87" t="s" s="0">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C87" t="s" s="0">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D87" t="s" s="0">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E87" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F87" t="s" s="0">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="G87" t="s" s="0">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="H87" t="s" s="0">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="0">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B88" t="s" s="0">
+        <v>426</v>
+      </c>
+      <c r="C88" t="s" s="0">
+        <v>427</v>
+      </c>
+      <c r="D88" t="s" s="0">
+        <v>428</v>
+      </c>
+      <c r="E88" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F88" t="s" s="0">
+        <v>429</v>
+      </c>
+      <c r="G88" t="s" s="0">
         <v>424</v>
       </c>
-      <c r="C88" t="s" s="0">
-        <v>425</v>
-      </c>
-      <c r="D88" t="s" s="0">
-        <v>426</v>
-      </c>
-      <c r="E88" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F88" t="s" s="0">
-        <v>427</v>
-      </c>
-      <c r="G88" t="s" s="0">
-        <v>422</v>
-      </c>
       <c r="H88" t="s" s="0">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="0">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B89" t="s" s="0">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C89" t="s" s="0">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D89" t="s" s="0">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E89" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F89" t="s" s="0">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G89" t="s" s="0">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="H89" t="s" s="0">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="0">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B90" t="s" s="0">
+        <v>436</v>
+      </c>
+      <c r="C90" t="s" s="0">
+        <v>437</v>
+      </c>
+      <c r="D90" t="s" s="0">
+        <v>438</v>
+      </c>
+      <c r="E90" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F90" t="s" s="0">
         <v>434</v>
       </c>
-      <c r="C90" t="s" s="0">
-        <v>435</v>
-      </c>
-      <c r="D90" t="s" s="0">
-        <v>436</v>
-      </c>
-      <c r="E90" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F90" t="s" s="0">
-        <v>432</v>
-      </c>
       <c r="G90" t="s" s="0">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="H90" t="s" s="0">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="0">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B91" t="s" s="0">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C91" t="s" s="0">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D91" t="s" s="0">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E91" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F91" t="s" s="0">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G91" t="s" s="0">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="H91" t="s" s="0">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="0">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B92" t="s" s="0">
+        <v>445</v>
+      </c>
+      <c r="C92" t="s" s="0">
+        <v>446</v>
+      </c>
+      <c r="D92" t="s" s="0">
+        <v>447</v>
+      </c>
+      <c r="E92" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F92" t="s" s="0">
+        <v>434</v>
+      </c>
+      <c r="G92" t="s" s="0">
         <v>443</v>
       </c>
-      <c r="C92" t="s" s="0">
-        <v>444</v>
-      </c>
-      <c r="D92" t="s" s="0">
-        <v>445</v>
-      </c>
-      <c r="E92" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F92" t="s" s="0">
-        <v>432</v>
-      </c>
-      <c r="G92" t="s" s="0">
-        <v>441</v>
-      </c>
       <c r="H92" t="s" s="0">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="0">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B93" t="s" s="0">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C93" t="s" s="0">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D93" t="s" s="0">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E93" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F93" t="s" s="0">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G93" t="s" s="0">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="H93" t="s" s="0">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="0">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B94" t="s" s="0">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C94" t="s" s="0">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D94" t="s" s="0">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E94" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F94" t="s" s="0">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G94" t="s" s="0">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="H94" t="s" s="0">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="0">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B95" t="s" s="0">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C95" t="s" s="0">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="D95" t="s" s="0">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E95" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F95" t="s" s="0">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G95" t="s" s="0">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="H95" t="s" s="0">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="0">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B96" t="s" s="0">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C96" t="s" s="0">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="D96" t="s" s="0">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="E96" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F96" t="s" s="0">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G96" t="s" s="0">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="H96" t="s" s="0">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="0">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B97" t="s" s="0">
+        <v>466</v>
+      </c>
+      <c r="C97" t="s" s="0">
+        <v>467</v>
+      </c>
+      <c r="D97" t="s" s="0">
+        <v>468</v>
+      </c>
+      <c r="E97" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F97" t="s" s="0">
+        <v>434</v>
+      </c>
+      <c r="G97" t="s" s="0">
         <v>464</v>
       </c>
-      <c r="C97" t="s" s="0">
-        <v>465</v>
-      </c>
-      <c r="D97" t="s" s="0">
-        <v>466</v>
-      </c>
-      <c r="E97" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F97" t="s" s="0">
-        <v>432</v>
-      </c>
-      <c r="G97" t="s" s="0">
-        <v>462</v>
-      </c>
       <c r="H97" t="s" s="0">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="0">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B98" t="s" s="0">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C98" t="s" s="0">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D98" t="s" s="0">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E98" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F98" t="s" s="0">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G98" t="s" s="0">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="H98" t="s" s="0">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="0">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B99" t="s" s="0">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C99" t="s" s="0">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="D99" t="s" s="0">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E99" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F99" t="s" s="0">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G99" t="s" s="0">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="H99" t="s" s="0">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="0">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B100" t="s" s="0">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C100" t="s" s="0">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="D100" t="s" s="0">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E100" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F100" t="s" s="0">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G100" t="s" s="0">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="H100" t="s" s="0">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="0">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B101" t="s" s="0">
+        <v>483</v>
+      </c>
+      <c r="C101" t="s" s="0">
+        <v>484</v>
+      </c>
+      <c r="D101" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="E101" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F101" t="s" s="0">
+        <v>434</v>
+      </c>
+      <c r="G101" t="s" s="0">
         <v>481</v>
       </c>
-      <c r="C101" t="s" s="0">
-        <v>482</v>
-      </c>
-      <c r="D101" t="s" s="0">
-        <v>483</v>
-      </c>
-      <c r="E101" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F101" t="s" s="0">
-        <v>432</v>
-      </c>
-      <c r="G101" t="s" s="0">
-        <v>479</v>
-      </c>
       <c r="H101" t="s" s="0">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="0">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B102" t="s" s="0">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C102" t="s" s="0">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="D102" t="s" s="0">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="E102" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F102" t="s" s="0">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G102" t="s" s="0">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="H102" t="s" s="0">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="0">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B103" t="s" s="0">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C103" t="s" s="0">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="D103" t="s" s="0">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E103" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F103" t="s" s="0">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="G103" t="s" s="0">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="H103" t="s" s="0">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="0">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B104" t="s" s="0">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C104" t="s" s="0">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="D104" t="s" s="0">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="E104" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F104" t="s" s="0">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="G104" t="s" s="0">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="H104" t="s" s="0">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="0">
+        <v>502</v>
+      </c>
+      <c r="B105" t="s" s="0">
+        <v>503</v>
+      </c>
+      <c r="C105" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D105" t="s" s="0">
+        <v>505</v>
+      </c>
+      <c r="E105" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F105" t="s" s="0">
         <v>500</v>
       </c>
-      <c r="B105" t="s" s="0">
+      <c r="G105" t="s" s="0">
         <v>501</v>
       </c>
-      <c r="C105" t="s" s="0">
-        <v>502</v>
-      </c>
-      <c r="D105" t="s" s="0">
-        <v>503</v>
-      </c>
-      <c r="E105" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F105" t="s" s="0">
-        <v>498</v>
-      </c>
-      <c r="G105" t="s" s="0">
-        <v>499</v>
-      </c>
       <c r="H105" t="s" s="0">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="0">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B106" t="s" s="0">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C106" t="s" s="0">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="D106" t="s" s="0">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="E106" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F106" t="s" s="0">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="G106" t="s" s="0">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="H106" t="s" s="0">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="0">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B107" t="s" s="0">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C107" t="s" s="0">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="D107" t="s" s="0">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="E107" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F107" t="s" s="0">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="G107" t="s" s="0">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="H107" t="s" s="0">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="0">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B108" t="s" s="0">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C108" t="s" s="0">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D108" t="s" s="0">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E108" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F108" t="s" s="0">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="G108" t="s" s="0">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="H108" t="s" s="0">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="0">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B109" t="s" s="0">
+        <v>520</v>
+      </c>
+      <c r="C109" t="s" s="0">
+        <v>521</v>
+      </c>
+      <c r="D109" t="s" s="0">
+        <v>522</v>
+      </c>
+      <c r="E109" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F109" t="s" s="0">
+        <v>500</v>
+      </c>
+      <c r="G109" t="s" s="0">
         <v>518</v>
       </c>
-      <c r="C109" t="s" s="0">
-        <v>519</v>
-      </c>
-      <c r="D109" t="s" s="0">
-        <v>520</v>
-      </c>
-      <c r="E109" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F109" t="s" s="0">
-        <v>498</v>
-      </c>
-      <c r="G109" t="s" s="0">
-        <v>516</v>
-      </c>
       <c r="H109" t="s" s="0">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="0">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B110" t="s" s="0">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C110" t="s" s="0">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="D110" t="s" s="0">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E110" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F110" t="s" s="0">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="G110" t="s" s="0">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="H110" t="s" s="0">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="0">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B111" t="s" s="0">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C111" t="s" s="0">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="D111" t="s" s="0">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="E111" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F111" t="s" s="0">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="G111" t="s" s="0">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="H111" t="s" s="0">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="0">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B112" t="s" s="0">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C112" t="s" s="0">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D112" t="s" s="0">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="E112" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F112" t="s" s="0">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="G112" t="s" s="0">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="H112" t="s" s="0">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="0">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B113" t="s" s="0">
+        <v>537</v>
+      </c>
+      <c r="C113" t="s" s="0">
+        <v>538</v>
+      </c>
+      <c r="D113" t="s" s="0">
+        <v>539</v>
+      </c>
+      <c r="E113" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F113" t="s" s="0">
+        <v>500</v>
+      </c>
+      <c r="G113" t="s" s="0">
         <v>535</v>
       </c>
-      <c r="C113" t="s" s="0">
-        <v>536</v>
-      </c>
-      <c r="D113" t="s" s="0">
-        <v>537</v>
-      </c>
-      <c r="E113" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F113" t="s" s="0">
-        <v>498</v>
-      </c>
-      <c r="G113" t="s" s="0">
-        <v>533</v>
-      </c>
       <c r="H113" t="s" s="0">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="0">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B114" t="s" s="0">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C114" t="s" s="0">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="D114" t="s" s="0">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="E114" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F114" t="s" s="0">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="G114" t="s" s="0">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="H114" t="s" s="0">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="0">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B115" t="s" s="0">
+        <v>547</v>
+      </c>
+      <c r="C115" t="s" s="0">
+        <v>548</v>
+      </c>
+      <c r="D115" t="s" s="0">
+        <v>549</v>
+      </c>
+      <c r="E115" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F115" t="s" s="0">
+        <v>550</v>
+      </c>
+      <c r="G115" t="s" s="0">
         <v>545</v>
       </c>
-      <c r="C115" t="s" s="0">
-        <v>546</v>
-      </c>
-      <c r="D115" t="s" s="0">
-        <v>547</v>
-      </c>
-      <c r="E115" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F115" t="s" s="0">
-        <v>548</v>
-      </c>
-      <c r="G115" t="s" s="0">
-        <v>543</v>
-      </c>
       <c r="H115" t="s" s="0">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="0">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B116" t="s" s="0">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C116" t="s" s="0">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="D116" t="s" s="0">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E116" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F116" t="s" s="0">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="G116" t="s" s="0">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="H116" t="s" s="0">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s" s="0">
+        <v>557</v>
+      </c>
+      <c r="B117" t="s" s="0">
+        <v>558</v>
+      </c>
+      <c r="C117" t="s" s="0">
+        <v>559</v>
+      </c>
+      <c r="D117" t="s" s="0">
+        <v>560</v>
+      </c>
+      <c r="E117" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F117" t="s" s="0">
         <v>555</v>
       </c>
-      <c r="B117" t="s" s="0">
+      <c r="G117" t="s" s="0">
         <v>556</v>
       </c>
-      <c r="C117" t="s" s="0">
-        <v>557</v>
-      </c>
-      <c r="D117" t="s" s="0">
-        <v>558</v>
-      </c>
-      <c r="E117" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F117" t="s" s="0">
-        <v>553</v>
-      </c>
-      <c r="G117" t="s" s="0">
-        <v>554</v>
-      </c>
       <c r="H117" t="s" s="0">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="0">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B118" t="s" s="0">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C118" t="s" s="0">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="D118" t="s" s="0">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="E118" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F118" t="s" s="0">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="G118" t="s" s="0">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="H118" t="s" s="0">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="0">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B119" t="s" s="0">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C119" t="s" s="0">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="D119" t="s" s="0">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="E119" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F119" t="s" s="0">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="G119" t="s" s="0">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="H119" t="s" s="0">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s" s="0">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B120" t="s" s="0">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C120" t="s" s="0">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="D120" t="s" s="0">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="E120" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F120" t="s" s="0">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="G120" t="s" s="0">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="H120" t="s" s="0">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="0">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B121" t="s" s="0">
+        <v>575</v>
+      </c>
+      <c r="C121" t="s" s="0">
+        <v>576</v>
+      </c>
+      <c r="D121" t="s" s="0">
+        <v>577</v>
+      </c>
+      <c r="E121" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F121" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="G121" t="s" s="0">
         <v>573</v>
       </c>
-      <c r="C121" t="s" s="0">
-        <v>574</v>
-      </c>
-      <c r="D121" t="s" s="0">
-        <v>575</v>
-      </c>
-      <c r="E121" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F121" t="s" s="0">
-        <v>553</v>
-      </c>
-      <c r="G121" t="s" s="0">
-        <v>571</v>
-      </c>
       <c r="H121" t="s" s="0">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="0">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B122" t="s" s="0">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C122" t="s" s="0">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="D122" t="s" s="0">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="E122" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F122" t="s" s="0">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="G122" t="s" s="0">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="H122" t="s" s="0">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="0">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B123" t="s" s="0">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C123" t="s" s="0">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="D123" t="s" s="0">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="E123" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F123" t="s" s="0">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="G123" t="s" s="0">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="H123" t="s" s="0">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="0">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B124" t="s" s="0">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C124" t="s" s="0">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="D124" t="s" s="0">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="E124" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F124" t="s" s="0">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="G124" t="s" s="0">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="H124" t="s" s="0">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="0">
+        <v>592</v>
+      </c>
+      <c r="B125" t="s" s="0">
+        <v>593</v>
+      </c>
+      <c r="C125" t="s" s="0">
+        <v>594</v>
+      </c>
+      <c r="D125" t="s" s="0">
+        <v>595</v>
+      </c>
+      <c r="E125" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F125" t="s" s="0">
         <v>590</v>
       </c>
-      <c r="B125" t="s" s="0">
+      <c r="G125" t="s" s="0">
         <v>591</v>
       </c>
-      <c r="C125" t="s" s="0">
-        <v>592</v>
-      </c>
-      <c r="D125" t="s" s="0">
-        <v>593</v>
-      </c>
-      <c r="E125" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F125" t="s" s="0">
-        <v>588</v>
-      </c>
-      <c r="G125" t="s" s="0">
-        <v>589</v>
-      </c>
       <c r="H125" t="s" s="0">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s" s="0">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B126" t="s" s="0">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C126" t="s" s="0">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="D126" t="s" s="0">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="E126" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F126" t="s" s="0">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="G126" t="s" s="0">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="H126" t="s" s="0">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s" s="0">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="B127" t="s" s="0">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="C127" t="s" s="0">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="D127" t="s" s="0">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E127" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F127" t="s" s="0">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="G127" t="s" s="0">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="H127" t="s" s="0">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s" s="0">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B128" t="s" s="0">
+        <v>606</v>
+      </c>
+      <c r="C128" t="s" s="0">
+        <v>607</v>
+      </c>
+      <c r="D128" t="s" s="0">
+        <v>608</v>
+      </c>
+      <c r="E128" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F128" t="s" s="0">
         <v>604</v>
       </c>
-      <c r="C128" t="s" s="0">
-        <v>605</v>
-      </c>
-      <c r="D128" t="s" s="0">
-        <v>606</v>
-      </c>
-      <c r="E128" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F128" t="s" s="0">
-        <v>602</v>
-      </c>
       <c r="G128" t="s" s="0">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="H128" t="s" s="0">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s" s="0">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B129" t="s" s="0">
+        <v>611</v>
+      </c>
+      <c r="C129" t="s" s="0">
+        <v>612</v>
+      </c>
+      <c r="D129" t="s" s="0">
+        <v>613</v>
+      </c>
+      <c r="E129" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F129" t="s" s="0">
+        <v>604</v>
+      </c>
+      <c r="G129" t="s" s="0">
         <v>609</v>
       </c>
-      <c r="C129" t="s" s="0">
-        <v>610</v>
-      </c>
-      <c r="D129" t="s" s="0">
-        <v>611</v>
-      </c>
-      <c r="E129" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F129" t="s" s="0">
-        <v>602</v>
-      </c>
-      <c r="G129" t="s" s="0">
-        <v>607</v>
-      </c>
       <c r="H129" t="s" s="0">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s" s="0">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="B130" t="s" s="0">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C130" t="s" s="0">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="D130" t="s" s="0">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="E130" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F130" t="s" s="0">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="G130" t="s" s="0">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="H130" t="s" s="0">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s" s="0">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B131" t="s" s="0">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C131" t="s" s="0">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="D131" t="s" s="0">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="E131" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F131" t="s" s="0">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="G131" t="s" s="0">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="H131" t="s" s="0">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s" s="0">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B132" t="s" s="0">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C132" t="s" s="0">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="D132" t="s" s="0">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="E132" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F132" t="s" s="0">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="G132" t="s" s="0">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="H132" t="s" s="0">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s" s="0">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="B133" t="s" s="0">
+        <v>628</v>
+      </c>
+      <c r="C133" t="s" s="0">
+        <v>629</v>
+      </c>
+      <c r="D133" t="s" s="0">
+        <v>630</v>
+      </c>
+      <c r="E133" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F133" t="s" s="0">
+        <v>604</v>
+      </c>
+      <c r="G133" t="s" s="0">
         <v>626</v>
       </c>
-      <c r="C133" t="s" s="0">
-        <v>627</v>
-      </c>
-      <c r="D133" t="s" s="0">
-        <v>628</v>
-      </c>
-      <c r="E133" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F133" t="s" s="0">
-        <v>602</v>
-      </c>
-      <c r="G133" t="s" s="0">
-        <v>624</v>
-      </c>
       <c r="H133" t="s" s="0">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="0">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B134" t="s" s="0">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="C134" t="s" s="0">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="D134" t="s" s="0">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="E134" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F134" t="s" s="0">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="G134" t="s" s="0">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="H134" t="s" s="0">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s" s="0">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B135" t="s" s="0">
+        <v>637</v>
+      </c>
+      <c r="C135" t="s" s="0">
+        <v>638</v>
+      </c>
+      <c r="D135" t="s" s="0">
+        <v>639</v>
+      </c>
+      <c r="E135" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F135" t="s" s="0">
         <v>635</v>
       </c>
-      <c r="C135" t="s" s="0">
-        <v>636</v>
-      </c>
-      <c r="D135" t="s" s="0">
-        <v>637</v>
-      </c>
-      <c r="E135" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F135" t="s" s="0">
-        <v>633</v>
-      </c>
       <c r="G135" t="s" s="0">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="H135" t="s" s="0">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s" s="0">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="B136" t="s" s="0">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="C136" t="s" s="0">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="D136" t="s" s="0">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="E136" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F136" t="s" s="0">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="G136" t="s" s="0">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="H136" t="s" s="0">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s" s="0">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="B137" t="s" s="0">
+        <v>646</v>
+      </c>
+      <c r="C137" t="s" s="0">
+        <v>647</v>
+      </c>
+      <c r="D137" t="s" s="0">
+        <v>648</v>
+      </c>
+      <c r="E137" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F137" t="s" s="0">
+        <v>635</v>
+      </c>
+      <c r="G137" t="s" s="0">
         <v>644</v>
       </c>
-      <c r="C137" t="s" s="0">
-        <v>645</v>
-      </c>
-      <c r="D137" t="s" s="0">
-        <v>646</v>
-      </c>
-      <c r="E137" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F137" t="s" s="0">
-        <v>633</v>
-      </c>
-      <c r="G137" t="s" s="0">
-        <v>642</v>
-      </c>
       <c r="H137" t="s" s="0">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s" s="0">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B138" t="s" s="0">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C138" t="s" s="0">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="D138" t="s" s="0">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="E138" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F138" t="s" s="0">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="G138" t="s" s="0">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="H138" t="s" s="0">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s" s="0">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B139" t="s" s="0">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="C139" t="s" s="0">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="D139" t="s" s="0">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="E139" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F139" t="s" s="0">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="G139" t="s" s="0">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="H139" t="s" s="0">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s" s="0">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B140" t="s" s="0">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="C140" t="s" s="0">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="D140" t="s" s="0">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="E140" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F140" t="s" s="0">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="G140" t="s" s="0">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="H140" t="s" s="0">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s" s="0">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="B141" t="s" s="0">
+        <v>667</v>
+      </c>
+      <c r="C141" t="s" s="0">
+        <v>668</v>
+      </c>
+      <c r="D141" t="s" s="0">
+        <v>669</v>
+      </c>
+      <c r="E141" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F141" t="s" s="0">
+        <v>670</v>
+      </c>
+      <c r="G141" t="s" s="0">
         <v>665</v>
       </c>
-      <c r="C141" t="s" s="0">
-        <v>666</v>
-      </c>
-      <c r="D141" t="s" s="0">
-        <v>667</v>
-      </c>
-      <c r="E141" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F141" t="s" s="0">
-        <v>668</v>
-      </c>
-      <c r="G141" t="s" s="0">
-        <v>663</v>
-      </c>
       <c r="H141" t="s" s="0">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s" s="0">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="B142" t="s" s="0">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="C142" t="s" s="0">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="D142" t="s" s="0">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="E142" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F142" t="s" s="0">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="G142" t="s" s="0">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="H142" t="s" s="0">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s" s="0">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="B143" t="s" s="0">
+        <v>678</v>
+      </c>
+      <c r="C143" t="s" s="0">
+        <v>679</v>
+      </c>
+      <c r="D143" t="s" s="0">
+        <v>680</v>
+      </c>
+      <c r="E143" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F143" t="s" s="0">
+        <v>681</v>
+      </c>
+      <c r="G143" t="s" s="0">
         <v>676</v>
       </c>
-      <c r="C143" t="s" s="0">
-        <v>677</v>
-      </c>
-      <c r="D143" t="s" s="0">
-        <v>678</v>
-      </c>
-      <c r="E143" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F143" t="s" s="0">
-        <v>679</v>
-      </c>
-      <c r="G143" t="s" s="0">
-        <v>674</v>
-      </c>
       <c r="H143" t="s" s="0">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s" s="0">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="B144" t="s" s="0">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="C144" t="s" s="0">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D144" t="s" s="0">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="E144" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F144" t="s" s="0">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="G144" t="s" s="0">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="H144" t="s" s="0">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s" s="0">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="B145" t="s" s="0">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="C145" t="s" s="0">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="D145" t="s" s="0">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="E145" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F145" t="s" s="0">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="G145" t="s" s="0">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="H145" t="s" s="0">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s" s="0">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="B146" t="s" s="0">
+        <v>694</v>
+      </c>
+      <c r="C146" t="s" s="0">
+        <v>695</v>
+      </c>
+      <c r="D146" t="s" s="0">
+        <v>696</v>
+      </c>
+      <c r="E146" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F146" t="s" s="0">
+        <v>697</v>
+      </c>
+      <c r="G146" t="s" s="0">
         <v>692</v>
       </c>
-      <c r="C146" t="s" s="0">
-        <v>693</v>
-      </c>
-      <c r="D146" t="s" s="0">
-        <v>694</v>
-      </c>
-      <c r="E146" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F146" t="s" s="0">
-        <v>695</v>
-      </c>
-      <c r="G146" t="s" s="0">
-        <v>690</v>
-      </c>
       <c r="H146" t="s" s="0">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s" s="0">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="B147" t="s" s="0">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="C147" t="s" s="0">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="D147" t="s" s="0">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="E147" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F147" t="s" s="0">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G147" t="s" s="0">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="H147" t="s" s="0">
-        <v>700</v>
+        <v>702</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s" s="0">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="B148" t="s" s="0">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="C148" t="s" s="0">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="D148" t="s" s="0">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="E148" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F148" t="s" s="0">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="G148" t="s" s="0">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="H148" t="s" s="0">
-        <v>705</v>
+        <v>707</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s" s="0">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B149" t="s" s="0">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="C149" t="s" s="0">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="D149" t="s" s="0">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="E149" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F149" t="s" s="0">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="G149" t="s" s="0">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="H149" t="s" s="0">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s" s="0">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="B150" t="s" s="0">
+        <v>714</v>
+      </c>
+      <c r="C150" t="s" s="0">
+        <v>715</v>
+      </c>
+      <c r="D150" t="s" s="0">
+        <v>716</v>
+      </c>
+      <c r="E150" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F150" t="s" s="0">
+        <v>500</v>
+      </c>
+      <c r="G150" t="s" s="0">
         <v>712</v>
       </c>
-      <c r="C150" t="s" s="0">
-        <v>713</v>
-      </c>
-      <c r="D150" t="s" s="0">
-        <v>714</v>
-      </c>
-      <c r="E150" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F150" t="s" s="0">
-        <v>498</v>
-      </c>
-      <c r="G150" t="s" s="0">
-        <v>710</v>
-      </c>
       <c r="H150" t="s" s="0">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s" s="0">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="B151" t="s" s="0">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="C151" t="s" s="0">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="D151" t="s" s="0">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="E151" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F151" t="s" s="0">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="G151" t="s" s="0">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="H151" t="s" s="0">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s" s="0">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="B152" t="s" s="0">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="C152" t="s" s="0">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="D152" t="s" s="0">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="E152" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F152" t="s" s="0">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="G152" t="s" s="0">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="H152" t="s" s="0">
-        <v>723</v>
+        <v>725</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s" s="0">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="B153" t="s" s="0">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="C153" t="s" s="0">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="D153" t="s" s="0">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="E153" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F153" t="s" s="0">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="G153" t="s" s="0">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="H153" t="s" s="0">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s" s="0">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="B154" t="s" s="0">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="C154" t="s" s="0">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="D154" t="s" s="0">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E154" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F154" t="s" s="0">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="G154" t="s" s="0">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="H154" t="s" s="0">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s" s="0">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="B155" t="s" s="0">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="C155" t="s" s="0">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="D155" t="s" s="0">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="E155" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F155" t="s" s="0">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="G155" t="s" s="0">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="H155" t="s" s="0">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s" s="0">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="B156" t="s" s="0">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="C156" t="s" s="0">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="D156" t="s" s="0">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="E156" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F156" t="s" s="0">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="G156" t="s" s="0">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="H156" t="s" s="0">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s" s="0">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="B157" t="s" s="0">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="C157" t="s" s="0">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="D157" t="s" s="0">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="E157" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F157" t="s" s="0">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="G157" t="s" s="0">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="H157" t="s" s="0">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s" s="0">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="B158" t="s" s="0">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="C158" t="s" s="0">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="D158" t="s" s="0">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="E158" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F158" t="s" s="0">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="G158" t="s" s="0">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="H158" t="s" s="0">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s" s="0">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="B159" t="s" s="0">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="C159" t="s" s="0">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="D159" t="s" s="0">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="E159" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F159" t="s" s="0">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="G159" t="s" s="0">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="H159" t="s" s="0">
-        <v>753</v>
+        <v>755</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s" s="0">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="B160" t="s" s="0">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="C160" t="s" s="0">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="D160" t="s" s="0">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="E160" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F160" t="s" s="0">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="G160" t="s" s="0">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="H160" t="s" s="0">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s" s="0">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="B161" t="s" s="0">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="C161" t="s" s="0">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="D161" t="s" s="0">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="E161" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F161" t="s" s="0">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="G161" t="s" s="0">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="H161" t="s" s="0">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s" s="0">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="B162" t="s" s="0">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="C162" t="s" s="0">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="D162" t="s" s="0">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="E162" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F162" t="s" s="0">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="G162" t="s" s="0">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="H162" t="s" s="0">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s" s="0">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="B163" t="s" s="0">
+        <v>771</v>
+      </c>
+      <c r="C163" t="s" s="0">
+        <v>772</v>
+      </c>
+      <c r="D163" t="s" s="0">
+        <v>773</v>
+      </c>
+      <c r="E163" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F163" t="s" s="0">
         <v>769</v>
       </c>
-      <c r="C163" t="s" s="0">
-        <v>770</v>
-      </c>
-      <c r="D163" t="s" s="0">
-        <v>771</v>
-      </c>
-      <c r="E163" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F163" t="s" s="0">
-        <v>767</v>
-      </c>
       <c r="G163" t="s" s="0">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="H163" t="s" s="0">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s" s="0">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="B164" t="s" s="0">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="C164" t="s" s="0">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="D164" t="s" s="0">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="E164" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F164" t="s" s="0">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="G164" t="s" s="0">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="H164" t="s" s="0">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s" s="0">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B165" t="s" s="0">
+        <v>780</v>
+      </c>
+      <c r="C165" t="s" s="0">
+        <v>781</v>
+      </c>
+      <c r="D165" t="s" s="0">
+        <v>782</v>
+      </c>
+      <c r="E165" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F165" t="s" s="0">
         <v>778</v>
       </c>
-      <c r="C165" t="s" s="0">
-        <v>779</v>
-      </c>
-      <c r="D165" t="s" s="0">
-        <v>780</v>
-      </c>
-      <c r="E165" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F165" t="s" s="0">
-        <v>776</v>
-      </c>
       <c r="G165" t="s" s="0">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="H165" t="s" s="0">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s" s="0">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="B166" t="s" s="0">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="C166" t="s" s="0">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="D166" t="s" s="0">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="E166" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F166" t="s" s="0">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="G166" t="s" s="0">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="H166" t="s" s="0">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s" s="0">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="B167" t="s" s="0">
+        <v>789</v>
+      </c>
+      <c r="C167" t="s" s="0">
+        <v>790</v>
+      </c>
+      <c r="D167" t="s" s="0">
+        <v>791</v>
+      </c>
+      <c r="E167" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F167" t="s" s="0">
         <v>787</v>
       </c>
-      <c r="C167" t="s" s="0">
-        <v>788</v>
-      </c>
-      <c r="D167" t="s" s="0">
-        <v>789</v>
-      </c>
-      <c r="E167" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F167" t="s" s="0">
-        <v>785</v>
-      </c>
       <c r="G167" t="s" s="0">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="H167" t="s" s="0">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s" s="0">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="B168" t="s" s="0">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="C168" t="s" s="0">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D168" t="s" s="0">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="E168" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F168" t="s" s="0">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="G168" t="s" s="0">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="H168" t="s" s="0">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s" s="0">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="B169" t="s" s="0">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="C169" t="s" s="0">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="D169" t="s" s="0">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="E169" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F169" t="s" s="0">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="G169" t="s" s="0">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="H169" t="s" s="0">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s" s="0">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="B170" t="s" s="0">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="C170" t="s" s="0">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="D170" t="s" s="0">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="E170" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F170" t="s" s="0">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="G170" t="s" s="0">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="H170" t="s" s="0">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s" s="0">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="B171" t="s" s="0">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="C171" t="s" s="0">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="D171" t="s" s="0">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="E171" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F171" t="s" s="0">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="G171" t="s" s="0">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="H171" t="s" s="0">
-        <v>810</v>
+        <v>812</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s" s="0">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="B172" t="s" s="0">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="C172" t="s" s="0">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="D172" t="s" s="0">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="E172" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F172" t="s" s="0">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="G172" t="s" s="0">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="H172" t="s" s="0">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s" s="0">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="B173" t="s" s="0">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="C173" t="s" s="0">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="D173" t="s" s="0">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="E173" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F173" t="s" s="0">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="G173" t="s" s="0">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="H173" t="s" s="0">
-        <v>821</v>
+        <v>823</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s" s="0">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="B174" t="s" s="0">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="C174" t="s" s="0">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="D174" t="s" s="0">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="E174" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F174" t="s" s="0">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="G174" t="s" s="0">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="H174" t="s" s="0">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s" s="0">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="B175" t="s" s="0">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="C175" t="s" s="0">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="D175" t="s" s="0">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="E175" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F175" t="s" s="0">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="G175" t="s" s="0">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="H175" t="s" s="0">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s" s="0">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="B176" t="s" s="0">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="C176" t="s" s="0">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="D176" t="s" s="0">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="E176" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F176" t="s" s="0">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="G176" t="s" s="0">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="H176" t="s" s="0">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s" s="0">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="B177" t="s" s="0">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="C177" t="s" s="0">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="D177" t="s" s="0">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="E177" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F177" t="s" s="0">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="G177" t="s" s="0">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="H177" t="s" s="0">
-        <v>840</v>
+        <v>842</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s" s="0">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="B178" t="s" s="0">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="C178" t="s" s="0">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="D178" t="s" s="0">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="E178" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F178" t="s" s="0">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="G178" t="s" s="0">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="H178" t="s" s="0">
-        <v>846</v>
+        <v>848</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s" s="0">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="B179" t="s" s="0">
+        <v>850</v>
+      </c>
+      <c r="C179" t="s" s="0">
+        <v>851</v>
+      </c>
+      <c r="D179" t="s" s="0">
+        <v>852</v>
+      </c>
+      <c r="E179" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F179" t="s" s="0">
+        <v>853</v>
+      </c>
+      <c r="G179" t="s" s="0">
         <v>848</v>
       </c>
-      <c r="C179" t="s" s="0">
-        <v>849</v>
-      </c>
-      <c r="D179" t="s" s="0">
-        <v>850</v>
-      </c>
-      <c r="E179" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F179" t="s" s="0">
-        <v>851</v>
-      </c>
-      <c r="G179" t="s" s="0">
-        <v>846</v>
-      </c>
       <c r="H179" t="s" s="0">
-        <v>846</v>
+        <v>848</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s" s="0">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="B180" t="s" s="0">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="C180" t="s" s="0">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="D180" t="s" s="0">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="E180" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F180" t="s" s="0">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="G180" t="s" s="0">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="H180" t="s" s="0">
-        <v>846</v>
+        <v>848</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s" s="0">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="B181" t="s" s="0">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="C181" t="s" s="0">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="D181" t="s" s="0">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="E181" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F181" t="s" s="0">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="G181" t="s" s="0">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="H181" t="s" s="0">
-        <v>846</v>
+        <v>848</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s" s="0">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="B182" t="s" s="0">
+        <v>865</v>
+      </c>
+      <c r="C182" t="s" s="0">
+        <v>866</v>
+      </c>
+      <c r="D182" t="s" s="0">
+        <v>867</v>
+      </c>
+      <c r="E182" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F182" t="s" s="0">
         <v>863</v>
       </c>
-      <c r="C182" t="s" s="0">
-        <v>864</v>
-      </c>
-      <c r="D182" t="s" s="0">
-        <v>865</v>
-      </c>
-      <c r="E182" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F182" t="s" s="0">
-        <v>861</v>
-      </c>
       <c r="G182" t="s" s="0">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="H182" t="s" s="0">
-        <v>846</v>
+        <v>848</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s" s="0">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="B183" t="s" s="0">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="C183" t="s" s="0">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="D183" t="s" s="0">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="E183" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F183" t="s" s="0">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="G183" t="s" s="0">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="H183" t="s" s="0">
-        <v>871</v>
+        <v>873</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s" s="0">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="B184" t="s" s="0">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="C184" t="s" s="0">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="D184" t="s" s="0">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="E184" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F184" t="s" s="0">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="G184" t="s" s="0">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="H184" t="s" s="0">
-        <v>878</v>
+        <v>880</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s" s="0">
+        <v>881</v>
+      </c>
+      <c r="B185" t="s" s="0">
+        <v>882</v>
+      </c>
+      <c r="C185" t="s" s="0">
+        <v>883</v>
+      </c>
+      <c r="D185" t="s" s="0">
+        <v>884</v>
+      </c>
+      <c r="E185" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F185" t="s" s="0">
+        <v>885</v>
+      </c>
+      <c r="G185" t="s" s="0">
         <v>879</v>
       </c>
-      <c r="B185" t="s" s="0">
-        <v>880</v>
-      </c>
-      <c r="C185" t="s" s="0">
-        <v>881</v>
-      </c>
-      <c r="D185" t="s" s="0">
-        <v>882</v>
-      </c>
-      <c r="E185" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F185" t="s" s="0">
-        <v>883</v>
-      </c>
-      <c r="G185" t="s" s="0">
-        <v>877</v>
-      </c>
       <c r="H185" t="s" s="0">
-        <v>877</v>
+        <v>879</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s" s="0">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="B186" t="s" s="0">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="C186" t="s" s="0">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="D186" t="s" s="0">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="E186" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F186" t="s" s="0">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="G186" t="s" s="0">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="H186" t="s" s="0">
-        <v>877</v>
+        <v>879</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s" s="0">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B187" t="s" s="0">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="C187" t="s" s="0">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="D187" t="s" s="0">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="E187" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F187" t="s" s="0">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="G187" t="s" s="0">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="H187" t="s" s="0">
-        <v>877</v>
+        <v>879</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s" s="0">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="B188" t="s" s="0">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="C188" t="s" s="0">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="D188" t="s" s="0">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="E188" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F188" t="s" s="0">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="G188" t="s" s="0">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="H188" t="s" s="0">
-        <v>877</v>
+        <v>879</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s" s="0">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="B189" t="s" s="0">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="C189" t="s" s="0">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="D189" t="s" s="0">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="E189" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F189" t="s" s="0">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="G189" t="s" s="0">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="H189" t="s" s="0">
-        <v>900</v>
+        <v>902</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="s" s="0">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="B190" t="s" s="0">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="C190" t="s" s="0">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="D190" t="s" s="0">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="E190" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F190" t="s" s="0">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="G190" t="s" s="0">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="H190" t="s" s="0">
-        <v>906</v>
+        <v>908</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s" s="0">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="B191" t="s" s="0">
+        <v>910</v>
+      </c>
+      <c r="C191" t="s" s="0">
+        <v>911</v>
+      </c>
+      <c r="D191" t="s" s="0">
+        <v>912</v>
+      </c>
+      <c r="E191" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F191" t="s" s="0">
+        <v>913</v>
+      </c>
+      <c r="G191" t="s" s="0">
         <v>908</v>
       </c>
-      <c r="C191" t="s" s="0">
-        <v>909</v>
-      </c>
-      <c r="D191" t="s" s="0">
-        <v>910</v>
-      </c>
-      <c r="E191" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F191" t="s" s="0">
-        <v>911</v>
-      </c>
-      <c r="G191" t="s" s="0">
-        <v>906</v>
-      </c>
       <c r="H191" t="s" s="0">
-        <v>906</v>
+        <v>908</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s" s="0">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="B192" t="s" s="0">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="C192" t="s" s="0">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="D192" t="s" s="0">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="E192" t="s" s="0">
         <v>12</v>
       </c>
       <c r="F192" t="s" s="0">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="G192" t="s" s="0">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="H192" t="s" s="0">
-        <v>916</v>
+        <v>918</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s" s="0">
+        <v>919</v>
+      </c>
+      <c r="B193" t="s" s="0">
+        <v>920</v>
+      </c>
+      <c r="C193" t="s" s="0">
+        <v>921</v>
+      </c>
+      <c r="D193" t="s" s="0">
+        <v>922</v>
+      </c>
+      <c r="E193" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F193" t="s" s="0">
+        <v>923</v>
+      </c>
+      <c r="G193" t="s" s="0">
+        <v>924</v>
+      </c>
+      <c r="H193" t="s" s="0">
+        <v>924</v>
       </c>
     </row>
   </sheetData>

--- a/data/movie.xlsx
+++ b/data/movie.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1544" uniqueCount="925">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1746" uniqueCount="1116">
   <si>
     <t>movieId</t>
   </si>
@@ -20,6 +20,9 @@
     <t>sourceId</t>
   </si>
   <si>
+    <t>sourceUrl</t>
+  </si>
+  <si>
     <t>movieName</t>
   </si>
   <si>
@@ -44,6 +47,9 @@
     <t>fven32261958</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fven32261958/</t>
+  </si>
+  <si>
     <t>不存在的罪人</t>
   </si>
   <si>
@@ -59,12 +65,18 @@
     <t>2026-10-09 09:45:18</t>
   </si>
   <si>
+    <t>2026-10-20 16:15:52</t>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
     <t>foen36586020</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/foen36586020/</t>
+  </si>
+  <si>
     <t>另一個媽咪</t>
   </si>
   <si>
@@ -77,6 +89,9 @@
     <t>fsjp92458256</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fsjp92458256/</t>
+  </si>
+  <si>
     <t>角落小夥伴電影版：從天而降的雲之冒險</t>
   </si>
   <si>
@@ -89,6 +104,9 @@
     <t>fien27681354</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fien27681354/</t>
+  </si>
+  <si>
     <t>金劫任務</t>
   </si>
   <si>
@@ -101,6 +119,9 @@
     <t>fhvi34700988</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fhvi34700988/</t>
+  </si>
+  <si>
     <t>鬼入室</t>
   </si>
   <si>
@@ -110,12 +131,18 @@
     <t>2026-10-09 09:45:20</t>
   </si>
   <si>
+    <t>2026-10-20 16:15:54</t>
+  </si>
+  <si>
     <t>6</t>
   </si>
   <si>
     <t>fmcn32432312</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fmcn32432312/</t>
+  </si>
+  <si>
     <t>拾荒法師</t>
   </si>
   <si>
@@ -128,6 +155,9 @@
     <t>fhjp91776196</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fhjp91776196/</t>
+  </si>
+  <si>
     <t>鋼之鍊金術師：嘆息之丘的聖星</t>
   </si>
   <si>
@@ -137,7 +167,7 @@
     <t>2011-10-28 00:00:00</t>
   </si>
   <si>
-    <t>2026-10-19 11:26:54</t>
+    <t>2026-10-20 16:16:03</t>
   </si>
   <si>
     <t>8</t>
@@ -146,6 +176,9 @@
     <t>fhvi38132338</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fhvi38132338/</t>
+  </si>
+  <si>
     <t>驚天劫機</t>
   </si>
   <si>
@@ -158,6 +191,9 @@
     <t>fsko95970896</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fsko95970896/</t>
+  </si>
+  <si>
     <t>SB19 Wakas at Simula: The Trilogy Concert Finale In Cinemas</t>
   </si>
   <si>
@@ -170,15 +206,15 @@
     <t>2026-10-09 09:45:22</t>
   </si>
   <si>
-    <t>2026-10-19 14:37:30</t>
-  </si>
-  <si>
     <t>10</t>
   </si>
   <si>
     <t>fear30781967</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fear30781967/</t>
+  </si>
+  <si>
     <t>獨裁大明星</t>
   </si>
   <si>
@@ -191,6 +227,9 @@
     <t>fden36510056</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fden36510056/</t>
+  </si>
+  <si>
     <t>紐約藝術家的性與愛</t>
   </si>
   <si>
@@ -203,6 +242,9 @@
     <t>fnfr35519445</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fnfr35519445/</t>
+  </si>
+  <si>
     <t>週末的尼諾</t>
   </si>
   <si>
@@ -215,6 +257,9 @@
     <t>fyjp43723335</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fyjp43723335/</t>
+  </si>
+  <si>
     <t>YORUSHIKA LIVE 「盜作」</t>
   </si>
   <si>
@@ -233,6 +278,9 @@
     <t>ftjp52665974</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/ftjp52665974/</t>
+  </si>
+  <si>
     <t>一個人旅行</t>
   </si>
   <si>
@@ -245,6 +293,9 @@
     <t>fden31450459</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fden31450459/</t>
+  </si>
+  <si>
     <t>挖掘者</t>
   </si>
   <si>
@@ -260,6 +311,9 @@
     <t>fgen36415524</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fgen36415524/</t>
+  </si>
+  <si>
     <t>神鬼劫案2：偷天換日</t>
   </si>
   <si>
@@ -275,6 +329,9 @@
     <t>fhcn95992257</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fhcn95992257/</t>
+  </si>
+  <si>
     <t>人吶，為什麼要跑步？</t>
   </si>
   <si>
@@ -290,6 +347,9 @@
     <t>flen43442522</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/flen43442522/</t>
+  </si>
+  <si>
     <t>Linkin Park: Unshatter</t>
   </si>
   <si>
@@ -299,12 +359,18 @@
     <t>2026-09-30 00:00:00</t>
   </si>
   <si>
+    <t>2026-10-20 16:15:56</t>
+  </si>
+  <si>
     <t>19</t>
   </si>
   <si>
     <t>fako38961056</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fako38961056/</t>
+  </si>
+  <si>
     <t>鬼6咒</t>
   </si>
   <si>
@@ -317,6 +383,9 @@
     <t>ftcn72266277</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/ftcn72266277/</t>
+  </si>
+  <si>
     <t>遠離祖靈的孩子</t>
   </si>
   <si>
@@ -329,6 +398,9 @@
     <t>fwcn37535198</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fwcn37535198/</t>
+  </si>
+  <si>
     <t>我們不是什麼</t>
   </si>
   <si>
@@ -344,6 +416,9 @@
     <t>fmru34965515</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fmru34965515/</t>
+  </si>
+  <si>
     <t>反對普丁的無名先生</t>
   </si>
   <si>
@@ -356,6 +431,9 @@
     <t>fien37964027</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fien37964027/</t>
+  </si>
+  <si>
     <t>與畢諾許共舞</t>
   </si>
   <si>
@@ -368,6 +446,9 @@
     <t>frko29452783</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/frko29452783/</t>
+  </si>
+  <si>
     <t>復活男</t>
   </si>
   <si>
@@ -380,6 +461,9 @@
     <t>fhen47526136</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fhen47526136/</t>
+  </si>
+  <si>
     <t>野獸之心</t>
   </si>
   <si>
@@ -398,6 +482,9 @@
     <t>ffen36583977</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/ffen36583977/</t>
+  </si>
+  <si>
     <t>誤闖遺忘島</t>
   </si>
   <si>
@@ -413,6 +500,9 @@
     <t>fpen34206385</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fpen34206385/</t>
+  </si>
+  <si>
     <t>實境誘捕</t>
   </si>
   <si>
@@ -425,6 +515,9 @@
     <t>fren31349844</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fren31349844/</t>
+  </si>
+  <si>
     <t>特種快遞</t>
   </si>
   <si>
@@ -437,6 +530,9 @@
     <t>fsjp39602215</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fsjp39602215/</t>
+  </si>
+  <si>
     <t>黑牢城</t>
   </si>
   <si>
@@ -452,28 +548,31 @@
     <t>fpjp99797607</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fpjp99797607/</t>
+  </si>
+  <si>
     <t>Perfume“Cold Sleep”-25 years Document</t>
   </si>
   <si>
     <t>https://www.atmovies.com.tw/photo101/fpjp99797607/pl_fpjp99797607.jpg</t>
   </si>
   <si>
-    <t>2026-10-19 14:37:27</t>
-  </si>
-  <si>
     <t>31</t>
   </si>
   <si>
     <t>fhth43380212</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fhth43380212/</t>
+  </si>
+  <si>
     <t>猛鬼大學：4不瞑目</t>
   </si>
   <si>
     <t>https://www.atmovies.com.tw/photo101/fhth43380212/pl_fhth43380212.jpg</t>
   </si>
   <si>
-    <t>2026-10-19 11:27:59</t>
+    <t>2026-10-20 16:15:58</t>
   </si>
   <si>
     <t>32</t>
@@ -482,6 +581,9 @@
     <t>fsno26446095</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fsno26446095/</t>
+  </si>
+  <si>
     <t>親愛的星上人</t>
   </si>
   <si>
@@ -494,6 +596,9 @@
     <t>fhjp42864901</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fhjp42864901/</t>
+  </si>
+  <si>
     <t>5秒生成完美犯罪</t>
   </si>
   <si>
@@ -509,6 +614,9 @@
     <t>fafr33298226</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>最後的單車上路</t>
   </si>
   <si>
@@ -521,6 +629,9 @@
     <t>fren35538033</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fren35538033/</t>
+  </si>
+  <si>
     <t>惡靈古堡：爆發夜</t>
   </si>
   <si>
@@ -530,12 +641,18 @@
     <t>2026-09-17 00:00:00</t>
   </si>
   <si>
+    <t>2026-10-20 16:15:59</t>
+  </si>
+  <si>
     <t>36</t>
   </si>
   <si>
     <t>fljp92878069</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fljp92878069/</t>
+  </si>
+  <si>
     <t>LOVE LIVE! 蓮之空女學院學園偶像俱樂部</t>
   </si>
   <si>
@@ -551,6 +668,9 @@
     <t>fbjp36205428</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fbjp36205428/</t>
+  </si>
+  <si>
     <t>懺悔</t>
   </si>
   <si>
@@ -566,6 +686,9 @@
     <t>fpen27550504</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fpen27550504/</t>
+  </si>
+  <si>
     <t>臥底情劫</t>
   </si>
   <si>
@@ -578,6 +701,9 @@
     <t>fwko41135043</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fwko41135043/</t>
+  </si>
+  <si>
     <t>夢想出擊</t>
   </si>
   <si>
@@ -590,6 +716,9 @@
     <t>fsen31549553</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fsen31549553/</t>
+  </si>
+  <si>
     <t>喵咪總動員</t>
   </si>
   <si>
@@ -602,6 +731,9 @@
     <t>ffde17070412</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/ffde17070412/</t>
+  </si>
+  <si>
     <t>變形卡夫卡</t>
   </si>
   <si>
@@ -617,6 +749,9 @@
     <t>ffko35303960</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/ffko35303960/</t>
+  </si>
+  <si>
     <t>成人童話</t>
   </si>
   <si>
@@ -629,6 +764,9 @@
     <t>fljp39094466</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fljp39094466/</t>
+  </si>
+  <si>
     <t>驀然回首</t>
   </si>
   <si>
@@ -644,6 +782,9 @@
     <t>ftjp50088222</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/ftjp50088222/</t>
+  </si>
+  <si>
     <t>颱風俱樂部</t>
   </si>
   <si>
@@ -683,6 +824,9 @@
     <t>focn43560584</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/focn43560584/</t>
+  </si>
+  <si>
     <t>怎麼可能我家的祖先是你家的鬼</t>
   </si>
   <si>
@@ -695,12 +839,18 @@
     <t>2026-10-09 09:45:42</t>
   </si>
   <si>
+    <t>2026-10-20 16:16:01</t>
+  </si>
+  <si>
     <t>48</t>
   </si>
   <si>
     <t>fmja14521412</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fmja14521412/</t>
+  </si>
+  <si>
     <t>劇場版 魔法少女小圓〈瓦爾普吉斯的迴天〉</t>
   </si>
   <si>
@@ -716,6 +866,9 @@
     <t>fhko27369017</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fhko27369017/</t>
+  </si>
+  <si>
     <t>希望：末日血戰</t>
   </si>
   <si>
@@ -743,6 +896,9 @@
     <t>fpcn46256167</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fpcn46256167/</t>
+  </si>
+  <si>
     <t>網紅老爸</t>
   </si>
   <si>
@@ -758,21 +914,24 @@
     <t>frcn38633224</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/frcn38633224/</t>
+  </si>
+  <si>
     <t>粽邪4：坤蒂拉娜</t>
   </si>
   <si>
     <t>https://www.atmovies.com.tw/photo101/frcn38633224/pl_frcn38633224.jpg</t>
   </si>
   <si>
-    <t>2026-10-19 11:27:55</t>
-  </si>
-  <si>
     <t>53</t>
   </si>
   <si>
     <t>fien14173636</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fien14173636/</t>
+  </si>
+  <si>
     <t>開放性邀請</t>
   </si>
   <si>
@@ -788,6 +947,9 @@
     <t>fmen32338669</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fmen32338669/</t>
+  </si>
+  <si>
     <t>玩命航線</t>
   </si>
   <si>
@@ -806,6 +968,9 @@
     <t>fpen29356163</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fpen29356163/</t>
+  </si>
+  <si>
     <t>汪汪隊立大功：恐龍大電影</t>
   </si>
   <si>
@@ -833,6 +998,9 @@
     <t>fdcn54620499</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fdcn54620499/</t>
+  </si>
+  <si>
     <t>終戰那一天</t>
   </si>
   <si>
@@ -845,6 +1013,9 @@
     <t>feen27165187</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/feen27165187/</t>
+  </si>
+  <si>
     <t>橡樹街末日</t>
   </si>
   <si>
@@ -857,12 +1028,18 @@
     <t>2026-10-09 09:45:48</t>
   </si>
   <si>
+    <t>2026-10-20 16:16:05</t>
+  </si>
+  <si>
     <t>59</t>
   </si>
   <si>
     <t>fbjp39400168</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fbjp39400168/</t>
+  </si>
+  <si>
     <t>藍色監獄</t>
   </si>
   <si>
@@ -875,6 +1052,9 @@
     <t>foen37287335</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/foen37287335/</t>
+  </si>
+  <si>
     <t>愛你致死不渝</t>
   </si>
   <si>
@@ -890,6 +1070,9 @@
     <t>fcjp41293342</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fcjp41293342/</t>
+  </si>
+  <si>
     <t>電影蠟筆小新：奇奇怪怪！我的妖怪假期</t>
   </si>
   <si>
@@ -902,6 +1085,9 @@
     <t>fsen22084616</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fsen22084616/</t>
+  </si>
+  <si>
     <t>蜘蛛人：重生日</t>
   </si>
   <si>
@@ -920,6 +1106,9 @@
     <t>fnjp39026173</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fnjp39026173/</t>
+  </si>
+  <si>
     <t>劇場版 吉伊卡哇 人魚島的秘密</t>
   </si>
   <si>
@@ -935,6 +1124,9 @@
     <t>foen33764258</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/foen33764258/</t>
+  </si>
+  <si>
     <t>奧德賽</t>
   </si>
   <si>
@@ -950,6 +1142,9 @@
     <t>fnjp38201958</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fnjp38201958/</t>
+  </si>
+  <si>
     <t>電影哆啦A夢：新‧大雄的海底鬼岩城</t>
   </si>
   <si>
@@ -965,6 +1160,9 @@
     <t>fdjp94776409</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fdjp94776409/</t>
+  </si>
+  <si>
     <t>名偵探柯南 高速公路的墮天使</t>
   </si>
   <si>
@@ -998,6 +1196,9 @@
     <t>fcfr31550312</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fcfr31550312/</t>
+  </si>
+  <si>
     <t>花神咖啡館</t>
   </si>
   <si>
@@ -1013,6 +1214,9 @@
     <t>fajp00297721</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fajp00297721/</t>
+  </si>
+  <si>
     <t>青春電幻物語</t>
   </si>
   <si>
@@ -1028,6 +1232,9 @@
     <t>faen64154796</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/faen64154796/</t>
+  </si>
+  <si>
     <t>復仇者聯盟：終局之戰</t>
   </si>
   <si>
@@ -1046,6 +1253,9 @@
     <t>fdtw30097791</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fdtw30097791/</t>
+  </si>
+  <si>
     <t>魯冰花(數位修復版)</t>
   </si>
   <si>
@@ -1076,6 +1286,9 @@
     <t>ffjp90246378</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/ffjp90246378/</t>
+  </si>
+  <si>
     <t>鋼之鍊金術師：香巴拉的征服者</t>
   </si>
   <si>
@@ -1085,15 +1298,15 @@
     <t>2005-12-23 00:00:00</t>
   </si>
   <si>
-    <t>2026-10-19 11:26:50</t>
-  </si>
-  <si>
     <t>74</t>
   </si>
   <si>
     <t>fgde32897929</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fgde32897929/</t>
+  </si>
+  <si>
     <t>極鼠方程式</t>
   </si>
   <si>
@@ -1112,6 +1325,9 @@
     <t>fmen27419466</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fmen27419466/</t>
+  </si>
+  <si>
     <t>海洋奇緣(真人版)</t>
   </si>
   <si>
@@ -1124,6 +1340,9 @@
     <t>fsen28682323</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fsen28682323/</t>
+  </si>
+  <si>
     <t>絕殺路人甲</t>
   </si>
   <si>
@@ -1139,6 +1358,9 @@
     <t>fmen32890033</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fmen32890033/</t>
+  </si>
+  <si>
     <t>小小兵&amp;大怪獸</t>
   </si>
   <si>
@@ -1154,6 +1376,9 @@
     <t>fkja39388678</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fkja39388678/</t>
+  </si>
+  <si>
     <t>電影版教場：驪歌</t>
   </si>
   <si>
@@ -1187,6 +1412,9 @@
     <t>fpcn36204735</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fpcn36204735/</t>
+  </si>
+  <si>
     <t>逆轉上半場</t>
   </si>
   <si>
@@ -1217,6 +1445,9 @@
     <t>fsen28671344</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fsen28671344/</t>
+  </si>
+  <si>
     <t>殘殺路人甲</t>
   </si>
   <si>
@@ -1247,6 +1478,9 @@
     <t>fsen23157384</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fsen23157384/</t>
+  </si>
+  <si>
     <t>末路相縫</t>
   </si>
   <si>
@@ -1277,6 +1511,9 @@
     <t>fpen12042730</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fpen12042730/</t>
+  </si>
+  <si>
     <t>極限返航</t>
   </si>
   <si>
@@ -1289,6 +1526,9 @@
     <t>2026-10-09 09:46:03</t>
   </si>
   <si>
+    <t>2026-10-20 16:16:07</t>
+  </si>
+  <si>
     <t>87</t>
   </si>
   <si>
@@ -1310,6 +1550,9 @@
     <t>fsen27419420</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fsen27419420/</t>
+  </si>
+  <si>
     <t>快打旋風</t>
   </si>
   <si>
@@ -1319,12 +1562,18 @@
     <t>2026-10-16 00:00:00</t>
   </si>
   <si>
+    <t>2026-10-20 16:15:50</t>
+  </si>
+  <si>
     <t>89</t>
   </si>
   <si>
     <t>fyjp43738759</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fyjp43738759/</t>
+  </si>
+  <si>
     <t>宛如星辰的你</t>
   </si>
   <si>
@@ -1337,6 +1586,9 @@
     <t>fwen28535715</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fwen28535715/</t>
+  </si>
+  <si>
     <t>逃出鯨吞</t>
   </si>
   <si>
@@ -1352,6 +1604,9 @@
     <t>fien43741215</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fien43741215/</t>
+  </si>
+  <si>
     <t>高年級實習生</t>
   </si>
   <si>
@@ -1376,6 +1631,9 @@
     <t>fnjp96510458</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fnjp96510458/</t>
+  </si>
+  <si>
     <t>遊戲人生（電視動畫 前篇）</t>
   </si>
   <si>
@@ -1388,6 +1646,9 @@
     <t>fpen34250044</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fpen34250044/</t>
+  </si>
+  <si>
     <t>紐約攝影師的日與夜</t>
   </si>
   <si>
@@ -1400,6 +1661,9 @@
     <t>facn33095008</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/facn33095008/</t>
+  </si>
+  <si>
     <t>刺殺小說家2</t>
   </si>
   <si>
@@ -1415,6 +1679,9 @@
     <t>fgjp43636575</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fgjp43636575/</t>
+  </si>
+  <si>
     <t>麵包超人電影版：潘坦與約定之星</t>
   </si>
   <si>
@@ -1427,6 +1694,9 @@
     <t>fwen45095076</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fwen45095076/</t>
+  </si>
+  <si>
     <t>駭速劫案</t>
   </si>
   <si>
@@ -1439,6 +1709,9 @@
     <t>fven27802226</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fven27802226/</t>
+  </si>
+  <si>
     <t>吳爾芙的夜與日</t>
   </si>
   <si>
@@ -1451,6 +1724,9 @@
     <t>fsjp51137145</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fsjp51137145/</t>
+  </si>
+  <si>
     <t>鼠一般的你</t>
   </si>
   <si>
@@ -1466,6 +1742,9 @@
     <t>fsma43440269</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fsma43440269/</t>
+  </si>
+  <si>
     <t>沙央</t>
   </si>
   <si>
@@ -1478,6 +1757,9 @@
     <t>fmen37511195</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fmen37511195/</t>
+  </si>
+  <si>
     <t>華倫夫人的職業 (英國國家劇院現場)</t>
   </si>
   <si>
@@ -1493,6 +1775,9 @@
     <t>fcen34890576</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fcen34890576/</t>
+  </si>
+  <si>
     <t>泥面人</t>
   </si>
   <si>
@@ -1508,6 +1793,9 @@
     <t>fsen37510326</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fsen37510326/</t>
+  </si>
+  <si>
     <t>社群清算</t>
   </si>
   <si>
@@ -1538,6 +1826,9 @@
     <t>fjfr36955518</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fjfr36955518/</t>
+  </si>
+  <si>
     <t>Jim Queen：肌情四射</t>
   </si>
   <si>
@@ -1550,6 +1841,9 @@
     <t>fpko43658893</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fpko43658893/</t>
+  </si>
+  <si>
     <t>樂園的孩子</t>
   </si>
   <si>
@@ -1562,6 +1856,9 @@
     <t>fpen12824390</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fpen12824390/</t>
+  </si>
+  <si>
     <t>嘟嘟魚的冒險</t>
   </si>
   <si>
@@ -1577,6 +1874,9 @@
     <t>fnjp95870591</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fnjp95870591/</t>
+  </si>
+  <si>
     <t>遊戲人生（電視動畫 後篇）</t>
   </si>
   <si>
@@ -1589,6 +1889,9 @@
     <t>flvi41782670</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/flvi41782670/</t>
+  </si>
+  <si>
     <t>鬼降靈</t>
   </si>
   <si>
@@ -1601,18 +1904,27 @@
     <t>fcjp39371353</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fcjp39371353/</t>
+  </si>
+  <si>
     <t>煙囪小鎮的普佩2：約定的鐘樓</t>
   </si>
   <si>
     <t>https://www.atmovies.com.tw/photo101/fcjp39371353/pl_fcjp39371353.jpg</t>
   </si>
   <si>
+    <t>2026-10-20 16:16:09</t>
+  </si>
+  <si>
     <t>111</t>
   </si>
   <si>
     <t>ftcn61276786</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/ftcn61276786/</t>
+  </si>
+  <si>
     <t>金三角孤軍淚</t>
   </si>
   <si>
@@ -1628,6 +1940,9 @@
     <t>fwcn37615065</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fwcn37615065/</t>
+  </si>
+  <si>
     <t>浪花男女</t>
   </si>
   <si>
@@ -1640,6 +1955,9 @@
     <t>fljp91162999</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fljp91162999/</t>
+  </si>
+  <si>
     <t>音樂劇《刀劍亂舞》〜月夜一縷〜現場直播</t>
   </si>
   <si>
@@ -1658,6 +1976,9 @@
     <t>fecn36958624</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fecn36958624/</t>
+  </si>
+  <si>
     <t>消失的金鳳娜</t>
   </si>
   <si>
@@ -1673,6 +1994,9 @@
     <t>fecn79633166</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fecn79633166/</t>
+  </si>
+  <si>
     <t>世紀初戀 楊麗花</t>
   </si>
   <si>
@@ -1691,6 +2015,9 @@
     <t>fmen13611778</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fmen13611778/</t>
+  </si>
+  <si>
     <t>即刻狂飆</t>
   </si>
   <si>
@@ -1703,6 +2030,9 @@
     <t>fmjp29631651</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fmjp29631651/</t>
+  </si>
+  <si>
     <t>完美配對謀殺案：真愛</t>
   </si>
   <si>
@@ -1715,18 +2045,27 @@
     <t>frin58178634</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/frin58178634/</t>
+  </si>
+  <si>
     <t>雙雄起義</t>
   </si>
   <si>
     <t>https://www.atmovies.com.tw/photo101/frin58178634/pl_frin58178634.jpg</t>
   </si>
   <si>
+    <t>2026-10-20 16:16:11</t>
+  </si>
+  <si>
     <t>119</t>
   </si>
   <si>
     <t>ftjp43691434</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/ftjp43691434/</t>
+  </si>
+  <si>
     <t>致遙不可及彼方的你</t>
   </si>
   <si>
@@ -1742,6 +2081,9 @@
     <t>fwcn37038996</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fwcn37038996/</t>
+  </si>
+  <si>
     <t>歡迎來到朵莉之家</t>
   </si>
   <si>
@@ -1754,6 +2096,9 @@
     <t>fwjp44090388</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fwjp44090388/</t>
+  </si>
+  <si>
     <t>出賣影子的女人</t>
   </si>
   <si>
@@ -1766,6 +2111,9 @@
     <t>foen27052428</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/foen27052428/</t>
+  </si>
+  <si>
     <t>歐威爾：2+2=5</t>
   </si>
   <si>
@@ -1778,6 +2126,9 @@
     <t>fdjp93432573</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fdjp93432573/</t>
+  </si>
+  <si>
     <t>名偵探柯南 第30號殺人事件</t>
   </si>
   <si>
@@ -1796,6 +2147,9 @@
     <t>fgjp34384661</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fgjp34384661/</t>
+  </si>
+  <si>
     <t>哥吉拉-0.0</t>
   </si>
   <si>
@@ -1808,6 +2162,9 @@
     <t>fcen39676060</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fcen39676060/</t>
+  </si>
+  <si>
     <t>CVF2026貓貓影片節</t>
   </si>
   <si>
@@ -1820,6 +2177,9 @@
     <t>facn35486511</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/facn35486511/</t>
+  </si>
+  <si>
     <t>告別的年代</t>
   </si>
   <si>
@@ -1835,6 +2195,9 @@
     <t>fhen35866986</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fhen35866986/</t>
+  </si>
+  <si>
     <t>搶銀行先修班</t>
   </si>
   <si>
@@ -1850,6 +2213,9 @@
     <t>feen38773219</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/feen38773219/</t>
+  </si>
+  <si>
     <t>聖誕驚奇夜</t>
   </si>
   <si>
@@ -1862,18 +2228,27 @@
     <t>fbjp40826527</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fbjp40826527/</t>
+  </si>
+  <si>
     <t>大搜查線N.E.W.</t>
   </si>
   <si>
     <t>https://www.atmovies.com.tw/photo101/fbjp40826527/pl_fbjp40826527.jpg</t>
   </si>
   <si>
+    <t>2026-10-20 16:16:13</t>
+  </si>
+  <si>
     <t>130</t>
   </si>
   <si>
     <t>fbjp39231777</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fbjp39231777/</t>
+  </si>
+  <si>
     <t>放送禁止：一夫三妻</t>
   </si>
   <si>
@@ -1886,6 +2261,9 @@
     <t>frjp38652027</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/frjp38652027/</t>
+  </si>
+  <si>
     <t>魔法科高中的劣等生 四葉繼承篇</t>
   </si>
   <si>
@@ -1901,6 +2279,9 @@
     <t>fnjp37694048</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fnjp37694048/</t>
+  </si>
+  <si>
     <t>高校人形金字塔</t>
   </si>
   <si>
@@ -1913,6 +2294,9 @@
     <t>fhen32558705</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fhen32558705/</t>
+  </si>
+  <si>
     <t>飢餓遊戲：黎明收割</t>
   </si>
   <si>
@@ -1928,6 +2312,9 @@
     <t>fbcn49610505</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fbcn49610505/</t>
+  </si>
+  <si>
     <t>重返巔峰北壁</t>
   </si>
   <si>
@@ -1940,6 +2327,9 @@
     <t>fbes35511966</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fbes35511966/</t>
+  </si>
+  <si>
     <t>黑球</t>
   </si>
   <si>
@@ -1955,6 +2345,9 @@
     <t>fwcn36563084</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fwcn36563084/</t>
+  </si>
+  <si>
     <t>善男信女</t>
   </si>
   <si>
@@ -1967,6 +2360,9 @@
     <t>fhen38077943</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fhen38077943/</t>
+  </si>
+  <si>
     <t>歡迎光臨魔法秘境</t>
   </si>
   <si>
@@ -1976,15 +2372,15 @@
     <t>2026-11-26 00:00:00</t>
   </si>
   <si>
-    <t>2026-10-19 11:26:26</t>
-  </si>
-  <si>
     <t>138</t>
   </si>
   <si>
     <t>ffen34966140</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/ffen34966140/</t>
+  </si>
+  <si>
     <t>門當父不對之親家駕到</t>
   </si>
   <si>
@@ -2000,6 +2396,9 @@
     <t>fcen52321555</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fcen52321555/</t>
+  </si>
+  <si>
     <t>戴帽子的貓</t>
   </si>
   <si>
@@ -2012,12 +2411,18 @@
     <t>2026-10-09 09:46:30</t>
   </si>
   <si>
+    <t>2026-10-20 16:16:15</t>
+  </si>
+  <si>
     <t>140</t>
   </si>
   <si>
     <t>fven32432428</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fven32432428/</t>
+  </si>
+  <si>
     <t>暴戾夜2</t>
   </si>
   <si>
@@ -2033,6 +2438,9 @@
     <t>fwen42582802</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fwen42582802/</t>
+  </si>
+  <si>
     <t>進擊的鼓手</t>
   </si>
   <si>
@@ -2051,6 +2459,9 @@
     <t>futh28766949</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/futh28766949/</t>
+  </si>
+  <si>
     <t>跳越時空的愛戀</t>
   </si>
   <si>
@@ -2066,21 +2477,24 @@
     <t>fbjp39335288</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fbjp39335288/</t>
+  </si>
+  <si>
     <t>劇場版</t>
   </si>
   <si>
     <t>https://www.atmovies.com.tw/photo101/fbjp39335288/pl_fbjp39335288.jpg</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>144</t>
   </si>
   <si>
     <t>fmone0412214</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fmone0412214/</t>
+  </si>
+  <si>
     <t>男歡女愛</t>
   </si>
   <si>
@@ -2099,6 +2513,9 @@
     <t>fszh45452981</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fszh45452981/</t>
+  </si>
+  <si>
     <t>國有器官</t>
   </si>
   <si>
@@ -2114,6 +2531,9 @@
     <t>ficn82691592</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/ficn82691592/</t>
+  </si>
+  <si>
     <t>我未許願先吹蠟燭</t>
   </si>
   <si>
@@ -2129,6 +2549,9 @@
     <t>feen31170389</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/feen31170389/</t>
+  </si>
+  <si>
     <t>屍變焚場</t>
   </si>
   <si>
@@ -2144,6 +2567,9 @@
     <t>fmen34542628</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fmen34542628/</t>
+  </si>
+  <si>
     <t>蒙克聲音拼貼</t>
   </si>
   <si>
@@ -2159,6 +2585,9 @@
     <t>fako33364791</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fako33364791/</t>
+  </si>
+  <si>
     <t>活命水特弓隊</t>
   </si>
   <si>
@@ -2171,6 +2600,9 @@
     <t>fajp75923132</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fajp75923132/</t>
+  </si>
+  <si>
     <t>加速世界 劇場版</t>
   </si>
   <si>
@@ -2183,21 +2615,24 @@
     <t>fcpl33305572</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fcpl33305572/</t>
+  </si>
+  <si>
     <t>蕭邦！蕭邦！</t>
   </si>
   <si>
     <t>https://www.atmovies.com.tw/photo101/fcpl33305572/pl_fcpl33305572.jpg</t>
   </si>
   <si>
-    <t>2026-10-19 11:38:38</t>
-  </si>
-  <si>
     <t>152</t>
   </si>
   <si>
     <t>ftjp95459925</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/ftjp95459925/</t>
+  </si>
+  <si>
     <t>2026秋山眞緒 Final 現場直播</t>
   </si>
   <si>
@@ -2213,6 +2648,9 @@
     <t>fcth44632295</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fcth44632295/</t>
+  </si>
+  <si>
     <t>薩滿的最後告解</t>
   </si>
   <si>
@@ -2225,6 +2663,9 @@
     <t>ften35298123</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/ften35298123/</t>
+  </si>
+  <si>
     <t>屍控片場性愛死</t>
   </si>
   <si>
@@ -2237,6 +2678,9 @@
     <t>fajp39382917</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fajp39382917/</t>
+  </si>
+  <si>
     <t>全家就弒你家</t>
   </si>
   <si>
@@ -2249,6 +2693,9 @@
     <t>fmtw53870342</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fmtw53870342/</t>
+  </si>
+  <si>
     <t>我要當總統</t>
   </si>
   <si>
@@ -2261,6 +2708,9 @@
     <t>fdcn25375197</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fdcn25375197/</t>
+  </si>
+  <si>
     <t>黑潮</t>
   </si>
   <si>
@@ -2273,21 +2723,24 @@
     <t>fsjp43722621</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fsjp43722621/</t>
+  </si>
+  <si>
     <t>跟我一起玩吧？</t>
   </si>
   <si>
     <t>https://www.atmovies.com.tw/photo101/fsjp43722621/pl_fsjp43722621.jpg</t>
   </si>
   <si>
-    <t>2026-10-19 11:38:36</t>
-  </si>
-  <si>
     <t>159</t>
   </si>
   <si>
     <t>fwcn39673991</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fwcn39673991/</t>
+  </si>
+  <si>
     <t>日光</t>
   </si>
   <si>
@@ -2300,6 +2753,9 @@
     <t>fben29355194</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fben29355194/</t>
+  </si>
+  <si>
     <t>紐約古書店尋寶記</t>
   </si>
   <si>
@@ -2315,6 +2771,9 @@
     <t>faen21357150</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/faen21357150/</t>
+  </si>
+  <si>
     <t>復仇者聯盟：末日崛起</t>
   </si>
   <si>
@@ -2330,6 +2789,9 @@
     <t>fden31378509</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fden31378509/</t>
+  </si>
+  <si>
     <t>沙丘：第三部</t>
   </si>
   <si>
@@ -2342,6 +2804,9 @@
     <t>facn35683770</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/facn35683770/</t>
+  </si>
+  <si>
     <t>泡泡糖女孩</t>
   </si>
   <si>
@@ -2357,6 +2822,9 @@
     <t>fwen29611136</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fwen29611136/</t>
+  </si>
+  <si>
     <t>就是柳柳的他</t>
   </si>
   <si>
@@ -2369,6 +2837,9 @@
     <t>fien34512981</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fien34512981/</t>
+  </si>
+  <si>
     <t>冰原歷險記6：沸常危機</t>
   </si>
   <si>
@@ -2384,6 +2855,9 @@
     <t>fcen36593129</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fcen36593129/</t>
+  </si>
+  <si>
     <t>復出之王</t>
   </si>
   <si>
@@ -2396,6 +2870,9 @@
     <t>fnen99077514</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fnen99077514/</t>
+  </si>
+  <si>
     <t>納尼亞：魔法師的外甥</t>
   </si>
   <si>
@@ -2411,6 +2888,9 @@
     <t>fgen26443610</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fgen26443610/</t>
+  </si>
+  <si>
     <t>貓的急轉彎</t>
   </si>
   <si>
@@ -2420,12 +2900,18 @@
     <t>2027-03-05 00:00:00</t>
   </si>
   <si>
+    <t>2026-10-20 16:16:16</t>
+  </si>
+  <si>
     <t>169</t>
   </si>
   <si>
     <t>fnen43609247</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fnen43609247/</t>
+  </si>
+  <si>
     <t>外星三寶團</t>
   </si>
   <si>
@@ -2435,12 +2921,18 @@
     <t>2027-04-04 00:00:00</t>
   </si>
   <si>
+    <t>2026-10-20 16:16:17</t>
+  </si>
+  <si>
     <t>170</t>
   </si>
   <si>
     <t>fsen46113186</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fsen46113186/</t>
+  </si>
+  <si>
     <t>史瑞克5</t>
   </si>
   <si>
@@ -2450,15 +2942,15 @@
     <t>2027-06-30 00:00:00</t>
   </si>
   <si>
-    <t>2026-10-19 11:38:34</t>
-  </si>
-  <si>
     <t>171</t>
   </si>
   <si>
     <t>fben35050152</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fben35050152/</t>
+  </si>
+  <si>
     <t>妙妙犬布麗電影</t>
   </si>
   <si>
@@ -2474,6 +2966,9 @@
     <t>fben19850008</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fben19850008/</t>
+  </si>
+  <si>
     <t>蝙蝠俠2</t>
   </si>
   <si>
@@ -2483,15 +2978,15 @@
     <t>2028-02-18 00:00:00</t>
   </si>
   <si>
-    <t>2026-10-19 11:38:32</t>
-  </si>
-  <si>
     <t>173</t>
   </si>
   <si>
     <t>fhcn43696728</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fhcn43696728/</t>
+  </si>
+  <si>
     <t>幸福快樂的日子</t>
   </si>
   <si>
@@ -2504,18 +2999,27 @@
     <t>fscn44979318</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fscn44979318/</t>
+  </si>
+  <si>
     <t>蕩蕩蕩寇誌</t>
   </si>
   <si>
     <t>https://www.atmovies.com.tw/photo101/fscn44979318/pl_fscn44979318.jpg</t>
   </si>
   <si>
+    <t>2026-10-20 16:16:18</t>
+  </si>
+  <si>
     <t>175</t>
   </si>
   <si>
     <t>faen38686316</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/faen38686316/</t>
+  </si>
+  <si>
     <t>大天使</t>
   </si>
   <si>
@@ -2531,6 +3035,9 @@
     <t>faen32557122</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/faen32557122/</t>
+  </si>
+  <si>
     <t>憤怒鳥玩電影3：全家總動員</t>
   </si>
   <si>
@@ -2549,6 +3056,9 @@
     <t>fren35606013</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fren35606013/</t>
+  </si>
+  <si>
     <t>全力救援</t>
   </si>
   <si>
@@ -2567,6 +3077,9 @@
     <t>fren35621542</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fren35621542/</t>
+  </si>
+  <si>
     <t>滯留</t>
   </si>
   <si>
@@ -2582,6 +3095,9 @@
     <t>fwen35514120</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fwen35514120/</t>
+  </si>
+  <si>
     <t>人狼沃武夫</t>
   </si>
   <si>
@@ -2597,6 +3113,9 @@
     <t>fcen31339071</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fcen31339071/</t>
+  </si>
+  <si>
     <t>可可瓜瓜大電影</t>
   </si>
   <si>
@@ -2606,12 +3125,18 @@
     <t>2027-02-26 00:00:00</t>
   </si>
   <si>
+    <t>2026-10-20 16:16:19</t>
+  </si>
+  <si>
     <t>181</t>
   </si>
   <si>
     <t>fken98992304</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fken98992304/</t>
+  </si>
+  <si>
     <t>K-POP:星夢 初登場</t>
   </si>
   <si>
@@ -2624,6 +3149,9 @@
     <t>feen32492552</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/feen32492552/</t>
+  </si>
+  <si>
     <t>大法師:殉道</t>
   </si>
   <si>
@@ -2642,6 +3170,9 @@
     <t>fsen56744566</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fsen56744566/</t>
+  </si>
+  <si>
     <t>音速小子4</t>
   </si>
   <si>
@@ -2654,15 +3185,15 @@
     <t>2026-10-19 11:23:07</t>
   </si>
   <si>
-    <t>2026-10-19 11:38:30</t>
-  </si>
-  <si>
     <t>184</t>
   </si>
   <si>
     <t>facn38893248</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/facn38893248/</t>
+  </si>
+  <si>
     <t>狂忘警探</t>
   </si>
   <si>
@@ -2672,12 +3203,18 @@
     <t>2027-03-26 00:00:00</t>
   </si>
   <si>
+    <t>2026-10-20 16:16:20</t>
+  </si>
+  <si>
     <t>185</t>
   </si>
   <si>
     <t>fwma47658526</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fwma47658526/</t>
+  </si>
+  <si>
     <t>我妳她</t>
   </si>
   <si>
@@ -2690,6 +3227,9 @@
     <t>fyen32104007</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fyen32104007/</t>
+  </si>
+  <si>
     <t>華盛頓崛起</t>
   </si>
   <si>
@@ -2702,6 +3242,9 @@
     <t>ftcn44934439</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/ftcn44934439/</t>
+  </si>
+  <si>
     <t>有用的人</t>
   </si>
   <si>
@@ -2714,6 +3257,9 @@
     <t>ftjp15437998</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/ftjp15437998/</t>
+  </si>
+  <si>
     <t>人魚戀習曲</t>
   </si>
   <si>
@@ -2729,6 +3275,9 @@
     <t>fjen26735127</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fjen26735127/</t>
+  </si>
+  <si>
     <t>野蠻遊戲：虛實世界</t>
   </si>
   <si>
@@ -2747,6 +3296,9 @@
     <t>fcen96779038</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/fcen96779038/</t>
+  </si>
+  <si>
     <t>歐瑞莎傳奇血與骨的孩子</t>
   </si>
   <si>
@@ -2762,6 +3314,9 @@
     <t>ften45500064</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/ften45500064/</t>
+  </si>
+  <si>
     <t>天羅地網</t>
   </si>
   <si>
@@ -2777,6 +3332,9 @@
     <t>ftko95405162</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/movie/ftko95405162/</t>
+  </si>
+  <si>
     <t>TWS VR CONCERT RUSH ROAD</t>
   </si>
   <si>
@@ -2787,6 +3345,21 @@
   </si>
   <si>
     <t>2026-10-19 14:35:52</t>
+  </si>
+  <si>
+    <t>193</t>
+  </si>
+  <si>
+    <t>fjjp00193253</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/movie/fjjp00193253/</t>
+  </si>
+  <si>
+    <t>人狼 (1998)</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/fjjp00193253/pl_fjjp00193253.jpg</t>
   </si>
 </sst>
 </file>
@@ -2831,7 +3404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H193"/>
+  <dimension ref="A1:I194"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -2859,4997 +3432,5605 @@
       <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
+      <c r="I1" t="s" s="0">
+        <v>8</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="I2" t="s" s="0">
+        <v>17</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G3" t="s" s="0">
         <v>15</v>
       </c>
-      <c r="B3" t="s" s="0">
+      <c r="H3" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="C3" t="s" s="0">
+      <c r="I3" t="s" s="0">
         <v>17</v>
-      </c>
-      <c r="D3" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="E3" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F3" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="G3" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="H3" t="s" s="0">
-        <v>14</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G4" t="s" s="0">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="I4" t="s" s="0">
+        <v>17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="I5" t="s" s="0">
+        <v>17</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="I6" t="s" s="0">
+        <v>39</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="F7" t="s" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G7" t="s" s="0">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="I7" t="s" s="0">
+        <v>39</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C8" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="H8" t="s" s="0">
         <v>38</v>
       </c>
-      <c r="D8" t="s" s="0">
-        <v>39</v>
-      </c>
-      <c r="E8" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F8" t="s" s="0">
-        <v>40</v>
-      </c>
-      <c r="G8" t="s" s="0">
-        <v>31</v>
-      </c>
-      <c r="H8" t="s" s="0">
-        <v>41</v>
+      <c r="I8" t="s" s="0">
+        <v>51</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="E9" t="s" s="0">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="F9" t="s" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G9" t="s" s="0">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="H9" t="s" s="0">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="I9" t="s" s="0">
+        <v>39</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E10" t="s" s="0">
-        <v>12</v>
+        <v>61</v>
       </c>
       <c r="F10" t="s" s="0">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="G10" t="s" s="0">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="H10" t="s" s="0">
-        <v>52</v>
+        <v>63</v>
+      </c>
+      <c r="I10" t="s" s="0">
+        <v>39</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E11" t="s" s="0">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="F11" t="s" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G11" t="s" s="0">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="H11" t="s" s="0">
-        <v>51</v>
+        <v>63</v>
+      </c>
+      <c r="I11" t="s" s="0">
+        <v>17</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="E12" t="s" s="0">
-        <v>12</v>
+        <v>73</v>
       </c>
       <c r="F12" t="s" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G12" t="s" s="0">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="H12" t="s" s="0">
-        <v>51</v>
+        <v>63</v>
+      </c>
+      <c r="I12" t="s" s="0">
+        <v>17</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="C13" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="E13" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="F13" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G13" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="H13" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="D13" t="s" s="0">
-        <v>64</v>
-      </c>
-      <c r="E13" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F13" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="G13" t="s" s="0">
-        <v>51</v>
-      </c>
-      <c r="H13" t="s" s="0">
-        <v>51</v>
+      <c r="I13" t="s" s="0">
+        <v>39</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="E14" t="s" s="0">
-        <v>12</v>
+        <v>83</v>
       </c>
       <c r="F14" t="s" s="0">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="G14" t="s" s="0">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="H14" t="s" s="0">
-        <v>70</v>
+        <v>85</v>
+      </c>
+      <c r="I14" t="s" s="0">
+        <v>39</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="E15" t="s" s="0">
-        <v>12</v>
+        <v>90</v>
       </c>
       <c r="F15" t="s" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G15" t="s" s="0">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="H15" t="s" s="0">
-        <v>70</v>
+        <v>85</v>
+      </c>
+      <c r="I15" t="s" s="0">
+        <v>39</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="E16" t="s" s="0">
-        <v>12</v>
+        <v>95</v>
       </c>
       <c r="F16" t="s" s="0">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="G16" t="s" s="0">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="H16" t="s" s="0">
-        <v>70</v>
+        <v>85</v>
+      </c>
+      <c r="I16" t="s" s="0">
+        <v>39</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="E17" t="s" s="0">
-        <v>12</v>
+        <v>101</v>
       </c>
       <c r="F17" t="s" s="0">
-        <v>84</v>
+        <v>14</v>
       </c>
       <c r="G17" t="s" s="0">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="H17" t="s" s="0">
-        <v>70</v>
+        <v>85</v>
+      </c>
+      <c r="I17" t="s" s="0">
+        <v>39</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="D18" t="s" s="0">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="E18" t="s" s="0">
-        <v>12</v>
+        <v>107</v>
       </c>
       <c r="F18" t="s" s="0">
-        <v>84</v>
+        <v>14</v>
       </c>
       <c r="G18" t="s" s="0">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="H18" t="s" s="0">
-        <v>89</v>
+        <v>108</v>
+      </c>
+      <c r="I18" t="s" s="0">
+        <v>39</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="D19" t="s" s="0">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="E19" t="s" s="0">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="F19" t="s" s="0">
-        <v>94</v>
+        <v>14</v>
       </c>
       <c r="G19" t="s" s="0">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="H19" t="s" s="0">
-        <v>89</v>
+        <v>108</v>
+      </c>
+      <c r="I19" t="s" s="0">
+        <v>115</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="D20" t="s" s="0">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="E20" t="s" s="0">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="F20" t="s" s="0">
-        <v>84</v>
+        <v>14</v>
       </c>
       <c r="G20" t="s" s="0">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="H20" t="s" s="0">
-        <v>89</v>
+        <v>108</v>
+      </c>
+      <c r="I20" t="s" s="0">
+        <v>115</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="D21" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="E21" t="s" s="0">
+        <v>125</v>
+      </c>
+      <c r="F21" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G21" t="s" s="0">
         <v>102</v>
       </c>
-      <c r="E21" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F21" t="s" s="0">
-        <v>84</v>
-      </c>
-      <c r="G21" t="s" s="0">
-        <v>89</v>
-      </c>
       <c r="H21" t="s" s="0">
-        <v>89</v>
+        <v>108</v>
+      </c>
+      <c r="I21" t="s" s="0">
+        <v>115</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="D22" t="s" s="0">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="E22" t="s" s="0">
-        <v>12</v>
+        <v>130</v>
       </c>
       <c r="F22" t="s" s="0">
-        <v>84</v>
+        <v>14</v>
       </c>
       <c r="G22" t="s" s="0">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="H22" t="s" s="0">
-        <v>107</v>
+        <v>131</v>
+      </c>
+      <c r="I22" t="s" s="0">
+        <v>39</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>108</v>
+        <v>132</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>109</v>
+        <v>133</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>110</v>
+        <v>134</v>
       </c>
       <c r="D23" t="s" s="0">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="E23" t="s" s="0">
-        <v>12</v>
+        <v>136</v>
       </c>
       <c r="F23" t="s" s="0">
-        <v>84</v>
+        <v>14</v>
       </c>
       <c r="G23" t="s" s="0">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="H23" t="s" s="0">
-        <v>107</v>
+        <v>131</v>
+      </c>
+      <c r="I23" t="s" s="0">
+        <v>39</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="D24" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="E24" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="F24" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G24" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="H24" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="I24" t="s" s="0">
         <v>115</v>
-      </c>
-      <c r="E24" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F24" t="s" s="0">
-        <v>84</v>
-      </c>
-      <c r="G24" t="s" s="0">
-        <v>107</v>
-      </c>
-      <c r="H24" t="s" s="0">
-        <v>107</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="D25" t="s" s="0">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="E25" t="s" s="0">
-        <v>12</v>
+        <v>146</v>
       </c>
       <c r="F25" t="s" s="0">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="G25" t="s" s="0">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="H25" t="s" s="0">
-        <v>107</v>
+        <v>131</v>
+      </c>
+      <c r="I25" t="s" s="0">
+        <v>115</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="D26" t="s" s="0">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="E26" t="s" s="0">
-        <v>12</v>
+        <v>151</v>
       </c>
       <c r="F26" t="s" s="0">
-        <v>124</v>
+        <v>14</v>
       </c>
       <c r="G26" t="s" s="0">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="H26" t="s" s="0">
-        <v>125</v>
+        <v>153</v>
+      </c>
+      <c r="I26" t="s" s="0">
+        <v>115</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="C27" t="s" s="0">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="D27" t="s" s="0">
-        <v>129</v>
+        <v>157</v>
       </c>
       <c r="E27" t="s" s="0">
-        <v>12</v>
+        <v>158</v>
       </c>
       <c r="F27" t="s" s="0">
-        <v>130</v>
+        <v>14</v>
       </c>
       <c r="G27" t="s" s="0">
-        <v>125</v>
+        <v>159</v>
       </c>
       <c r="H27" t="s" s="0">
-        <v>125</v>
+        <v>153</v>
+      </c>
+      <c r="I27" t="s" s="0">
+        <v>115</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>131</v>
+        <v>160</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>132</v>
+        <v>161</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>133</v>
+        <v>162</v>
       </c>
       <c r="D28" t="s" s="0">
-        <v>134</v>
+        <v>163</v>
       </c>
       <c r="E28" t="s" s="0">
-        <v>12</v>
+        <v>164</v>
       </c>
       <c r="F28" t="s" s="0">
-        <v>124</v>
+        <v>14</v>
       </c>
       <c r="G28" t="s" s="0">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="H28" t="s" s="0">
-        <v>125</v>
+        <v>153</v>
+      </c>
+      <c r="I28" t="s" s="0">
+        <v>115</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>136</v>
+        <v>166</v>
       </c>
       <c r="C29" t="s" s="0">
-        <v>137</v>
+        <v>167</v>
       </c>
       <c r="D29" t="s" s="0">
-        <v>138</v>
+        <v>168</v>
       </c>
       <c r="E29" t="s" s="0">
-        <v>12</v>
+        <v>169</v>
       </c>
       <c r="F29" t="s" s="0">
-        <v>124</v>
+        <v>14</v>
       </c>
       <c r="G29" t="s" s="0">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="H29" t="s" s="0">
-        <v>125</v>
+        <v>153</v>
+      </c>
+      <c r="I29" t="s" s="0">
+        <v>115</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>139</v>
+        <v>170</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>140</v>
+        <v>171</v>
       </c>
       <c r="C30" t="s" s="0">
-        <v>141</v>
+        <v>172</v>
       </c>
       <c r="D30" t="s" s="0">
-        <v>142</v>
+        <v>173</v>
       </c>
       <c r="E30" t="s" s="0">
-        <v>12</v>
+        <v>174</v>
       </c>
       <c r="F30" t="s" s="0">
-        <v>124</v>
+        <v>14</v>
       </c>
       <c r="G30" t="s" s="0">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="H30" t="s" s="0">
-        <v>143</v>
+        <v>175</v>
+      </c>
+      <c r="I30" t="s" s="0">
+        <v>115</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>145</v>
+        <v>177</v>
       </c>
       <c r="C31" t="s" s="0">
-        <v>146</v>
+        <v>178</v>
       </c>
       <c r="D31" t="s" s="0">
-        <v>147</v>
+        <v>179</v>
       </c>
       <c r="E31" t="s" s="0">
-        <v>12</v>
+        <v>180</v>
       </c>
       <c r="F31" t="s" s="0">
-        <v>124</v>
+        <v>14</v>
       </c>
       <c r="G31" t="s" s="0">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="H31" t="s" s="0">
-        <v>148</v>
+        <v>175</v>
+      </c>
+      <c r="I31" t="s" s="0">
+        <v>115</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>149</v>
+        <v>181</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>150</v>
+        <v>182</v>
       </c>
       <c r="C32" t="s" s="0">
-        <v>151</v>
+        <v>183</v>
       </c>
       <c r="D32" t="s" s="0">
+        <v>184</v>
+      </c>
+      <c r="E32" t="s" s="0">
+        <v>185</v>
+      </c>
+      <c r="F32" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G32" t="s" s="0">
         <v>152</v>
       </c>
-      <c r="E32" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F32" t="s" s="0">
-        <v>124</v>
-      </c>
-      <c r="G32" t="s" s="0">
-        <v>143</v>
-      </c>
       <c r="H32" t="s" s="0">
-        <v>153</v>
+        <v>175</v>
+      </c>
+      <c r="I32" t="s" s="0">
+        <v>186</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>154</v>
+        <v>187</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>155</v>
+        <v>188</v>
       </c>
       <c r="C33" t="s" s="0">
-        <v>156</v>
+        <v>189</v>
       </c>
       <c r="D33" t="s" s="0">
-        <v>157</v>
+        <v>190</v>
       </c>
       <c r="E33" t="s" s="0">
-        <v>12</v>
+        <v>191</v>
       </c>
       <c r="F33" t="s" s="0">
-        <v>124</v>
+        <v>14</v>
       </c>
       <c r="G33" t="s" s="0">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="H33" t="s" s="0">
-        <v>143</v>
+        <v>175</v>
+      </c>
+      <c r="I33" t="s" s="0">
+        <v>115</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>158</v>
+        <v>192</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>159</v>
+        <v>193</v>
       </c>
       <c r="C34" t="s" s="0">
-        <v>160</v>
+        <v>194</v>
       </c>
       <c r="D34" t="s" s="0">
-        <v>161</v>
+        <v>195</v>
       </c>
       <c r="E34" t="s" s="0">
-        <v>12</v>
+        <v>196</v>
       </c>
       <c r="F34" t="s" s="0">
-        <v>124</v>
+        <v>14</v>
       </c>
       <c r="G34" t="s" s="0">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="H34" t="s" s="0">
-        <v>162</v>
+        <v>197</v>
+      </c>
+      <c r="I34" t="s" s="0">
+        <v>186</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>163</v>
+        <v>198</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>164</v>
+        <v>199</v>
       </c>
       <c r="C35" t="s" s="0">
-        <v>165</v>
+        <v>200</v>
       </c>
       <c r="D35" t="s" s="0">
-        <v>166</v>
+        <v>201</v>
       </c>
       <c r="E35" t="s" s="0">
-        <v>12</v>
+        <v>202</v>
       </c>
       <c r="F35" t="s" s="0">
-        <v>124</v>
+        <v>14</v>
       </c>
       <c r="G35" t="s" s="0">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="H35" t="s" s="0">
-        <v>162</v>
+        <v>197</v>
+      </c>
+      <c r="I35" t="s" s="0">
+        <v>197</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>167</v>
+        <v>203</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>168</v>
+        <v>204</v>
       </c>
       <c r="C36" t="s" s="0">
-        <v>169</v>
+        <v>205</v>
       </c>
       <c r="D36" t="s" s="0">
-        <v>170</v>
+        <v>206</v>
       </c>
       <c r="E36" t="s" s="0">
-        <v>12</v>
+        <v>207</v>
       </c>
       <c r="F36" t="s" s="0">
-        <v>171</v>
+        <v>14</v>
       </c>
       <c r="G36" t="s" s="0">
-        <v>162</v>
+        <v>208</v>
       </c>
       <c r="H36" t="s" s="0">
-        <v>162</v>
+        <v>197</v>
+      </c>
+      <c r="I36" t="s" s="0">
+        <v>209</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>172</v>
+        <v>210</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>173</v>
+        <v>211</v>
       </c>
       <c r="C37" t="s" s="0">
-        <v>174</v>
+        <v>212</v>
       </c>
       <c r="D37" t="s" s="0">
-        <v>175</v>
+        <v>213</v>
       </c>
       <c r="E37" t="s" s="0">
-        <v>12</v>
+        <v>214</v>
       </c>
       <c r="F37" t="s" s="0">
-        <v>176</v>
+        <v>14</v>
       </c>
       <c r="G37" t="s" s="0">
-        <v>162</v>
+        <v>215</v>
       </c>
       <c r="H37" t="s" s="0">
-        <v>162</v>
+        <v>197</v>
+      </c>
+      <c r="I37" t="s" s="0">
+        <v>186</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>177</v>
+        <v>216</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>178</v>
+        <v>217</v>
       </c>
       <c r="C38" t="s" s="0">
-        <v>179</v>
+        <v>218</v>
       </c>
       <c r="D38" t="s" s="0">
-        <v>180</v>
+        <v>219</v>
       </c>
       <c r="E38" t="s" s="0">
-        <v>12</v>
+        <v>220</v>
       </c>
       <c r="F38" t="s" s="0">
-        <v>176</v>
+        <v>14</v>
       </c>
       <c r="G38" t="s" s="0">
-        <v>181</v>
+        <v>215</v>
       </c>
       <c r="H38" t="s" s="0">
-        <v>181</v>
+        <v>221</v>
+      </c>
+      <c r="I38" t="s" s="0">
+        <v>186</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>182</v>
+        <v>222</v>
       </c>
       <c r="B39" t="s" s="0">
-        <v>183</v>
+        <v>223</v>
       </c>
       <c r="C39" t="s" s="0">
-        <v>184</v>
+        <v>224</v>
       </c>
       <c r="D39" t="s" s="0">
-        <v>185</v>
+        <v>225</v>
       </c>
       <c r="E39" t="s" s="0">
-        <v>12</v>
+        <v>226</v>
       </c>
       <c r="F39" t="s" s="0">
-        <v>176</v>
+        <v>14</v>
       </c>
       <c r="G39" t="s" s="0">
-        <v>181</v>
+        <v>215</v>
       </c>
       <c r="H39" t="s" s="0">
-        <v>181</v>
+        <v>221</v>
+      </c>
+      <c r="I39" t="s" s="0">
+        <v>209</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>186</v>
+        <v>227</v>
       </c>
       <c r="B40" t="s" s="0">
-        <v>187</v>
+        <v>228</v>
       </c>
       <c r="C40" t="s" s="0">
-        <v>188</v>
+        <v>229</v>
       </c>
       <c r="D40" t="s" s="0">
-        <v>189</v>
+        <v>230</v>
       </c>
       <c r="E40" t="s" s="0">
-        <v>12</v>
+        <v>231</v>
       </c>
       <c r="F40" t="s" s="0">
-        <v>176</v>
+        <v>14</v>
       </c>
       <c r="G40" t="s" s="0">
-        <v>181</v>
+        <v>215</v>
       </c>
       <c r="H40" t="s" s="0">
-        <v>181</v>
+        <v>221</v>
+      </c>
+      <c r="I40" t="s" s="0">
+        <v>209</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>190</v>
+        <v>232</v>
       </c>
       <c r="B41" t="s" s="0">
-        <v>191</v>
+        <v>233</v>
       </c>
       <c r="C41" t="s" s="0">
-        <v>192</v>
+        <v>234</v>
       </c>
       <c r="D41" t="s" s="0">
-        <v>193</v>
+        <v>235</v>
       </c>
       <c r="E41" t="s" s="0">
-        <v>12</v>
+        <v>236</v>
       </c>
       <c r="F41" t="s" s="0">
-        <v>176</v>
+        <v>14</v>
       </c>
       <c r="G41" t="s" s="0">
-        <v>181</v>
+        <v>215</v>
       </c>
       <c r="H41" t="s" s="0">
-        <v>181</v>
+        <v>221</v>
+      </c>
+      <c r="I41" t="s" s="0">
+        <v>209</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>194</v>
+        <v>237</v>
       </c>
       <c r="B42" t="s" s="0">
-        <v>195</v>
+        <v>238</v>
       </c>
       <c r="C42" t="s" s="0">
-        <v>196</v>
+        <v>239</v>
       </c>
       <c r="D42" t="s" s="0">
-        <v>197</v>
+        <v>240</v>
       </c>
       <c r="E42" t="s" s="0">
-        <v>12</v>
+        <v>241</v>
       </c>
       <c r="F42" t="s" s="0">
-        <v>176</v>
+        <v>14</v>
       </c>
       <c r="G42" t="s" s="0">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="H42" t="s" s="0">
-        <v>198</v>
+        <v>242</v>
+      </c>
+      <c r="I42" t="s" s="0">
+        <v>209</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>199</v>
+        <v>243</v>
       </c>
       <c r="B43" t="s" s="0">
-        <v>200</v>
+        <v>244</v>
       </c>
       <c r="C43" t="s" s="0">
-        <v>201</v>
+        <v>245</v>
       </c>
       <c r="D43" t="s" s="0">
-        <v>202</v>
+        <v>246</v>
       </c>
       <c r="E43" t="s" s="0">
-        <v>12</v>
+        <v>247</v>
       </c>
       <c r="F43" t="s" s="0">
-        <v>176</v>
+        <v>14</v>
       </c>
       <c r="G43" t="s" s="0">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="H43" t="s" s="0">
-        <v>198</v>
+        <v>242</v>
+      </c>
+      <c r="I43" t="s" s="0">
+        <v>209</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>203</v>
+        <v>248</v>
       </c>
       <c r="B44" t="s" s="0">
-        <v>204</v>
+        <v>249</v>
       </c>
       <c r="C44" t="s" s="0">
-        <v>205</v>
+        <v>250</v>
       </c>
       <c r="D44" t="s" s="0">
-        <v>206</v>
+        <v>251</v>
       </c>
       <c r="E44" t="s" s="0">
-        <v>12</v>
+        <v>252</v>
       </c>
       <c r="F44" t="s" s="0">
-        <v>207</v>
+        <v>14</v>
       </c>
       <c r="G44" t="s" s="0">
-        <v>198</v>
+        <v>253</v>
       </c>
       <c r="H44" t="s" s="0">
-        <v>198</v>
+        <v>242</v>
+      </c>
+      <c r="I44" t="s" s="0">
+        <v>209</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>208</v>
+        <v>254</v>
       </c>
       <c r="B45" t="s" s="0">
+        <v>255</v>
+      </c>
+      <c r="C45" t="s" s="0">
+        <v>256</v>
+      </c>
+      <c r="D45" t="s" s="0">
+        <v>257</v>
+      </c>
+      <c r="E45" t="s" s="0">
+        <v>258</v>
+      </c>
+      <c r="F45" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G45" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="H45" t="s" s="0">
+        <v>242</v>
+      </c>
+      <c r="I45" t="s" s="0">
         <v>209</v>
-      </c>
-      <c r="C45" t="s" s="0">
-        <v>210</v>
-      </c>
-      <c r="D45" t="s" s="0">
-        <v>211</v>
-      </c>
-      <c r="E45" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F45" t="s" s="0">
-        <v>207</v>
-      </c>
-      <c r="G45" t="s" s="0">
-        <v>198</v>
-      </c>
-      <c r="H45" t="s" s="0">
-        <v>198</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>212</v>
+        <v>259</v>
       </c>
       <c r="B46" t="s" s="0">
-        <v>213</v>
+        <v>260</v>
       </c>
       <c r="C46" t="s" s="0">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="D46" t="s" s="0">
-        <v>215</v>
+        <v>261</v>
       </c>
       <c r="E46" t="s" s="0">
-        <v>12</v>
+        <v>262</v>
       </c>
       <c r="F46" t="s" s="0">
-        <v>207</v>
+        <v>14</v>
       </c>
       <c r="G46" t="s" s="0">
-        <v>198</v>
+        <v>253</v>
       </c>
       <c r="H46" t="s" s="0">
-        <v>198</v>
+        <v>242</v>
+      </c>
+      <c r="I46" t="s" s="0">
+        <v>242</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>216</v>
+        <v>263</v>
       </c>
       <c r="B47" t="s" s="0">
-        <v>217</v>
+        <v>264</v>
       </c>
       <c r="C47" t="s" s="0">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="D47" t="s" s="0">
-        <v>219</v>
+        <v>265</v>
       </c>
       <c r="E47" t="s" s="0">
-        <v>12</v>
+        <v>266</v>
       </c>
       <c r="F47" t="s" s="0">
-        <v>207</v>
+        <v>14</v>
       </c>
       <c r="G47" t="s" s="0">
-        <v>220</v>
+        <v>253</v>
       </c>
       <c r="H47" t="s" s="0">
-        <v>220</v>
+        <v>267</v>
+      </c>
+      <c r="I47" t="s" s="0">
+        <v>267</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>221</v>
+        <v>268</v>
       </c>
       <c r="B48" t="s" s="0">
-        <v>222</v>
+        <v>269</v>
       </c>
       <c r="C48" t="s" s="0">
-        <v>223</v>
+        <v>270</v>
       </c>
       <c r="D48" t="s" s="0">
-        <v>224</v>
+        <v>271</v>
       </c>
       <c r="E48" t="s" s="0">
-        <v>12</v>
+        <v>272</v>
       </c>
       <c r="F48" t="s" s="0">
-        <v>225</v>
+        <v>14</v>
       </c>
       <c r="G48" t="s" s="0">
-        <v>226</v>
+        <v>273</v>
       </c>
       <c r="H48" t="s" s="0">
-        <v>226</v>
+        <v>274</v>
+      </c>
+      <c r="I48" t="s" s="0">
+        <v>275</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>227</v>
+        <v>276</v>
       </c>
       <c r="B49" t="s" s="0">
-        <v>228</v>
+        <v>277</v>
       </c>
       <c r="C49" t="s" s="0">
-        <v>229</v>
+        <v>278</v>
       </c>
       <c r="D49" t="s" s="0">
-        <v>230</v>
+        <v>279</v>
       </c>
       <c r="E49" t="s" s="0">
-        <v>12</v>
+        <v>280</v>
       </c>
       <c r="F49" t="s" s="0">
-        <v>231</v>
+        <v>14</v>
       </c>
       <c r="G49" t="s" s="0">
-        <v>226</v>
+        <v>281</v>
       </c>
       <c r="H49" t="s" s="0">
-        <v>226</v>
+        <v>274</v>
+      </c>
+      <c r="I49" t="s" s="0">
+        <v>275</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>232</v>
+        <v>282</v>
       </c>
       <c r="B50" t="s" s="0">
-        <v>233</v>
+        <v>283</v>
       </c>
       <c r="C50" t="s" s="0">
-        <v>234</v>
+        <v>284</v>
       </c>
       <c r="D50" t="s" s="0">
-        <v>235</v>
+        <v>285</v>
       </c>
       <c r="E50" t="s" s="0">
-        <v>12</v>
+        <v>286</v>
       </c>
       <c r="F50" t="s" s="0">
-        <v>231</v>
+        <v>14</v>
       </c>
       <c r="G50" t="s" s="0">
-        <v>226</v>
+        <v>281</v>
       </c>
       <c r="H50" t="s" s="0">
-        <v>226</v>
+        <v>274</v>
+      </c>
+      <c r="I50" t="s" s="0">
+        <v>275</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>236</v>
+        <v>287</v>
       </c>
       <c r="B51" t="s" s="0">
-        <v>237</v>
+        <v>288</v>
       </c>
       <c r="C51" t="s" s="0">
-        <v>238</v>
+        <v>200</v>
       </c>
       <c r="D51" t="s" s="0">
-        <v>239</v>
+        <v>289</v>
       </c>
       <c r="E51" t="s" s="0">
-        <v>12</v>
+        <v>290</v>
       </c>
       <c r="F51" t="s" s="0">
-        <v>231</v>
+        <v>14</v>
       </c>
       <c r="G51" t="s" s="0">
-        <v>240</v>
+        <v>281</v>
       </c>
       <c r="H51" t="s" s="0">
-        <v>240</v>
+        <v>291</v>
+      </c>
+      <c r="I51" t="s" s="0">
+        <v>291</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>241</v>
+        <v>292</v>
       </c>
       <c r="B52" t="s" s="0">
-        <v>242</v>
+        <v>293</v>
       </c>
       <c r="C52" t="s" s="0">
-        <v>243</v>
+        <v>294</v>
       </c>
       <c r="D52" t="s" s="0">
-        <v>244</v>
+        <v>295</v>
       </c>
       <c r="E52" t="s" s="0">
-        <v>12</v>
+        <v>296</v>
       </c>
       <c r="F52" t="s" s="0">
-        <v>245</v>
+        <v>14</v>
       </c>
       <c r="G52" t="s" s="0">
-        <v>240</v>
+        <v>297</v>
       </c>
       <c r="H52" t="s" s="0">
-        <v>240</v>
+        <v>291</v>
+      </c>
+      <c r="I52" t="s" s="0">
+        <v>275</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>246</v>
+        <v>298</v>
       </c>
       <c r="B53" t="s" s="0">
-        <v>247</v>
+        <v>299</v>
       </c>
       <c r="C53" t="s" s="0">
-        <v>248</v>
+        <v>300</v>
       </c>
       <c r="D53" t="s" s="0">
-        <v>249</v>
+        <v>301</v>
       </c>
       <c r="E53" t="s" s="0">
-        <v>12</v>
+        <v>302</v>
       </c>
       <c r="F53" t="s" s="0">
-        <v>245</v>
+        <v>14</v>
       </c>
       <c r="G53" t="s" s="0">
-        <v>240</v>
+        <v>297</v>
       </c>
       <c r="H53" t="s" s="0">
-        <v>250</v>
+        <v>291</v>
+      </c>
+      <c r="I53" t="s" s="0">
+        <v>275</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>251</v>
+        <v>303</v>
       </c>
       <c r="B54" t="s" s="0">
-        <v>252</v>
+        <v>304</v>
       </c>
       <c r="C54" t="s" s="0">
-        <v>253</v>
+        <v>305</v>
       </c>
       <c r="D54" t="s" s="0">
-        <v>254</v>
+        <v>306</v>
       </c>
       <c r="E54" t="s" s="0">
-        <v>12</v>
+        <v>307</v>
       </c>
       <c r="F54" t="s" s="0">
-        <v>255</v>
+        <v>14</v>
       </c>
       <c r="G54" t="s" s="0">
-        <v>240</v>
+        <v>308</v>
       </c>
       <c r="H54" t="s" s="0">
-        <v>240</v>
+        <v>291</v>
+      </c>
+      <c r="I54" t="s" s="0">
+        <v>275</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>256</v>
+        <v>309</v>
       </c>
       <c r="B55" t="s" s="0">
-        <v>257</v>
+        <v>310</v>
       </c>
       <c r="C55" t="s" s="0">
-        <v>258</v>
+        <v>311</v>
       </c>
       <c r="D55" t="s" s="0">
-        <v>259</v>
+        <v>312</v>
       </c>
       <c r="E55" t="s" s="0">
-        <v>12</v>
+        <v>313</v>
       </c>
       <c r="F55" t="s" s="0">
-        <v>260</v>
+        <v>14</v>
       </c>
       <c r="G55" t="s" s="0">
-        <v>261</v>
+        <v>314</v>
       </c>
       <c r="H55" t="s" s="0">
-        <v>261</v>
+        <v>315</v>
+      </c>
+      <c r="I55" t="s" s="0">
+        <v>275</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>262</v>
+        <v>316</v>
       </c>
       <c r="B56" t="s" s="0">
-        <v>263</v>
+        <v>317</v>
       </c>
       <c r="C56" t="s" s="0">
-        <v>264</v>
+        <v>318</v>
       </c>
       <c r="D56" t="s" s="0">
-        <v>265</v>
+        <v>319</v>
       </c>
       <c r="E56" t="s" s="0">
-        <v>12</v>
+        <v>320</v>
       </c>
       <c r="F56" t="s" s="0">
-        <v>266</v>
+        <v>14</v>
       </c>
       <c r="G56" t="s" s="0">
-        <v>261</v>
+        <v>321</v>
       </c>
       <c r="H56" t="s" s="0">
-        <v>261</v>
+        <v>315</v>
+      </c>
+      <c r="I56" t="s" s="0">
+        <v>275</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>267</v>
+        <v>322</v>
       </c>
       <c r="B57" t="s" s="0">
-        <v>268</v>
+        <v>323</v>
       </c>
       <c r="C57" t="s" s="0">
-        <v>269</v>
+        <v>200</v>
       </c>
       <c r="D57" t="s" s="0">
-        <v>270</v>
+        <v>324</v>
       </c>
       <c r="E57" t="s" s="0">
-        <v>12</v>
+        <v>325</v>
       </c>
       <c r="F57" t="s" s="0">
-        <v>266</v>
+        <v>14</v>
       </c>
       <c r="G57" t="s" s="0">
-        <v>261</v>
+        <v>321</v>
       </c>
       <c r="H57" t="s" s="0">
-        <v>261</v>
+        <v>315</v>
+      </c>
+      <c r="I57" t="s" s="0">
+        <v>315</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>271</v>
+        <v>326</v>
       </c>
       <c r="B58" t="s" s="0">
-        <v>272</v>
+        <v>327</v>
       </c>
       <c r="C58" t="s" s="0">
-        <v>273</v>
+        <v>328</v>
       </c>
       <c r="D58" t="s" s="0">
-        <v>274</v>
+        <v>329</v>
       </c>
       <c r="E58" t="s" s="0">
-        <v>12</v>
+        <v>330</v>
       </c>
       <c r="F58" t="s" s="0">
-        <v>266</v>
+        <v>14</v>
       </c>
       <c r="G58" t="s" s="0">
-        <v>261</v>
+        <v>321</v>
       </c>
       <c r="H58" t="s" s="0">
-        <v>261</v>
+        <v>315</v>
+      </c>
+      <c r="I58" t="s" s="0">
+        <v>275</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>275</v>
+        <v>331</v>
       </c>
       <c r="B59" t="s" s="0">
-        <v>276</v>
+        <v>332</v>
       </c>
       <c r="C59" t="s" s="0">
-        <v>277</v>
+        <v>333</v>
       </c>
       <c r="D59" t="s" s="0">
-        <v>278</v>
+        <v>334</v>
       </c>
       <c r="E59" t="s" s="0">
-        <v>12</v>
+        <v>335</v>
       </c>
       <c r="F59" t="s" s="0">
-        <v>279</v>
+        <v>14</v>
       </c>
       <c r="G59" t="s" s="0">
-        <v>280</v>
+        <v>336</v>
       </c>
       <c r="H59" t="s" s="0">
-        <v>280</v>
+        <v>337</v>
+      </c>
+      <c r="I59" t="s" s="0">
+        <v>338</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>281</v>
+        <v>339</v>
       </c>
       <c r="B60" t="s" s="0">
-        <v>282</v>
+        <v>340</v>
       </c>
       <c r="C60" t="s" s="0">
-        <v>283</v>
+        <v>341</v>
       </c>
       <c r="D60" t="s" s="0">
-        <v>284</v>
+        <v>342</v>
       </c>
       <c r="E60" t="s" s="0">
-        <v>12</v>
+        <v>343</v>
       </c>
       <c r="F60" t="s" s="0">
-        <v>279</v>
+        <v>14</v>
       </c>
       <c r="G60" t="s" s="0">
-        <v>280</v>
+        <v>336</v>
       </c>
       <c r="H60" t="s" s="0">
-        <v>280</v>
+        <v>337</v>
+      </c>
+      <c r="I60" t="s" s="0">
+        <v>275</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>285</v>
+        <v>344</v>
       </c>
       <c r="B61" t="s" s="0">
-        <v>286</v>
+        <v>345</v>
       </c>
       <c r="C61" t="s" s="0">
-        <v>287</v>
+        <v>346</v>
       </c>
       <c r="D61" t="s" s="0">
-        <v>288</v>
+        <v>347</v>
       </c>
       <c r="E61" t="s" s="0">
-        <v>12</v>
+        <v>348</v>
       </c>
       <c r="F61" t="s" s="0">
-        <v>289</v>
+        <v>14</v>
       </c>
       <c r="G61" t="s" s="0">
-        <v>280</v>
+        <v>349</v>
       </c>
       <c r="H61" t="s" s="0">
-        <v>280</v>
+        <v>337</v>
+      </c>
+      <c r="I61" t="s" s="0">
+        <v>275</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>290</v>
+        <v>350</v>
       </c>
       <c r="B62" t="s" s="0">
-        <v>291</v>
+        <v>351</v>
       </c>
       <c r="C62" t="s" s="0">
-        <v>292</v>
+        <v>352</v>
       </c>
       <c r="D62" t="s" s="0">
-        <v>293</v>
+        <v>353</v>
       </c>
       <c r="E62" t="s" s="0">
-        <v>12</v>
+        <v>354</v>
       </c>
       <c r="F62" t="s" s="0">
-        <v>289</v>
+        <v>14</v>
       </c>
       <c r="G62" t="s" s="0">
-        <v>280</v>
+        <v>349</v>
       </c>
       <c r="H62" t="s" s="0">
-        <v>280</v>
+        <v>337</v>
+      </c>
+      <c r="I62" t="s" s="0">
+        <v>275</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>294</v>
+        <v>355</v>
       </c>
       <c r="B63" t="s" s="0">
-        <v>295</v>
+        <v>356</v>
       </c>
       <c r="C63" t="s" s="0">
-        <v>296</v>
+        <v>357</v>
       </c>
       <c r="D63" t="s" s="0">
-        <v>297</v>
+        <v>358</v>
       </c>
       <c r="E63" t="s" s="0">
-        <v>12</v>
+        <v>359</v>
       </c>
       <c r="F63" t="s" s="0">
-        <v>298</v>
+        <v>14</v>
       </c>
       <c r="G63" t="s" s="0">
-        <v>299</v>
+        <v>360</v>
       </c>
       <c r="H63" t="s" s="0">
-        <v>299</v>
+        <v>361</v>
+      </c>
+      <c r="I63" t="s" s="0">
+        <v>51</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>300</v>
+        <v>362</v>
       </c>
       <c r="B64" t="s" s="0">
-        <v>301</v>
+        <v>363</v>
       </c>
       <c r="C64" t="s" s="0">
-        <v>302</v>
+        <v>364</v>
       </c>
       <c r="D64" t="s" s="0">
-        <v>303</v>
+        <v>365</v>
       </c>
       <c r="E64" t="s" s="0">
-        <v>12</v>
+        <v>366</v>
       </c>
       <c r="F64" t="s" s="0">
-        <v>304</v>
+        <v>14</v>
       </c>
       <c r="G64" t="s" s="0">
-        <v>299</v>
+        <v>367</v>
       </c>
       <c r="H64" t="s" s="0">
-        <v>299</v>
+        <v>361</v>
+      </c>
+      <c r="I64" t="s" s="0">
+        <v>51</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>305</v>
+        <v>368</v>
       </c>
       <c r="B65" t="s" s="0">
-        <v>306</v>
+        <v>369</v>
       </c>
       <c r="C65" t="s" s="0">
-        <v>307</v>
+        <v>370</v>
       </c>
       <c r="D65" t="s" s="0">
-        <v>308</v>
+        <v>371</v>
       </c>
       <c r="E65" t="s" s="0">
-        <v>12</v>
+        <v>372</v>
       </c>
       <c r="F65" t="s" s="0">
-        <v>309</v>
+        <v>14</v>
       </c>
       <c r="G65" t="s" s="0">
-        <v>299</v>
+        <v>373</v>
       </c>
       <c r="H65" t="s" s="0">
-        <v>299</v>
+        <v>361</v>
+      </c>
+      <c r="I65" t="s" s="0">
+        <v>51</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>310</v>
+        <v>374</v>
       </c>
       <c r="B66" t="s" s="0">
-        <v>311</v>
+        <v>375</v>
       </c>
       <c r="C66" t="s" s="0">
-        <v>312</v>
+        <v>376</v>
       </c>
       <c r="D66" t="s" s="0">
-        <v>313</v>
+        <v>377</v>
       </c>
       <c r="E66" t="s" s="0">
-        <v>12</v>
+        <v>378</v>
       </c>
       <c r="F66" t="s" s="0">
-        <v>314</v>
+        <v>14</v>
       </c>
       <c r="G66" t="s" s="0">
-        <v>299</v>
+        <v>379</v>
       </c>
       <c r="H66" t="s" s="0">
-        <v>299</v>
+        <v>361</v>
+      </c>
+      <c r="I66" t="s" s="0">
+        <v>51</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>315</v>
+        <v>380</v>
       </c>
       <c r="B67" t="s" s="0">
-        <v>316</v>
+        <v>381</v>
       </c>
       <c r="C67" t="s" s="0">
-        <v>317</v>
+        <v>382</v>
       </c>
       <c r="D67" t="s" s="0">
-        <v>318</v>
+        <v>383</v>
       </c>
       <c r="E67" t="s" s="0">
-        <v>12</v>
+        <v>384</v>
       </c>
       <c r="F67" t="s" s="0">
-        <v>319</v>
+        <v>14</v>
       </c>
       <c r="G67" t="s" s="0">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="H67" t="s" s="0">
-        <v>320</v>
+        <v>386</v>
+      </c>
+      <c r="I67" t="s" s="0">
+        <v>51</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>321</v>
+        <v>387</v>
       </c>
       <c r="B68" t="s" s="0">
-        <v>322</v>
+        <v>388</v>
       </c>
       <c r="C68" t="s" s="0">
-        <v>323</v>
+        <v>200</v>
       </c>
       <c r="D68" t="s" s="0">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="E68" t="s" s="0">
-        <v>12</v>
+        <v>390</v>
       </c>
       <c r="F68" t="s" s="0">
-        <v>325</v>
+        <v>14</v>
       </c>
       <c r="G68" t="s" s="0">
-        <v>320</v>
+        <v>391</v>
       </c>
       <c r="H68" t="s" s="0">
-        <v>320</v>
+        <v>386</v>
+      </c>
+      <c r="I68" t="s" s="0">
+        <v>386</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>326</v>
+        <v>392</v>
       </c>
       <c r="B69" t="s" s="0">
-        <v>327</v>
+        <v>393</v>
       </c>
       <c r="C69" t="s" s="0">
-        <v>328</v>
+        <v>394</v>
       </c>
       <c r="D69" t="s" s="0">
-        <v>329</v>
+        <v>395</v>
       </c>
       <c r="E69" t="s" s="0">
-        <v>12</v>
+        <v>396</v>
       </c>
       <c r="F69" t="s" s="0">
-        <v>330</v>
+        <v>14</v>
       </c>
       <c r="G69" t="s" s="0">
-        <v>320</v>
+        <v>397</v>
       </c>
       <c r="H69" t="s" s="0">
-        <v>320</v>
+        <v>386</v>
+      </c>
+      <c r="I69" t="s" s="0">
+        <v>51</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>331</v>
+        <v>398</v>
       </c>
       <c r="B70" t="s" s="0">
-        <v>332</v>
+        <v>399</v>
       </c>
       <c r="C70" t="s" s="0">
-        <v>333</v>
+        <v>400</v>
       </c>
       <c r="D70" t="s" s="0">
-        <v>334</v>
+        <v>401</v>
       </c>
       <c r="E70" t="s" s="0">
-        <v>12</v>
+        <v>402</v>
       </c>
       <c r="F70" t="s" s="0">
-        <v>335</v>
+        <v>14</v>
       </c>
       <c r="G70" t="s" s="0">
-        <v>320</v>
+        <v>403</v>
       </c>
       <c r="H70" t="s" s="0">
-        <v>320</v>
+        <v>386</v>
+      </c>
+      <c r="I70" t="s" s="0">
+        <v>51</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>336</v>
+        <v>404</v>
       </c>
       <c r="B71" t="s" s="0">
-        <v>337</v>
+        <v>405</v>
       </c>
       <c r="C71" t="s" s="0">
-        <v>338</v>
+        <v>406</v>
       </c>
       <c r="D71" t="s" s="0">
-        <v>339</v>
+        <v>407</v>
       </c>
       <c r="E71" t="s" s="0">
-        <v>12</v>
+        <v>408</v>
       </c>
       <c r="F71" t="s" s="0">
-        <v>340</v>
+        <v>14</v>
       </c>
       <c r="G71" t="s" s="0">
-        <v>341</v>
+        <v>409</v>
       </c>
       <c r="H71" t="s" s="0">
-        <v>341</v>
+        <v>410</v>
+      </c>
+      <c r="I71" t="s" s="0">
+        <v>51</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>342</v>
+        <v>411</v>
       </c>
       <c r="B72" t="s" s="0">
-        <v>343</v>
+        <v>412</v>
       </c>
       <c r="C72" t="s" s="0">
-        <v>344</v>
+        <v>413</v>
       </c>
       <c r="D72" t="s" s="0">
-        <v>345</v>
+        <v>414</v>
       </c>
       <c r="E72" t="s" s="0">
-        <v>12</v>
+        <v>415</v>
       </c>
       <c r="F72" t="s" s="0">
-        <v>346</v>
+        <v>14</v>
       </c>
       <c r="G72" t="s" s="0">
-        <v>341</v>
+        <v>416</v>
       </c>
       <c r="H72" t="s" s="0">
-        <v>341</v>
+        <v>410</v>
+      </c>
+      <c r="I72" t="s" s="0">
+        <v>51</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>347</v>
+        <v>417</v>
       </c>
       <c r="B73" t="s" s="0">
-        <v>348</v>
+        <v>418</v>
       </c>
       <c r="C73" t="s" s="0">
-        <v>349</v>
+        <v>200</v>
       </c>
       <c r="D73" t="s" s="0">
-        <v>350</v>
+        <v>419</v>
       </c>
       <c r="E73" t="s" s="0">
-        <v>12</v>
+        <v>420</v>
       </c>
       <c r="F73" t="s" s="0">
-        <v>351</v>
+        <v>14</v>
       </c>
       <c r="G73" t="s" s="0">
-        <v>341</v>
+        <v>421</v>
       </c>
       <c r="H73" t="s" s="0">
-        <v>341</v>
+        <v>410</v>
+      </c>
+      <c r="I73" t="s" s="0">
+        <v>410</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>352</v>
+        <v>422</v>
       </c>
       <c r="B74" t="s" s="0">
-        <v>353</v>
+        <v>423</v>
       </c>
       <c r="C74" t="s" s="0">
-        <v>354</v>
+        <v>424</v>
       </c>
       <c r="D74" t="s" s="0">
-        <v>355</v>
+        <v>425</v>
       </c>
       <c r="E74" t="s" s="0">
-        <v>12</v>
+        <v>426</v>
       </c>
       <c r="F74" t="s" s="0">
-        <v>356</v>
+        <v>14</v>
       </c>
       <c r="G74" t="s" s="0">
-        <v>341</v>
+        <v>427</v>
       </c>
       <c r="H74" t="s" s="0">
-        <v>357</v>
+        <v>410</v>
+      </c>
+      <c r="I74" t="s" s="0">
+        <v>338</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>358</v>
+        <v>428</v>
       </c>
       <c r="B75" t="s" s="0">
-        <v>359</v>
+        <v>429</v>
       </c>
       <c r="C75" t="s" s="0">
-        <v>360</v>
+        <v>430</v>
       </c>
       <c r="D75" t="s" s="0">
-        <v>361</v>
+        <v>431</v>
       </c>
       <c r="E75" t="s" s="0">
-        <v>12</v>
+        <v>432</v>
       </c>
       <c r="F75" t="s" s="0">
-        <v>362</v>
+        <v>14</v>
       </c>
       <c r="G75" t="s" s="0">
-        <v>363</v>
+        <v>433</v>
       </c>
       <c r="H75" t="s" s="0">
-        <v>363</v>
+        <v>434</v>
+      </c>
+      <c r="I75" t="s" s="0">
+        <v>338</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>364</v>
+        <v>435</v>
       </c>
       <c r="B76" t="s" s="0">
-        <v>365</v>
+        <v>436</v>
       </c>
       <c r="C76" t="s" s="0">
-        <v>366</v>
+        <v>437</v>
       </c>
       <c r="D76" t="s" s="0">
-        <v>367</v>
+        <v>438</v>
       </c>
       <c r="E76" t="s" s="0">
-        <v>12</v>
+        <v>439</v>
       </c>
       <c r="F76" t="s" s="0">
-        <v>314</v>
+        <v>14</v>
       </c>
       <c r="G76" t="s" s="0">
-        <v>363</v>
+        <v>379</v>
       </c>
       <c r="H76" t="s" s="0">
-        <v>363</v>
+        <v>434</v>
+      </c>
+      <c r="I76" t="s" s="0">
+        <v>338</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>368</v>
+        <v>440</v>
       </c>
       <c r="B77" t="s" s="0">
-        <v>369</v>
+        <v>441</v>
       </c>
       <c r="C77" t="s" s="0">
-        <v>370</v>
+        <v>442</v>
       </c>
       <c r="D77" t="s" s="0">
-        <v>371</v>
+        <v>443</v>
       </c>
       <c r="E77" t="s" s="0">
-        <v>12</v>
+        <v>444</v>
       </c>
       <c r="F77" t="s" s="0">
-        <v>372</v>
+        <v>14</v>
       </c>
       <c r="G77" t="s" s="0">
-        <v>363</v>
+        <v>445</v>
       </c>
       <c r="H77" t="s" s="0">
-        <v>363</v>
+        <v>434</v>
+      </c>
+      <c r="I77" t="s" s="0">
+        <v>338</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>373</v>
+        <v>446</v>
       </c>
       <c r="B78" t="s" s="0">
-        <v>374</v>
+        <v>447</v>
       </c>
       <c r="C78" t="s" s="0">
-        <v>375</v>
+        <v>448</v>
       </c>
       <c r="D78" t="s" s="0">
-        <v>376</v>
+        <v>449</v>
       </c>
       <c r="E78" t="s" s="0">
-        <v>12</v>
+        <v>450</v>
       </c>
       <c r="F78" t="s" s="0">
-        <v>377</v>
+        <v>14</v>
       </c>
       <c r="G78" t="s" s="0">
-        <v>363</v>
+        <v>451</v>
       </c>
       <c r="H78" t="s" s="0">
-        <v>363</v>
+        <v>434</v>
+      </c>
+      <c r="I78" t="s" s="0">
+        <v>338</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>378</v>
+        <v>452</v>
       </c>
       <c r="B79" t="s" s="0">
-        <v>379</v>
+        <v>453</v>
       </c>
       <c r="C79" t="s" s="0">
-        <v>380</v>
+        <v>454</v>
       </c>
       <c r="D79" t="s" s="0">
-        <v>381</v>
+        <v>455</v>
       </c>
       <c r="E79" t="s" s="0">
-        <v>12</v>
+        <v>456</v>
       </c>
       <c r="F79" t="s" s="0">
-        <v>382</v>
+        <v>14</v>
       </c>
       <c r="G79" t="s" s="0">
-        <v>383</v>
+        <v>457</v>
       </c>
       <c r="H79" t="s" s="0">
-        <v>383</v>
+        <v>458</v>
+      </c>
+      <c r="I79" t="s" s="0">
+        <v>338</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>384</v>
+        <v>459</v>
       </c>
       <c r="B80" t="s" s="0">
+        <v>460</v>
+      </c>
+      <c r="C80" t="s" s="0">
+        <v>200</v>
+      </c>
+      <c r="D80" t="s" s="0">
+        <v>461</v>
+      </c>
+      <c r="E80" t="s" s="0">
+        <v>462</v>
+      </c>
+      <c r="F80" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G80" t="s" s="0">
         <v>385</v>
       </c>
-      <c r="C80" t="s" s="0">
-        <v>386</v>
-      </c>
-      <c r="D80" t="s" s="0">
-        <v>387</v>
-      </c>
-      <c r="E80" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F80" t="s" s="0">
-        <v>319</v>
-      </c>
-      <c r="G80" t="s" s="0">
-        <v>388</v>
-      </c>
       <c r="H80" t="s" s="0">
-        <v>388</v>
+        <v>463</v>
+      </c>
+      <c r="I80" t="s" s="0">
+        <v>463</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>389</v>
+        <v>464</v>
       </c>
       <c r="B81" t="s" s="0">
-        <v>390</v>
+        <v>465</v>
       </c>
       <c r="C81" t="s" s="0">
-        <v>391</v>
+        <v>466</v>
       </c>
       <c r="D81" t="s" s="0">
-        <v>392</v>
+        <v>467</v>
       </c>
       <c r="E81" t="s" s="0">
-        <v>12</v>
+        <v>468</v>
       </c>
       <c r="F81" t="s" s="0">
-        <v>393</v>
+        <v>14</v>
       </c>
       <c r="G81" t="s" s="0">
-        <v>388</v>
+        <v>469</v>
       </c>
       <c r="H81" t="s" s="0">
-        <v>388</v>
+        <v>463</v>
+      </c>
+      <c r="I81" t="s" s="0">
+        <v>338</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>394</v>
+        <v>470</v>
       </c>
       <c r="B82" t="s" s="0">
-        <v>395</v>
+        <v>471</v>
       </c>
       <c r="C82" t="s" s="0">
-        <v>396</v>
+        <v>200</v>
       </c>
       <c r="D82" t="s" s="0">
-        <v>397</v>
+        <v>472</v>
       </c>
       <c r="E82" t="s" s="0">
-        <v>12</v>
+        <v>473</v>
       </c>
       <c r="F82" t="s" s="0">
-        <v>398</v>
+        <v>14</v>
       </c>
       <c r="G82" t="s" s="0">
-        <v>388</v>
+        <v>474</v>
       </c>
       <c r="H82" t="s" s="0">
-        <v>388</v>
+        <v>463</v>
+      </c>
+      <c r="I82" t="s" s="0">
+        <v>463</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>399</v>
+        <v>475</v>
       </c>
       <c r="B83" t="s" s="0">
-        <v>400</v>
+        <v>476</v>
       </c>
       <c r="C83" t="s" s="0">
-        <v>401</v>
+        <v>477</v>
       </c>
       <c r="D83" t="s" s="0">
-        <v>402</v>
+        <v>478</v>
       </c>
       <c r="E83" t="s" s="0">
-        <v>12</v>
+        <v>479</v>
       </c>
       <c r="F83" t="s" s="0">
-        <v>403</v>
+        <v>14</v>
       </c>
       <c r="G83" t="s" s="0">
-        <v>404</v>
+        <v>480</v>
       </c>
       <c r="H83" t="s" s="0">
-        <v>404</v>
+        <v>481</v>
+      </c>
+      <c r="I83" t="s" s="0">
+        <v>338</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>405</v>
+        <v>482</v>
       </c>
       <c r="B84" t="s" s="0">
-        <v>406</v>
+        <v>483</v>
       </c>
       <c r="C84" t="s" s="0">
-        <v>407</v>
+        <v>200</v>
       </c>
       <c r="D84" t="s" s="0">
-        <v>408</v>
+        <v>484</v>
       </c>
       <c r="E84" t="s" s="0">
-        <v>12</v>
+        <v>485</v>
       </c>
       <c r="F84" t="s" s="0">
-        <v>403</v>
+        <v>14</v>
       </c>
       <c r="G84" t="s" s="0">
-        <v>404</v>
+        <v>480</v>
       </c>
       <c r="H84" t="s" s="0">
-        <v>404</v>
+        <v>481</v>
+      </c>
+      <c r="I84" t="s" s="0">
+        <v>481</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
-        <v>409</v>
+        <v>486</v>
       </c>
       <c r="B85" t="s" s="0">
-        <v>410</v>
+        <v>487</v>
       </c>
       <c r="C85" t="s" s="0">
-        <v>411</v>
+        <v>488</v>
       </c>
       <c r="D85" t="s" s="0">
-        <v>412</v>
+        <v>489</v>
       </c>
       <c r="E85" t="s" s="0">
-        <v>12</v>
+        <v>490</v>
       </c>
       <c r="F85" t="s" s="0">
-        <v>413</v>
+        <v>14</v>
       </c>
       <c r="G85" t="s" s="0">
-        <v>404</v>
+        <v>491</v>
       </c>
       <c r="H85" t="s" s="0">
-        <v>404</v>
+        <v>481</v>
+      </c>
+      <c r="I85" t="s" s="0">
+        <v>338</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="0">
-        <v>414</v>
+        <v>492</v>
       </c>
       <c r="B86" t="s" s="0">
-        <v>415</v>
+        <v>493</v>
       </c>
       <c r="C86" t="s" s="0">
-        <v>416</v>
+        <v>200</v>
       </c>
       <c r="D86" t="s" s="0">
-        <v>417</v>
+        <v>494</v>
       </c>
       <c r="E86" t="s" s="0">
-        <v>12</v>
+        <v>495</v>
       </c>
       <c r="F86" t="s" s="0">
-        <v>418</v>
+        <v>14</v>
       </c>
       <c r="G86" t="s" s="0">
-        <v>404</v>
+        <v>496</v>
       </c>
       <c r="H86" t="s" s="0">
-        <v>404</v>
+        <v>481</v>
+      </c>
+      <c r="I86" t="s" s="0">
+        <v>481</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="0">
-        <v>419</v>
+        <v>497</v>
       </c>
       <c r="B87" t="s" s="0">
-        <v>420</v>
+        <v>498</v>
       </c>
       <c r="C87" t="s" s="0">
-        <v>421</v>
+        <v>499</v>
       </c>
       <c r="D87" t="s" s="0">
-        <v>422</v>
+        <v>500</v>
       </c>
       <c r="E87" t="s" s="0">
-        <v>12</v>
+        <v>501</v>
       </c>
       <c r="F87" t="s" s="0">
-        <v>423</v>
+        <v>14</v>
       </c>
       <c r="G87" t="s" s="0">
-        <v>424</v>
+        <v>502</v>
       </c>
       <c r="H87" t="s" s="0">
-        <v>424</v>
+        <v>503</v>
+      </c>
+      <c r="I87" t="s" s="0">
+        <v>504</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="0">
-        <v>425</v>
+        <v>505</v>
       </c>
       <c r="B88" t="s" s="0">
-        <v>426</v>
+        <v>506</v>
       </c>
       <c r="C88" t="s" s="0">
-        <v>427</v>
+        <v>200</v>
       </c>
       <c r="D88" t="s" s="0">
-        <v>428</v>
+        <v>507</v>
       </c>
       <c r="E88" t="s" s="0">
-        <v>12</v>
+        <v>508</v>
       </c>
       <c r="F88" t="s" s="0">
-        <v>429</v>
+        <v>14</v>
       </c>
       <c r="G88" t="s" s="0">
-        <v>424</v>
+        <v>509</v>
       </c>
       <c r="H88" t="s" s="0">
-        <v>424</v>
+        <v>503</v>
+      </c>
+      <c r="I88" t="s" s="0">
+        <v>503</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="0">
-        <v>430</v>
+        <v>510</v>
       </c>
       <c r="B89" t="s" s="0">
-        <v>431</v>
+        <v>511</v>
       </c>
       <c r="C89" t="s" s="0">
-        <v>432</v>
+        <v>512</v>
       </c>
       <c r="D89" t="s" s="0">
-        <v>433</v>
+        <v>513</v>
       </c>
       <c r="E89" t="s" s="0">
-        <v>12</v>
+        <v>514</v>
       </c>
       <c r="F89" t="s" s="0">
-        <v>434</v>
+        <v>14</v>
       </c>
       <c r="G89" t="s" s="0">
-        <v>424</v>
+        <v>515</v>
       </c>
       <c r="H89" t="s" s="0">
-        <v>424</v>
+        <v>503</v>
+      </c>
+      <c r="I89" t="s" s="0">
+        <v>516</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="0">
-        <v>435</v>
+        <v>517</v>
       </c>
       <c r="B90" t="s" s="0">
-        <v>436</v>
+        <v>518</v>
       </c>
       <c r="C90" t="s" s="0">
-        <v>437</v>
+        <v>519</v>
       </c>
       <c r="D90" t="s" s="0">
-        <v>438</v>
+        <v>520</v>
       </c>
       <c r="E90" t="s" s="0">
-        <v>12</v>
+        <v>521</v>
       </c>
       <c r="F90" t="s" s="0">
-        <v>434</v>
+        <v>14</v>
       </c>
       <c r="G90" t="s" s="0">
-        <v>424</v>
+        <v>515</v>
       </c>
       <c r="H90" t="s" s="0">
-        <v>424</v>
+        <v>503</v>
+      </c>
+      <c r="I90" t="s" s="0">
+        <v>516</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="0">
-        <v>439</v>
+        <v>522</v>
       </c>
       <c r="B91" t="s" s="0">
-        <v>440</v>
+        <v>523</v>
       </c>
       <c r="C91" t="s" s="0">
-        <v>441</v>
+        <v>524</v>
       </c>
       <c r="D91" t="s" s="0">
-        <v>442</v>
+        <v>525</v>
       </c>
       <c r="E91" t="s" s="0">
-        <v>12</v>
+        <v>526</v>
       </c>
       <c r="F91" t="s" s="0">
-        <v>434</v>
+        <v>14</v>
       </c>
       <c r="G91" t="s" s="0">
-        <v>443</v>
+        <v>515</v>
       </c>
       <c r="H91" t="s" s="0">
-        <v>443</v>
+        <v>527</v>
+      </c>
+      <c r="I91" t="s" s="0">
+        <v>516</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="0">
-        <v>444</v>
+        <v>528</v>
       </c>
       <c r="B92" t="s" s="0">
-        <v>445</v>
+        <v>529</v>
       </c>
       <c r="C92" t="s" s="0">
-        <v>446</v>
+        <v>530</v>
       </c>
       <c r="D92" t="s" s="0">
-        <v>447</v>
+        <v>531</v>
       </c>
       <c r="E92" t="s" s="0">
-        <v>12</v>
+        <v>532</v>
       </c>
       <c r="F92" t="s" s="0">
-        <v>434</v>
+        <v>14</v>
       </c>
       <c r="G92" t="s" s="0">
-        <v>443</v>
+        <v>515</v>
       </c>
       <c r="H92" t="s" s="0">
-        <v>443</v>
+        <v>527</v>
+      </c>
+      <c r="I92" t="s" s="0">
+        <v>516</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="0">
-        <v>448</v>
+        <v>533</v>
       </c>
       <c r="B93" t="s" s="0">
-        <v>449</v>
+        <v>534</v>
       </c>
       <c r="C93" t="s" s="0">
-        <v>450</v>
+        <v>200</v>
       </c>
       <c r="D93" t="s" s="0">
-        <v>451</v>
+        <v>535</v>
       </c>
       <c r="E93" t="s" s="0">
-        <v>12</v>
+        <v>536</v>
       </c>
       <c r="F93" t="s" s="0">
-        <v>434</v>
+        <v>14</v>
       </c>
       <c r="G93" t="s" s="0">
-        <v>443</v>
+        <v>515</v>
       </c>
       <c r="H93" t="s" s="0">
-        <v>443</v>
+        <v>527</v>
+      </c>
+      <c r="I93" t="s" s="0">
+        <v>527</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="0">
-        <v>452</v>
+        <v>537</v>
       </c>
       <c r="B94" t="s" s="0">
-        <v>453</v>
+        <v>538</v>
       </c>
       <c r="C94" t="s" s="0">
-        <v>454</v>
+        <v>539</v>
       </c>
       <c r="D94" t="s" s="0">
-        <v>455</v>
+        <v>540</v>
       </c>
       <c r="E94" t="s" s="0">
-        <v>12</v>
+        <v>541</v>
       </c>
       <c r="F94" t="s" s="0">
-        <v>434</v>
+        <v>14</v>
       </c>
       <c r="G94" t="s" s="0">
-        <v>443</v>
+        <v>515</v>
       </c>
       <c r="H94" t="s" s="0">
-        <v>443</v>
+        <v>527</v>
+      </c>
+      <c r="I94" t="s" s="0">
+        <v>17</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="0">
-        <v>456</v>
+        <v>542</v>
       </c>
       <c r="B95" t="s" s="0">
-        <v>457</v>
+        <v>543</v>
       </c>
       <c r="C95" t="s" s="0">
-        <v>458</v>
+        <v>544</v>
       </c>
       <c r="D95" t="s" s="0">
-        <v>459</v>
+        <v>545</v>
       </c>
       <c r="E95" t="s" s="0">
-        <v>12</v>
+        <v>546</v>
       </c>
       <c r="F95" t="s" s="0">
-        <v>434</v>
+        <v>14</v>
       </c>
       <c r="G95" t="s" s="0">
-        <v>443</v>
+        <v>515</v>
       </c>
       <c r="H95" t="s" s="0">
-        <v>443</v>
+        <v>527</v>
+      </c>
+      <c r="I95" t="s" s="0">
+        <v>516</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="0">
-        <v>460</v>
+        <v>547</v>
       </c>
       <c r="B96" t="s" s="0">
-        <v>461</v>
+        <v>548</v>
       </c>
       <c r="C96" t="s" s="0">
-        <v>462</v>
+        <v>549</v>
       </c>
       <c r="D96" t="s" s="0">
-        <v>463</v>
+        <v>550</v>
       </c>
       <c r="E96" t="s" s="0">
-        <v>12</v>
+        <v>551</v>
       </c>
       <c r="F96" t="s" s="0">
-        <v>434</v>
+        <v>14</v>
       </c>
       <c r="G96" t="s" s="0">
-        <v>464</v>
+        <v>515</v>
       </c>
       <c r="H96" t="s" s="0">
-        <v>464</v>
+        <v>552</v>
+      </c>
+      <c r="I96" t="s" s="0">
+        <v>17</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="0">
-        <v>465</v>
+        <v>553</v>
       </c>
       <c r="B97" t="s" s="0">
-        <v>466</v>
+        <v>554</v>
       </c>
       <c r="C97" t="s" s="0">
-        <v>467</v>
+        <v>555</v>
       </c>
       <c r="D97" t="s" s="0">
-        <v>468</v>
+        <v>556</v>
       </c>
       <c r="E97" t="s" s="0">
-        <v>12</v>
+        <v>557</v>
       </c>
       <c r="F97" t="s" s="0">
-        <v>434</v>
+        <v>14</v>
       </c>
       <c r="G97" t="s" s="0">
-        <v>464</v>
+        <v>515</v>
       </c>
       <c r="H97" t="s" s="0">
-        <v>464</v>
+        <v>552</v>
+      </c>
+      <c r="I97" t="s" s="0">
+        <v>516</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="0">
-        <v>469</v>
+        <v>558</v>
       </c>
       <c r="B98" t="s" s="0">
-        <v>470</v>
+        <v>559</v>
       </c>
       <c r="C98" t="s" s="0">
-        <v>471</v>
+        <v>560</v>
       </c>
       <c r="D98" t="s" s="0">
-        <v>472</v>
+        <v>561</v>
       </c>
       <c r="E98" t="s" s="0">
-        <v>12</v>
+        <v>562</v>
       </c>
       <c r="F98" t="s" s="0">
-        <v>434</v>
+        <v>14</v>
       </c>
       <c r="G98" t="s" s="0">
-        <v>464</v>
+        <v>515</v>
       </c>
       <c r="H98" t="s" s="0">
-        <v>464</v>
+        <v>552</v>
+      </c>
+      <c r="I98" t="s" s="0">
+        <v>516</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="0">
-        <v>473</v>
+        <v>563</v>
       </c>
       <c r="B99" t="s" s="0">
-        <v>474</v>
+        <v>564</v>
       </c>
       <c r="C99" t="s" s="0">
-        <v>475</v>
+        <v>565</v>
       </c>
       <c r="D99" t="s" s="0">
-        <v>476</v>
+        <v>566</v>
       </c>
       <c r="E99" t="s" s="0">
-        <v>12</v>
+        <v>567</v>
       </c>
       <c r="F99" t="s" s="0">
-        <v>434</v>
+        <v>14</v>
       </c>
       <c r="G99" t="s" s="0">
-        <v>464</v>
+        <v>515</v>
       </c>
       <c r="H99" t="s" s="0">
-        <v>464</v>
+        <v>552</v>
+      </c>
+      <c r="I99" t="s" s="0">
+        <v>516</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="0">
-        <v>477</v>
+        <v>568</v>
       </c>
       <c r="B100" t="s" s="0">
-        <v>478</v>
+        <v>569</v>
       </c>
       <c r="C100" t="s" s="0">
-        <v>479</v>
+        <v>570</v>
       </c>
       <c r="D100" t="s" s="0">
-        <v>480</v>
+        <v>571</v>
       </c>
       <c r="E100" t="s" s="0">
-        <v>12</v>
+        <v>572</v>
       </c>
       <c r="F100" t="s" s="0">
-        <v>434</v>
+        <v>14</v>
       </c>
       <c r="G100" t="s" s="0">
-        <v>481</v>
+        <v>515</v>
       </c>
       <c r="H100" t="s" s="0">
-        <v>481</v>
+        <v>573</v>
+      </c>
+      <c r="I100" t="s" s="0">
+        <v>516</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="0">
-        <v>482</v>
+        <v>574</v>
       </c>
       <c r="B101" t="s" s="0">
-        <v>483</v>
+        <v>575</v>
       </c>
       <c r="C101" t="s" s="0">
-        <v>484</v>
+        <v>576</v>
       </c>
       <c r="D101" t="s" s="0">
-        <v>485</v>
+        <v>577</v>
       </c>
       <c r="E101" t="s" s="0">
-        <v>12</v>
+        <v>578</v>
       </c>
       <c r="F101" t="s" s="0">
-        <v>434</v>
+        <v>14</v>
       </c>
       <c r="G101" t="s" s="0">
-        <v>481</v>
+        <v>515</v>
       </c>
       <c r="H101" t="s" s="0">
-        <v>481</v>
+        <v>573</v>
+      </c>
+      <c r="I101" t="s" s="0">
+        <v>516</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="0">
-        <v>486</v>
+        <v>579</v>
       </c>
       <c r="B102" t="s" s="0">
-        <v>487</v>
+        <v>580</v>
       </c>
       <c r="C102" t="s" s="0">
-        <v>488</v>
+        <v>581</v>
       </c>
       <c r="D102" t="s" s="0">
-        <v>489</v>
+        <v>582</v>
       </c>
       <c r="E102" t="s" s="0">
-        <v>12</v>
+        <v>583</v>
       </c>
       <c r="F102" t="s" s="0">
-        <v>490</v>
+        <v>14</v>
       </c>
       <c r="G102" t="s" s="0">
-        <v>481</v>
+        <v>584</v>
       </c>
       <c r="H102" t="s" s="0">
-        <v>481</v>
+        <v>573</v>
+      </c>
+      <c r="I102" t="s" s="0">
+        <v>17</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="0">
-        <v>491</v>
+        <v>585</v>
       </c>
       <c r="B103" t="s" s="0">
-        <v>492</v>
+        <v>586</v>
       </c>
       <c r="C103" t="s" s="0">
-        <v>493</v>
+        <v>587</v>
       </c>
       <c r="D103" t="s" s="0">
-        <v>494</v>
+        <v>588</v>
       </c>
       <c r="E103" t="s" s="0">
-        <v>12</v>
+        <v>589</v>
       </c>
       <c r="F103" t="s" s="0">
-        <v>495</v>
+        <v>14</v>
       </c>
       <c r="G103" t="s" s="0">
-        <v>481</v>
+        <v>590</v>
       </c>
       <c r="H103" t="s" s="0">
-        <v>481</v>
+        <v>573</v>
+      </c>
+      <c r="I103" t="s" s="0">
+        <v>504</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="0">
-        <v>496</v>
+        <v>591</v>
       </c>
       <c r="B104" t="s" s="0">
-        <v>497</v>
+        <v>592</v>
       </c>
       <c r="C104" t="s" s="0">
-        <v>498</v>
+        <v>593</v>
       </c>
       <c r="D104" t="s" s="0">
-        <v>499</v>
+        <v>594</v>
       </c>
       <c r="E104" t="s" s="0">
-        <v>12</v>
+        <v>595</v>
       </c>
       <c r="F104" t="s" s="0">
-        <v>500</v>
+        <v>14</v>
       </c>
       <c r="G104" t="s" s="0">
-        <v>501</v>
+        <v>596</v>
       </c>
       <c r="H104" t="s" s="0">
-        <v>501</v>
+        <v>597</v>
+      </c>
+      <c r="I104" t="s" s="0">
+        <v>504</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="0">
-        <v>502</v>
+        <v>598</v>
       </c>
       <c r="B105" t="s" s="0">
-        <v>503</v>
+        <v>599</v>
       </c>
       <c r="C105" t="s" s="0">
-        <v>504</v>
+        <v>200</v>
       </c>
       <c r="D105" t="s" s="0">
-        <v>505</v>
+        <v>600</v>
       </c>
       <c r="E105" t="s" s="0">
-        <v>12</v>
+        <v>601</v>
       </c>
       <c r="F105" t="s" s="0">
-        <v>500</v>
+        <v>14</v>
       </c>
       <c r="G105" t="s" s="0">
-        <v>501</v>
+        <v>596</v>
       </c>
       <c r="H105" t="s" s="0">
-        <v>501</v>
+        <v>597</v>
+      </c>
+      <c r="I105" t="s" s="0">
+        <v>597</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="0">
-        <v>506</v>
+        <v>602</v>
       </c>
       <c r="B106" t="s" s="0">
-        <v>507</v>
+        <v>603</v>
       </c>
       <c r="C106" t="s" s="0">
-        <v>508</v>
+        <v>604</v>
       </c>
       <c r="D106" t="s" s="0">
-        <v>509</v>
+        <v>605</v>
       </c>
       <c r="E106" t="s" s="0">
-        <v>12</v>
+        <v>606</v>
       </c>
       <c r="F106" t="s" s="0">
-        <v>500</v>
+        <v>14</v>
       </c>
       <c r="G106" t="s" s="0">
-        <v>501</v>
+        <v>596</v>
       </c>
       <c r="H106" t="s" s="0">
-        <v>501</v>
+        <v>597</v>
+      </c>
+      <c r="I106" t="s" s="0">
+        <v>504</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="0">
-        <v>510</v>
+        <v>607</v>
       </c>
       <c r="B107" t="s" s="0">
-        <v>511</v>
+        <v>608</v>
       </c>
       <c r="C107" t="s" s="0">
-        <v>512</v>
+        <v>609</v>
       </c>
       <c r="D107" t="s" s="0">
-        <v>513</v>
+        <v>610</v>
       </c>
       <c r="E107" t="s" s="0">
-        <v>12</v>
+        <v>611</v>
       </c>
       <c r="F107" t="s" s="0">
-        <v>500</v>
+        <v>14</v>
       </c>
       <c r="G107" t="s" s="0">
-        <v>501</v>
+        <v>596</v>
       </c>
       <c r="H107" t="s" s="0">
-        <v>501</v>
+        <v>597</v>
+      </c>
+      <c r="I107" t="s" s="0">
+        <v>504</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="0">
-        <v>514</v>
+        <v>612</v>
       </c>
       <c r="B108" t="s" s="0">
-        <v>515</v>
+        <v>613</v>
       </c>
       <c r="C108" t="s" s="0">
-        <v>516</v>
+        <v>614</v>
       </c>
       <c r="D108" t="s" s="0">
-        <v>517</v>
+        <v>615</v>
       </c>
       <c r="E108" t="s" s="0">
-        <v>12</v>
+        <v>616</v>
       </c>
       <c r="F108" t="s" s="0">
-        <v>500</v>
+        <v>14</v>
       </c>
       <c r="G108" t="s" s="0">
-        <v>518</v>
+        <v>596</v>
       </c>
       <c r="H108" t="s" s="0">
-        <v>518</v>
+        <v>617</v>
+      </c>
+      <c r="I108" t="s" s="0">
+        <v>504</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="0">
-        <v>519</v>
+        <v>618</v>
       </c>
       <c r="B109" t="s" s="0">
-        <v>520</v>
+        <v>619</v>
       </c>
       <c r="C109" t="s" s="0">
-        <v>521</v>
+        <v>620</v>
       </c>
       <c r="D109" t="s" s="0">
-        <v>522</v>
+        <v>621</v>
       </c>
       <c r="E109" t="s" s="0">
-        <v>12</v>
+        <v>622</v>
       </c>
       <c r="F109" t="s" s="0">
-        <v>500</v>
+        <v>14</v>
       </c>
       <c r="G109" t="s" s="0">
-        <v>518</v>
+        <v>596</v>
       </c>
       <c r="H109" t="s" s="0">
-        <v>518</v>
+        <v>617</v>
+      </c>
+      <c r="I109" t="s" s="0">
+        <v>504</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="0">
-        <v>523</v>
+        <v>623</v>
       </c>
       <c r="B110" t="s" s="0">
-        <v>524</v>
+        <v>624</v>
       </c>
       <c r="C110" t="s" s="0">
-        <v>525</v>
+        <v>625</v>
       </c>
       <c r="D110" t="s" s="0">
-        <v>526</v>
+        <v>626</v>
       </c>
       <c r="E110" t="s" s="0">
-        <v>12</v>
+        <v>627</v>
       </c>
       <c r="F110" t="s" s="0">
-        <v>500</v>
+        <v>14</v>
       </c>
       <c r="G110" t="s" s="0">
-        <v>518</v>
+        <v>596</v>
       </c>
       <c r="H110" t="s" s="0">
-        <v>518</v>
+        <v>617</v>
+      </c>
+      <c r="I110" t="s" s="0">
+        <v>504</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="0">
-        <v>527</v>
+        <v>628</v>
       </c>
       <c r="B111" t="s" s="0">
-        <v>528</v>
+        <v>629</v>
       </c>
       <c r="C111" t="s" s="0">
-        <v>529</v>
+        <v>630</v>
       </c>
       <c r="D111" t="s" s="0">
-        <v>530</v>
+        <v>631</v>
       </c>
       <c r="E111" t="s" s="0">
-        <v>12</v>
+        <v>632</v>
       </c>
       <c r="F111" t="s" s="0">
-        <v>500</v>
+        <v>14</v>
       </c>
       <c r="G111" t="s" s="0">
-        <v>518</v>
+        <v>596</v>
       </c>
       <c r="H111" t="s" s="0">
-        <v>518</v>
+        <v>617</v>
+      </c>
+      <c r="I111" t="s" s="0">
+        <v>633</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="0">
-        <v>531</v>
+        <v>634</v>
       </c>
       <c r="B112" t="s" s="0">
-        <v>532</v>
+        <v>635</v>
       </c>
       <c r="C112" t="s" s="0">
-        <v>533</v>
+        <v>636</v>
       </c>
       <c r="D112" t="s" s="0">
-        <v>534</v>
+        <v>637</v>
       </c>
       <c r="E112" t="s" s="0">
-        <v>12</v>
+        <v>638</v>
       </c>
       <c r="F112" t="s" s="0">
-        <v>500</v>
+        <v>14</v>
       </c>
       <c r="G112" t="s" s="0">
-        <v>535</v>
+        <v>596</v>
       </c>
       <c r="H112" t="s" s="0">
-        <v>535</v>
+        <v>639</v>
+      </c>
+      <c r="I112" t="s" s="0">
+        <v>504</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="0">
-        <v>536</v>
+        <v>640</v>
       </c>
       <c r="B113" t="s" s="0">
-        <v>537</v>
+        <v>641</v>
       </c>
       <c r="C113" t="s" s="0">
-        <v>538</v>
+        <v>642</v>
       </c>
       <c r="D113" t="s" s="0">
-        <v>539</v>
+        <v>643</v>
       </c>
       <c r="E113" t="s" s="0">
-        <v>12</v>
+        <v>644</v>
       </c>
       <c r="F113" t="s" s="0">
-        <v>500</v>
+        <v>14</v>
       </c>
       <c r="G113" t="s" s="0">
-        <v>535</v>
+        <v>596</v>
       </c>
       <c r="H113" t="s" s="0">
-        <v>535</v>
+        <v>639</v>
+      </c>
+      <c r="I113" t="s" s="0">
+        <v>504</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="0">
-        <v>540</v>
+        <v>645</v>
       </c>
       <c r="B114" t="s" s="0">
-        <v>541</v>
+        <v>646</v>
       </c>
       <c r="C114" t="s" s="0">
-        <v>542</v>
+        <v>647</v>
       </c>
       <c r="D114" t="s" s="0">
-        <v>543</v>
+        <v>648</v>
       </c>
       <c r="E114" t="s" s="0">
-        <v>12</v>
+        <v>649</v>
       </c>
       <c r="F114" t="s" s="0">
-        <v>544</v>
+        <v>14</v>
       </c>
       <c r="G114" t="s" s="0">
-        <v>545</v>
+        <v>650</v>
       </c>
       <c r="H114" t="s" s="0">
-        <v>545</v>
+        <v>651</v>
+      </c>
+      <c r="I114" t="s" s="0">
+        <v>633</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="0">
-        <v>546</v>
+        <v>652</v>
       </c>
       <c r="B115" t="s" s="0">
-        <v>547</v>
+        <v>653</v>
       </c>
       <c r="C115" t="s" s="0">
-        <v>548</v>
+        <v>654</v>
       </c>
       <c r="D115" t="s" s="0">
-        <v>549</v>
+        <v>655</v>
       </c>
       <c r="E115" t="s" s="0">
-        <v>12</v>
+        <v>656</v>
       </c>
       <c r="F115" t="s" s="0">
-        <v>550</v>
+        <v>14</v>
       </c>
       <c r="G115" t="s" s="0">
-        <v>545</v>
+        <v>657</v>
       </c>
       <c r="H115" t="s" s="0">
-        <v>545</v>
+        <v>651</v>
+      </c>
+      <c r="I115" t="s" s="0">
+        <v>633</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="0">
-        <v>551</v>
+        <v>658</v>
       </c>
       <c r="B116" t="s" s="0">
-        <v>552</v>
+        <v>659</v>
       </c>
       <c r="C116" t="s" s="0">
-        <v>553</v>
+        <v>660</v>
       </c>
       <c r="D116" t="s" s="0">
-        <v>554</v>
+        <v>661</v>
       </c>
       <c r="E116" t="s" s="0">
-        <v>12</v>
+        <v>662</v>
       </c>
       <c r="F116" t="s" s="0">
-        <v>555</v>
+        <v>14</v>
       </c>
       <c r="G116" t="s" s="0">
-        <v>556</v>
+        <v>663</v>
       </c>
       <c r="H116" t="s" s="0">
-        <v>556</v>
+        <v>664</v>
+      </c>
+      <c r="I116" t="s" s="0">
+        <v>633</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s" s="0">
-        <v>557</v>
+        <v>665</v>
       </c>
       <c r="B117" t="s" s="0">
-        <v>558</v>
+        <v>666</v>
       </c>
       <c r="C117" t="s" s="0">
-        <v>559</v>
+        <v>667</v>
       </c>
       <c r="D117" t="s" s="0">
-        <v>560</v>
+        <v>668</v>
       </c>
       <c r="E117" t="s" s="0">
-        <v>12</v>
+        <v>669</v>
       </c>
       <c r="F117" t="s" s="0">
-        <v>555</v>
+        <v>14</v>
       </c>
       <c r="G117" t="s" s="0">
-        <v>556</v>
+        <v>663</v>
       </c>
       <c r="H117" t="s" s="0">
-        <v>556</v>
+        <v>664</v>
+      </c>
+      <c r="I117" t="s" s="0">
+        <v>633</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="0">
-        <v>561</v>
+        <v>670</v>
       </c>
       <c r="B118" t="s" s="0">
-        <v>562</v>
+        <v>671</v>
       </c>
       <c r="C118" t="s" s="0">
-        <v>563</v>
+        <v>672</v>
       </c>
       <c r="D118" t="s" s="0">
-        <v>564</v>
+        <v>673</v>
       </c>
       <c r="E118" t="s" s="0">
-        <v>12</v>
+        <v>674</v>
       </c>
       <c r="F118" t="s" s="0">
-        <v>555</v>
+        <v>14</v>
       </c>
       <c r="G118" t="s" s="0">
-        <v>556</v>
+        <v>663</v>
       </c>
       <c r="H118" t="s" s="0">
-        <v>556</v>
+        <v>664</v>
+      </c>
+      <c r="I118" t="s" s="0">
+        <v>633</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="0">
-        <v>565</v>
+        <v>675</v>
       </c>
       <c r="B119" t="s" s="0">
-        <v>566</v>
+        <v>676</v>
       </c>
       <c r="C119" t="s" s="0">
-        <v>567</v>
+        <v>677</v>
       </c>
       <c r="D119" t="s" s="0">
-        <v>568</v>
+        <v>678</v>
       </c>
       <c r="E119" t="s" s="0">
-        <v>12</v>
+        <v>679</v>
       </c>
       <c r="F119" t="s" s="0">
-        <v>555</v>
+        <v>14</v>
       </c>
       <c r="G119" t="s" s="0">
-        <v>556</v>
+        <v>663</v>
       </c>
       <c r="H119" t="s" s="0">
-        <v>556</v>
+        <v>664</v>
+      </c>
+      <c r="I119" t="s" s="0">
+        <v>680</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s" s="0">
-        <v>569</v>
+        <v>681</v>
       </c>
       <c r="B120" t="s" s="0">
-        <v>570</v>
+        <v>682</v>
       </c>
       <c r="C120" t="s" s="0">
-        <v>571</v>
+        <v>683</v>
       </c>
       <c r="D120" t="s" s="0">
-        <v>572</v>
+        <v>684</v>
       </c>
       <c r="E120" t="s" s="0">
-        <v>12</v>
+        <v>685</v>
       </c>
       <c r="F120" t="s" s="0">
-        <v>555</v>
+        <v>14</v>
       </c>
       <c r="G120" t="s" s="0">
-        <v>573</v>
+        <v>663</v>
       </c>
       <c r="H120" t="s" s="0">
-        <v>573</v>
+        <v>686</v>
+      </c>
+      <c r="I120" t="s" s="0">
+        <v>633</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="0">
-        <v>574</v>
+        <v>687</v>
       </c>
       <c r="B121" t="s" s="0">
-        <v>575</v>
+        <v>688</v>
       </c>
       <c r="C121" t="s" s="0">
-        <v>576</v>
+        <v>689</v>
       </c>
       <c r="D121" t="s" s="0">
-        <v>577</v>
+        <v>690</v>
       </c>
       <c r="E121" t="s" s="0">
-        <v>12</v>
+        <v>691</v>
       </c>
       <c r="F121" t="s" s="0">
-        <v>555</v>
+        <v>14</v>
       </c>
       <c r="G121" t="s" s="0">
-        <v>573</v>
+        <v>663</v>
       </c>
       <c r="H121" t="s" s="0">
-        <v>573</v>
+        <v>686</v>
+      </c>
+      <c r="I121" t="s" s="0">
+        <v>680</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="0">
-        <v>578</v>
+        <v>692</v>
       </c>
       <c r="B122" t="s" s="0">
-        <v>579</v>
+        <v>693</v>
       </c>
       <c r="C122" t="s" s="0">
-        <v>580</v>
+        <v>694</v>
       </c>
       <c r="D122" t="s" s="0">
-        <v>581</v>
+        <v>695</v>
       </c>
       <c r="E122" t="s" s="0">
-        <v>12</v>
+        <v>696</v>
       </c>
       <c r="F122" t="s" s="0">
-        <v>555</v>
+        <v>14</v>
       </c>
       <c r="G122" t="s" s="0">
-        <v>573</v>
+        <v>663</v>
       </c>
       <c r="H122" t="s" s="0">
-        <v>573</v>
+        <v>686</v>
+      </c>
+      <c r="I122" t="s" s="0">
+        <v>633</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="0">
-        <v>582</v>
+        <v>697</v>
       </c>
       <c r="B123" t="s" s="0">
-        <v>583</v>
+        <v>698</v>
       </c>
       <c r="C123" t="s" s="0">
-        <v>584</v>
+        <v>699</v>
       </c>
       <c r="D123" t="s" s="0">
-        <v>585</v>
+        <v>700</v>
       </c>
       <c r="E123" t="s" s="0">
-        <v>12</v>
+        <v>701</v>
       </c>
       <c r="F123" t="s" s="0">
-        <v>555</v>
+        <v>14</v>
       </c>
       <c r="G123" t="s" s="0">
-        <v>573</v>
+        <v>663</v>
       </c>
       <c r="H123" t="s" s="0">
-        <v>573</v>
+        <v>686</v>
+      </c>
+      <c r="I123" t="s" s="0">
+        <v>680</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="0">
-        <v>586</v>
+        <v>702</v>
       </c>
       <c r="B124" t="s" s="0">
-        <v>587</v>
+        <v>703</v>
       </c>
       <c r="C124" t="s" s="0">
-        <v>588</v>
+        <v>704</v>
       </c>
       <c r="D124" t="s" s="0">
-        <v>589</v>
+        <v>705</v>
       </c>
       <c r="E124" t="s" s="0">
-        <v>12</v>
+        <v>706</v>
       </c>
       <c r="F124" t="s" s="0">
-        <v>590</v>
+        <v>14</v>
       </c>
       <c r="G124" t="s" s="0">
-        <v>591</v>
+        <v>707</v>
       </c>
       <c r="H124" t="s" s="0">
-        <v>591</v>
+        <v>708</v>
+      </c>
+      <c r="I124" t="s" s="0">
+        <v>680</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="0">
-        <v>592</v>
+        <v>709</v>
       </c>
       <c r="B125" t="s" s="0">
-        <v>593</v>
+        <v>710</v>
       </c>
       <c r="C125" t="s" s="0">
-        <v>594</v>
+        <v>711</v>
       </c>
       <c r="D125" t="s" s="0">
-        <v>595</v>
+        <v>712</v>
       </c>
       <c r="E125" t="s" s="0">
-        <v>12</v>
+        <v>713</v>
       </c>
       <c r="F125" t="s" s="0">
-        <v>590</v>
+        <v>14</v>
       </c>
       <c r="G125" t="s" s="0">
-        <v>591</v>
+        <v>707</v>
       </c>
       <c r="H125" t="s" s="0">
-        <v>591</v>
+        <v>708</v>
+      </c>
+      <c r="I125" t="s" s="0">
+        <v>680</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s" s="0">
-        <v>596</v>
+        <v>714</v>
       </c>
       <c r="B126" t="s" s="0">
-        <v>597</v>
+        <v>715</v>
       </c>
       <c r="C126" t="s" s="0">
-        <v>598</v>
+        <v>716</v>
       </c>
       <c r="D126" t="s" s="0">
-        <v>599</v>
+        <v>717</v>
       </c>
       <c r="E126" t="s" s="0">
-        <v>12</v>
+        <v>718</v>
       </c>
       <c r="F126" t="s" s="0">
-        <v>590</v>
+        <v>14</v>
       </c>
       <c r="G126" t="s" s="0">
-        <v>591</v>
+        <v>707</v>
       </c>
       <c r="H126" t="s" s="0">
-        <v>591</v>
+        <v>708</v>
+      </c>
+      <c r="I126" t="s" s="0">
+        <v>680</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s" s="0">
-        <v>600</v>
+        <v>719</v>
       </c>
       <c r="B127" t="s" s="0">
-        <v>601</v>
+        <v>720</v>
       </c>
       <c r="C127" t="s" s="0">
-        <v>602</v>
+        <v>721</v>
       </c>
       <c r="D127" t="s" s="0">
-        <v>603</v>
+        <v>722</v>
       </c>
       <c r="E127" t="s" s="0">
-        <v>12</v>
+        <v>723</v>
       </c>
       <c r="F127" t="s" s="0">
-        <v>604</v>
+        <v>14</v>
       </c>
       <c r="G127" t="s" s="0">
-        <v>591</v>
+        <v>724</v>
       </c>
       <c r="H127" t="s" s="0">
-        <v>591</v>
+        <v>708</v>
+      </c>
+      <c r="I127" t="s" s="0">
+        <v>680</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s" s="0">
-        <v>605</v>
+        <v>725</v>
       </c>
       <c r="B128" t="s" s="0">
-        <v>606</v>
+        <v>726</v>
       </c>
       <c r="C128" t="s" s="0">
-        <v>607</v>
+        <v>727</v>
       </c>
       <c r="D128" t="s" s="0">
-        <v>608</v>
+        <v>728</v>
       </c>
       <c r="E128" t="s" s="0">
-        <v>12</v>
+        <v>729</v>
       </c>
       <c r="F128" t="s" s="0">
-        <v>604</v>
+        <v>14</v>
       </c>
       <c r="G128" t="s" s="0">
-        <v>609</v>
+        <v>724</v>
       </c>
       <c r="H128" t="s" s="0">
-        <v>609</v>
+        <v>730</v>
+      </c>
+      <c r="I128" t="s" s="0">
+        <v>680</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s" s="0">
-        <v>610</v>
+        <v>731</v>
       </c>
       <c r="B129" t="s" s="0">
-        <v>611</v>
+        <v>732</v>
       </c>
       <c r="C129" t="s" s="0">
-        <v>612</v>
+        <v>733</v>
       </c>
       <c r="D129" t="s" s="0">
-        <v>613</v>
+        <v>734</v>
       </c>
       <c r="E129" t="s" s="0">
-        <v>12</v>
+        <v>735</v>
       </c>
       <c r="F129" t="s" s="0">
-        <v>604</v>
+        <v>14</v>
       </c>
       <c r="G129" t="s" s="0">
-        <v>609</v>
+        <v>724</v>
       </c>
       <c r="H129" t="s" s="0">
-        <v>609</v>
+        <v>730</v>
+      </c>
+      <c r="I129" t="s" s="0">
+        <v>680</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s" s="0">
-        <v>614</v>
+        <v>736</v>
       </c>
       <c r="B130" t="s" s="0">
-        <v>615</v>
+        <v>737</v>
       </c>
       <c r="C130" t="s" s="0">
-        <v>616</v>
+        <v>738</v>
       </c>
       <c r="D130" t="s" s="0">
-        <v>617</v>
+        <v>739</v>
       </c>
       <c r="E130" t="s" s="0">
-        <v>12</v>
+        <v>740</v>
       </c>
       <c r="F130" t="s" s="0">
-        <v>604</v>
+        <v>14</v>
       </c>
       <c r="G130" t="s" s="0">
-        <v>609</v>
+        <v>724</v>
       </c>
       <c r="H130" t="s" s="0">
-        <v>609</v>
+        <v>730</v>
+      </c>
+      <c r="I130" t="s" s="0">
+        <v>741</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s" s="0">
-        <v>618</v>
+        <v>742</v>
       </c>
       <c r="B131" t="s" s="0">
-        <v>619</v>
+        <v>743</v>
       </c>
       <c r="C131" t="s" s="0">
-        <v>620</v>
+        <v>744</v>
       </c>
       <c r="D131" t="s" s="0">
-        <v>621</v>
+        <v>745</v>
       </c>
       <c r="E131" t="s" s="0">
-        <v>12</v>
+        <v>746</v>
       </c>
       <c r="F131" t="s" s="0">
-        <v>604</v>
+        <v>14</v>
       </c>
       <c r="G131" t="s" s="0">
-        <v>609</v>
+        <v>724</v>
       </c>
       <c r="H131" t="s" s="0">
-        <v>609</v>
+        <v>730</v>
+      </c>
+      <c r="I131" t="s" s="0">
+        <v>741</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s" s="0">
-        <v>622</v>
+        <v>747</v>
       </c>
       <c r="B132" t="s" s="0">
-        <v>623</v>
+        <v>748</v>
       </c>
       <c r="C132" t="s" s="0">
-        <v>624</v>
+        <v>749</v>
       </c>
       <c r="D132" t="s" s="0">
-        <v>625</v>
+        <v>750</v>
       </c>
       <c r="E132" t="s" s="0">
-        <v>12</v>
+        <v>751</v>
       </c>
       <c r="F132" t="s" s="0">
-        <v>604</v>
+        <v>14</v>
       </c>
       <c r="G132" t="s" s="0">
-        <v>626</v>
+        <v>724</v>
       </c>
       <c r="H132" t="s" s="0">
-        <v>626</v>
+        <v>752</v>
+      </c>
+      <c r="I132" t="s" s="0">
+        <v>741</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s" s="0">
-        <v>627</v>
+        <v>753</v>
       </c>
       <c r="B133" t="s" s="0">
-        <v>628</v>
+        <v>754</v>
       </c>
       <c r="C133" t="s" s="0">
-        <v>629</v>
+        <v>755</v>
       </c>
       <c r="D133" t="s" s="0">
-        <v>630</v>
+        <v>756</v>
       </c>
       <c r="E133" t="s" s="0">
-        <v>12</v>
+        <v>757</v>
       </c>
       <c r="F133" t="s" s="0">
-        <v>604</v>
+        <v>14</v>
       </c>
       <c r="G133" t="s" s="0">
-        <v>626</v>
+        <v>724</v>
       </c>
       <c r="H133" t="s" s="0">
-        <v>626</v>
+        <v>752</v>
+      </c>
+      <c r="I133" t="s" s="0">
+        <v>741</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="0">
-        <v>631</v>
+        <v>758</v>
       </c>
       <c r="B134" t="s" s="0">
-        <v>632</v>
+        <v>759</v>
       </c>
       <c r="C134" t="s" s="0">
-        <v>633</v>
+        <v>760</v>
       </c>
       <c r="D134" t="s" s="0">
-        <v>634</v>
+        <v>761</v>
       </c>
       <c r="E134" t="s" s="0">
-        <v>12</v>
+        <v>762</v>
       </c>
       <c r="F134" t="s" s="0">
-        <v>635</v>
+        <v>14</v>
       </c>
       <c r="G134" t="s" s="0">
-        <v>626</v>
+        <v>763</v>
       </c>
       <c r="H134" t="s" s="0">
-        <v>626</v>
+        <v>752</v>
+      </c>
+      <c r="I134" t="s" s="0">
+        <v>741</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s" s="0">
-        <v>636</v>
+        <v>764</v>
       </c>
       <c r="B135" t="s" s="0">
-        <v>637</v>
+        <v>765</v>
       </c>
       <c r="C135" t="s" s="0">
-        <v>638</v>
+        <v>766</v>
       </c>
       <c r="D135" t="s" s="0">
-        <v>639</v>
+        <v>767</v>
       </c>
       <c r="E135" t="s" s="0">
-        <v>12</v>
+        <v>768</v>
       </c>
       <c r="F135" t="s" s="0">
-        <v>635</v>
+        <v>14</v>
       </c>
       <c r="G135" t="s" s="0">
-        <v>626</v>
+        <v>763</v>
       </c>
       <c r="H135" t="s" s="0">
-        <v>626</v>
+        <v>752</v>
+      </c>
+      <c r="I135" t="s" s="0">
+        <v>741</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s" s="0">
-        <v>640</v>
+        <v>769</v>
       </c>
       <c r="B136" t="s" s="0">
-        <v>641</v>
+        <v>770</v>
       </c>
       <c r="C136" t="s" s="0">
-        <v>642</v>
+        <v>771</v>
       </c>
       <c r="D136" t="s" s="0">
-        <v>643</v>
+        <v>772</v>
       </c>
       <c r="E136" t="s" s="0">
-        <v>12</v>
+        <v>773</v>
       </c>
       <c r="F136" t="s" s="0">
-        <v>635</v>
+        <v>14</v>
       </c>
       <c r="G136" t="s" s="0">
-        <v>644</v>
+        <v>763</v>
       </c>
       <c r="H136" t="s" s="0">
-        <v>644</v>
+        <v>774</v>
+      </c>
+      <c r="I136" t="s" s="0">
+        <v>741</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s" s="0">
-        <v>645</v>
+        <v>775</v>
       </c>
       <c r="B137" t="s" s="0">
-        <v>646</v>
+        <v>776</v>
       </c>
       <c r="C137" t="s" s="0">
-        <v>647</v>
+        <v>777</v>
       </c>
       <c r="D137" t="s" s="0">
-        <v>648</v>
+        <v>778</v>
       </c>
       <c r="E137" t="s" s="0">
-        <v>12</v>
+        <v>779</v>
       </c>
       <c r="F137" t="s" s="0">
-        <v>635</v>
+        <v>14</v>
       </c>
       <c r="G137" t="s" s="0">
-        <v>644</v>
+        <v>763</v>
       </c>
       <c r="H137" t="s" s="0">
-        <v>644</v>
+        <v>774</v>
+      </c>
+      <c r="I137" t="s" s="0">
+        <v>741</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s" s="0">
-        <v>649</v>
+        <v>780</v>
       </c>
       <c r="B138" t="s" s="0">
-        <v>650</v>
+        <v>781</v>
       </c>
       <c r="C138" t="s" s="0">
-        <v>651</v>
+        <v>782</v>
       </c>
       <c r="D138" t="s" s="0">
-        <v>652</v>
+        <v>783</v>
       </c>
       <c r="E138" t="s" s="0">
-        <v>12</v>
+        <v>784</v>
       </c>
       <c r="F138" t="s" s="0">
-        <v>653</v>
+        <v>14</v>
       </c>
       <c r="G138" t="s" s="0">
-        <v>644</v>
+        <v>785</v>
       </c>
       <c r="H138" t="s" s="0">
-        <v>654</v>
+        <v>774</v>
+      </c>
+      <c r="I138" t="s" s="0">
+        <v>741</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s" s="0">
-        <v>655</v>
+        <v>786</v>
       </c>
       <c r="B139" t="s" s="0">
-        <v>656</v>
+        <v>787</v>
       </c>
       <c r="C139" t="s" s="0">
-        <v>657</v>
+        <v>788</v>
       </c>
       <c r="D139" t="s" s="0">
-        <v>658</v>
+        <v>789</v>
       </c>
       <c r="E139" t="s" s="0">
-        <v>12</v>
+        <v>790</v>
       </c>
       <c r="F139" t="s" s="0">
-        <v>659</v>
+        <v>14</v>
       </c>
       <c r="G139" t="s" s="0">
-        <v>644</v>
+        <v>791</v>
       </c>
       <c r="H139" t="s" s="0">
-        <v>644</v>
+        <v>774</v>
+      </c>
+      <c r="I139" t="s" s="0">
+        <v>741</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s" s="0">
-        <v>660</v>
+        <v>792</v>
       </c>
       <c r="B140" t="s" s="0">
-        <v>661</v>
+        <v>793</v>
       </c>
       <c r="C140" t="s" s="0">
-        <v>662</v>
+        <v>794</v>
       </c>
       <c r="D140" t="s" s="0">
-        <v>663</v>
+        <v>795</v>
       </c>
       <c r="E140" t="s" s="0">
-        <v>12</v>
+        <v>796</v>
       </c>
       <c r="F140" t="s" s="0">
-        <v>664</v>
+        <v>14</v>
       </c>
       <c r="G140" t="s" s="0">
-        <v>665</v>
+        <v>797</v>
       </c>
       <c r="H140" t="s" s="0">
-        <v>665</v>
+        <v>798</v>
+      </c>
+      <c r="I140" t="s" s="0">
+        <v>799</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s" s="0">
-        <v>666</v>
+        <v>800</v>
       </c>
       <c r="B141" t="s" s="0">
-        <v>667</v>
+        <v>801</v>
       </c>
       <c r="C141" t="s" s="0">
-        <v>668</v>
+        <v>802</v>
       </c>
       <c r="D141" t="s" s="0">
-        <v>669</v>
+        <v>803</v>
       </c>
       <c r="E141" t="s" s="0">
-        <v>12</v>
+        <v>804</v>
       </c>
       <c r="F141" t="s" s="0">
-        <v>670</v>
+        <v>14</v>
       </c>
       <c r="G141" t="s" s="0">
-        <v>665</v>
+        <v>805</v>
       </c>
       <c r="H141" t="s" s="0">
-        <v>665</v>
+        <v>798</v>
+      </c>
+      <c r="I141" t="s" s="0">
+        <v>799</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s" s="0">
-        <v>671</v>
+        <v>806</v>
       </c>
       <c r="B142" t="s" s="0">
-        <v>672</v>
+        <v>807</v>
       </c>
       <c r="C142" t="s" s="0">
-        <v>673</v>
+        <v>808</v>
       </c>
       <c r="D142" t="s" s="0">
-        <v>674</v>
+        <v>809</v>
       </c>
       <c r="E142" t="s" s="0">
-        <v>12</v>
+        <v>810</v>
       </c>
       <c r="F142" t="s" s="0">
-        <v>675</v>
+        <v>14</v>
       </c>
       <c r="G142" t="s" s="0">
-        <v>676</v>
+        <v>811</v>
       </c>
       <c r="H142" t="s" s="0">
-        <v>676</v>
+        <v>812</v>
+      </c>
+      <c r="I142" t="s" s="0">
+        <v>516</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s" s="0">
-        <v>677</v>
+        <v>813</v>
       </c>
       <c r="B143" t="s" s="0">
-        <v>678</v>
+        <v>814</v>
       </c>
       <c r="C143" t="s" s="0">
-        <v>679</v>
+        <v>815</v>
       </c>
       <c r="D143" t="s" s="0">
-        <v>680</v>
+        <v>816</v>
       </c>
       <c r="E143" t="s" s="0">
-        <v>12</v>
+        <v>817</v>
       </c>
       <c r="F143" t="s" s="0">
-        <v>681</v>
+        <v>14</v>
       </c>
       <c r="G143" t="s" s="0">
-        <v>676</v>
+        <v>818</v>
       </c>
       <c r="H143" t="s" s="0">
-        <v>676</v>
+        <v>812</v>
+      </c>
+      <c r="I143" t="s" s="0">
+        <v>516</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s" s="0">
-        <v>682</v>
+        <v>819</v>
       </c>
       <c r="B144" t="s" s="0">
-        <v>683</v>
+        <v>820</v>
       </c>
       <c r="C144" t="s" s="0">
-        <v>684</v>
+        <v>821</v>
       </c>
       <c r="D144" t="s" s="0">
-        <v>685</v>
+        <v>822</v>
       </c>
       <c r="E144" t="s" s="0">
-        <v>12</v>
+        <v>823</v>
       </c>
       <c r="F144" t="s" s="0">
-        <v>686</v>
+        <v>14</v>
       </c>
       <c r="G144" t="s" s="0">
-        <v>676</v>
+        <v>200</v>
       </c>
       <c r="H144" t="s" s="0">
-        <v>676</v>
+        <v>812</v>
+      </c>
+      <c r="I144" t="s" s="0">
+        <v>17</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s" s="0">
-        <v>687</v>
+        <v>824</v>
       </c>
       <c r="B145" t="s" s="0">
-        <v>688</v>
+        <v>825</v>
       </c>
       <c r="C145" t="s" s="0">
-        <v>689</v>
+        <v>826</v>
       </c>
       <c r="D145" t="s" s="0">
-        <v>690</v>
+        <v>827</v>
       </c>
       <c r="E145" t="s" s="0">
-        <v>12</v>
+        <v>828</v>
       </c>
       <c r="F145" t="s" s="0">
-        <v>691</v>
+        <v>14</v>
       </c>
       <c r="G145" t="s" s="0">
-        <v>692</v>
+        <v>829</v>
       </c>
       <c r="H145" t="s" s="0">
-        <v>692</v>
+        <v>830</v>
+      </c>
+      <c r="I145" t="s" s="0">
+        <v>51</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s" s="0">
-        <v>693</v>
+        <v>831</v>
       </c>
       <c r="B146" t="s" s="0">
-        <v>694</v>
+        <v>832</v>
       </c>
       <c r="C146" t="s" s="0">
-        <v>695</v>
+        <v>833</v>
       </c>
       <c r="D146" t="s" s="0">
-        <v>696</v>
+        <v>834</v>
       </c>
       <c r="E146" t="s" s="0">
-        <v>12</v>
+        <v>835</v>
       </c>
       <c r="F146" t="s" s="0">
-        <v>697</v>
+        <v>14</v>
       </c>
       <c r="G146" t="s" s="0">
-        <v>692</v>
+        <v>836</v>
       </c>
       <c r="H146" t="s" s="0">
-        <v>692</v>
+        <v>830</v>
+      </c>
+      <c r="I146" t="s" s="0">
+        <v>51</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s" s="0">
-        <v>698</v>
+        <v>837</v>
       </c>
       <c r="B147" t="s" s="0">
-        <v>699</v>
+        <v>838</v>
       </c>
       <c r="C147" t="s" s="0">
-        <v>700</v>
+        <v>839</v>
       </c>
       <c r="D147" t="s" s="0">
-        <v>701</v>
+        <v>840</v>
       </c>
       <c r="E147" t="s" s="0">
-        <v>12</v>
+        <v>841</v>
       </c>
       <c r="F147" t="s" s="0">
-        <v>266</v>
+        <v>14</v>
       </c>
       <c r="G147" t="s" s="0">
-        <v>702</v>
+        <v>321</v>
       </c>
       <c r="H147" t="s" s="0">
-        <v>702</v>
+        <v>842</v>
+      </c>
+      <c r="I147" t="s" s="0">
+        <v>338</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s" s="0">
-        <v>703</v>
+        <v>843</v>
       </c>
       <c r="B148" t="s" s="0">
-        <v>704</v>
+        <v>844</v>
       </c>
       <c r="C148" t="s" s="0">
-        <v>705</v>
+        <v>845</v>
       </c>
       <c r="D148" t="s" s="0">
-        <v>706</v>
+        <v>846</v>
       </c>
       <c r="E148" t="s" s="0">
-        <v>12</v>
+        <v>847</v>
       </c>
       <c r="F148" t="s" s="0">
-        <v>314</v>
+        <v>14</v>
       </c>
       <c r="G148" t="s" s="0">
-        <v>707</v>
+        <v>379</v>
       </c>
       <c r="H148" t="s" s="0">
-        <v>707</v>
+        <v>848</v>
+      </c>
+      <c r="I148" t="s" s="0">
+        <v>338</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s" s="0">
-        <v>708</v>
+        <v>849</v>
       </c>
       <c r="B149" t="s" s="0">
-        <v>709</v>
+        <v>850</v>
       </c>
       <c r="C149" t="s" s="0">
-        <v>710</v>
+        <v>851</v>
       </c>
       <c r="D149" t="s" s="0">
-        <v>711</v>
+        <v>852</v>
       </c>
       <c r="E149" t="s" s="0">
-        <v>12</v>
+        <v>853</v>
       </c>
       <c r="F149" t="s" s="0">
-        <v>500</v>
+        <v>14</v>
       </c>
       <c r="G149" t="s" s="0">
-        <v>712</v>
+        <v>596</v>
       </c>
       <c r="H149" t="s" s="0">
-        <v>712</v>
+        <v>854</v>
+      </c>
+      <c r="I149" t="s" s="0">
+        <v>504</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s" s="0">
-        <v>713</v>
+        <v>855</v>
       </c>
       <c r="B150" t="s" s="0">
-        <v>714</v>
+        <v>856</v>
       </c>
       <c r="C150" t="s" s="0">
-        <v>715</v>
+        <v>857</v>
       </c>
       <c r="D150" t="s" s="0">
-        <v>716</v>
+        <v>858</v>
       </c>
       <c r="E150" t="s" s="0">
-        <v>12</v>
+        <v>859</v>
       </c>
       <c r="F150" t="s" s="0">
-        <v>500</v>
+        <v>14</v>
       </c>
       <c r="G150" t="s" s="0">
-        <v>712</v>
+        <v>596</v>
       </c>
       <c r="H150" t="s" s="0">
-        <v>712</v>
+        <v>854</v>
+      </c>
+      <c r="I150" t="s" s="0">
+        <v>504</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s" s="0">
-        <v>717</v>
+        <v>860</v>
       </c>
       <c r="B151" t="s" s="0">
-        <v>718</v>
+        <v>861</v>
       </c>
       <c r="C151" t="s" s="0">
-        <v>719</v>
+        <v>862</v>
       </c>
       <c r="D151" t="s" s="0">
-        <v>720</v>
+        <v>863</v>
       </c>
       <c r="E151" t="s" s="0">
-        <v>12</v>
+        <v>864</v>
       </c>
       <c r="F151" t="s" s="0">
-        <v>500</v>
+        <v>14</v>
       </c>
       <c r="G151" t="s" s="0">
-        <v>712</v>
+        <v>596</v>
       </c>
       <c r="H151" t="s" s="0">
-        <v>712</v>
+        <v>854</v>
+      </c>
+      <c r="I151" t="s" s="0">
+        <v>633</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s" s="0">
-        <v>721</v>
+        <v>865</v>
       </c>
       <c r="B152" t="s" s="0">
-        <v>722</v>
+        <v>866</v>
       </c>
       <c r="C152" t="s" s="0">
-        <v>723</v>
+        <v>867</v>
       </c>
       <c r="D152" t="s" s="0">
-        <v>724</v>
+        <v>868</v>
       </c>
       <c r="E152" t="s" s="0">
-        <v>12</v>
+        <v>869</v>
       </c>
       <c r="F152" t="s" s="0">
-        <v>500</v>
+        <v>14</v>
       </c>
       <c r="G152" t="s" s="0">
-        <v>712</v>
+        <v>596</v>
       </c>
       <c r="H152" t="s" s="0">
-        <v>725</v>
+        <v>854</v>
+      </c>
+      <c r="I152" t="s" s="0">
+        <v>633</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s" s="0">
-        <v>726</v>
+        <v>870</v>
       </c>
       <c r="B153" t="s" s="0">
-        <v>727</v>
+        <v>871</v>
       </c>
       <c r="C153" t="s" s="0">
-        <v>728</v>
+        <v>872</v>
       </c>
       <c r="D153" t="s" s="0">
-        <v>729</v>
+        <v>873</v>
       </c>
       <c r="E153" t="s" s="0">
-        <v>12</v>
+        <v>874</v>
       </c>
       <c r="F153" t="s" s="0">
-        <v>730</v>
+        <v>14</v>
       </c>
       <c r="G153" t="s" s="0">
-        <v>712</v>
+        <v>875</v>
       </c>
       <c r="H153" t="s" s="0">
-        <v>712</v>
+        <v>854</v>
+      </c>
+      <c r="I153" t="s" s="0">
+        <v>633</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s" s="0">
-        <v>731</v>
+        <v>876</v>
       </c>
       <c r="B154" t="s" s="0">
-        <v>732</v>
+        <v>877</v>
       </c>
       <c r="C154" t="s" s="0">
-        <v>733</v>
+        <v>878</v>
       </c>
       <c r="D154" t="s" s="0">
-        <v>734</v>
+        <v>879</v>
       </c>
       <c r="E154" t="s" s="0">
-        <v>12</v>
+        <v>880</v>
       </c>
       <c r="F154" t="s" s="0">
-        <v>555</v>
+        <v>14</v>
       </c>
       <c r="G154" t="s" s="0">
-        <v>712</v>
+        <v>663</v>
       </c>
       <c r="H154" t="s" s="0">
-        <v>712</v>
+        <v>854</v>
+      </c>
+      <c r="I154" t="s" s="0">
+        <v>633</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s" s="0">
-        <v>735</v>
+        <v>881</v>
       </c>
       <c r="B155" t="s" s="0">
-        <v>736</v>
+        <v>882</v>
       </c>
       <c r="C155" t="s" s="0">
-        <v>737</v>
+        <v>883</v>
       </c>
       <c r="D155" t="s" s="0">
-        <v>738</v>
+        <v>884</v>
       </c>
       <c r="E155" t="s" s="0">
-        <v>12</v>
+        <v>885</v>
       </c>
       <c r="F155" t="s" s="0">
-        <v>555</v>
+        <v>14</v>
       </c>
       <c r="G155" t="s" s="0">
-        <v>712</v>
+        <v>663</v>
       </c>
       <c r="H155" t="s" s="0">
-        <v>712</v>
+        <v>854</v>
+      </c>
+      <c r="I155" t="s" s="0">
+        <v>680</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s" s="0">
-        <v>739</v>
+        <v>886</v>
       </c>
       <c r="B156" t="s" s="0">
-        <v>740</v>
+        <v>887</v>
       </c>
       <c r="C156" t="s" s="0">
-        <v>741</v>
+        <v>888</v>
       </c>
       <c r="D156" t="s" s="0">
-        <v>742</v>
+        <v>889</v>
       </c>
       <c r="E156" t="s" s="0">
-        <v>12</v>
+        <v>890</v>
       </c>
       <c r="F156" t="s" s="0">
-        <v>590</v>
+        <v>14</v>
       </c>
       <c r="G156" t="s" s="0">
-        <v>712</v>
+        <v>707</v>
       </c>
       <c r="H156" t="s" s="0">
-        <v>712</v>
+        <v>854</v>
+      </c>
+      <c r="I156" t="s" s="0">
+        <v>680</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s" s="0">
-        <v>743</v>
+        <v>891</v>
       </c>
       <c r="B157" t="s" s="0">
-        <v>744</v>
+        <v>892</v>
       </c>
       <c r="C157" t="s" s="0">
-        <v>745</v>
+        <v>893</v>
       </c>
       <c r="D157" t="s" s="0">
-        <v>746</v>
+        <v>894</v>
       </c>
       <c r="E157" t="s" s="0">
-        <v>12</v>
+        <v>895</v>
       </c>
       <c r="F157" t="s" s="0">
-        <v>590</v>
+        <v>14</v>
       </c>
       <c r="G157" t="s" s="0">
-        <v>712</v>
+        <v>707</v>
       </c>
       <c r="H157" t="s" s="0">
-        <v>712</v>
+        <v>854</v>
+      </c>
+      <c r="I157" t="s" s="0">
+        <v>680</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s" s="0">
-        <v>747</v>
+        <v>896</v>
       </c>
       <c r="B158" t="s" s="0">
-        <v>748</v>
+        <v>897</v>
       </c>
       <c r="C158" t="s" s="0">
-        <v>749</v>
+        <v>898</v>
       </c>
       <c r="D158" t="s" s="0">
-        <v>750</v>
+        <v>899</v>
       </c>
       <c r="E158" t="s" s="0">
-        <v>12</v>
+        <v>900</v>
       </c>
       <c r="F158" t="s" s="0">
-        <v>604</v>
+        <v>14</v>
       </c>
       <c r="G158" t="s" s="0">
-        <v>712</v>
+        <v>724</v>
       </c>
       <c r="H158" t="s" s="0">
-        <v>712</v>
+        <v>854</v>
+      </c>
+      <c r="I158" t="s" s="0">
+        <v>741</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s" s="0">
-        <v>751</v>
+        <v>901</v>
       </c>
       <c r="B159" t="s" s="0">
-        <v>752</v>
+        <v>902</v>
       </c>
       <c r="C159" t="s" s="0">
-        <v>753</v>
+        <v>903</v>
       </c>
       <c r="D159" t="s" s="0">
-        <v>754</v>
+        <v>904</v>
       </c>
       <c r="E159" t="s" s="0">
-        <v>12</v>
+        <v>905</v>
       </c>
       <c r="F159" t="s" s="0">
-        <v>604</v>
+        <v>14</v>
       </c>
       <c r="G159" t="s" s="0">
-        <v>712</v>
+        <v>724</v>
       </c>
       <c r="H159" t="s" s="0">
-        <v>755</v>
+        <v>854</v>
+      </c>
+      <c r="I159" t="s" s="0">
+        <v>741</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s" s="0">
-        <v>756</v>
+        <v>906</v>
       </c>
       <c r="B160" t="s" s="0">
-        <v>757</v>
+        <v>907</v>
       </c>
       <c r="C160" t="s" s="0">
-        <v>758</v>
+        <v>908</v>
       </c>
       <c r="D160" t="s" s="0">
-        <v>759</v>
+        <v>909</v>
       </c>
       <c r="E160" t="s" s="0">
-        <v>12</v>
+        <v>910</v>
       </c>
       <c r="F160" t="s" s="0">
-        <v>670</v>
+        <v>14</v>
       </c>
       <c r="G160" t="s" s="0">
-        <v>712</v>
+        <v>805</v>
       </c>
       <c r="H160" t="s" s="0">
-        <v>712</v>
+        <v>854</v>
+      </c>
+      <c r="I160" t="s" s="0">
+        <v>799</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s" s="0">
-        <v>760</v>
+        <v>911</v>
       </c>
       <c r="B161" t="s" s="0">
-        <v>761</v>
+        <v>912</v>
       </c>
       <c r="C161" t="s" s="0">
-        <v>762</v>
+        <v>913</v>
       </c>
       <c r="D161" t="s" s="0">
-        <v>763</v>
+        <v>914</v>
       </c>
       <c r="E161" t="s" s="0">
-        <v>12</v>
+        <v>915</v>
       </c>
       <c r="F161" t="s" s="0">
-        <v>764</v>
+        <v>14</v>
       </c>
       <c r="G161" t="s" s="0">
-        <v>712</v>
+        <v>916</v>
       </c>
       <c r="H161" t="s" s="0">
-        <v>712</v>
+        <v>854</v>
+      </c>
+      <c r="I161" t="s" s="0">
+        <v>799</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s" s="0">
-        <v>765</v>
+        <v>917</v>
       </c>
       <c r="B162" t="s" s="0">
-        <v>766</v>
+        <v>918</v>
       </c>
       <c r="C162" t="s" s="0">
-        <v>767</v>
+        <v>919</v>
       </c>
       <c r="D162" t="s" s="0">
-        <v>768</v>
+        <v>920</v>
       </c>
       <c r="E162" t="s" s="0">
-        <v>12</v>
+        <v>921</v>
       </c>
       <c r="F162" t="s" s="0">
-        <v>769</v>
+        <v>14</v>
       </c>
       <c r="G162" t="s" s="0">
-        <v>712</v>
+        <v>922</v>
       </c>
       <c r="H162" t="s" s="0">
-        <v>712</v>
+        <v>854</v>
+      </c>
+      <c r="I162" t="s" s="0">
+        <v>799</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s" s="0">
-        <v>770</v>
+        <v>923</v>
       </c>
       <c r="B163" t="s" s="0">
-        <v>771</v>
+        <v>924</v>
       </c>
       <c r="C163" t="s" s="0">
-        <v>772</v>
+        <v>925</v>
       </c>
       <c r="D163" t="s" s="0">
-        <v>773</v>
+        <v>926</v>
       </c>
       <c r="E163" t="s" s="0">
-        <v>12</v>
+        <v>927</v>
       </c>
       <c r="F163" t="s" s="0">
-        <v>769</v>
+        <v>14</v>
       </c>
       <c r="G163" t="s" s="0">
-        <v>712</v>
+        <v>922</v>
       </c>
       <c r="H163" t="s" s="0">
-        <v>712</v>
+        <v>854</v>
+      </c>
+      <c r="I163" t="s" s="0">
+        <v>799</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s" s="0">
-        <v>774</v>
+        <v>928</v>
       </c>
       <c r="B164" t="s" s="0">
-        <v>775</v>
+        <v>929</v>
       </c>
       <c r="C164" t="s" s="0">
-        <v>776</v>
+        <v>930</v>
       </c>
       <c r="D164" t="s" s="0">
-        <v>777</v>
+        <v>931</v>
       </c>
       <c r="E164" t="s" s="0">
-        <v>12</v>
+        <v>932</v>
       </c>
       <c r="F164" t="s" s="0">
-        <v>778</v>
+        <v>14</v>
       </c>
       <c r="G164" t="s" s="0">
-        <v>712</v>
+        <v>933</v>
       </c>
       <c r="H164" t="s" s="0">
-        <v>712</v>
+        <v>854</v>
+      </c>
+      <c r="I164" t="s" s="0">
+        <v>799</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s" s="0">
-        <v>779</v>
+        <v>934</v>
       </c>
       <c r="B165" t="s" s="0">
-        <v>780</v>
+        <v>935</v>
       </c>
       <c r="C165" t="s" s="0">
-        <v>781</v>
+        <v>936</v>
       </c>
       <c r="D165" t="s" s="0">
-        <v>782</v>
+        <v>937</v>
       </c>
       <c r="E165" t="s" s="0">
-        <v>12</v>
+        <v>938</v>
       </c>
       <c r="F165" t="s" s="0">
-        <v>778</v>
+        <v>14</v>
       </c>
       <c r="G165" t="s" s="0">
-        <v>712</v>
+        <v>933</v>
       </c>
       <c r="H165" t="s" s="0">
-        <v>712</v>
+        <v>854</v>
+      </c>
+      <c r="I165" t="s" s="0">
+        <v>799</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s" s="0">
-        <v>783</v>
+        <v>939</v>
       </c>
       <c r="B166" t="s" s="0">
-        <v>784</v>
+        <v>940</v>
       </c>
       <c r="C166" t="s" s="0">
-        <v>785</v>
+        <v>941</v>
       </c>
       <c r="D166" t="s" s="0">
-        <v>786</v>
+        <v>942</v>
       </c>
       <c r="E166" t="s" s="0">
-        <v>12</v>
+        <v>943</v>
       </c>
       <c r="F166" t="s" s="0">
-        <v>787</v>
+        <v>14</v>
       </c>
       <c r="G166" t="s" s="0">
-        <v>712</v>
+        <v>944</v>
       </c>
       <c r="H166" t="s" s="0">
-        <v>712</v>
+        <v>854</v>
+      </c>
+      <c r="I166" t="s" s="0">
+        <v>799</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s" s="0">
-        <v>788</v>
+        <v>945</v>
       </c>
       <c r="B167" t="s" s="0">
-        <v>789</v>
+        <v>946</v>
       </c>
       <c r="C167" t="s" s="0">
-        <v>790</v>
+        <v>947</v>
       </c>
       <c r="D167" t="s" s="0">
-        <v>791</v>
+        <v>948</v>
       </c>
       <c r="E167" t="s" s="0">
-        <v>12</v>
+        <v>949</v>
       </c>
       <c r="F167" t="s" s="0">
-        <v>787</v>
+        <v>14</v>
       </c>
       <c r="G167" t="s" s="0">
-        <v>712</v>
+        <v>944</v>
       </c>
       <c r="H167" t="s" s="0">
-        <v>712</v>
+        <v>854</v>
+      </c>
+      <c r="I167" t="s" s="0">
+        <v>799</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s" s="0">
-        <v>792</v>
+        <v>950</v>
       </c>
       <c r="B168" t="s" s="0">
-        <v>793</v>
+        <v>951</v>
       </c>
       <c r="C168" t="s" s="0">
-        <v>794</v>
+        <v>952</v>
       </c>
       <c r="D168" t="s" s="0">
-        <v>795</v>
+        <v>953</v>
       </c>
       <c r="E168" t="s" s="0">
-        <v>12</v>
+        <v>954</v>
       </c>
       <c r="F168" t="s" s="0">
-        <v>796</v>
+        <v>14</v>
       </c>
       <c r="G168" t="s" s="0">
-        <v>712</v>
+        <v>955</v>
       </c>
       <c r="H168" t="s" s="0">
-        <v>712</v>
+        <v>854</v>
+      </c>
+      <c r="I168" t="s" s="0">
+        <v>799</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s" s="0">
-        <v>797</v>
+        <v>956</v>
       </c>
       <c r="B169" t="s" s="0">
-        <v>798</v>
+        <v>957</v>
       </c>
       <c r="C169" t="s" s="0">
-        <v>799</v>
+        <v>958</v>
       </c>
       <c r="D169" t="s" s="0">
-        <v>800</v>
+        <v>959</v>
       </c>
       <c r="E169" t="s" s="0">
-        <v>12</v>
+        <v>960</v>
       </c>
       <c r="F169" t="s" s="0">
-        <v>801</v>
+        <v>14</v>
       </c>
       <c r="G169" t="s" s="0">
-        <v>712</v>
+        <v>961</v>
       </c>
       <c r="H169" t="s" s="0">
-        <v>712</v>
+        <v>854</v>
+      </c>
+      <c r="I169" t="s" s="0">
+        <v>962</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s" s="0">
-        <v>802</v>
+        <v>963</v>
       </c>
       <c r="B170" t="s" s="0">
-        <v>803</v>
+        <v>964</v>
       </c>
       <c r="C170" t="s" s="0">
-        <v>804</v>
+        <v>965</v>
       </c>
       <c r="D170" t="s" s="0">
-        <v>805</v>
+        <v>966</v>
       </c>
       <c r="E170" t="s" s="0">
-        <v>12</v>
+        <v>967</v>
       </c>
       <c r="F170" t="s" s="0">
-        <v>806</v>
+        <v>14</v>
       </c>
       <c r="G170" t="s" s="0">
-        <v>712</v>
+        <v>968</v>
       </c>
       <c r="H170" t="s" s="0">
-        <v>712</v>
+        <v>854</v>
+      </c>
+      <c r="I170" t="s" s="0">
+        <v>969</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s" s="0">
-        <v>807</v>
+        <v>970</v>
       </c>
       <c r="B171" t="s" s="0">
-        <v>808</v>
+        <v>971</v>
       </c>
       <c r="C171" t="s" s="0">
-        <v>809</v>
+        <v>972</v>
       </c>
       <c r="D171" t="s" s="0">
-        <v>810</v>
+        <v>973</v>
       </c>
       <c r="E171" t="s" s="0">
-        <v>12</v>
+        <v>974</v>
       </c>
       <c r="F171" t="s" s="0">
-        <v>811</v>
+        <v>14</v>
       </c>
       <c r="G171" t="s" s="0">
-        <v>712</v>
+        <v>975</v>
       </c>
       <c r="H171" t="s" s="0">
-        <v>812</v>
+        <v>854</v>
+      </c>
+      <c r="I171" t="s" s="0">
+        <v>969</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s" s="0">
-        <v>813</v>
+        <v>976</v>
       </c>
       <c r="B172" t="s" s="0">
-        <v>814</v>
+        <v>977</v>
       </c>
       <c r="C172" t="s" s="0">
-        <v>815</v>
+        <v>978</v>
       </c>
       <c r="D172" t="s" s="0">
-        <v>816</v>
+        <v>979</v>
       </c>
       <c r="E172" t="s" s="0">
-        <v>12</v>
+        <v>980</v>
       </c>
       <c r="F172" t="s" s="0">
-        <v>817</v>
+        <v>14</v>
       </c>
       <c r="G172" t="s" s="0">
-        <v>712</v>
+        <v>981</v>
       </c>
       <c r="H172" t="s" s="0">
-        <v>712</v>
+        <v>854</v>
+      </c>
+      <c r="I172" t="s" s="0">
+        <v>969</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s" s="0">
-        <v>818</v>
+        <v>982</v>
       </c>
       <c r="B173" t="s" s="0">
-        <v>819</v>
+        <v>983</v>
       </c>
       <c r="C173" t="s" s="0">
-        <v>820</v>
+        <v>984</v>
       </c>
       <c r="D173" t="s" s="0">
-        <v>821</v>
+        <v>985</v>
       </c>
       <c r="E173" t="s" s="0">
-        <v>12</v>
+        <v>986</v>
       </c>
       <c r="F173" t="s" s="0">
-        <v>822</v>
+        <v>14</v>
       </c>
       <c r="G173" t="s" s="0">
-        <v>712</v>
+        <v>987</v>
       </c>
       <c r="H173" t="s" s="0">
-        <v>823</v>
+        <v>854</v>
+      </c>
+      <c r="I173" t="s" s="0">
+        <v>969</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s" s="0">
-        <v>824</v>
+        <v>988</v>
       </c>
       <c r="B174" t="s" s="0">
-        <v>825</v>
+        <v>989</v>
       </c>
       <c r="C174" t="s" s="0">
-        <v>826</v>
+        <v>990</v>
       </c>
       <c r="D174" t="s" s="0">
-        <v>827</v>
+        <v>991</v>
       </c>
       <c r="E174" t="s" s="0">
-        <v>12</v>
+        <v>992</v>
       </c>
       <c r="F174" t="s" s="0">
-        <v>686</v>
+        <v>14</v>
       </c>
       <c r="G174" t="s" s="0">
-        <v>712</v>
+        <v>200</v>
       </c>
       <c r="H174" t="s" s="0">
-        <v>712</v>
+        <v>854</v>
+      </c>
+      <c r="I174" t="s" s="0">
+        <v>969</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s" s="0">
-        <v>828</v>
+        <v>993</v>
       </c>
       <c r="B175" t="s" s="0">
-        <v>829</v>
+        <v>994</v>
       </c>
       <c r="C175" t="s" s="0">
-        <v>830</v>
+        <v>995</v>
       </c>
       <c r="D175" t="s" s="0">
-        <v>831</v>
+        <v>996</v>
       </c>
       <c r="E175" t="s" s="0">
-        <v>12</v>
+        <v>997</v>
       </c>
       <c r="F175" t="s" s="0">
-        <v>686</v>
+        <v>14</v>
       </c>
       <c r="G175" t="s" s="0">
-        <v>712</v>
+        <v>200</v>
       </c>
       <c r="H175" t="s" s="0">
-        <v>712</v>
+        <v>854</v>
+      </c>
+      <c r="I175" t="s" s="0">
+        <v>998</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s" s="0">
-        <v>832</v>
+        <v>999</v>
       </c>
       <c r="B176" t="s" s="0">
-        <v>833</v>
+        <v>1000</v>
       </c>
       <c r="C176" t="s" s="0">
-        <v>834</v>
+        <v>1001</v>
       </c>
       <c r="D176" t="s" s="0">
-        <v>835</v>
+        <v>1002</v>
       </c>
       <c r="E176" t="s" s="0">
-        <v>12</v>
+        <v>1003</v>
       </c>
       <c r="F176" t="s" s="0">
-        <v>836</v>
+        <v>14</v>
       </c>
       <c r="G176" t="s" s="0">
-        <v>712</v>
+        <v>1004</v>
       </c>
       <c r="H176" t="s" s="0">
-        <v>712</v>
+        <v>854</v>
+      </c>
+      <c r="I176" t="s" s="0">
+        <v>998</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s" s="0">
-        <v>837</v>
+        <v>1005</v>
       </c>
       <c r="B177" t="s" s="0">
-        <v>838</v>
+        <v>1006</v>
       </c>
       <c r="C177" t="s" s="0">
-        <v>839</v>
+        <v>1007</v>
       </c>
       <c r="D177" t="s" s="0">
-        <v>840</v>
+        <v>1008</v>
       </c>
       <c r="E177" t="s" s="0">
-        <v>12</v>
+        <v>1009</v>
       </c>
       <c r="F177" t="s" s="0">
-        <v>841</v>
+        <v>14</v>
       </c>
       <c r="G177" t="s" s="0">
-        <v>842</v>
+        <v>1010</v>
       </c>
       <c r="H177" t="s" s="0">
-        <v>842</v>
+        <v>1011</v>
+      </c>
+      <c r="I177" t="s" s="0">
+        <v>969</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s" s="0">
-        <v>843</v>
+        <v>1012</v>
       </c>
       <c r="B178" t="s" s="0">
-        <v>844</v>
+        <v>1013</v>
       </c>
       <c r="C178" t="s" s="0">
-        <v>845</v>
+        <v>1014</v>
       </c>
       <c r="D178" t="s" s="0">
-        <v>846</v>
+        <v>1015</v>
       </c>
       <c r="E178" t="s" s="0">
-        <v>12</v>
+        <v>1016</v>
       </c>
       <c r="F178" t="s" s="0">
-        <v>847</v>
+        <v>14</v>
       </c>
       <c r="G178" t="s" s="0">
-        <v>848</v>
+        <v>1017</v>
       </c>
       <c r="H178" t="s" s="0">
-        <v>848</v>
+        <v>1018</v>
+      </c>
+      <c r="I178" t="s" s="0">
+        <v>998</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s" s="0">
-        <v>849</v>
+        <v>1019</v>
       </c>
       <c r="B179" t="s" s="0">
-        <v>850</v>
+        <v>1020</v>
       </c>
       <c r="C179" t="s" s="0">
-        <v>851</v>
+        <v>1021</v>
       </c>
       <c r="D179" t="s" s="0">
-        <v>852</v>
+        <v>1022</v>
       </c>
       <c r="E179" t="s" s="0">
-        <v>12</v>
+        <v>1023</v>
       </c>
       <c r="F179" t="s" s="0">
-        <v>853</v>
+        <v>14</v>
       </c>
       <c r="G179" t="s" s="0">
-        <v>848</v>
+        <v>1024</v>
       </c>
       <c r="H179" t="s" s="0">
-        <v>848</v>
+        <v>1018</v>
+      </c>
+      <c r="I179" t="s" s="0">
+        <v>998</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s" s="0">
-        <v>854</v>
+        <v>1025</v>
       </c>
       <c r="B180" t="s" s="0">
-        <v>855</v>
+        <v>1026</v>
       </c>
       <c r="C180" t="s" s="0">
-        <v>856</v>
+        <v>1027</v>
       </c>
       <c r="D180" t="s" s="0">
-        <v>857</v>
+        <v>1028</v>
       </c>
       <c r="E180" t="s" s="0">
-        <v>12</v>
+        <v>1029</v>
       </c>
       <c r="F180" t="s" s="0">
-        <v>858</v>
+        <v>14</v>
       </c>
       <c r="G180" t="s" s="0">
-        <v>848</v>
+        <v>1030</v>
       </c>
       <c r="H180" t="s" s="0">
-        <v>848</v>
+        <v>1018</v>
+      </c>
+      <c r="I180" t="s" s="0">
+        <v>998</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s" s="0">
-        <v>859</v>
+        <v>1031</v>
       </c>
       <c r="B181" t="s" s="0">
-        <v>860</v>
+        <v>1032</v>
       </c>
       <c r="C181" t="s" s="0">
-        <v>861</v>
+        <v>1033</v>
       </c>
       <c r="D181" t="s" s="0">
-        <v>862</v>
+        <v>1034</v>
       </c>
       <c r="E181" t="s" s="0">
-        <v>12</v>
+        <v>1035</v>
       </c>
       <c r="F181" t="s" s="0">
-        <v>863</v>
+        <v>14</v>
       </c>
       <c r="G181" t="s" s="0">
-        <v>848</v>
+        <v>1036</v>
       </c>
       <c r="H181" t="s" s="0">
-        <v>848</v>
+        <v>1018</v>
+      </c>
+      <c r="I181" t="s" s="0">
+        <v>1037</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s" s="0">
-        <v>864</v>
+        <v>1038</v>
       </c>
       <c r="B182" t="s" s="0">
-        <v>865</v>
+        <v>1039</v>
       </c>
       <c r="C182" t="s" s="0">
-        <v>866</v>
+        <v>1040</v>
       </c>
       <c r="D182" t="s" s="0">
-        <v>867</v>
+        <v>1041</v>
       </c>
       <c r="E182" t="s" s="0">
-        <v>12</v>
+        <v>1042</v>
       </c>
       <c r="F182" t="s" s="0">
-        <v>863</v>
+        <v>14</v>
       </c>
       <c r="G182" t="s" s="0">
-        <v>848</v>
+        <v>1036</v>
       </c>
       <c r="H182" t="s" s="0">
-        <v>848</v>
+        <v>1018</v>
+      </c>
+      <c r="I182" t="s" s="0">
+        <v>998</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s" s="0">
-        <v>868</v>
+        <v>1043</v>
       </c>
       <c r="B183" t="s" s="0">
-        <v>869</v>
+        <v>1044</v>
       </c>
       <c r="C183" t="s" s="0">
-        <v>870</v>
+        <v>1045</v>
       </c>
       <c r="D183" t="s" s="0">
-        <v>871</v>
+        <v>1046</v>
       </c>
       <c r="E183" t="s" s="0">
-        <v>12</v>
+        <v>1047</v>
       </c>
       <c r="F183" t="s" s="0">
-        <v>872</v>
+        <v>14</v>
       </c>
       <c r="G183" t="s" s="0">
-        <v>873</v>
+        <v>1048</v>
       </c>
       <c r="H183" t="s" s="0">
-        <v>873</v>
+        <v>1049</v>
+      </c>
+      <c r="I183" t="s" s="0">
+        <v>1037</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s" s="0">
-        <v>874</v>
+        <v>1050</v>
       </c>
       <c r="B184" t="s" s="0">
-        <v>875</v>
+        <v>1051</v>
       </c>
       <c r="C184" t="s" s="0">
-        <v>876</v>
+        <v>1052</v>
       </c>
       <c r="D184" t="s" s="0">
-        <v>877</v>
+        <v>1053</v>
       </c>
       <c r="E184" t="s" s="0">
-        <v>12</v>
+        <v>1054</v>
       </c>
       <c r="F184" t="s" s="0">
-        <v>878</v>
+        <v>14</v>
       </c>
       <c r="G184" t="s" s="0">
-        <v>879</v>
+        <v>1055</v>
       </c>
       <c r="H184" t="s" s="0">
-        <v>880</v>
+        <v>1056</v>
+      </c>
+      <c r="I184" t="s" s="0">
+        <v>1037</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s" s="0">
-        <v>881</v>
+        <v>1057</v>
       </c>
       <c r="B185" t="s" s="0">
-        <v>882</v>
+        <v>1058</v>
       </c>
       <c r="C185" t="s" s="0">
-        <v>883</v>
+        <v>1059</v>
       </c>
       <c r="D185" t="s" s="0">
-        <v>884</v>
+        <v>1060</v>
       </c>
       <c r="E185" t="s" s="0">
-        <v>12</v>
+        <v>1061</v>
       </c>
       <c r="F185" t="s" s="0">
-        <v>885</v>
+        <v>14</v>
       </c>
       <c r="G185" t="s" s="0">
-        <v>879</v>
+        <v>1062</v>
       </c>
       <c r="H185" t="s" s="0">
-        <v>879</v>
+        <v>1056</v>
+      </c>
+      <c r="I185" t="s" s="0">
+        <v>1063</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s" s="0">
-        <v>886</v>
+        <v>1064</v>
       </c>
       <c r="B186" t="s" s="0">
-        <v>887</v>
+        <v>1065</v>
       </c>
       <c r="C186" t="s" s="0">
-        <v>888</v>
+        <v>1066</v>
       </c>
       <c r="D186" t="s" s="0">
-        <v>889</v>
+        <v>1067</v>
       </c>
       <c r="E186" t="s" s="0">
-        <v>12</v>
+        <v>1068</v>
       </c>
       <c r="F186" t="s" s="0">
-        <v>686</v>
+        <v>14</v>
       </c>
       <c r="G186" t="s" s="0">
-        <v>879</v>
+        <v>200</v>
       </c>
       <c r="H186" t="s" s="0">
-        <v>879</v>
+        <v>1056</v>
+      </c>
+      <c r="I186" t="s" s="0">
+        <v>1063</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s" s="0">
-        <v>890</v>
+        <v>1069</v>
       </c>
       <c r="B187" t="s" s="0">
-        <v>891</v>
+        <v>1070</v>
       </c>
       <c r="C187" t="s" s="0">
-        <v>892</v>
+        <v>1071</v>
       </c>
       <c r="D187" t="s" s="0">
-        <v>893</v>
+        <v>1072</v>
       </c>
       <c r="E187" t="s" s="0">
-        <v>12</v>
+        <v>1073</v>
       </c>
       <c r="F187" t="s" s="0">
-        <v>686</v>
+        <v>14</v>
       </c>
       <c r="G187" t="s" s="0">
-        <v>879</v>
+        <v>200</v>
       </c>
       <c r="H187" t="s" s="0">
-        <v>879</v>
+        <v>1056</v>
+      </c>
+      <c r="I187" t="s" s="0">
+        <v>1063</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s" s="0">
-        <v>894</v>
+        <v>1074</v>
       </c>
       <c r="B188" t="s" s="0">
-        <v>895</v>
+        <v>1075</v>
       </c>
       <c r="C188" t="s" s="0">
-        <v>896</v>
+        <v>1076</v>
       </c>
       <c r="D188" t="s" s="0">
-        <v>897</v>
+        <v>1077</v>
       </c>
       <c r="E188" t="s" s="0">
-        <v>12</v>
+        <v>1078</v>
       </c>
       <c r="F188" t="s" s="0">
-        <v>686</v>
+        <v>14</v>
       </c>
       <c r="G188" t="s" s="0">
-        <v>879</v>
+        <v>200</v>
       </c>
       <c r="H188" t="s" s="0">
-        <v>879</v>
+        <v>1056</v>
+      </c>
+      <c r="I188" t="s" s="0">
+        <v>1063</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s" s="0">
-        <v>898</v>
+        <v>1079</v>
       </c>
       <c r="B189" t="s" s="0">
-        <v>899</v>
+        <v>1080</v>
       </c>
       <c r="C189" t="s" s="0">
-        <v>900</v>
+        <v>1081</v>
       </c>
       <c r="D189" t="s" s="0">
-        <v>901</v>
+        <v>1082</v>
       </c>
       <c r="E189" t="s" s="0">
-        <v>12</v>
+        <v>1083</v>
       </c>
       <c r="F189" t="s" s="0">
-        <v>686</v>
+        <v>14</v>
       </c>
       <c r="G189" t="s" s="0">
-        <v>902</v>
+        <v>200</v>
       </c>
       <c r="H189" t="s" s="0">
-        <v>902</v>
+        <v>1084</v>
+      </c>
+      <c r="I189" t="s" s="0">
+        <v>1063</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="s" s="0">
-        <v>903</v>
+        <v>1085</v>
       </c>
       <c r="B190" t="s" s="0">
-        <v>904</v>
+        <v>1086</v>
       </c>
       <c r="C190" t="s" s="0">
-        <v>905</v>
+        <v>1087</v>
       </c>
       <c r="D190" t="s" s="0">
-        <v>906</v>
+        <v>1088</v>
       </c>
       <c r="E190" t="s" s="0">
-        <v>12</v>
+        <v>1089</v>
       </c>
       <c r="F190" t="s" s="0">
-        <v>907</v>
+        <v>14</v>
       </c>
       <c r="G190" t="s" s="0">
-        <v>908</v>
+        <v>1090</v>
       </c>
       <c r="H190" t="s" s="0">
-        <v>908</v>
+        <v>1091</v>
+      </c>
+      <c r="I190" t="s" s="0">
+        <v>1063</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s" s="0">
-        <v>909</v>
+        <v>1092</v>
       </c>
       <c r="B191" t="s" s="0">
-        <v>910</v>
+        <v>1093</v>
       </c>
       <c r="C191" t="s" s="0">
-        <v>911</v>
+        <v>1094</v>
       </c>
       <c r="D191" t="s" s="0">
-        <v>912</v>
+        <v>1095</v>
       </c>
       <c r="E191" t="s" s="0">
-        <v>12</v>
+        <v>1096</v>
       </c>
       <c r="F191" t="s" s="0">
-        <v>913</v>
+        <v>14</v>
       </c>
       <c r="G191" t="s" s="0">
-        <v>908</v>
+        <v>1097</v>
       </c>
       <c r="H191" t="s" s="0">
-        <v>908</v>
+        <v>1091</v>
+      </c>
+      <c r="I191" t="s" s="0">
+        <v>1063</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s" s="0">
-        <v>914</v>
+        <v>1098</v>
       </c>
       <c r="B192" t="s" s="0">
-        <v>915</v>
+        <v>1099</v>
       </c>
       <c r="C192" t="s" s="0">
-        <v>916</v>
+        <v>1100</v>
       </c>
       <c r="D192" t="s" s="0">
-        <v>917</v>
+        <v>1101</v>
       </c>
       <c r="E192" t="s" s="0">
-        <v>12</v>
+        <v>1102</v>
       </c>
       <c r="F192" t="s" s="0">
-        <v>801</v>
+        <v>14</v>
       </c>
       <c r="G192" t="s" s="0">
-        <v>918</v>
+        <v>961</v>
       </c>
       <c r="H192" t="s" s="0">
-        <v>918</v>
+        <v>1103</v>
+      </c>
+      <c r="I192" t="s" s="0">
+        <v>1063</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s" s="0">
-        <v>919</v>
+        <v>1104</v>
       </c>
       <c r="B193" t="s" s="0">
-        <v>920</v>
+        <v>1105</v>
       </c>
       <c r="C193" t="s" s="0">
-        <v>921</v>
+        <v>1106</v>
       </c>
       <c r="D193" t="s" s="0">
-        <v>922</v>
+        <v>1107</v>
       </c>
       <c r="E193" t="s" s="0">
-        <v>12</v>
+        <v>1108</v>
       </c>
       <c r="F193" t="s" s="0">
-        <v>923</v>
+        <v>14</v>
       </c>
       <c r="G193" t="s" s="0">
-        <v>924</v>
+        <v>1109</v>
       </c>
       <c r="H193" t="s" s="0">
-        <v>924</v>
+        <v>1110</v>
+      </c>
+      <c r="I193" t="s" s="0">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s" s="0">
+        <v>1111</v>
+      </c>
+      <c r="B194" t="s" s="0">
+        <v>1112</v>
+      </c>
+      <c r="C194" t="s" s="0">
+        <v>1113</v>
+      </c>
+      <c r="D194" t="s" s="0">
+        <v>1114</v>
+      </c>
+      <c r="E194" t="s" s="0">
+        <v>1115</v>
+      </c>
+      <c r="F194" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G194" t="s" s="0">
+        <v>515</v>
+      </c>
+      <c r="H194" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="I194" t="s" s="0">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/data/movie.xlsx
+++ b/data/movie.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1746" uniqueCount="1116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1755" uniqueCount="1123">
   <si>
     <t>movieId</t>
   </si>
@@ -2480,12 +2480,15 @@
     <t>https://www.atmovies.com.tw/movie/fbjp39335288/</t>
   </si>
   <si>
-    <t>劇場版</t>
+    <t>劇場版 BANG DREAM! AVE MUJICA PRIMA AURORA</t>
   </si>
   <si>
     <t>https://www.atmovies.com.tw/photo101/fbjp39335288/pl_fbjp39335288.jpg</t>
   </si>
   <si>
+    <t>2026-10-20 16:27:03</t>
+  </si>
+  <si>
     <t>144</t>
   </si>
   <si>
@@ -3360,6 +3363,24 @@
   </si>
   <si>
     <t>https://www.atmovies.com.tw/photo101/fjjp00193253/pl_fjjp00193253.jpg</t>
+  </si>
+  <si>
+    <t>1002</t>
+  </si>
+  <si>
+    <t>fscn37566261</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/movie/fscn37566261/</t>
+  </si>
+  <si>
+    <t>晚窒息</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/fscn37566261/pl_fscn37566261.jpg</t>
+  </si>
+  <si>
+    <t>2026-10-21 09:11:36</t>
   </si>
 </sst>
 </file>
@@ -3404,7 +3425,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:I194"/>
+  <dimension ref="A1:I195"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -7580,33 +7601,33 @@
         <v>812</v>
       </c>
       <c r="I144" t="s" s="0">
-        <v>17</v>
+        <v>824</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s" s="0">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B145" t="s" s="0">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="C145" t="s" s="0">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="D145" t="s" s="0">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="E145" t="s" s="0">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="F145" t="s" s="0">
         <v>14</v>
       </c>
       <c r="G145" t="s" s="0">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="H145" t="s" s="0">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="I145" t="s" s="0">
         <v>51</v>
@@ -7614,28 +7635,28 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="0">
+        <v>832</v>
+      </c>
+      <c r="B146" t="s" s="0">
+        <v>833</v>
+      </c>
+      <c r="C146" t="s" s="0">
+        <v>834</v>
+      </c>
+      <c r="D146" t="s" s="0">
+        <v>835</v>
+      </c>
+      <c r="E146" t="s" s="0">
+        <v>836</v>
+      </c>
+      <c r="F146" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G146" t="s" s="0">
+        <v>837</v>
+      </c>
+      <c r="H146" t="s" s="0">
         <v>831</v>
-      </c>
-      <c r="B146" t="s" s="0">
-        <v>832</v>
-      </c>
-      <c r="C146" t="s" s="0">
-        <v>833</v>
-      </c>
-      <c r="D146" t="s" s="0">
-        <v>834</v>
-      </c>
-      <c r="E146" t="s" s="0">
-        <v>835</v>
-      </c>
-      <c r="F146" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="G146" t="s" s="0">
-        <v>836</v>
-      </c>
-      <c r="H146" t="s" s="0">
-        <v>830</v>
       </c>
       <c r="I146" t="s" s="0">
         <v>51</v>
@@ -7643,19 +7664,19 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="0">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B147" t="s" s="0">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="C147" t="s" s="0">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="D147" t="s" s="0">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="E147" t="s" s="0">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="F147" t="s" s="0">
         <v>14</v>
@@ -7664,7 +7685,7 @@
         <v>321</v>
       </c>
       <c r="H147" t="s" s="0">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="I147" t="s" s="0">
         <v>338</v>
@@ -7672,19 +7693,19 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="0">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B148" t="s" s="0">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="C148" t="s" s="0">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="D148" t="s" s="0">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="E148" t="s" s="0">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="F148" t="s" s="0">
         <v>14</v>
@@ -7693,7 +7714,7 @@
         <v>379</v>
       </c>
       <c r="H148" t="s" s="0">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="I148" t="s" s="0">
         <v>338</v>
@@ -7701,19 +7722,19 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="0">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B149" t="s" s="0">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C149" t="s" s="0">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="D149" t="s" s="0">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="E149" t="s" s="0">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="F149" t="s" s="0">
         <v>14</v>
@@ -7722,7 +7743,7 @@
         <v>596</v>
       </c>
       <c r="H149" t="s" s="0">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="I149" t="s" s="0">
         <v>504</v>
@@ -7730,19 +7751,19 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="0">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B150" t="s" s="0">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="C150" t="s" s="0">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="D150" t="s" s="0">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="E150" t="s" s="0">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="F150" t="s" s="0">
         <v>14</v>
@@ -7751,7 +7772,7 @@
         <v>596</v>
       </c>
       <c r="H150" t="s" s="0">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="I150" t="s" s="0">
         <v>504</v>
@@ -7759,19 +7780,19 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="0">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B151" t="s" s="0">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C151" t="s" s="0">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="D151" t="s" s="0">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="E151" t="s" s="0">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="F151" t="s" s="0">
         <v>14</v>
@@ -7780,7 +7801,7 @@
         <v>596</v>
       </c>
       <c r="H151" t="s" s="0">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="I151" t="s" s="0">
         <v>633</v>
@@ -7788,19 +7809,19 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="0">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B152" t="s" s="0">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C152" t="s" s="0">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="D152" t="s" s="0">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="E152" t="s" s="0">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="F152" t="s" s="0">
         <v>14</v>
@@ -7809,7 +7830,7 @@
         <v>596</v>
       </c>
       <c r="H152" t="s" s="0">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="I152" t="s" s="0">
         <v>633</v>
@@ -7817,28 +7838,28 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="0">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B153" t="s" s="0">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="C153" t="s" s="0">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="D153" t="s" s="0">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="E153" t="s" s="0">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="F153" t="s" s="0">
         <v>14</v>
       </c>
       <c r="G153" t="s" s="0">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H153" t="s" s="0">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="I153" t="s" s="0">
         <v>633</v>
@@ -7846,19 +7867,19 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="0">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="B154" t="s" s="0">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="C154" t="s" s="0">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="D154" t="s" s="0">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="E154" t="s" s="0">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="F154" t="s" s="0">
         <v>14</v>
@@ -7867,7 +7888,7 @@
         <v>663</v>
       </c>
       <c r="H154" t="s" s="0">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="I154" t="s" s="0">
         <v>633</v>
@@ -7875,19 +7896,19 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="0">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="B155" t="s" s="0">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="C155" t="s" s="0">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="D155" t="s" s="0">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="E155" t="s" s="0">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="F155" t="s" s="0">
         <v>14</v>
@@ -7896,7 +7917,7 @@
         <v>663</v>
       </c>
       <c r="H155" t="s" s="0">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="I155" t="s" s="0">
         <v>680</v>
@@ -7904,19 +7925,19 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="0">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B156" t="s" s="0">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="C156" t="s" s="0">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="D156" t="s" s="0">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="E156" t="s" s="0">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="F156" t="s" s="0">
         <v>14</v>
@@ -7925,7 +7946,7 @@
         <v>707</v>
       </c>
       <c r="H156" t="s" s="0">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="I156" t="s" s="0">
         <v>680</v>
@@ -7933,19 +7954,19 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="0">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B157" t="s" s="0">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C157" t="s" s="0">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="D157" t="s" s="0">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="E157" t="s" s="0">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="F157" t="s" s="0">
         <v>14</v>
@@ -7954,7 +7975,7 @@
         <v>707</v>
       </c>
       <c r="H157" t="s" s="0">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="I157" t="s" s="0">
         <v>680</v>
@@ -7962,19 +7983,19 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="0">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B158" t="s" s="0">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="C158" t="s" s="0">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="D158" t="s" s="0">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="E158" t="s" s="0">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="F158" t="s" s="0">
         <v>14</v>
@@ -7983,7 +8004,7 @@
         <v>724</v>
       </c>
       <c r="H158" t="s" s="0">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="I158" t="s" s="0">
         <v>741</v>
@@ -7991,19 +8012,19 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="0">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B159" t="s" s="0">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="C159" t="s" s="0">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="D159" t="s" s="0">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="E159" t="s" s="0">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="F159" t="s" s="0">
         <v>14</v>
@@ -8012,7 +8033,7 @@
         <v>724</v>
       </c>
       <c r="H159" t="s" s="0">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="I159" t="s" s="0">
         <v>741</v>
@@ -8020,19 +8041,19 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="0">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B160" t="s" s="0">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="C160" t="s" s="0">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="D160" t="s" s="0">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="E160" t="s" s="0">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="F160" t="s" s="0">
         <v>14</v>
@@ -8041,7 +8062,7 @@
         <v>805</v>
       </c>
       <c r="H160" t="s" s="0">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="I160" t="s" s="0">
         <v>799</v>
@@ -8049,28 +8070,28 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="0">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B161" t="s" s="0">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="C161" t="s" s="0">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="D161" t="s" s="0">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="E161" t="s" s="0">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="F161" t="s" s="0">
         <v>14</v>
       </c>
       <c r="G161" t="s" s="0">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="H161" t="s" s="0">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="I161" t="s" s="0">
         <v>799</v>
@@ -8078,28 +8099,28 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="0">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B162" t="s" s="0">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="C162" t="s" s="0">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="D162" t="s" s="0">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="E162" t="s" s="0">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="F162" t="s" s="0">
         <v>14</v>
       </c>
       <c r="G162" t="s" s="0">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="H162" t="s" s="0">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="I162" t="s" s="0">
         <v>799</v>
@@ -8107,28 +8128,28 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="0">
+        <v>924</v>
+      </c>
+      <c r="B163" t="s" s="0">
+        <v>925</v>
+      </c>
+      <c r="C163" t="s" s="0">
+        <v>926</v>
+      </c>
+      <c r="D163" t="s" s="0">
+        <v>927</v>
+      </c>
+      <c r="E163" t="s" s="0">
+        <v>928</v>
+      </c>
+      <c r="F163" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G163" t="s" s="0">
         <v>923</v>
       </c>
-      <c r="B163" t="s" s="0">
-        <v>924</v>
-      </c>
-      <c r="C163" t="s" s="0">
-        <v>925</v>
-      </c>
-      <c r="D163" t="s" s="0">
-        <v>926</v>
-      </c>
-      <c r="E163" t="s" s="0">
-        <v>927</v>
-      </c>
-      <c r="F163" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="G163" t="s" s="0">
-        <v>922</v>
-      </c>
       <c r="H163" t="s" s="0">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="I163" t="s" s="0">
         <v>799</v>
@@ -8136,28 +8157,28 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="0">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B164" t="s" s="0">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="C164" t="s" s="0">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="D164" t="s" s="0">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="E164" t="s" s="0">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="F164" t="s" s="0">
         <v>14</v>
       </c>
       <c r="G164" t="s" s="0">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="H164" t="s" s="0">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="I164" t="s" s="0">
         <v>799</v>
@@ -8165,28 +8186,28 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="0">
+        <v>935</v>
+      </c>
+      <c r="B165" t="s" s="0">
+        <v>936</v>
+      </c>
+      <c r="C165" t="s" s="0">
+        <v>937</v>
+      </c>
+      <c r="D165" t="s" s="0">
+        <v>938</v>
+      </c>
+      <c r="E165" t="s" s="0">
+        <v>939</v>
+      </c>
+      <c r="F165" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G165" t="s" s="0">
         <v>934</v>
       </c>
-      <c r="B165" t="s" s="0">
-        <v>935</v>
-      </c>
-      <c r="C165" t="s" s="0">
-        <v>936</v>
-      </c>
-      <c r="D165" t="s" s="0">
-        <v>937</v>
-      </c>
-      <c r="E165" t="s" s="0">
-        <v>938</v>
-      </c>
-      <c r="F165" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="G165" t="s" s="0">
-        <v>933</v>
-      </c>
       <c r="H165" t="s" s="0">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="I165" t="s" s="0">
         <v>799</v>
@@ -8194,28 +8215,28 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="0">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B166" t="s" s="0">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="C166" t="s" s="0">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="D166" t="s" s="0">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="E166" t="s" s="0">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="F166" t="s" s="0">
         <v>14</v>
       </c>
       <c r="G166" t="s" s="0">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="H166" t="s" s="0">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="I166" t="s" s="0">
         <v>799</v>
@@ -8223,28 +8244,28 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="0">
+        <v>946</v>
+      </c>
+      <c r="B167" t="s" s="0">
+        <v>947</v>
+      </c>
+      <c r="C167" t="s" s="0">
+        <v>948</v>
+      </c>
+      <c r="D167" t="s" s="0">
+        <v>949</v>
+      </c>
+      <c r="E167" t="s" s="0">
+        <v>950</v>
+      </c>
+      <c r="F167" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G167" t="s" s="0">
         <v>945</v>
       </c>
-      <c r="B167" t="s" s="0">
-        <v>946</v>
-      </c>
-      <c r="C167" t="s" s="0">
-        <v>947</v>
-      </c>
-      <c r="D167" t="s" s="0">
-        <v>948</v>
-      </c>
-      <c r="E167" t="s" s="0">
-        <v>949</v>
-      </c>
-      <c r="F167" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="G167" t="s" s="0">
-        <v>944</v>
-      </c>
       <c r="H167" t="s" s="0">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="I167" t="s" s="0">
         <v>799</v>
@@ -8252,28 +8273,28 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="0">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B168" t="s" s="0">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="C168" t="s" s="0">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="D168" t="s" s="0">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="E168" t="s" s="0">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="F168" t="s" s="0">
         <v>14</v>
       </c>
       <c r="G168" t="s" s="0">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="H168" t="s" s="0">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="I168" t="s" s="0">
         <v>799</v>
@@ -8281,164 +8302,164 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="0">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B169" t="s" s="0">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="C169" t="s" s="0">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="D169" t="s" s="0">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="E169" t="s" s="0">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="F169" t="s" s="0">
         <v>14</v>
       </c>
       <c r="G169" t="s" s="0">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="H169" t="s" s="0">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="I169" t="s" s="0">
-        <v>962</v>
+        <v>963</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s" s="0">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B170" t="s" s="0">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="C170" t="s" s="0">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="D170" t="s" s="0">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="E170" t="s" s="0">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="F170" t="s" s="0">
         <v>14</v>
       </c>
       <c r="G170" t="s" s="0">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="H170" t="s" s="0">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="I170" t="s" s="0">
-        <v>969</v>
+        <v>970</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s" s="0">
+        <v>971</v>
+      </c>
+      <c r="B171" t="s" s="0">
+        <v>972</v>
+      </c>
+      <c r="C171" t="s" s="0">
+        <v>973</v>
+      </c>
+      <c r="D171" t="s" s="0">
+        <v>974</v>
+      </c>
+      <c r="E171" t="s" s="0">
+        <v>975</v>
+      </c>
+      <c r="F171" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G171" t="s" s="0">
+        <v>976</v>
+      </c>
+      <c r="H171" t="s" s="0">
+        <v>855</v>
+      </c>
+      <c r="I171" t="s" s="0">
         <v>970</v>
-      </c>
-      <c r="B171" t="s" s="0">
-        <v>971</v>
-      </c>
-      <c r="C171" t="s" s="0">
-        <v>972</v>
-      </c>
-      <c r="D171" t="s" s="0">
-        <v>973</v>
-      </c>
-      <c r="E171" t="s" s="0">
-        <v>974</v>
-      </c>
-      <c r="F171" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="G171" t="s" s="0">
-        <v>975</v>
-      </c>
-      <c r="H171" t="s" s="0">
-        <v>854</v>
-      </c>
-      <c r="I171" t="s" s="0">
-        <v>969</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s" s="0">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B172" t="s" s="0">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="C172" t="s" s="0">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="D172" t="s" s="0">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="E172" t="s" s="0">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="F172" t="s" s="0">
         <v>14</v>
       </c>
       <c r="G172" t="s" s="0">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="H172" t="s" s="0">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="I172" t="s" s="0">
-        <v>969</v>
+        <v>970</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s" s="0">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B173" t="s" s="0">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="C173" t="s" s="0">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="D173" t="s" s="0">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="E173" t="s" s="0">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="F173" t="s" s="0">
         <v>14</v>
       </c>
       <c r="G173" t="s" s="0">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H173" t="s" s="0">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="I173" t="s" s="0">
-        <v>969</v>
+        <v>970</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s" s="0">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="B174" t="s" s="0">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="C174" t="s" s="0">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="D174" t="s" s="0">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="E174" t="s" s="0">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="F174" t="s" s="0">
         <v>14</v>
@@ -8447,27 +8468,27 @@
         <v>200</v>
       </c>
       <c r="H174" t="s" s="0">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="I174" t="s" s="0">
-        <v>969</v>
+        <v>970</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s" s="0">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="B175" t="s" s="0">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="C175" t="s" s="0">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="D175" t="s" s="0">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="E175" t="s" s="0">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="F175" t="s" s="0">
         <v>14</v>
@@ -8476,317 +8497,317 @@
         <v>200</v>
       </c>
       <c r="H175" t="s" s="0">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="I175" t="s" s="0">
-        <v>998</v>
+        <v>999</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s" s="0">
+        <v>1000</v>
+      </c>
+      <c r="B176" t="s" s="0">
+        <v>1001</v>
+      </c>
+      <c r="C176" t="s" s="0">
+        <v>1002</v>
+      </c>
+      <c r="D176" t="s" s="0">
+        <v>1003</v>
+      </c>
+      <c r="E176" t="s" s="0">
+        <v>1004</v>
+      </c>
+      <c r="F176" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G176" t="s" s="0">
+        <v>1005</v>
+      </c>
+      <c r="H176" t="s" s="0">
+        <v>855</v>
+      </c>
+      <c r="I176" t="s" s="0">
         <v>999</v>
-      </c>
-      <c r="B176" t="s" s="0">
-        <v>1000</v>
-      </c>
-      <c r="C176" t="s" s="0">
-        <v>1001</v>
-      </c>
-      <c r="D176" t="s" s="0">
-        <v>1002</v>
-      </c>
-      <c r="E176" t="s" s="0">
-        <v>1003</v>
-      </c>
-      <c r="F176" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="G176" t="s" s="0">
-        <v>1004</v>
-      </c>
-      <c r="H176" t="s" s="0">
-        <v>854</v>
-      </c>
-      <c r="I176" t="s" s="0">
-        <v>998</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s" s="0">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B177" t="s" s="0">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="C177" t="s" s="0">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="D177" t="s" s="0">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="E177" t="s" s="0">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="F177" t="s" s="0">
         <v>14</v>
       </c>
       <c r="G177" t="s" s="0">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H177" t="s" s="0">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="I177" t="s" s="0">
-        <v>969</v>
+        <v>970</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s" s="0">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B178" t="s" s="0">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="C178" t="s" s="0">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D178" t="s" s="0">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="E178" t="s" s="0">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="F178" t="s" s="0">
         <v>14</v>
       </c>
       <c r="G178" t="s" s="0">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="H178" t="s" s="0">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="I178" t="s" s="0">
-        <v>998</v>
+        <v>999</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s" s="0">
+        <v>1020</v>
+      </c>
+      <c r="B179" t="s" s="0">
+        <v>1021</v>
+      </c>
+      <c r="C179" t="s" s="0">
+        <v>1022</v>
+      </c>
+      <c r="D179" t="s" s="0">
+        <v>1023</v>
+      </c>
+      <c r="E179" t="s" s="0">
+        <v>1024</v>
+      </c>
+      <c r="F179" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G179" t="s" s="0">
+        <v>1025</v>
+      </c>
+      <c r="H179" t="s" s="0">
         <v>1019</v>
       </c>
-      <c r="B179" t="s" s="0">
-        <v>1020</v>
-      </c>
-      <c r="C179" t="s" s="0">
-        <v>1021</v>
-      </c>
-      <c r="D179" t="s" s="0">
-        <v>1022</v>
-      </c>
-      <c r="E179" t="s" s="0">
-        <v>1023</v>
-      </c>
-      <c r="F179" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="G179" t="s" s="0">
-        <v>1024</v>
-      </c>
-      <c r="H179" t="s" s="0">
-        <v>1018</v>
-      </c>
       <c r="I179" t="s" s="0">
-        <v>998</v>
+        <v>999</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s" s="0">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="B180" t="s" s="0">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="C180" t="s" s="0">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="D180" t="s" s="0">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="E180" t="s" s="0">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="F180" t="s" s="0">
         <v>14</v>
       </c>
       <c r="G180" t="s" s="0">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="H180" t="s" s="0">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="I180" t="s" s="0">
-        <v>998</v>
+        <v>999</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s" s="0">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="B181" t="s" s="0">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="C181" t="s" s="0">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="D181" t="s" s="0">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="E181" t="s" s="0">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="F181" t="s" s="0">
         <v>14</v>
       </c>
       <c r="G181" t="s" s="0">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="H181" t="s" s="0">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="I181" t="s" s="0">
-        <v>1037</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s" s="0">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="B182" t="s" s="0">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="C182" t="s" s="0">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="D182" t="s" s="0">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="E182" t="s" s="0">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="F182" t="s" s="0">
         <v>14</v>
       </c>
       <c r="G182" t="s" s="0">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="H182" t="s" s="0">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="I182" t="s" s="0">
-        <v>998</v>
+        <v>999</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s" s="0">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="B183" t="s" s="0">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="C183" t="s" s="0">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="D183" t="s" s="0">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="E183" t="s" s="0">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="F183" t="s" s="0">
         <v>14</v>
       </c>
       <c r="G183" t="s" s="0">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="H183" t="s" s="0">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="I183" t="s" s="0">
-        <v>1037</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s" s="0">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B184" t="s" s="0">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="C184" t="s" s="0">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="D184" t="s" s="0">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="E184" t="s" s="0">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="F184" t="s" s="0">
         <v>14</v>
       </c>
       <c r="G184" t="s" s="0">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="H184" t="s" s="0">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="I184" t="s" s="0">
-        <v>1037</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s" s="0">
+        <v>1058</v>
+      </c>
+      <c r="B185" t="s" s="0">
+        <v>1059</v>
+      </c>
+      <c r="C185" t="s" s="0">
+        <v>1060</v>
+      </c>
+      <c r="D185" t="s" s="0">
+        <v>1061</v>
+      </c>
+      <c r="E185" t="s" s="0">
+        <v>1062</v>
+      </c>
+      <c r="F185" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G185" t="s" s="0">
+        <v>1063</v>
+      </c>
+      <c r="H185" t="s" s="0">
         <v>1057</v>
       </c>
-      <c r="B185" t="s" s="0">
-        <v>1058</v>
-      </c>
-      <c r="C185" t="s" s="0">
-        <v>1059</v>
-      </c>
-      <c r="D185" t="s" s="0">
-        <v>1060</v>
-      </c>
-      <c r="E185" t="s" s="0">
-        <v>1061</v>
-      </c>
-      <c r="F185" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="G185" t="s" s="0">
-        <v>1062</v>
-      </c>
-      <c r="H185" t="s" s="0">
-        <v>1056</v>
-      </c>
       <c r="I185" t="s" s="0">
-        <v>1063</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s" s="0">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="B186" t="s" s="0">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="C186" t="s" s="0">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="D186" t="s" s="0">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="E186" t="s" s="0">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="F186" t="s" s="0">
         <v>14</v>
@@ -8795,27 +8816,27 @@
         <v>200</v>
       </c>
       <c r="H186" t="s" s="0">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="I186" t="s" s="0">
-        <v>1063</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s" s="0">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="B187" t="s" s="0">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="C187" t="s" s="0">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="D187" t="s" s="0">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="E187" t="s" s="0">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="F187" t="s" s="0">
         <v>14</v>
@@ -8824,27 +8845,27 @@
         <v>200</v>
       </c>
       <c r="H187" t="s" s="0">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="I187" t="s" s="0">
-        <v>1063</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s" s="0">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B188" t="s" s="0">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="C188" t="s" s="0">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="D188" t="s" s="0">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="E188" t="s" s="0">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="F188" t="s" s="0">
         <v>14</v>
@@ -8853,27 +8874,27 @@
         <v>200</v>
       </c>
       <c r="H188" t="s" s="0">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="I188" t="s" s="0">
-        <v>1063</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s" s="0">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="B189" t="s" s="0">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="C189" t="s" s="0">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="D189" t="s" s="0">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="E189" t="s" s="0">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="F189" t="s" s="0">
         <v>14</v>
@@ -8882,123 +8903,123 @@
         <v>200</v>
       </c>
       <c r="H189" t="s" s="0">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="I189" t="s" s="0">
-        <v>1063</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="s" s="0">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="B190" t="s" s="0">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="C190" t="s" s="0">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="D190" t="s" s="0">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="E190" t="s" s="0">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="F190" t="s" s="0">
         <v>14</v>
       </c>
       <c r="G190" t="s" s="0">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="H190" t="s" s="0">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="I190" t="s" s="0">
-        <v>1063</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s" s="0">
+        <v>1093</v>
+      </c>
+      <c r="B191" t="s" s="0">
+        <v>1094</v>
+      </c>
+      <c r="C191" t="s" s="0">
+        <v>1095</v>
+      </c>
+      <c r="D191" t="s" s="0">
+        <v>1096</v>
+      </c>
+      <c r="E191" t="s" s="0">
+        <v>1097</v>
+      </c>
+      <c r="F191" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G191" t="s" s="0">
+        <v>1098</v>
+      </c>
+      <c r="H191" t="s" s="0">
         <v>1092</v>
       </c>
-      <c r="B191" t="s" s="0">
-        <v>1093</v>
-      </c>
-      <c r="C191" t="s" s="0">
-        <v>1094</v>
-      </c>
-      <c r="D191" t="s" s="0">
-        <v>1095</v>
-      </c>
-      <c r="E191" t="s" s="0">
-        <v>1096</v>
-      </c>
-      <c r="F191" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="G191" t="s" s="0">
-        <v>1097</v>
-      </c>
-      <c r="H191" t="s" s="0">
-        <v>1091</v>
-      </c>
       <c r="I191" t="s" s="0">
-        <v>1063</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s" s="0">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="B192" t="s" s="0">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="C192" t="s" s="0">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="D192" t="s" s="0">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="E192" t="s" s="0">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="F192" t="s" s="0">
         <v>14</v>
       </c>
       <c r="G192" t="s" s="0">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="H192" t="s" s="0">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="I192" t="s" s="0">
-        <v>1063</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s" s="0">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B193" t="s" s="0">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="C193" t="s" s="0">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="D193" t="s" s="0">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="E193" t="s" s="0">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="F193" t="s" s="0">
         <v>14</v>
       </c>
       <c r="G193" t="s" s="0">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="H193" t="s" s="0">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="I193" t="s" s="0">
         <v>17</v>
@@ -9006,19 +9027,19 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="0">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="B194" t="s" s="0">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="C194" t="s" s="0">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="D194" t="s" s="0">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="E194" t="s" s="0">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="F194" t="s" s="0">
         <v>14</v>
@@ -9031,6 +9052,35 @@
       </c>
       <c r="I194" t="s" s="0">
         <v>17</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s" s="0">
+        <v>1117</v>
+      </c>
+      <c r="B195" t="s" s="0">
+        <v>1118</v>
+      </c>
+      <c r="C195" t="s" s="0">
+        <v>1119</v>
+      </c>
+      <c r="D195" t="s" s="0">
+        <v>1120</v>
+      </c>
+      <c r="E195" t="s" s="0">
+        <v>1121</v>
+      </c>
+      <c r="F195" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G195" t="s" s="0">
+        <v>791</v>
+      </c>
+      <c r="H195" t="s" s="0">
+        <v>1122</v>
+      </c>
+      <c r="I195" t="s" s="0">
+        <v>1122</v>
       </c>
     </row>
   </sheetData>

--- a/data/movie.xlsx
+++ b/data/movie.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1755" uniqueCount="1123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1917" uniqueCount="1232">
   <si>
     <t>movieId</t>
   </si>
@@ -2237,24 +2237,30 @@
     <t>https://www.atmovies.com.tw/photo101/fbjp40826527/pl_fbjp40826527.jpg</t>
   </si>
   <si>
+    <t>2026-11-27 00:00:00</t>
+  </si>
+  <si>
+    <t>2026-10-24 23:39:26</t>
+  </si>
+  <si>
+    <t>130</t>
+  </si>
+  <si>
+    <t>fbjp39231777</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/movie/fbjp39231777/</t>
+  </si>
+  <si>
+    <t>放送禁止：一夫三妻</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/fbjp39231777/pl_fbjp39231777.jpg</t>
+  </si>
+  <si>
     <t>2026-10-20 16:16:13</t>
   </si>
   <si>
-    <t>130</t>
-  </si>
-  <si>
-    <t>fbjp39231777</t>
-  </si>
-  <si>
-    <t>https://www.atmovies.com.tw/movie/fbjp39231777/</t>
-  </si>
-  <si>
-    <t>放送禁止：一夫三妻</t>
-  </si>
-  <si>
-    <t>https://www.atmovies.com.tw/photo101/fbjp39231777/pl_fbjp39231777.jpg</t>
-  </si>
-  <si>
     <t>131</t>
   </si>
   <si>
@@ -2387,9 +2393,6 @@
     <t>https://www.atmovies.com.tw/photo101/ffen34966140/pl_ffen34966140.jpg</t>
   </si>
   <si>
-    <t>2026-11-27 00:00:00</t>
-  </si>
-  <si>
     <t>139</t>
   </si>
   <si>
@@ -3365,7 +3368,7 @@
     <t>https://www.atmovies.com.tw/photo101/fjjp00193253/pl_fjjp00193253.jpg</t>
   </si>
   <si>
-    <t>1002</t>
+    <t>194</t>
   </si>
   <si>
     <t>fscn37566261</t>
@@ -3381,6 +3384,330 @@
   </si>
   <si>
     <t>2026-10-21 09:11:36</t>
+  </si>
+  <si>
+    <t>195</t>
+  </si>
+  <si>
+    <t>fgen23289160</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/movie/fgen23289160/</t>
+  </si>
+  <si>
+    <t>哥吉拉-1.0</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/fgen23289160/pl_fgen23289160.jpg</t>
+  </si>
+  <si>
+    <t>2025-01-29 00:00:00</t>
+  </si>
+  <si>
+    <t>2026-10-24 23:29:55</t>
+  </si>
+  <si>
+    <t>196</t>
+  </si>
+  <si>
+    <t>flen40258746</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/movie/flen40258746/</t>
+  </si>
+  <si>
+    <t>危險關係—Lesley Manville版 (英國國家劇院現場)</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/flen40258746/pl_flen40258746.jpg</t>
+  </si>
+  <si>
+    <t>2026-09-22 00:00:00</t>
+  </si>
+  <si>
+    <t>2026-10-24 23:30:03</t>
+  </si>
+  <si>
+    <t>197</t>
+  </si>
+  <si>
+    <t>flen29781139</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/movie/flen29781139/</t>
+  </si>
+  <si>
+    <t>太空百合戰鬥姬</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/flen29781139/pl_flen29781139.jpg</t>
+  </si>
+  <si>
+    <t>2026-01-23 00:00:00</t>
+  </si>
+  <si>
+    <t>2026-10-24 23:30:07</t>
+  </si>
+  <si>
+    <t>198</t>
+  </si>
+  <si>
+    <t>fako92197800</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/movie/fako92197800/</t>
+  </si>
+  <si>
+    <t>ATEEZ演唱會電影</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/fako92197800/pl_fako92197800.jpg</t>
+  </si>
+  <si>
+    <t>2025-05-09 00:00:00</t>
+  </si>
+  <si>
+    <t>2026-10-24 23:30:08</t>
+  </si>
+  <si>
+    <t>199</t>
+  </si>
+  <si>
+    <t>fikr28997098</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/movie/fikr28997098/</t>
+  </si>
+  <si>
+    <t>IU CONCERT THE GOLDEN HOUR</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/fikr28997098/pl_fikr28997098.jpg</t>
+  </si>
+  <si>
+    <t>2022-09-28 00:00:00</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>fmfr78767908</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/movie/fmfr78767908/</t>
+  </si>
+  <si>
+    <t>麥特與麥斯</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/fmfr78767908/pl_fmfr78767908.jpg</t>
+  </si>
+  <si>
+    <t>2021-12-30 00:00:00</t>
+  </si>
+  <si>
+    <t>201</t>
+  </si>
+  <si>
+    <t>feko92601241</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/movie/feko92601241/</t>
+  </si>
+  <si>
+    <t>ENHYPEN WORLD TOUR BLOOD SAGA</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/feko92601241/pl_feko92601241.jpg</t>
+  </si>
+  <si>
+    <t>2026-10-24 23:30:10</t>
+  </si>
+  <si>
+    <t>202</t>
+  </si>
+  <si>
+    <t>fhko95518357</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/movie/fhko95518357/</t>
+  </si>
+  <si>
+    <t>HYBE CHEERING PARTY</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/fhko95518357/pl_fhko95518357.jpg</t>
+  </si>
+  <si>
+    <t>203</t>
+  </si>
+  <si>
+    <t>fsko94495333</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/movie/fsko94495333/</t>
+  </si>
+  <si>
+    <t>SEVENTEEN WORLD TOUR NEW</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/fsko94495333/pl_fsko94495333.jpg</t>
+  </si>
+  <si>
+    <t>204</t>
+  </si>
+  <si>
+    <t>ftkr95741254</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/movie/ftkr95741254/</t>
+  </si>
+  <si>
+    <t>TOMORROW X TOGETHER WORLD TOUR ACT TOMOR TOMORROW X TOGETHER WORLD TOUR ACT TOMORROW</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/ftkr95741254/pl_ftkr95741254.jpg</t>
+  </si>
+  <si>
+    <t>205</t>
+  </si>
+  <si>
+    <t>fozh32369769</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/movie/fozh32369769/</t>
+  </si>
+  <si>
+    <t>再次成為神</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/fozh32369769/pl_fozh32369769.jpg</t>
+  </si>
+  <si>
+    <t>206</t>
+  </si>
+  <si>
+    <t>fwko55645479</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/movie/fwko55645479/</t>
+  </si>
+  <si>
+    <t>世界的主人</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/fwko55645479/pl_fwko55645479.jpg</t>
+  </si>
+  <si>
+    <t>207</t>
+  </si>
+  <si>
+    <t>ften29355505</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/movie/ften29355505/</t>
+  </si>
+  <si>
+    <t>玩具總動員5</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/ften29355505/pl_ften29355505.jpg</t>
+  </si>
+  <si>
+    <t>2026-06-17 00:00:00</t>
+  </si>
+  <si>
+    <t>2026-10-24 23:30:12</t>
+  </si>
+  <si>
+    <t>208</t>
+  </si>
+  <si>
+    <t>fuhk38857175</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/movie/fuhk38857175/</t>
+  </si>
+  <si>
+    <t>UFO離奇命案</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/fuhk38857175/pl_fuhk38857175.jpg</t>
+  </si>
+  <si>
+    <t>2026-10-24 23:30:14</t>
+  </si>
+  <si>
+    <t>209</t>
+  </si>
+  <si>
+    <t>fven39649289</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/movie/fven39649289/</t>
+  </si>
+  <si>
+    <t>暮光禁地</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/fven39649289/pl_fven39649289.jpg</t>
+  </si>
+  <si>
+    <t>210</t>
+  </si>
+  <si>
+    <t>ftko39233100</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/movie/ftko39233100/</t>
+  </si>
+  <si>
+    <t>老千：惡魔之歌</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/ftko39233100/pl_ftko39233100.jpg</t>
+  </si>
+  <si>
+    <t>2026-10-24 23:30:16</t>
+  </si>
+  <si>
+    <t>211</t>
+  </si>
+  <si>
+    <t>fscn44935524</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/movie/fscn44935524/</t>
+  </si>
+  <si>
+    <t>花臉貓：修羅道</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/fscn44935524/pl_fscn44935524.jpg</t>
+  </si>
+  <si>
+    <t>2026-10-24 23:30:24</t>
+  </si>
+  <si>
+    <t>212</t>
+  </si>
+  <si>
+    <t>foth38223449</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/movie/foth38223449/</t>
+  </si>
+  <si>
+    <t>噬血蜈蚣</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/photo101/foth38223449/pl_foth38223449.jpg</t>
+  </si>
+  <si>
+    <t>2027-01-08 00:00:00</t>
+  </si>
+  <si>
+    <t>2026-10-24 23:30:25</t>
   </si>
 </sst>
 </file>
@@ -3425,7 +3752,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:I195"/>
+  <dimension ref="A1:I213"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -7189,30 +7516,30 @@
         <v>14</v>
       </c>
       <c r="G130" t="s" s="0">
-        <v>724</v>
+        <v>741</v>
       </c>
       <c r="H130" t="s" s="0">
         <v>730</v>
       </c>
       <c r="I130" t="s" s="0">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s" s="0">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B131" t="s" s="0">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C131" t="s" s="0">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="D131" t="s" s="0">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="E131" t="s" s="0">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="F131" t="s" s="0">
         <v>14</v>
@@ -7224,24 +7551,24 @@
         <v>730</v>
       </c>
       <c r="I131" t="s" s="0">
-        <v>741</v>
+        <v>748</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s" s="0">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="B132" t="s" s="0">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="C132" t="s" s="0">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="D132" t="s" s="0">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="E132" t="s" s="0">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="F132" t="s" s="0">
         <v>14</v>
@@ -7250,27 +7577,27 @@
         <v>724</v>
       </c>
       <c r="H132" t="s" s="0">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="I132" t="s" s="0">
-        <v>741</v>
+        <v>748</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s" s="0">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="B133" t="s" s="0">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="C133" t="s" s="0">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="D133" t="s" s="0">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="E133" t="s" s="0">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="F133" t="s" s="0">
         <v>14</v>
@@ -7279,268 +7606,268 @@
         <v>724</v>
       </c>
       <c r="H133" t="s" s="0">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="I133" t="s" s="0">
-        <v>741</v>
+        <v>748</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="0">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="B134" t="s" s="0">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="C134" t="s" s="0">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="D134" t="s" s="0">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="E134" t="s" s="0">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="F134" t="s" s="0">
         <v>14</v>
       </c>
       <c r="G134" t="s" s="0">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="H134" t="s" s="0">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="I134" t="s" s="0">
-        <v>741</v>
+        <v>748</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s" s="0">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="B135" t="s" s="0">
+        <v>767</v>
+      </c>
+      <c r="C135" t="s" s="0">
+        <v>768</v>
+      </c>
+      <c r="D135" t="s" s="0">
+        <v>769</v>
+      </c>
+      <c r="E135" t="s" s="0">
+        <v>770</v>
+      </c>
+      <c r="F135" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G135" t="s" s="0">
         <v>765</v>
       </c>
-      <c r="C135" t="s" s="0">
-        <v>766</v>
-      </c>
-      <c r="D135" t="s" s="0">
-        <v>767</v>
-      </c>
-      <c r="E135" t="s" s="0">
-        <v>768</v>
-      </c>
-      <c r="F135" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="G135" t="s" s="0">
-        <v>763</v>
-      </c>
       <c r="H135" t="s" s="0">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="I135" t="s" s="0">
-        <v>741</v>
+        <v>748</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s" s="0">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="B136" t="s" s="0">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="C136" t="s" s="0">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="D136" t="s" s="0">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="E136" t="s" s="0">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="F136" t="s" s="0">
         <v>14</v>
       </c>
       <c r="G136" t="s" s="0">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="H136" t="s" s="0">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="I136" t="s" s="0">
-        <v>741</v>
+        <v>748</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s" s="0">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="B137" t="s" s="0">
+        <v>778</v>
+      </c>
+      <c r="C137" t="s" s="0">
+        <v>779</v>
+      </c>
+      <c r="D137" t="s" s="0">
+        <v>780</v>
+      </c>
+      <c r="E137" t="s" s="0">
+        <v>781</v>
+      </c>
+      <c r="F137" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G137" t="s" s="0">
+        <v>765</v>
+      </c>
+      <c r="H137" t="s" s="0">
         <v>776</v>
       </c>
-      <c r="C137" t="s" s="0">
-        <v>777</v>
-      </c>
-      <c r="D137" t="s" s="0">
-        <v>778</v>
-      </c>
-      <c r="E137" t="s" s="0">
-        <v>779</v>
-      </c>
-      <c r="F137" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="G137" t="s" s="0">
-        <v>763</v>
-      </c>
-      <c r="H137" t="s" s="0">
-        <v>774</v>
-      </c>
       <c r="I137" t="s" s="0">
-        <v>741</v>
+        <v>748</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s" s="0">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="B138" t="s" s="0">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="C138" t="s" s="0">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="D138" t="s" s="0">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="E138" t="s" s="0">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="F138" t="s" s="0">
         <v>14</v>
       </c>
       <c r="G138" t="s" s="0">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="H138" t="s" s="0">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="I138" t="s" s="0">
-        <v>741</v>
+        <v>748</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s" s="0">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="B139" t="s" s="0">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="C139" t="s" s="0">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="D139" t="s" s="0">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="E139" t="s" s="0">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="F139" t="s" s="0">
         <v>14</v>
       </c>
       <c r="G139" t="s" s="0">
-        <v>791</v>
+        <v>741</v>
       </c>
       <c r="H139" t="s" s="0">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="I139" t="s" s="0">
-        <v>741</v>
+        <v>748</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s" s="0">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B140" t="s" s="0">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C140" t="s" s="0">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="D140" t="s" s="0">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="E140" t="s" s="0">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="F140" t="s" s="0">
         <v>14</v>
       </c>
       <c r="G140" t="s" s="0">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H140" t="s" s="0">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="I140" t="s" s="0">
-        <v>799</v>
+        <v>800</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s" s="0">
+        <v>801</v>
+      </c>
+      <c r="B141" t="s" s="0">
+        <v>802</v>
+      </c>
+      <c r="C141" t="s" s="0">
+        <v>803</v>
+      </c>
+      <c r="D141" t="s" s="0">
+        <v>804</v>
+      </c>
+      <c r="E141" t="s" s="0">
+        <v>805</v>
+      </c>
+      <c r="F141" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G141" t="s" s="0">
+        <v>806</v>
+      </c>
+      <c r="H141" t="s" s="0">
+        <v>799</v>
+      </c>
+      <c r="I141" t="s" s="0">
         <v>800</v>
-      </c>
-      <c r="B141" t="s" s="0">
-        <v>801</v>
-      </c>
-      <c r="C141" t="s" s="0">
-        <v>802</v>
-      </c>
-      <c r="D141" t="s" s="0">
-        <v>803</v>
-      </c>
-      <c r="E141" t="s" s="0">
-        <v>804</v>
-      </c>
-      <c r="F141" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="G141" t="s" s="0">
-        <v>805</v>
-      </c>
-      <c r="H141" t="s" s="0">
-        <v>798</v>
-      </c>
-      <c r="I141" t="s" s="0">
-        <v>799</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s" s="0">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B142" t="s" s="0">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C142" t="s" s="0">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="D142" t="s" s="0">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="E142" t="s" s="0">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="F142" t="s" s="0">
         <v>14</v>
       </c>
       <c r="G142" t="s" s="0">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H142" t="s" s="0">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="I142" t="s" s="0">
         <v>516</v>
@@ -7548,28 +7875,28 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="0">
+        <v>814</v>
+      </c>
+      <c r="B143" t="s" s="0">
+        <v>815</v>
+      </c>
+      <c r="C143" t="s" s="0">
+        <v>816</v>
+      </c>
+      <c r="D143" t="s" s="0">
+        <v>817</v>
+      </c>
+      <c r="E143" t="s" s="0">
+        <v>818</v>
+      </c>
+      <c r="F143" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G143" t="s" s="0">
+        <v>819</v>
+      </c>
+      <c r="H143" t="s" s="0">
         <v>813</v>
-      </c>
-      <c r="B143" t="s" s="0">
-        <v>814</v>
-      </c>
-      <c r="C143" t="s" s="0">
-        <v>815</v>
-      </c>
-      <c r="D143" t="s" s="0">
-        <v>816</v>
-      </c>
-      <c r="E143" t="s" s="0">
-        <v>817</v>
-      </c>
-      <c r="F143" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="G143" t="s" s="0">
-        <v>818</v>
-      </c>
-      <c r="H143" t="s" s="0">
-        <v>812</v>
       </c>
       <c r="I143" t="s" s="0">
         <v>516</v>
@@ -7577,19 +7904,19 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="0">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B144" t="s" s="0">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C144" t="s" s="0">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="D144" t="s" s="0">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="E144" t="s" s="0">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="F144" t="s" s="0">
         <v>14</v>
@@ -7598,36 +7925,36 @@
         <v>200</v>
       </c>
       <c r="H144" t="s" s="0">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="I144" t="s" s="0">
-        <v>824</v>
+        <v>825</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s" s="0">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B145" t="s" s="0">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C145" t="s" s="0">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="D145" t="s" s="0">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="E145" t="s" s="0">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="F145" t="s" s="0">
         <v>14</v>
       </c>
       <c r="G145" t="s" s="0">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="H145" t="s" s="0">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="I145" t="s" s="0">
         <v>51</v>
@@ -7635,28 +7962,28 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="0">
+        <v>833</v>
+      </c>
+      <c r="B146" t="s" s="0">
+        <v>834</v>
+      </c>
+      <c r="C146" t="s" s="0">
+        <v>835</v>
+      </c>
+      <c r="D146" t="s" s="0">
+        <v>836</v>
+      </c>
+      <c r="E146" t="s" s="0">
+        <v>837</v>
+      </c>
+      <c r="F146" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G146" t="s" s="0">
+        <v>838</v>
+      </c>
+      <c r="H146" t="s" s="0">
         <v>832</v>
-      </c>
-      <c r="B146" t="s" s="0">
-        <v>833</v>
-      </c>
-      <c r="C146" t="s" s="0">
-        <v>834</v>
-      </c>
-      <c r="D146" t="s" s="0">
-        <v>835</v>
-      </c>
-      <c r="E146" t="s" s="0">
-        <v>836</v>
-      </c>
-      <c r="F146" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="G146" t="s" s="0">
-        <v>837</v>
-      </c>
-      <c r="H146" t="s" s="0">
-        <v>831</v>
       </c>
       <c r="I146" t="s" s="0">
         <v>51</v>
@@ -7664,19 +7991,19 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="0">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B147" t="s" s="0">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C147" t="s" s="0">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="D147" t="s" s="0">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="E147" t="s" s="0">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="F147" t="s" s="0">
         <v>14</v>
@@ -7685,7 +8012,7 @@
         <v>321</v>
       </c>
       <c r="H147" t="s" s="0">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="I147" t="s" s="0">
         <v>338</v>
@@ -7693,19 +8020,19 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="0">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B148" t="s" s="0">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="C148" t="s" s="0">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="D148" t="s" s="0">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="E148" t="s" s="0">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="F148" t="s" s="0">
         <v>14</v>
@@ -7714,7 +8041,7 @@
         <v>379</v>
       </c>
       <c r="H148" t="s" s="0">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="I148" t="s" s="0">
         <v>338</v>
@@ -7722,19 +8049,19 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="0">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B149" t="s" s="0">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C149" t="s" s="0">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="D149" t="s" s="0">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="E149" t="s" s="0">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="F149" t="s" s="0">
         <v>14</v>
@@ -7743,7 +8070,7 @@
         <v>596</v>
       </c>
       <c r="H149" t="s" s="0">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="I149" t="s" s="0">
         <v>504</v>
@@ -7751,19 +8078,19 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="0">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B150" t="s" s="0">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="C150" t="s" s="0">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="D150" t="s" s="0">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="E150" t="s" s="0">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="F150" t="s" s="0">
         <v>14</v>
@@ -7772,7 +8099,7 @@
         <v>596</v>
       </c>
       <c r="H150" t="s" s="0">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="I150" t="s" s="0">
         <v>504</v>
@@ -7780,19 +8107,19 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="0">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B151" t="s" s="0">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="C151" t="s" s="0">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="D151" t="s" s="0">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="E151" t="s" s="0">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="F151" t="s" s="0">
         <v>14</v>
@@ -7801,7 +8128,7 @@
         <v>596</v>
       </c>
       <c r="H151" t="s" s="0">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="I151" t="s" s="0">
         <v>633</v>
@@ -7809,19 +8136,19 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="0">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B152" t="s" s="0">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="C152" t="s" s="0">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="D152" t="s" s="0">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="E152" t="s" s="0">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="F152" t="s" s="0">
         <v>14</v>
@@ -7830,7 +8157,7 @@
         <v>596</v>
       </c>
       <c r="H152" t="s" s="0">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="I152" t="s" s="0">
         <v>633</v>
@@ -7838,28 +8165,28 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="0">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B153" t="s" s="0">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C153" t="s" s="0">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="D153" t="s" s="0">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="E153" t="s" s="0">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="F153" t="s" s="0">
         <v>14</v>
       </c>
       <c r="G153" t="s" s="0">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H153" t="s" s="0">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="I153" t="s" s="0">
         <v>633</v>
@@ -7867,19 +8194,19 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="0">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B154" t="s" s="0">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="C154" t="s" s="0">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="D154" t="s" s="0">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="E154" t="s" s="0">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="F154" t="s" s="0">
         <v>14</v>
@@ -7888,7 +8215,7 @@
         <v>663</v>
       </c>
       <c r="H154" t="s" s="0">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="I154" t="s" s="0">
         <v>633</v>
@@ -7896,19 +8223,19 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="0">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B155" t="s" s="0">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="C155" t="s" s="0">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="D155" t="s" s="0">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="E155" t="s" s="0">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="F155" t="s" s="0">
         <v>14</v>
@@ -7917,7 +8244,7 @@
         <v>663</v>
       </c>
       <c r="H155" t="s" s="0">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="I155" t="s" s="0">
         <v>680</v>
@@ -7925,19 +8252,19 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="0">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="B156" t="s" s="0">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="C156" t="s" s="0">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="D156" t="s" s="0">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="E156" t="s" s="0">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="F156" t="s" s="0">
         <v>14</v>
@@ -7946,7 +8273,7 @@
         <v>707</v>
       </c>
       <c r="H156" t="s" s="0">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="I156" t="s" s="0">
         <v>680</v>
@@ -7954,19 +8281,19 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="0">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B157" t="s" s="0">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="C157" t="s" s="0">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="D157" t="s" s="0">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="E157" t="s" s="0">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="F157" t="s" s="0">
         <v>14</v>
@@ -7975,7 +8302,7 @@
         <v>707</v>
       </c>
       <c r="H157" t="s" s="0">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="I157" t="s" s="0">
         <v>680</v>
@@ -7983,19 +8310,19 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="0">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B158" t="s" s="0">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="C158" t="s" s="0">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="D158" t="s" s="0">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="E158" t="s" s="0">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="F158" t="s" s="0">
         <v>14</v>
@@ -8004,27 +8331,27 @@
         <v>724</v>
       </c>
       <c r="H158" t="s" s="0">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="I158" t="s" s="0">
-        <v>741</v>
+        <v>748</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s" s="0">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B159" t="s" s="0">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="C159" t="s" s="0">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="D159" t="s" s="0">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="E159" t="s" s="0">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="F159" t="s" s="0">
         <v>14</v>
@@ -8033,433 +8360,433 @@
         <v>724</v>
       </c>
       <c r="H159" t="s" s="0">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="I159" t="s" s="0">
-        <v>741</v>
+        <v>748</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s" s="0">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B160" t="s" s="0">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="C160" t="s" s="0">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="D160" t="s" s="0">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="E160" t="s" s="0">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="F160" t="s" s="0">
         <v>14</v>
       </c>
       <c r="G160" t="s" s="0">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H160" t="s" s="0">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="I160" t="s" s="0">
-        <v>799</v>
+        <v>800</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s" s="0">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B161" t="s" s="0">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="C161" t="s" s="0">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="D161" t="s" s="0">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="E161" t="s" s="0">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="F161" t="s" s="0">
         <v>14</v>
       </c>
       <c r="G161" t="s" s="0">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="H161" t="s" s="0">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="I161" t="s" s="0">
-        <v>799</v>
+        <v>800</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s" s="0">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B162" t="s" s="0">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="C162" t="s" s="0">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="D162" t="s" s="0">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="E162" t="s" s="0">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="F162" t="s" s="0">
         <v>14</v>
       </c>
       <c r="G162" t="s" s="0">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="H162" t="s" s="0">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="I162" t="s" s="0">
-        <v>799</v>
+        <v>800</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s" s="0">
+        <v>925</v>
+      </c>
+      <c r="B163" t="s" s="0">
+        <v>926</v>
+      </c>
+      <c r="C163" t="s" s="0">
+        <v>927</v>
+      </c>
+      <c r="D163" t="s" s="0">
+        <v>928</v>
+      </c>
+      <c r="E163" t="s" s="0">
+        <v>929</v>
+      </c>
+      <c r="F163" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G163" t="s" s="0">
         <v>924</v>
       </c>
-      <c r="B163" t="s" s="0">
-        <v>925</v>
-      </c>
-      <c r="C163" t="s" s="0">
-        <v>926</v>
-      </c>
-      <c r="D163" t="s" s="0">
-        <v>927</v>
-      </c>
-      <c r="E163" t="s" s="0">
-        <v>928</v>
-      </c>
-      <c r="F163" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="G163" t="s" s="0">
-        <v>923</v>
-      </c>
       <c r="H163" t="s" s="0">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="I163" t="s" s="0">
-        <v>799</v>
+        <v>800</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s" s="0">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B164" t="s" s="0">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="C164" t="s" s="0">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="D164" t="s" s="0">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="E164" t="s" s="0">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="F164" t="s" s="0">
         <v>14</v>
       </c>
       <c r="G164" t="s" s="0">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="H164" t="s" s="0">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="I164" t="s" s="0">
-        <v>799</v>
+        <v>800</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s" s="0">
+        <v>936</v>
+      </c>
+      <c r="B165" t="s" s="0">
+        <v>937</v>
+      </c>
+      <c r="C165" t="s" s="0">
+        <v>938</v>
+      </c>
+      <c r="D165" t="s" s="0">
+        <v>939</v>
+      </c>
+      <c r="E165" t="s" s="0">
+        <v>940</v>
+      </c>
+      <c r="F165" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G165" t="s" s="0">
         <v>935</v>
       </c>
-      <c r="B165" t="s" s="0">
-        <v>936</v>
-      </c>
-      <c r="C165" t="s" s="0">
-        <v>937</v>
-      </c>
-      <c r="D165" t="s" s="0">
-        <v>938</v>
-      </c>
-      <c r="E165" t="s" s="0">
-        <v>939</v>
-      </c>
-      <c r="F165" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="G165" t="s" s="0">
-        <v>934</v>
-      </c>
       <c r="H165" t="s" s="0">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="I165" t="s" s="0">
-        <v>799</v>
+        <v>800</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s" s="0">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B166" t="s" s="0">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="C166" t="s" s="0">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="D166" t="s" s="0">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="E166" t="s" s="0">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F166" t="s" s="0">
         <v>14</v>
       </c>
       <c r="G166" t="s" s="0">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="H166" t="s" s="0">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="I166" t="s" s="0">
-        <v>799</v>
+        <v>800</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s" s="0">
+        <v>947</v>
+      </c>
+      <c r="B167" t="s" s="0">
+        <v>948</v>
+      </c>
+      <c r="C167" t="s" s="0">
+        <v>949</v>
+      </c>
+      <c r="D167" t="s" s="0">
+        <v>950</v>
+      </c>
+      <c r="E167" t="s" s="0">
+        <v>951</v>
+      </c>
+      <c r="F167" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G167" t="s" s="0">
         <v>946</v>
       </c>
-      <c r="B167" t="s" s="0">
-        <v>947</v>
-      </c>
-      <c r="C167" t="s" s="0">
-        <v>948</v>
-      </c>
-      <c r="D167" t="s" s="0">
-        <v>949</v>
-      </c>
-      <c r="E167" t="s" s="0">
-        <v>950</v>
-      </c>
-      <c r="F167" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="G167" t="s" s="0">
-        <v>945</v>
-      </c>
       <c r="H167" t="s" s="0">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="I167" t="s" s="0">
-        <v>799</v>
+        <v>800</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s" s="0">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="B168" t="s" s="0">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="C168" t="s" s="0">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="D168" t="s" s="0">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="E168" t="s" s="0">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="F168" t="s" s="0">
         <v>14</v>
       </c>
       <c r="G168" t="s" s="0">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="H168" t="s" s="0">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="I168" t="s" s="0">
-        <v>799</v>
+        <v>800</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s" s="0">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B169" t="s" s="0">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="C169" t="s" s="0">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="D169" t="s" s="0">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="E169" t="s" s="0">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="F169" t="s" s="0">
         <v>14</v>
       </c>
       <c r="G169" t="s" s="0">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="H169" t="s" s="0">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="I169" t="s" s="0">
-        <v>963</v>
+        <v>964</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s" s="0">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B170" t="s" s="0">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="C170" t="s" s="0">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="D170" t="s" s="0">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="E170" t="s" s="0">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="F170" t="s" s="0">
         <v>14</v>
       </c>
       <c r="G170" t="s" s="0">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="H170" t="s" s="0">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="I170" t="s" s="0">
-        <v>970</v>
+        <v>971</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s" s="0">
+        <v>972</v>
+      </c>
+      <c r="B171" t="s" s="0">
+        <v>973</v>
+      </c>
+      <c r="C171" t="s" s="0">
+        <v>974</v>
+      </c>
+      <c r="D171" t="s" s="0">
+        <v>975</v>
+      </c>
+      <c r="E171" t="s" s="0">
+        <v>976</v>
+      </c>
+      <c r="F171" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G171" t="s" s="0">
+        <v>977</v>
+      </c>
+      <c r="H171" t="s" s="0">
+        <v>856</v>
+      </c>
+      <c r="I171" t="s" s="0">
         <v>971</v>
-      </c>
-      <c r="B171" t="s" s="0">
-        <v>972</v>
-      </c>
-      <c r="C171" t="s" s="0">
-        <v>973</v>
-      </c>
-      <c r="D171" t="s" s="0">
-        <v>974</v>
-      </c>
-      <c r="E171" t="s" s="0">
-        <v>975</v>
-      </c>
-      <c r="F171" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="G171" t="s" s="0">
-        <v>976</v>
-      </c>
-      <c r="H171" t="s" s="0">
-        <v>855</v>
-      </c>
-      <c r="I171" t="s" s="0">
-        <v>970</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s" s="0">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B172" t="s" s="0">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="C172" t="s" s="0">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="D172" t="s" s="0">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="E172" t="s" s="0">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="F172" t="s" s="0">
         <v>14</v>
       </c>
       <c r="G172" t="s" s="0">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H172" t="s" s="0">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="I172" t="s" s="0">
-        <v>970</v>
+        <v>971</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s" s="0">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B173" t="s" s="0">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="C173" t="s" s="0">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="D173" t="s" s="0">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="E173" t="s" s="0">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="F173" t="s" s="0">
         <v>14</v>
       </c>
       <c r="G173" t="s" s="0">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H173" t="s" s="0">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="I173" t="s" s="0">
-        <v>970</v>
+        <v>971</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s" s="0">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="B174" t="s" s="0">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="C174" t="s" s="0">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="D174" t="s" s="0">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="E174" t="s" s="0">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="F174" t="s" s="0">
         <v>14</v>
@@ -8468,27 +8795,27 @@
         <v>200</v>
       </c>
       <c r="H174" t="s" s="0">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="I174" t="s" s="0">
-        <v>970</v>
+        <v>971</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s" s="0">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="B175" t="s" s="0">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="C175" t="s" s="0">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="D175" t="s" s="0">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="E175" t="s" s="0">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="F175" t="s" s="0">
         <v>14</v>
@@ -8497,317 +8824,317 @@
         <v>200</v>
       </c>
       <c r="H175" t="s" s="0">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="I175" t="s" s="0">
-        <v>999</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s" s="0">
+        <v>1001</v>
+      </c>
+      <c r="B176" t="s" s="0">
+        <v>1002</v>
+      </c>
+      <c r="C176" t="s" s="0">
+        <v>1003</v>
+      </c>
+      <c r="D176" t="s" s="0">
+        <v>1004</v>
+      </c>
+      <c r="E176" t="s" s="0">
+        <v>1005</v>
+      </c>
+      <c r="F176" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G176" t="s" s="0">
+        <v>1006</v>
+      </c>
+      <c r="H176" t="s" s="0">
+        <v>856</v>
+      </c>
+      <c r="I176" t="s" s="0">
         <v>1000</v>
-      </c>
-      <c r="B176" t="s" s="0">
-        <v>1001</v>
-      </c>
-      <c r="C176" t="s" s="0">
-        <v>1002</v>
-      </c>
-      <c r="D176" t="s" s="0">
-        <v>1003</v>
-      </c>
-      <c r="E176" t="s" s="0">
-        <v>1004</v>
-      </c>
-      <c r="F176" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="G176" t="s" s="0">
-        <v>1005</v>
-      </c>
-      <c r="H176" t="s" s="0">
-        <v>855</v>
-      </c>
-      <c r="I176" t="s" s="0">
-        <v>999</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s" s="0">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B177" t="s" s="0">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="C177" t="s" s="0">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="D177" t="s" s="0">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="E177" t="s" s="0">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="F177" t="s" s="0">
         <v>14</v>
       </c>
       <c r="G177" t="s" s="0">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H177" t="s" s="0">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="I177" t="s" s="0">
-        <v>970</v>
+        <v>971</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s" s="0">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="B178" t="s" s="0">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="C178" t="s" s="0">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="D178" t="s" s="0">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="E178" t="s" s="0">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="F178" t="s" s="0">
         <v>14</v>
       </c>
       <c r="G178" t="s" s="0">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="H178" t="s" s="0">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="I178" t="s" s="0">
-        <v>999</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s" s="0">
+        <v>1021</v>
+      </c>
+      <c r="B179" t="s" s="0">
+        <v>1022</v>
+      </c>
+      <c r="C179" t="s" s="0">
+        <v>1023</v>
+      </c>
+      <c r="D179" t="s" s="0">
+        <v>1024</v>
+      </c>
+      <c r="E179" t="s" s="0">
+        <v>1025</v>
+      </c>
+      <c r="F179" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G179" t="s" s="0">
+        <v>1026</v>
+      </c>
+      <c r="H179" t="s" s="0">
         <v>1020</v>
       </c>
-      <c r="B179" t="s" s="0">
-        <v>1021</v>
-      </c>
-      <c r="C179" t="s" s="0">
-        <v>1022</v>
-      </c>
-      <c r="D179" t="s" s="0">
-        <v>1023</v>
-      </c>
-      <c r="E179" t="s" s="0">
-        <v>1024</v>
-      </c>
-      <c r="F179" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="G179" t="s" s="0">
-        <v>1025</v>
-      </c>
-      <c r="H179" t="s" s="0">
-        <v>1019</v>
-      </c>
       <c r="I179" t="s" s="0">
-        <v>999</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s" s="0">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B180" t="s" s="0">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="C180" t="s" s="0">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="D180" t="s" s="0">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="E180" t="s" s="0">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="F180" t="s" s="0">
         <v>14</v>
       </c>
       <c r="G180" t="s" s="0">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="H180" t="s" s="0">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="I180" t="s" s="0">
-        <v>999</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s" s="0">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="B181" t="s" s="0">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="C181" t="s" s="0">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="D181" t="s" s="0">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="E181" t="s" s="0">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="F181" t="s" s="0">
         <v>14</v>
       </c>
       <c r="G181" t="s" s="0">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="H181" t="s" s="0">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="I181" t="s" s="0">
-        <v>1038</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s" s="0">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B182" t="s" s="0">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="C182" t="s" s="0">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="D182" t="s" s="0">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="E182" t="s" s="0">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="F182" t="s" s="0">
         <v>14</v>
       </c>
       <c r="G182" t="s" s="0">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="H182" t="s" s="0">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="I182" t="s" s="0">
-        <v>999</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s" s="0">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="B183" t="s" s="0">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="C183" t="s" s="0">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="D183" t="s" s="0">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="E183" t="s" s="0">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="F183" t="s" s="0">
         <v>14</v>
       </c>
       <c r="G183" t="s" s="0">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="H183" t="s" s="0">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="I183" t="s" s="0">
-        <v>1038</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s" s="0">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="B184" t="s" s="0">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="C184" t="s" s="0">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="D184" t="s" s="0">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="E184" t="s" s="0">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="F184" t="s" s="0">
         <v>14</v>
       </c>
       <c r="G184" t="s" s="0">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="H184" t="s" s="0">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="I184" t="s" s="0">
-        <v>1038</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s" s="0">
+        <v>1059</v>
+      </c>
+      <c r="B185" t="s" s="0">
+        <v>1060</v>
+      </c>
+      <c r="C185" t="s" s="0">
+        <v>1061</v>
+      </c>
+      <c r="D185" t="s" s="0">
+        <v>1062</v>
+      </c>
+      <c r="E185" t="s" s="0">
+        <v>1063</v>
+      </c>
+      <c r="F185" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G185" t="s" s="0">
+        <v>1064</v>
+      </c>
+      <c r="H185" t="s" s="0">
         <v>1058</v>
       </c>
-      <c r="B185" t="s" s="0">
-        <v>1059</v>
-      </c>
-      <c r="C185" t="s" s="0">
-        <v>1060</v>
-      </c>
-      <c r="D185" t="s" s="0">
-        <v>1061</v>
-      </c>
-      <c r="E185" t="s" s="0">
-        <v>1062</v>
-      </c>
-      <c r="F185" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="G185" t="s" s="0">
-        <v>1063</v>
-      </c>
-      <c r="H185" t="s" s="0">
-        <v>1057</v>
-      </c>
       <c r="I185" t="s" s="0">
-        <v>1064</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s" s="0">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B186" t="s" s="0">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="C186" t="s" s="0">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="D186" t="s" s="0">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="E186" t="s" s="0">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="F186" t="s" s="0">
         <v>14</v>
@@ -8816,27 +9143,27 @@
         <v>200</v>
       </c>
       <c r="H186" t="s" s="0">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="I186" t="s" s="0">
-        <v>1064</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s" s="0">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="B187" t="s" s="0">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="C187" t="s" s="0">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="D187" t="s" s="0">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="E187" t="s" s="0">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="F187" t="s" s="0">
         <v>14</v>
@@ -8845,27 +9172,27 @@
         <v>200</v>
       </c>
       <c r="H187" t="s" s="0">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="I187" t="s" s="0">
-        <v>1064</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s" s="0">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="B188" t="s" s="0">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="C188" t="s" s="0">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="D188" t="s" s="0">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="E188" t="s" s="0">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="F188" t="s" s="0">
         <v>14</v>
@@ -8874,27 +9201,27 @@
         <v>200</v>
       </c>
       <c r="H188" t="s" s="0">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="I188" t="s" s="0">
-        <v>1064</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s" s="0">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="B189" t="s" s="0">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="C189" t="s" s="0">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="D189" t="s" s="0">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="E189" t="s" s="0">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="F189" t="s" s="0">
         <v>14</v>
@@ -8903,123 +9230,123 @@
         <v>200</v>
       </c>
       <c r="H189" t="s" s="0">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="I189" t="s" s="0">
-        <v>1064</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="s" s="0">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B190" t="s" s="0">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="C190" t="s" s="0">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="D190" t="s" s="0">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="E190" t="s" s="0">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="F190" t="s" s="0">
         <v>14</v>
       </c>
       <c r="G190" t="s" s="0">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="H190" t="s" s="0">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="I190" t="s" s="0">
-        <v>1064</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s" s="0">
+        <v>1094</v>
+      </c>
+      <c r="B191" t="s" s="0">
+        <v>1095</v>
+      </c>
+      <c r="C191" t="s" s="0">
+        <v>1096</v>
+      </c>
+      <c r="D191" t="s" s="0">
+        <v>1097</v>
+      </c>
+      <c r="E191" t="s" s="0">
+        <v>1098</v>
+      </c>
+      <c r="F191" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G191" t="s" s="0">
+        <v>1099</v>
+      </c>
+      <c r="H191" t="s" s="0">
         <v>1093</v>
       </c>
-      <c r="B191" t="s" s="0">
-        <v>1094</v>
-      </c>
-      <c r="C191" t="s" s="0">
-        <v>1095</v>
-      </c>
-      <c r="D191" t="s" s="0">
-        <v>1096</v>
-      </c>
-      <c r="E191" t="s" s="0">
-        <v>1097</v>
-      </c>
-      <c r="F191" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="G191" t="s" s="0">
-        <v>1098</v>
-      </c>
-      <c r="H191" t="s" s="0">
-        <v>1092</v>
-      </c>
       <c r="I191" t="s" s="0">
-        <v>1064</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s" s="0">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="B192" t="s" s="0">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="C192" t="s" s="0">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="D192" t="s" s="0">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="E192" t="s" s="0">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="F192" t="s" s="0">
         <v>14</v>
       </c>
       <c r="G192" t="s" s="0">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="H192" t="s" s="0">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="I192" t="s" s="0">
-        <v>1064</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s" s="0">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="B193" t="s" s="0">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="C193" t="s" s="0">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="D193" t="s" s="0">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="E193" t="s" s="0">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="F193" t="s" s="0">
         <v>14</v>
       </c>
       <c r="G193" t="s" s="0">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H193" t="s" s="0">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="I193" t="s" s="0">
         <v>17</v>
@@ -9027,19 +9354,19 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="0">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="B194" t="s" s="0">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="C194" t="s" s="0">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="D194" t="s" s="0">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E194" t="s" s="0">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="F194" t="s" s="0">
         <v>14</v>
@@ -9056,31 +9383,553 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="0">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="B195" t="s" s="0">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="C195" t="s" s="0">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="D195" t="s" s="0">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="E195" t="s" s="0">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="F195" t="s" s="0">
         <v>14</v>
       </c>
       <c r="G195" t="s" s="0">
-        <v>791</v>
+        <v>741</v>
       </c>
       <c r="H195" t="s" s="0">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="I195" t="s" s="0">
-        <v>1122</v>
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s" s="0">
+        <v>1124</v>
+      </c>
+      <c r="B196" t="s" s="0">
+        <v>1125</v>
+      </c>
+      <c r="C196" t="s" s="0">
+        <v>1126</v>
+      </c>
+      <c r="D196" t="s" s="0">
+        <v>1127</v>
+      </c>
+      <c r="E196" t="s" s="0">
+        <v>1128</v>
+      </c>
+      <c r="F196" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G196" t="s" s="0">
+        <v>1129</v>
+      </c>
+      <c r="H196" t="s" s="0">
+        <v>1130</v>
+      </c>
+      <c r="I196" t="s" s="0">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s" s="0">
+        <v>1131</v>
+      </c>
+      <c r="B197" t="s" s="0">
+        <v>1132</v>
+      </c>
+      <c r="C197" t="s" s="0">
+        <v>1133</v>
+      </c>
+      <c r="D197" t="s" s="0">
+        <v>1134</v>
+      </c>
+      <c r="E197" t="s" s="0">
+        <v>1135</v>
+      </c>
+      <c r="F197" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G197" t="s" s="0">
+        <v>1136</v>
+      </c>
+      <c r="H197" t="s" s="0">
+        <v>1137</v>
+      </c>
+      <c r="I197" t="s" s="0">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s" s="0">
+        <v>1138</v>
+      </c>
+      <c r="B198" t="s" s="0">
+        <v>1139</v>
+      </c>
+      <c r="C198" t="s" s="0">
+        <v>1140</v>
+      </c>
+      <c r="D198" t="s" s="0">
+        <v>1141</v>
+      </c>
+      <c r="E198" t="s" s="0">
+        <v>1142</v>
+      </c>
+      <c r="F198" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G198" t="s" s="0">
+        <v>1143</v>
+      </c>
+      <c r="H198" t="s" s="0">
+        <v>1144</v>
+      </c>
+      <c r="I198" t="s" s="0">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s" s="0">
+        <v>1145</v>
+      </c>
+      <c r="B199" t="s" s="0">
+        <v>1146</v>
+      </c>
+      <c r="C199" t="s" s="0">
+        <v>1147</v>
+      </c>
+      <c r="D199" t="s" s="0">
+        <v>1148</v>
+      </c>
+      <c r="E199" t="s" s="0">
+        <v>1149</v>
+      </c>
+      <c r="F199" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G199" t="s" s="0">
+        <v>1150</v>
+      </c>
+      <c r="H199" t="s" s="0">
+        <v>1151</v>
+      </c>
+      <c r="I199" t="s" s="0">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s" s="0">
+        <v>1152</v>
+      </c>
+      <c r="B200" t="s" s="0">
+        <v>1153</v>
+      </c>
+      <c r="C200" t="s" s="0">
+        <v>1154</v>
+      </c>
+      <c r="D200" t="s" s="0">
+        <v>1155</v>
+      </c>
+      <c r="E200" t="s" s="0">
+        <v>1156</v>
+      </c>
+      <c r="F200" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G200" t="s" s="0">
+        <v>1157</v>
+      </c>
+      <c r="H200" t="s" s="0">
+        <v>1151</v>
+      </c>
+      <c r="I200" t="s" s="0">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s" s="0">
+        <v>1158</v>
+      </c>
+      <c r="B201" t="s" s="0">
+        <v>1159</v>
+      </c>
+      <c r="C201" t="s" s="0">
+        <v>1160</v>
+      </c>
+      <c r="D201" t="s" s="0">
+        <v>1161</v>
+      </c>
+      <c r="E201" t="s" s="0">
+        <v>1162</v>
+      </c>
+      <c r="F201" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G201" t="s" s="0">
+        <v>1163</v>
+      </c>
+      <c r="H201" t="s" s="0">
+        <v>1151</v>
+      </c>
+      <c r="I201" t="s" s="0">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="s" s="0">
+        <v>1164</v>
+      </c>
+      <c r="B202" t="s" s="0">
+        <v>1165</v>
+      </c>
+      <c r="C202" t="s" s="0">
+        <v>1166</v>
+      </c>
+      <c r="D202" t="s" s="0">
+        <v>1167</v>
+      </c>
+      <c r="E202" t="s" s="0">
+        <v>1168</v>
+      </c>
+      <c r="F202" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G202" t="s" s="0">
+        <v>200</v>
+      </c>
+      <c r="H202" t="s" s="0">
+        <v>1169</v>
+      </c>
+      <c r="I202" t="s" s="0">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="s" s="0">
+        <v>1170</v>
+      </c>
+      <c r="B203" t="s" s="0">
+        <v>1171</v>
+      </c>
+      <c r="C203" t="s" s="0">
+        <v>1172</v>
+      </c>
+      <c r="D203" t="s" s="0">
+        <v>1173</v>
+      </c>
+      <c r="E203" t="s" s="0">
+        <v>1174</v>
+      </c>
+      <c r="F203" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G203" t="s" s="0">
+        <v>200</v>
+      </c>
+      <c r="H203" t="s" s="0">
+        <v>1169</v>
+      </c>
+      <c r="I203" t="s" s="0">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="s" s="0">
+        <v>1175</v>
+      </c>
+      <c r="B204" t="s" s="0">
+        <v>1176</v>
+      </c>
+      <c r="C204" t="s" s="0">
+        <v>1177</v>
+      </c>
+      <c r="D204" t="s" s="0">
+        <v>1178</v>
+      </c>
+      <c r="E204" t="s" s="0">
+        <v>1179</v>
+      </c>
+      <c r="F204" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G204" t="s" s="0">
+        <v>200</v>
+      </c>
+      <c r="H204" t="s" s="0">
+        <v>1169</v>
+      </c>
+      <c r="I204" t="s" s="0">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="s" s="0">
+        <v>1180</v>
+      </c>
+      <c r="B205" t="s" s="0">
+        <v>1181</v>
+      </c>
+      <c r="C205" t="s" s="0">
+        <v>1182</v>
+      </c>
+      <c r="D205" t="s" s="0">
+        <v>1183</v>
+      </c>
+      <c r="E205" t="s" s="0">
+        <v>1184</v>
+      </c>
+      <c r="F205" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G205" t="s" s="0">
+        <v>200</v>
+      </c>
+      <c r="H205" t="s" s="0">
+        <v>1169</v>
+      </c>
+      <c r="I205" t="s" s="0">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="s" s="0">
+        <v>1185</v>
+      </c>
+      <c r="B206" t="s" s="0">
+        <v>1186</v>
+      </c>
+      <c r="C206" t="s" s="0">
+        <v>1187</v>
+      </c>
+      <c r="D206" t="s" s="0">
+        <v>1188</v>
+      </c>
+      <c r="E206" t="s" s="0">
+        <v>1189</v>
+      </c>
+      <c r="F206" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G206" t="s" s="0">
+        <v>200</v>
+      </c>
+      <c r="H206" t="s" s="0">
+        <v>1169</v>
+      </c>
+      <c r="I206" t="s" s="0">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="s" s="0">
+        <v>1190</v>
+      </c>
+      <c r="B207" t="s" s="0">
+        <v>1191</v>
+      </c>
+      <c r="C207" t="s" s="0">
+        <v>1192</v>
+      </c>
+      <c r="D207" t="s" s="0">
+        <v>1193</v>
+      </c>
+      <c r="E207" t="s" s="0">
+        <v>1194</v>
+      </c>
+      <c r="F207" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G207" t="s" s="0">
+        <v>373</v>
+      </c>
+      <c r="H207" t="s" s="0">
+        <v>1169</v>
+      </c>
+      <c r="I207" t="s" s="0">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="s" s="0">
+        <v>1195</v>
+      </c>
+      <c r="B208" t="s" s="0">
+        <v>1196</v>
+      </c>
+      <c r="C208" t="s" s="0">
+        <v>1197</v>
+      </c>
+      <c r="D208" t="s" s="0">
+        <v>1198</v>
+      </c>
+      <c r="E208" t="s" s="0">
+        <v>1199</v>
+      </c>
+      <c r="F208" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G208" t="s" s="0">
+        <v>1200</v>
+      </c>
+      <c r="H208" t="s" s="0">
+        <v>1201</v>
+      </c>
+      <c r="I208" t="s" s="0">
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="s" s="0">
+        <v>1202</v>
+      </c>
+      <c r="B209" t="s" s="0">
+        <v>1203</v>
+      </c>
+      <c r="C209" t="s" s="0">
+        <v>1204</v>
+      </c>
+      <c r="D209" t="s" s="0">
+        <v>1205</v>
+      </c>
+      <c r="E209" t="s" s="0">
+        <v>1206</v>
+      </c>
+      <c r="F209" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G209" t="s" s="0">
+        <v>707</v>
+      </c>
+      <c r="H209" t="s" s="0">
+        <v>1207</v>
+      </c>
+      <c r="I209" t="s" s="0">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="s" s="0">
+        <v>1208</v>
+      </c>
+      <c r="B210" t="s" s="0">
+        <v>1209</v>
+      </c>
+      <c r="C210" t="s" s="0">
+        <v>1210</v>
+      </c>
+      <c r="D210" t="s" s="0">
+        <v>1211</v>
+      </c>
+      <c r="E210" t="s" s="0">
+        <v>1212</v>
+      </c>
+      <c r="F210" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G210" t="s" s="0">
+        <v>707</v>
+      </c>
+      <c r="H210" t="s" s="0">
+        <v>1207</v>
+      </c>
+      <c r="I210" t="s" s="0">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="s" s="0">
+        <v>1213</v>
+      </c>
+      <c r="B211" t="s" s="0">
+        <v>1214</v>
+      </c>
+      <c r="C211" t="s" s="0">
+        <v>1215</v>
+      </c>
+      <c r="D211" t="s" s="0">
+        <v>1216</v>
+      </c>
+      <c r="E211" t="s" s="0">
+        <v>1217</v>
+      </c>
+      <c r="F211" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G211" t="s" s="0">
+        <v>707</v>
+      </c>
+      <c r="H211" t="s" s="0">
+        <v>1218</v>
+      </c>
+      <c r="I211" t="s" s="0">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="s" s="0">
+        <v>1219</v>
+      </c>
+      <c r="B212" t="s" s="0">
+        <v>1220</v>
+      </c>
+      <c r="C212" t="s" s="0">
+        <v>1221</v>
+      </c>
+      <c r="D212" t="s" s="0">
+        <v>1222</v>
+      </c>
+      <c r="E212" t="s" s="0">
+        <v>1223</v>
+      </c>
+      <c r="F212" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G212" t="s" s="0">
+        <v>1038</v>
+      </c>
+      <c r="H212" t="s" s="0">
+        <v>1224</v>
+      </c>
+      <c r="I212" t="s" s="0">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="s" s="0">
+        <v>1225</v>
+      </c>
+      <c r="B213" t="s" s="0">
+        <v>1226</v>
+      </c>
+      <c r="C213" t="s" s="0">
+        <v>1227</v>
+      </c>
+      <c r="D213" t="s" s="0">
+        <v>1228</v>
+      </c>
+      <c r="E213" t="s" s="0">
+        <v>1229</v>
+      </c>
+      <c r="F213" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G213" t="s" s="0">
+        <v>1230</v>
+      </c>
+      <c r="H213" t="s" s="0">
+        <v>1231</v>
+      </c>
+      <c r="I213" t="s" s="0">
+        <v>1231</v>
       </c>
     </row>
   </sheetData>
